--- a/laptop_gearvn_all.xlsx
+++ b/laptop_gearvn_all.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:36</t>
+          <t>2026-09-20 11:54:25</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:42</t>
+          <t>2026-09-20 11:54:31</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:47</t>
+          <t>2026-09-20 11:54:37</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:52</t>
+          <t>2026-09-20 11:54:42</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:57</t>
+          <t>2026-09-20 11:54:47</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:02</t>
+          <t>2026-09-20 11:54:52</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:07</t>
+          <t>2026-09-20 11:54:57</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:12</t>
+          <t>2026-09-20 11:55:02</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:17</t>
+          <t>2026-09-20 11:55:07</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:22</t>
+          <t>2026-09-20 11:55:12</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:27</t>
+          <t>2026-09-20 11:55:18</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:32</t>
+          <t>2026-09-20 11:55:23</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:37</t>
+          <t>2026-09-20 11:55:28</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:42</t>
+          <t>2026-09-20 11:55:33</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:48</t>
+          <t>2026-09-20 11:55:38</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:53</t>
+          <t>2026-09-20 11:55:43</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:58</t>
+          <t>2026-09-20 11:55:48</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:02</t>
+          <t>2026-09-20 11:55:53</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:08</t>
+          <t>2026-09-20 11:55:58</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:12</t>
+          <t>2026-09-20 11:56:03</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:17</t>
+          <t>2026-09-20 11:56:08</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:22</t>
+          <t>2026-09-20 11:56:13</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:27</t>
+          <t>2026-09-20 11:56:18</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:32</t>
+          <t>2026-09-20 11:56:23</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:37</t>
+          <t>2026-09-20 11:56:28</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:42</t>
+          <t>2026-09-20 11:56:33</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:47</t>
+          <t>2026-09-20 11:56:38</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:52</t>
+          <t>2026-09-20 11:56:43</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:57</t>
+          <t>2026-09-20 11:56:48</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:02</t>
+          <t>2026-09-20 11:56:53</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:07</t>
+          <t>2026-09-20 11:56:58</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:12</t>
+          <t>2026-09-20 11:57:03</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:17</t>
+          <t>2026-09-20 11:57:08</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:22</t>
+          <t>2026-09-20 11:57:13</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:27</t>
+          <t>2026-09-20 11:57:18</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:31</t>
+          <t>2026-09-20 11:57:23</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:37</t>
+          <t>2026-09-20 11:57:28</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:42</t>
+          <t>2026-09-20 11:57:33</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:47</t>
+          <t>2026-09-20 11:57:38</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:52</t>
+          <t>2026-09-20 11:57:43</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:57</t>
+          <t>2026-09-20 11:57:48</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:01</t>
+          <t>2026-09-20 11:57:53</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:07</t>
+          <t>2026-09-20 11:57:58</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:11</t>
+          <t>2026-09-20 11:58:03</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:16</t>
+          <t>2026-09-20 11:58:08</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:21</t>
+          <t>2026-09-20 11:58:13</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:26</t>
+          <t>2026-09-20 11:58:18</t>
         </is>
       </c>
     </row>
@@ -2434,21 +2434,27 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:31</t>
+          <t>2026-09-20 11:58:23</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Max C13VF-421VN (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA / Win 11)</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>44990000</v>
-      </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
+        <v>26390000</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>30490000</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2458,73 +2464,75 @@
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13vf-421vn-i7-13620h-rtx-5060-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T11:01:57.991+07:00</t>
+          <t>2026-09-03T11:54:54.747+07:00</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:37</t>
+          <t>2026-09-20 11:54:22</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Max C13WE-422VN (I7-13620H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>42990000</v>
-      </c>
-      <c r="C51" s="2" t="inlineStr"/>
-      <c r="D51" s="2" t="inlineStr"/>
+        <v>30690000</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>35990000</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
-        </is>
-      </c>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn-i7-13620h-rtx-5050-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:38:57.001+07:00</t>
+          <t>2026-07-31T11:19:13.274+07:00</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:43</t>
+          <t>2026-09-20 11:54:27</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 G2 P5405CAA-NZ0223W (Ultra 7-356H/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>34890000</v>
+        <v>39190000</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>35990000</v>
+        <v>41990000</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2533,82 +2541,78 @@
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
-        </is>
-      </c>
+      <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-g2-p5405caa-nz0223w-ultra-7-356h-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T14:54:13.66+07:00</t>
+          <t>2026-08-03T11:12:45.933+07:00</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:48</t>
+          <t>2026-09-20 11:54:32</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0016W (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>48490000</v>
+        <v>28790000</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>52990000</v>
+        <v>30990000</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: QHD (2560x1440) | Tần số quét: 165 Hz</t>
-        </is>
-      </c>
+      <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0016w-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T14:49:48.046+07:00</t>
+          <t>2026-08-03T10:54:41.9+07:00</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:53</t>
+          <t>2026-09-20 11:54:37</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0017W (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>79990000</v>
+        <v>36290000</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>80990000</v>
+        <v>38990000</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2619,36 +2623,42 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: Arc | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0017w-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:43:38.331+07:00</t>
+          <t>2026-09-10T13:51:05.888+07:00</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:58</t>
+          <t>2026-09-20 11:54:42</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0442WS (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>85990000</v>
-      </c>
-      <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="inlineStr"/>
+        <v>37190000</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2657,293 +2667,303 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Arc 140V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0442ws-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T10:30:35.835+07:00</t>
+          <t>2026-08-03T09:55:42.594+07:00</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:03</t>
+          <t>2026-09-20 11:54:47</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0450WS (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>67690000</v>
+        <v>29790000</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>73990000</v>
+        <v>31990000</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4060 | Kích thước màn hình: 16 inch</t>
+          <t>Card đồ họa: Intel Arc 130V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0450ws-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27T14:36:44.954+07:00</t>
+          <t>2026-08-03T09:56:18.911+07:00</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:08</t>
+          <t>2026-09-20 11:54:52</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop GIGABYTE AERO X16 4WHN3VNC93AH (Ryzen AI 9 465/ RTX 5070 8GB/ 16GB/ 512GB/ 16" QHD+ 165Hz/ Win 11)</t>
+          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>54990000</v>
+        <v>199990000</v>
       </c>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="inlineStr"/>
-      <c r="E57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-x16-4whn3vnc93ah-ryzen-ai-9-465-rtx-5070-8gb-16gb-512gb-16-qhd-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:49:41.514+07:00</t>
+          <t>2026-09-18T11:12:30.954+07:00</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:13</t>
+          <t>2026-09-20 11:54:57</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop GIGABYTE AORUS Master 16 6XJM4VNE64SH (Ryzen 9 9955HX3D/ RTX 5070 Ti 12GB/ 32GB/ 1TB/ 16" QHD+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB027W (Core 3/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>86990000</v>
+        <v>22990000</v>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aorus-master-16-6xjm4vne64sh-ryzen-9-9955hx3d-rtx-5070-ti-12gb-32gb-1tb-16-qhd-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb027w-core-3-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T11:03:18.048+07:00</t>
+          <t>2026-08-18T16:52:41.33+07:00</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:18</t>
+          <t>2026-09-20 11:55:02</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop GIGABYTE Gaming A16 EVHS3VN893SH (Ultra 9-185H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB029W (Core 7/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
+        <v>35490000</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-gaming-a16-evhs3vn893sh-ultra-9-185h-rtx-5060-8gb-16gb-512gb-16-fhd-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb029w-core-7-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:36:39.051+07:00</t>
+          <t>2026-08-20T15:05:22.575+07:00</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:23</t>
+          <t>2026-09-20 11:55:07</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 15-fd1289TU C2CV8PA (Ultra 7-155H/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB219W (Core 5/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
+        <v>26990000</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-hp-15-fd1289tu-c2cv8pa-ultra-7-155h-16gb-512gb-15-6-fhd-ips-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb219w-core-5-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:33:44.001+07:00</t>
+          <t>2026-08-28T13:46:08.34+07:00</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:28</t>
+          <t>2026-09-20 11:55:12</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 250 G10 A06FDPT (I7-1355U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB220W (Core 7/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>23490000</v>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>25590000</v>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>-8%</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
+        <v>30490000</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-hp-250-g10-a06fdpt-i7-1355u-8gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb220w-core-7-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:31:30.682+07:00</t>
+          <t>2026-08-20T11:43:31.989+07:00</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:33</t>
+          <t>2026-09-20 11:55:17</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP ProBook 450 G10 B73TPAT (I5-1334U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus Vivobook 14 X1404V (Core 5-120U/ 8GB/ 256GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>23990000</v>
+        <v>16590000</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>24990000</v>
+        <v>18990000</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+          <t>-13%</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Iris Xe Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-hp-probook-450-g10-b73tpat-i5-1334u-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404v-core-5-120u-8gb-256gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:31:53.385+07:00</t>
+          <t>2026-08-07T13:41:37.603+07:00</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:38</t>
+          <t>2026-09-20 11:55:22</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 83RQ00DBVN (Core 3-304/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VA-EB355W (Core 7-150U/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>24990000</v>
+        <v>25990000</v>
       </c>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="inlineStr"/>
@@ -2955,33 +2975,33 @@
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-14iwc11-83rq00dbvn-core-3-304-8gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb355w-core-7-150u-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:16:44.995+07:00</t>
+          <t>2026-08-20T11:17:32.016+07:00</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:43</t>
+          <t>2026-09-20 11:55:27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB005YVN (Ryzen 5-125/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VA-EB609W (Core 3-100U/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>25990000</v>
+        <v>21990000</v>
       </c>
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr"/>
@@ -2991,34 +3011,44 @@
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb005yvn-ryzen-5-125-8gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb609w-core-3-100u-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T15:01:44.794+07:00</t>
+          <t>2026-08-18T16:33:25.424+07:00</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:48</t>
+          <t>2026-09-20 11:55:32</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB0060VN (Ryzen 7-155/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VAP-V14.C58256 (Core 5-120U/ 16GB/ 256GB/ 14" FHD IPS/ Win 11/ Quiet Blue)</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="C65" s="2" t="inlineStr"/>
-      <c r="D65" s="2" t="inlineStr"/>
+        <v>17890000</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>18990000</v>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3028,68 +3058,72 @@
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb0060vn-ryzen-7-155-8gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404vap-v14-c58256-core-5-120u-8gb-256gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T14:35:59.897+07:00</t>
+          <t>2026-09-14T17:42:34.369+07:00</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:53</t>
+          <t>2026-09-20 11:55:37</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 83S1003GVN</t>
+          <t>Laptop Asus VivoBook 14 X1407AA-LY360W (Ultra 5-325/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>44540000</v>
+        <v>26490000</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>47990000</v>
+        <v>26990000</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr"/>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-83s1003gvn</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407aa-ly360w-ultra-5-325-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T10:29:16.152+07:00</t>
+          <t>2026-08-07T15:46:33.275+07:00</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:58</t>
+          <t>2026-09-20 11:55:42</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 OLED 83S1006RVN (Ryzen AI 7-445/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1407CA-LY203W (Ultra 5-225H/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>32990000</v>
+        <v>33490000</v>
       </c>
       <c r="C67" s="2" t="inlineStr"/>
       <c r="D67" s="2" t="inlineStr"/>
@@ -3101,33 +3135,33 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-oled-83s1006rvn-ryzen-ai-7-445-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407ca-ly203w-ultra-5-225h-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T11:54:44.05+07:00</t>
+          <t>2026-08-20T10:22:08.041+07:00</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:03</t>
+          <t>2026-09-20 11:55:47</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00ABVN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1504MA-BQ633W (Core 7-350/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>30990000</v>
+        <v>30490000</v>
       </c>
       <c r="C68" s="2" t="inlineStr"/>
       <c r="D68" s="2" t="inlineStr"/>
@@ -3137,35 +3171,31 @@
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00abvn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1504ma-bq633w-core-7-350-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T14:05:59.687+07:00</t>
+          <t>2026-08-18T15:20:11.716+07:00</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:08</t>
+          <t>2026-09-20 11:55:52</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00F5VN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 15 X1504MA-BQ632W (Core 5-320/ 8GB/ 512GB/ 15" FHD IPS)</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>34990000</v>
+        <v>26990000</v>
       </c>
       <c r="C69" s="2" t="inlineStr"/>
       <c r="D69" s="2" t="inlineStr"/>
@@ -3175,35 +3205,31 @@
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00f5vn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq632w-core-5-320-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:17:34.624+07:00</t>
+          <t>2026-08-18T15:43:54.381+07:00</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:13</t>
+          <t>2026-09-20 11:55:57</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002EVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 15 X1504VA-BQ165W (Core 5-120U/ 8GB/ 512GB/ 15" FHD IPS)</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>55990000</v>
+        <v>20990000</v>
       </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="inlineStr"/>
@@ -3213,73 +3239,71 @@
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
-        </is>
-      </c>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002evn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504va-bq165w-core-5-120u-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T10:21:35.763+07:00</t>
+          <t>2026-08-18T16:12:00.028+07:00</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:18</t>
+          <t>2026-09-20 11:56:02</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002FVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Asus Vivobook 16 X1605VA-MB1826W (I3-1315U/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>55990000</v>
-      </c>
-      <c r="C71" s="2" t="inlineStr"/>
-      <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>15390000</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>15990000</v>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 16 inch | Dòng CPU: i3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002fvn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1605va-mb1826w-i3-1315u-8gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T20:29:51.634+07:00</t>
+          <t>2026-09-09T10:45:38.083+07:00</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:23</t>
+          <t>2026-09-20 11:56:07</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0075VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 16 X1607CA-MB387W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD IPS)</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>46990000</v>
+        <v>33490000</v>
       </c>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="inlineStr"/>
@@ -3289,31 +3313,35 @@
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0075vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb387w-ultra-5-225h-16gb-512gb-16-fhd-ips</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:19:34.771+07:00</t>
+          <t>2026-08-20T16:08:06.906+07:00</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:28</t>
+          <t>2026-09-20 11:56:12</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0076VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 16 X1607CA-MB399W (Ultra 7-255H/ 16GB/ 512GB/ 16" FHD IPS)</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>46990000</v>
+        <v>36490000</v>
       </c>
       <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="inlineStr"/>
@@ -3323,35 +3351,31 @@
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0076vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb399w-ultra-7-255h-16gb-512gb-16-fhd-ips</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:20:20.027+07:00</t>
+          <t>2026-08-20T15:36:19.591+07:00</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:33</t>
+          <t>2026-09-20 11:56:17</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK0015VN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook Flip TP3407AA-SG029W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>72990000</v>
+        <v>41990000</v>
       </c>
       <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="inlineStr"/>
@@ -3363,71 +3387,73 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk0015vn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-flip-tp3407aa-sg029w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:21:45.74+07:00</t>
+          <t>2026-08-18T14:55:40.249+07:00</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:38</t>
+          <t>2026-09-20 11:56:22</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK006GVN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
+          <t>Laptop Asus Vivobook Go 14 E1404FA-EB935W (Ryzen 5-7430U/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>72990000</v>
-      </c>
-      <c r="C75" s="2" t="inlineStr"/>
-      <c r="D75" s="2" t="inlineStr"/>
+        <v>20490000</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>28490000</v>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>-28%</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
-        </is>
-      </c>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk006gvn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1404fa-eb935w-ryzen-5-7430u-16gb-512gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:23:05.36+07:00</t>
+          <t>2026-08-13T09:46:28.801+07:00</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:43</t>
+          <t>2026-09-20 11:56:27</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 POLED 83QK009PVN (Ultra X9-378H/ 32GB/ 1TB/ 14" 2.8K WQXGA POLED Touch/ Win 11)</t>
+          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ4821W (Ryzen 5/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>70990000</v>
+        <v>22990000</v>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="inlineStr"/>
@@ -3439,158 +3465,146 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-poled-83qk009pvn-ultra-x9-378h-32gb-1tb-14-2-8k-wqxga-poled-touch-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1504fa-bq4821w-ryzen-5-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T20:11:25.828+07:00</t>
+          <t>2026-08-18T14:05:39.37+07:00</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:48</t>
+          <t>2026-09-20 11:56:32</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ340W (Ryzen 5/ 16GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>33900000</v>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>34900000</v>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>28490000</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr"/>
+      <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-go-15-e1504fa-bq340w-ryzen-5-16gb-512gb-156-fhd-ips</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:39:36.938+07:00</t>
+          <t>2026-08-18T14:28:58.285+07:00</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:53</t>
+          <t>2026-09-20 11:56:37</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 M3407KA-SF034W (Ryzen AI 5-330/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>36900000</v>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>37900000</v>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
+        <v>33990000</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-m3407ka-sf034w-ryzen-ai-5-330-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:34:21.041+07:00</t>
+          <t>2026-08-18T12:02:07.653+07:00</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:58</t>
+          <t>2026-09-20 11:56:42</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407AA-SF032W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>44900000</v>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>46490000</v>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr"/>
+        <v>40490000</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf032w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:43:00.949+07:00</t>
+          <t>2026-08-18T10:00:42.045+07:00</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:03</t>
+          <t>2026-09-20 11:56:47</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407AA-SF945W (Ultra 5-325/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>23990000</v>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>37490000</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3599,153 +3613,147 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf945w-ultra-5-325-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:36:48.562+07:00</t>
+          <t>2026-08-18T11:09:17.449+07:00</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:08</t>
+          <t>2026-09-20 11:56:52</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407QA-SF043W (QC X126100/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>61990000</v>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>62990000</v>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>25990000</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr"/>
+      <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407qa-sf043w-qc-x126100-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:29:18.09+07:00</t>
+          <t>2026-08-18T09:15:59.141+07:00</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:13</t>
+          <t>2026-09-20 11:56:57</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407VA-LY147W (Core 5-210H/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>33990000</v>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v>37990000</v>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
-      </c>
+        <v>34990000</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407va-ly147w-core-5-210h-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T10:03:31.114+07:00</t>
+          <t>2026-08-18T11:42:14.925+07:00</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:18</t>
+          <t>2026-09-20 11:57:02</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
+          <t>Laptop ASUS Vivobook S 16 S3607AA-SH042W (Ultra 5-325/ 16GB/ 512GB/ 16" FHD OLED)</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>25490000</v>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>37490000</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr"/>
+      <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-16-s3607aa-sh042w-ultra-5-325-16gb-512gb-16-fhd-oled</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:41:40.106+07:00</t>
+          <t>2026-08-18T10:44:16.77+07:00</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:23</t>
+          <t>2026-09-20 11:57:07</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14S AI+ G3MG-050VN (Ultra 7-355/ 16GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 16 S3607CA-SH080W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD OLED)</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>36490000</v>
+        <v>35990000</v>
       </c>
       <c r="C84" s="2" t="inlineStr"/>
       <c r="D84" s="2" t="inlineStr"/>
@@ -3755,38 +3763,42 @@
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14s-ai-g3mg-050vn-ultra-7-355-16gb-1tb-14-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-16-s3607ca-sh080w-ultra-5-225h-16gb-512gb-16-fhd-oled</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T14:08:29.354+07:00</t>
+          <t>2026-08-18T10:21:29.428+07:00</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:28</t>
+          <t>2026-09-20 11:57:12</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
+          <t>Laptop ASUS VivoBook S14 S3407CA-SF913W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>22190000</v>
+        <v>27890000</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>22690000</v>
+        <v>29990000</v>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -3797,86 +3809,70 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s14-s3407ca-sf913w-ultra-5-225h-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T15:28:04.144+07:00</t>
+          <t>2026-09-08T17:02:01.429+07:00</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:33</t>
+          <t>2026-09-20 11:57:17</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UM3406GA-QD075W (Ryzen 7/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>43990000</v>
-      </c>
-      <c r="C86" s="2" t="n">
-        <v>44990000</v>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>39990000</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
-        </is>
-      </c>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ga-qd075w-ryzen-7-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:49:42.234+07:00</t>
+          <t>2026-08-17T16:03:07.024+07:00</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:38</t>
+          <t>2026-09-20 11:57:22</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1531W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED)</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>33990000</v>
-      </c>
-      <c r="C87" s="2" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>42990000</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr"/>
+      <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3885,40 +3881,40 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 7 | Dung lượng SSD: 1024 GB | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1531w-ultra-9-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T16:07:23.364+07:00</t>
+          <t>2026-08-18T08:45:55.514+07:00</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:43</t>
+          <t>2026-09-20 11:57:26</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1713W (Ultra 5-225H/ 16GB/ 512GB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>37990000</v>
+        <v>31990000</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>39990000</v>
+        <v>38990000</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-18%</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -3929,42 +3925,36 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 13.3 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1713w-ultra-5-225h-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T11:20:56.718+07:00</t>
+          <t>2026-09-11T11:57:10.625+07:00</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:48</t>
+          <t>2026-09-20 11:57:31</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN (Ultra 7-355/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST630W (Ultra 7-255H/ 16GB/ 512GB/ 14" 3K OLED)</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>46990000</v>
-      </c>
-      <c r="C89" s="2" t="n">
-        <v>48990000</v>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>40990000</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr"/>
+      <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3973,33 +3963,33 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st630w-ultra-7-255h-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31T14:41:10.864+07:00</t>
+          <t>2026-08-17T15:05:39.807+07:00</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:53</t>
+          <t>2026-09-20 11:57:36</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3407NA-QD132WS (Snapdragon X2 Elite X2E-88-100/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>59990000</v>
+        <v>48990000</v>
       </c>
       <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr"/>
@@ -4009,110 +3999,114 @@
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd132ws-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:54:52.677+07:00</t>
+          <t>2026-08-24T11:47:13.916+07:00</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:58</t>
+          <t>2026-09-20 11:57:41</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop ASUS Zenbook A14 UX3407NA-QD254W (Snapdragon X2 Elite X2E-88-100/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>59990000</v>
+        <v>63990000</v>
       </c>
       <c r="C91" s="2" t="inlineStr"/>
       <c r="D91" s="2" t="inlineStr"/>
-      <c r="E91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd254w-32gb-1tb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T10:17:43.984+07:00</t>
+          <t>2026-08-24T11:46:55.101+07:00</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:03</t>
+          <t>2026-09-20 11:57:46</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/ RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop ASUS Zenbook A16 UX3607OA-SQ137WS (Snapdragon X2 Elite Extreme X2E94100/ 24GB/ 512GB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>82990000</v>
-      </c>
-      <c r="C92" s="2" t="n">
-        <v>83990000</v>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>-1%</t>
-        </is>
-      </c>
+        <v>58990000</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr"/>
+      <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 16 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 24 GB</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-16-ux3607oa-sq137ws-24gb-512gb-16-3k-oled</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T18:03:22.38+07:00</t>
+          <t>2026-08-24T11:43:18.337+07:00</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:08</t>
+          <t>2026-09-20 11:57:51</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN138WS (Ultra X9/ 32GB/ 1TB/ 14" 3K OLED Touch 144Hz)</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>86990000</v>
-      </c>
-      <c r="C93" s="2" t="n">
-        <v>87990000</v>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>-1%</t>
-        </is>
-      </c>
+        <v>89990000</v>
+      </c>
+      <c r="C93" s="2" t="inlineStr"/>
+      <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4121,325 +4115,313 @@
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn138ws-ultra-x9-32gb-1tb-14-3k-oled-touch-144hz</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:49:19.952+07:00</t>
+          <t>2026-08-17T12:04:03.945+07:00</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:13</t>
+          <t>2026-09-20 11:57:56</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA / Win 11)</t>
+          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN439WS (Ultra X7/ 32GB/ 512GB/ 14" 3K OLED Touch 144Hz)</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>26390000</v>
-      </c>
-      <c r="C94" s="2" t="n">
-        <v>30490000</v>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>-13%</t>
-        </is>
-      </c>
+        <v>82990000</v>
+      </c>
+      <c r="C94" s="2" t="inlineStr"/>
+      <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn439ws-ultra-x7-32gb-512gb-14-3k-oled-touch-144hz</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03T11:54:54.747+07:00</t>
+          <t>2026-08-17T11:44:06.982+07:00</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:34</t>
+          <t>2026-09-20 11:58:01</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
+          <t>Laptop ASUS Zenbook Pro Art HN7306EA-LX050W (Ryzen AI Max+ 395/ 32GB/ 1TB/ 13.3" 3K OLED Touch)</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>30690000</v>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>-15%</t>
-        </is>
-      </c>
+        <v>76990000</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr"/>
+      <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 13.3 inch | Dòng CPU: Ryzen AI MAX+ | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-pro-art-hn7306ea-lx050w-ryzen-ai-max-395-32gb-1tb-13-3-3k-oled-touch</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T11:19:13.274+07:00</t>
+          <t>2026-08-17T11:16:12.092+07:00</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:39</t>
+          <t>2026-09-20 11:58:06</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 G2 P5405CAA-NZ0223W (Ultra 7-356H/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop ASUS Zenbook S 14 UX5406AA-SU348W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED Touch)</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>39190000</v>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v>41990000</v>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>50990000</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr"/>
+      <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-g2-p5405caa-nz0223w-ultra-7-356h-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-s-14-ux5406aa-su348w-ultra-9-16gb-512gb-14-3k-oled-touch</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T11:12:45.933+07:00</t>
+          <t>2026-08-17T10:26:19.879+07:00</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:44</t>
+          <t>2026-09-20 11:58:11</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0016W (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop ASUS Zenbook S 15 UM5606GA-SS441W (Ryzen AI 9 465/ 16GB/ 512GB/ 15" 3K OLED)</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>28790000</v>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>49490000</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr"/>
+      <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ryzen AI 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0016w-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-s-15-um5606ga-ss441w-ryzen-ai-9-465-16gb-512gb-15-3k-oled</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T10:54:41.9+07:00</t>
+          <t>2026-08-17T10:51:02.985+07:00</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:49</t>
+          <t>2026-09-20 11:58:16</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0017W (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>36290000</v>
+        <v>22990000</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>38990000</v>
+        <v>23990000</v>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: Arc | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Card đồ họa tích hợp - Qualcomm® Adreno™ | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0017w-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:51:05.888+07:00</t>
+          <t>2026-07-16T09:43:41.692+07:00</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:54</t>
+          <t>2026-09-20 11:54:24</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0442WS (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AG14-72P-563L (Core 5 120U/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>37190000</v>
+        <v>19490000</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>39990000</v>
+        <v>22990000</v>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc 140V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0442ws-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ag14-72p-563l</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T09:55:42.594+07:00</t>
+          <t>2026-09-09T17:24:08.222+07:00</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:59</t>
+          <t>2026-09-20 11:54:29</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0450WS (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>29790000</v>
+        <v>23990000</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>31990000</v>
+        <v>25990000</v>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc 130V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® ARC™ Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0450ws-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T09:56:18.911+07:00</t>
+          <t>2026-07-16T15:00:45.83+07:00</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:04</t>
+          <t>2026-09-20 11:54:35</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M (Ultra 9-185H/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>199990000</v>
+        <v>29990000</v>
       </c>
       <c r="C101" s="2" t="inlineStr"/>
       <c r="D101" s="2" t="inlineStr"/>
@@ -4449,975 +4431,1049 @@
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
-        </is>
-      </c>
+      <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-16gb-512gb-14-fhd-ips-win-11</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T11:12:30.954+07:00</t>
+          <t>2026-09-09T09:48:08.298+07:00</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:09</t>
+          <t>2026-09-20 11:54:40</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB027W (Core 3/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
         <v>22990000</v>
       </c>
-      <c r="C102" s="2" t="inlineStr"/>
-      <c r="D102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="n">
+        <v>25990000</v>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb027w-core-3-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:52:41.33+07:00</t>
+          <t>2026-09-11T21:08:15.03+07:00</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:14</t>
+          <t>2026-09-20 11:54:45</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB029W (Core 7/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Aspire Go 15 AI AG15-52P-52WT (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>35490000</v>
+        <v>22990000</v>
       </c>
       <c r="C103" s="2" t="inlineStr"/>
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb029w-core-7-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-52p-52wt</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T15:05:22.575+07:00</t>
+          <t>2026-09-08T09:27:37.618+07:00</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:19</t>
+          <t>2026-09-20 11:54:50</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB219W (Core 5/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Aspire Go 15 AG15 72P 54GY (Intel Core 5/ 16GB/ 512GB/ Intel UHD/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>26990000</v>
-      </c>
-      <c r="C104" s="2" t="inlineStr"/>
-      <c r="D104" s="2" t="inlineStr"/>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>19490000</v>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>-19%</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb219w-core-5-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-72p-54gy</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T13:46:08.34+07:00</t>
+          <t>2026-09-09T17:24:34.893+07:00</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:24</t>
+          <t>2026-09-20 11:54:55</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB220W (Core 7/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>30490000</v>
-      </c>
-      <c r="C105" s="2" t="inlineStr"/>
-      <c r="D105" s="2" t="inlineStr"/>
+        <v>20990000</v>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>21990000</v>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb220w-core-7-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:43:31.989+07:00</t>
+          <t>2026-07-17T09:17:18.78+07:00</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:29</t>
+          <t>2026-09-20 11:55:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1404V (Core 5-120U/ 8GB/ 256GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 (Ryzen 3 5400U/ 8GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>16590000</v>
+        <v>15990000</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>18990000</v>
+        <v>17590000</v>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
-        </is>
-      </c>
+      <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404v-core-5-120u-8gb-256gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-45p-r7z3</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T13:41:37.603+07:00</t>
+          <t>2026-09-09T17:28:26.25+07:00</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:33</t>
+          <t>2026-09-20 11:55:05</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VA-EB355W (Core 7-150U/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR (Ryzen 5 3500U/ 8GB/ 512GB/ 14.0" FHD IPS)</t>
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="C107" s="2" t="inlineStr"/>
-      <c r="D107" s="2" t="inlineStr"/>
+        <v>17990000</v>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>19990000</v>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb355w-core-7-150u-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:17:32.016+07:00</t>
+          <t>2026-09-17T11:14:52.788+07:00</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:38</t>
+          <t>2026-09-20 11:55:10</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VA-EB609W (Core 3-100U/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 16GB/ 512GB/ 14.0" FHD+ IPS)</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>21990000</v>
-      </c>
-      <c r="C108" s="2" t="inlineStr"/>
-      <c r="D108" s="2" t="inlineStr"/>
+        <v>22990000</v>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
-        </is>
-      </c>
+      <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb609w-core-3-100u-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:33:25.424+07:00</t>
+          <t>2026-09-11T21:14:04.587+07:00</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:43</t>
+          <t>2026-09-20 11:55:15</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VAP-V14.C58256 (Core 5-120U/ 16GB/ 256GB/ 14" FHD IPS/ Win 11/ Quiet Blue)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-57P-54YV (Core 5 315/ 8GB/ 512GB)</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>17890000</v>
+        <v>23990000</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>18990000</v>
+        <v>24990000</v>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404vap-v14-c58256-core-5-120u-8gb-256gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-54yv-core-5-315-8gb-512gb</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:42:34.369+07:00</t>
+          <t>2026-07-06T14:01:15.719+07:00</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:48</t>
+          <t>2026-09-20 11:55:20</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus VivoBook 14 X1407AA-LY360W (Ultra 5-325/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14.0" FHD+ IPS)</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>26490000</v>
+        <v>24990000</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>26990000</v>
+        <v>25990000</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407aa-ly360w-ultra-5-325-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T15:46:33.275+07:00</t>
+          <t>2026-07-16T15:07:04.792+07:00</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:53</t>
+          <t>2026-09-20 11:55:25</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1407CA-LY203W (Ultra 5-225H/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-57P-76KR (Core 7 350/ 8GB/ 512GB)</t>
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>33490000</v>
-      </c>
-      <c r="C111" s="2" t="inlineStr"/>
-      <c r="D111" s="2" t="inlineStr"/>
+        <v>25990000</v>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>26990000</v>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407ca-ly203w-ultra-5-225h-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-76kr-core-7-350-8gb-512gb</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T10:22:08.041+07:00</t>
+          <t>2026-07-06T12:03:11.649+07:00</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:58</t>
+          <t>2026-09-20 11:55:30</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1504MA-BQ633W (Core 7-350/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN (Core 3-N350/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>30490000</v>
-      </c>
-      <c r="C112" s="2" t="inlineStr"/>
-      <c r="D112" s="2" t="inlineStr"/>
+        <v>16990000</v>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>18990000</v>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1504ma-bq633w-core-7-350-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al15-36p-30tn</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T15:20:11.716+07:00</t>
+          <t>2026-08-20T11:31:44.094+07:00</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:03</t>
+          <t>2026-09-20 11:55:35</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504MA-BQ632W (Core 5-320/ 8GB/ 512GB/ 15" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>26990000</v>
-      </c>
-      <c r="C113" s="2" t="inlineStr"/>
-      <c r="D113" s="2" t="inlineStr"/>
+        <v>17990000</v>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq632w-core-5-320-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T15:43:54.381+07:00</t>
+          <t>2026-07-03T14:20:10.941+07:00</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:08</t>
+          <t>2026-09-20 11:55:40</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504VA-BQ165W (Core 5-120U/ 8GB/ 512GB/ 15" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>20990000</v>
-      </c>
-      <c r="C114" s="2" t="inlineStr"/>
-      <c r="D114" s="2" t="inlineStr"/>
+        <v>19590000</v>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>21990000</v>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504va-bq165w-core-5-120u-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:12:00.028+07:00</t>
+          <t>2026-08-11T14:50:36.616+07:00</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:13</t>
+          <t>2026-09-20 11:55:45</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 16 X1605VA-MB1826W (I3-1315U/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5 3500U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>15390000</v>
+        <v>17990000</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>15990000</v>
+        <v>19990000</v>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr"/>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+        </is>
+      </c>
       <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 16 inch | Dòng CPU: i3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
-        </is>
-      </c>
+      <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1605va-mb1826w-i3-1315u-8gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T10:45:38.083+07:00</t>
+          <t>2026-09-17T10:40:38.213+07:00</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:18</t>
+          <t>2026-09-20 11:55:50</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 16 X1607CA-MB387W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-411P-R1CM (Ryzen 5 3500U/ 8GB/ 256GB)</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>33490000</v>
-      </c>
-      <c r="C116" s="2" t="inlineStr"/>
-      <c r="D116" s="2" t="inlineStr"/>
+        <v>17990000</v>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>18990000</v>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb387w-ultra-5-225h-16gb-512gb-16-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r1cm-ryzen-5-3500u-8gb-256gb</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T16:08:06.906+07:00</t>
+          <t>2026-07-06T14:26:56.746+07:00</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:23</t>
+          <t>2026-09-20 11:55:55</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 16 X1607CA-MB399W (Ultra 7-255H/ 16GB/ 512GB/ 16" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-411P-R7YP (Ryzen 3 3200U/ 8GB/ 256GB)</t>
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>36490000</v>
-      </c>
-      <c r="C117" s="2" t="inlineStr"/>
-      <c r="D117" s="2" t="inlineStr"/>
+        <v>15990000</v>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>16990000</v>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb399w-ultra-7-255h-16gb-512gb-16-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r7yp-ryzen-3-3200u-8gb-256gb</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T15:36:19.591+07:00</t>
+          <t>2026-07-06T14:48:50.246+07:00</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:28</t>
+          <t>2026-09-20 11:56:00</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Flip TP3407AA-SG029W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-44P-R4UH (Ryzen 7 7730U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>41990000</v>
-      </c>
-      <c r="C118" s="2" t="inlineStr"/>
-      <c r="D118" s="2" t="inlineStr"/>
+        <v>21890000</v>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-flip-tp3407aa-sg029w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-44p-r4uh</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T14:55:40.249+07:00</t>
+          <t>2026-09-09T17:27:57.208+07:00</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:33</t>
+          <t>2026-09-20 11:56:05</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook Go 14 E1404FA-EB935W (Ryzen 5-7430U/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C (Ryzen 3 5400U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>20490000</v>
+        <v>15990000</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>28490000</v>
+        <v>16990000</v>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>-28%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1404fa-eb935w-ryzen-5-7430u-16gb-512gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-46p-r73c</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T09:46:28.801+07:00</t>
+          <t>2026-09-09T17:28:20.555+07:00</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:38</t>
+          <t>2026-09-20 11:56:10</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ4821W (Ryzen 5/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R5MN (Ryzen 5 5625U/ 8GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>22990000</v>
-      </c>
-      <c r="C120" s="2" t="inlineStr"/>
-      <c r="D120" s="2" t="inlineStr"/>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>16490000</v>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>16990000</v>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1504fa-bq4821w-ryzen-5-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r5mn</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T14:05:39.37+07:00</t>
+          <t>2026-08-30T16:07:13.447+07:00</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:43</t>
+          <t>2026-09-20 11:56:15</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ340W (Ryzen 5/ 16GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q (Ryzen 7 5825U/ 8GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>28490000</v>
-      </c>
-      <c r="C121" s="2" t="inlineStr"/>
-      <c r="D121" s="2" t="inlineStr"/>
+        <v>18990000</v>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>20490000</v>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-go-15-e1504fa-bq340w-ryzen-5-16gb-512gb-156-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r86q-ryzen-7-5825u-8gb-512gb-windows-11-home-sl</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T14:28:58.285+07:00</t>
+          <t>2026-09-09T17:26:23.345+07:00</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:48</t>
+          <t>2026-09-20 11:56:20</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 M3407KA-SF034W (Ryzen AI 5-330/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-49P-R6XX (Ryzen 5 7430U/ 8GB/ 512GB/15.6"/ Win 11)</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>33990000</v>
-      </c>
-      <c r="C122" s="2" t="inlineStr"/>
-      <c r="D122" s="2" t="inlineStr"/>
+        <v>18590000</v>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>20990000</v>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-m3407ka-sf034w-ryzen-ai-5-330-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-49p-r6xx-ryzen-5-7430u-8gb-512gb-15-6-win-11</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T12:02:07.653+07:00</t>
+          <t>2026-08-21T13:56:25.879+07:00</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:53</t>
+          <t>2026-09-20 11:56:24</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407AA-SF032W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC (Core 5-120U/ 16GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>40490000</v>
-      </c>
-      <c r="C123" s="2" t="inlineStr"/>
-      <c r="D123" s="2" t="inlineStr"/>
+        <v>21990000</v>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf032w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56ec-core-5-120u-8gb-512gb-15-6-fhd-ips</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T10:00:42.045+07:00</t>
+          <t>2026-08-20T11:36:16.413+07:00</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:58</t>
+          <t>2026-09-20 11:56:29</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407AA-SF945W (Ultra 5-325/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>37490000</v>
-      </c>
-      <c r="C124" s="2" t="inlineStr"/>
-      <c r="D124" s="2" t="inlineStr"/>
+        <v>18890000</v>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>24990000</v>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>-24%</t>
+        </is>
+      </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf945w-ultra-5-325-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T11:09:17.449+07:00</t>
+          <t>2026-08-24T10:45:08.009+07:00</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:03</t>
+          <t>2026-09-20 11:56:34</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407QA-SF043W (QC X126100/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="C125" s="2" t="inlineStr"/>
-      <c r="D125" s="2" t="inlineStr"/>
+        <v>24990000</v>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>27990000</v>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® Arc™ Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407qa-sf043w-qc-x126100-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T09:15:59.141+07:00</t>
+          <t>2026-07-16T15:19:10.843+07:00</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:08</t>
+          <t>2026-09-20 11:56:39</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407VA-LY147W (Core 5-210H/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
+        <v>28990000</v>
+      </c>
+      <c r="C126" s="2" t="n">
         <v>34990000</v>
       </c>
-      <c r="C126" s="2" t="inlineStr"/>
-      <c r="D126" s="2" t="inlineStr"/>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>-17%</t>
+        </is>
+      </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® Arc™ Graphics 130V | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407va-ly147w-core-5-210h-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T11:42:14.925+07:00</t>
+          <t>2026-06-25T15:46:36.845+07:00</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:12</t>
+          <t>2026-09-20 11:56:44</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 16 S3607AA-SH042W (Ultra 5-325/ 16GB/ 512GB/ 16" FHD OLED)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF (Core 3-304/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>37490000</v>
+        <v>21990000</v>
       </c>
       <c r="C127" s="2" t="inlineStr"/>
       <c r="D127" s="2" t="inlineStr"/>
@@ -5427,35 +5483,31 @@
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-16-s3607aa-sh042w-ultra-5-325-16gb-512gb-16-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-34nf-core-3-304-12gb-512gb-14-fhd-ips-120hz-win-11</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T10:44:16.77+07:00</t>
+          <t>2026-09-09T11:33:09.974+07:00</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:17</t>
+          <t>2026-09-20 11:56:50</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 16 S3607CA-SH080W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD OLED)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV (Core 5-320/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>35990000</v>
+        <v>24990000</v>
       </c>
       <c r="C128" s="2" t="inlineStr"/>
       <c r="D128" s="2" t="inlineStr"/>
@@ -5465,350 +5517,372 @@
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-16-s3607ca-sh080w-ultra-5-225h-16gb-512gb-16-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-52bv-core-5-320-12gb-512gb-14-wuxga-ips-120hz-win-11</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T10:21:29.428+07:00</t>
+          <t>2026-09-10T09:29:56.638+07:00</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:22</t>
+          <t>2026-09-20 11:56:55</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS VivoBook S14 S3407CA-SF913W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>27890000</v>
-      </c>
-      <c r="C129" s="2" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>40990000</v>
+      </c>
+      <c r="C129" s="2" t="inlineStr"/>
+      <c r="D129" s="2" t="inlineStr"/>
+      <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr"/>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s14-s3407ca-sf913w-ultra-5-225h-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T17:02:01.429+07:00</t>
+          <t>2026-08-14T11:08:27.137+07:00</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:27</t>
+          <t>2026-09-20 11:57:00</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UM3406GA-QD075W (Ryzen 7/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="C130" s="2" t="inlineStr"/>
-      <c r="D130" s="2" t="inlineStr"/>
+        <v>29990000</v>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
-      <c r="G130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ga-qd075w-ryzen-7-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T16:03:07.024+07:00</t>
+          <t>2026-09-10T16:12:16.172+07:00</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:32</t>
+          <t>2026-09-20 11:57:05</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1531W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>42990000</v>
-      </c>
-      <c r="C131" s="2" t="inlineStr"/>
-      <c r="D131" s="2" t="inlineStr"/>
+        <v>49990000</v>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>54990000</v>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® Arc™ B390 GPU (đồ họa tích hợp) | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1531w-ultra-9-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T08:45:55.514+07:00</t>
+          <t>2026-08-28T15:51:47.551+07:00</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:37</t>
+          <t>2026-09-20 11:57:10</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1713W (Ultra 5-225H/ 16GB/ 512GB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop Acer Swift Go AI OLED SFG14-75-765M (Ultra 7-258V/ 32GB/ 512GB/ 14" FHD+ OLED/ Win11)</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>31990000</v>
+        <v>39990000</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>38990000</v>
+        <v>40990000</v>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>-18%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® Arc™ Graphics 140V | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1713w-ultra-5-225h-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-ai-oled-sfg14-75-765m-14-fhd-oled-u7-258v-32lp-512gb-win</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T11:57:10.625+07:00</t>
+          <t>2026-08-14T10:47:31.44+07:00</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:42</t>
+          <t>2026-09-20 11:57:15</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST630W (Ultra 7-255H/ 16GB/ 512GB/ 14" 3K OLED)</t>
+          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>40990000</v>
+        <v>32999000</v>
       </c>
       <c r="C133" s="2" t="inlineStr"/>
       <c r="D133" s="2" t="inlineStr"/>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st630w-ultra-7-255h-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T15:05:39.807+07:00</t>
+          <t>2026-09-15T14:38:31.288+07:00</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:47</t>
+          <t>2026-09-20 11:57:20</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3407NA-QD132WS (Snapdragon X2 Elite X2E-88-100/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>48990000</v>
-      </c>
-      <c r="C134" s="2" t="inlineStr"/>
-      <c r="D134" s="2" t="inlineStr"/>
+        <v>31490000</v>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>32490000</v>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® Arc™ 130T Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd132ws-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:47:13.916+07:00</t>
+          <t>2026-06-25T15:45:41.503+07:00</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:52</t>
+          <t>2026-09-20 11:57:25</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook A14 UX3407NA-QD254W (Snapdragon X2 Elite X2E-88-100/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop Acer Swift X SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" 2.8K OLED/ Win 11/ Office)</t>
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>63990000</v>
-      </c>
-      <c r="C135" s="2" t="inlineStr"/>
-      <c r="D135" s="2" t="inlineStr"/>
+        <v>35990000</v>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>45990000</v>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>-22%</t>
+        </is>
+      </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6 | Kích thước màn hình: 14.5 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd254w-32gb-1tb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:46:55.101+07:00</t>
+          <t>2026-09-14T15:56:38.644+07:00</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:57</t>
+          <t>2026-09-20 11:57:30</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook A16 UX3607OA-SQ137WS (Snapdragon X2 Elite Extreme X2E94100/ 24GB/ 512GB/ 16" 3K OLED/ Win 11)</t>
+          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>58990000</v>
-      </c>
-      <c r="C136" s="2" t="inlineStr"/>
-      <c r="D136" s="2" t="inlineStr"/>
+        <v>43990000</v>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>49490000</v>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 16 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 24 GB</t>
+          <t>Card đồ họa: RTX 4060 | Kích thước màn hình: 14.5 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-16-ux3607oa-sq137ws-24gb-512gb-16-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:43:18.337+07:00</t>
+          <t>2026-07-03T15:10:56.836+07:00</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:02</t>
+          <t>2026-09-20 11:57:35</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN138WS (Ultra X9/ 32GB/ 1TB/ 14" 3K OLED Touch 144Hz)</t>
+          <t>Laptop ASUS ExpertBook B1 BM1403CDA-S61611W (Ryzen 5-150/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>89990000</v>
-      </c>
-      <c r="C137" s="2" t="inlineStr"/>
-      <c r="D137" s="2" t="inlineStr"/>
+        <v>18800000</v>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>22490000</v>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>-16%</t>
+        </is>
+      </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5817,36 +5891,42 @@
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: AMD Radeon™ Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn138ws-ultra-x9-32gb-1tb-14-3k-oled-touch-144hz</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-b1-bm1403cda-s61611w</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T12:04:03.945+07:00</t>
+          <t>2026-08-24T10:27:49.398+07:00</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:07</t>
+          <t>2026-09-20 11:57:40</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN439WS (Ultra X7/ 32GB/ 512GB/ 14" 3K OLED Touch 144Hz)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H08-50W (Core 5-210H/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>82990000</v>
-      </c>
-      <c r="C138" s="2" t="inlineStr"/>
-      <c r="D138" s="2" t="inlineStr"/>
+        <v>19490000</v>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>21990000</v>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5855,36 +5935,42 @@
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn439ws-ultra-x7-32gb-512gb-14-3k-oled-touch-144hz</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h08-50w</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T11:44:06.982+07:00</t>
+          <t>2026-07-31T11:09:14.14+07:00</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:11</t>
+          <t>2026-09-20 11:57:45</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook Pro Art HN7306EA-LX050W (Ryzen AI Max+ 395/ 32GB/ 1TB/ 13.3" 3K OLED Touch)</t>
+          <t>Laptop Asus ExpertBook P1 P1403CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>76990000</v>
-      </c>
-      <c r="C139" s="2" t="inlineStr"/>
-      <c r="D139" s="2" t="inlineStr"/>
+        <v>24290000</v>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>26990000</v>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5893,74 +5979,82 @@
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 13.3 inch | Dòng CPU: Ryzen AI MAX+ | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-pro-art-hn7306ea-lx050w-ryzen-ai-max-395-32gb-1tb-13-3-3k-oled-touch</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h16-63ws-core-5-210h-16gb-512gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T11:16:12.092+07:00</t>
+          <t>2026-08-03T15:06:02.246+07:00</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:16</t>
+          <t>2026-09-20 11:57:50</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook S 14 UX5406AA-SU348W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED Touch)</t>
+          <t>Laptop Asus ExpertBook P1 P1403CVA-C7H16-50W (Core 7-240H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>50990000</v>
-      </c>
-      <c r="C140" s="2" t="inlineStr"/>
-      <c r="D140" s="2" t="inlineStr"/>
+        <v>28990000</v>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-s-14-ux5406aa-su348w-ultra-9-16gb-512gb-14-3k-oled-touch</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c7h16-50w-core-7-240h-16gb-512gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T10:26:19.879+07:00</t>
+          <t>2026-08-03T14:43:57.168+07:00</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:21</t>
+          <t>2026-09-20 11:57:55</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook S 15 UM5606GA-SS441W (Ryzen AI 9 465/ 16GB/ 512GB/ 15" 3K OLED)</t>
+          <t>Laptop Asus ExpertBook P1 P1503CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>49490000</v>
-      </c>
-      <c r="C141" s="2" t="inlineStr"/>
-      <c r="D141" s="2" t="inlineStr"/>
+        <v>24290000</v>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>26990000</v>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5969,164 +6063,174 @@
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ryzen AI 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-s-15-um5606ga-ss441w-ryzen-ai-9-465-16gb-512gb-15-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1503cva-c5h16-63ws-core-5-210h-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T10:51:02.985+07:00</t>
+          <t>2026-08-03T14:03:33.213+07:00</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:26</t>
+          <t>2026-09-20 11:58:00</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1 P1403CVA-C3U08-50W (Core 3-100U/ 8GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>22990000</v>
+        <v>15490000</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>23990000</v>
+        <v>17990000</v>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Card đồ họa tích hợp - Qualcomm® Adreno™ | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c3u08-50w</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T09:43:41.692+07:00</t>
+          <t>2026-07-31T13:53:40.042+07:00</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:42</t>
+          <t>2026-09-20 11:58:05</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AG14-72P-563L (Core 5 120U/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>19490000</v>
+        <v>23390000</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>22990000</v>
+        <v>27990000</v>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr"/>
+          <t>-16%</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ag14-72p-563l</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T17:24:08.222+07:00</t>
+          <t>2026-08-12T10:19:47.487+07:00</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:49</t>
+          <t>2026-09-20 11:58:10</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U516S8W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>23990000</v>
+        <v>26390000</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>25990000</v>
+        <v>29990000</v>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® ARC™ Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u516s8w-ultra-5-225h-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T15:00:45.83+07:00</t>
+          <t>2026-08-03T11:57:56.626+07:00</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:54</t>
+          <t>2026-09-20 11:58:15</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M (Ultra 9-185H/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U716S8W (Ultra 7-255H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="C145" s="2" t="inlineStr"/>
-      <c r="D145" s="2" t="inlineStr"/>
+        <v>30590000</v>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>34990000</v>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6136,1046 +6240,972 @@
       <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-16gb-512gb-14-fhd-ips-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u716s8w-ultra-7-255h-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T09:48:08.298+07:00</t>
+          <t>2026-09-06T13:46:08.673+07:00</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:59</t>
+          <t>2026-09-20 11:58:20</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Max C13VF-421VN (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>22990000</v>
-      </c>
-      <c r="C146" s="2" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>44990000</v>
+      </c>
+      <c r="C146" s="2" t="inlineStr"/>
+      <c r="D146" s="2" t="inlineStr"/>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13vf-421vn-i7-13620h-rtx-5060-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T21:08:15.03+07:00</t>
+          <t>2026-07-27T11:01:57.991+07:00</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:04</t>
+          <t>2026-09-20 11:54:20</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AI AG15-52P-52WT (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Max C13WE-422VN (I7-13620H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>22990000</v>
+        <v>42990000</v>
       </c>
       <c r="C147" s="2" t="inlineStr"/>
       <c r="D147" s="2" t="inlineStr"/>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-52p-52wt</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn-i7-13620h-rtx-5050-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T09:27:37.618+07:00</t>
+          <t>2026-07-27T10:38:57.001+07:00</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:09</t>
+          <t>2026-09-20 11:54:25</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AG15 72P 54GY (Intel Core 5/ 16GB/ 512GB/ Intel UHD/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>19490000</v>
+        <v>34890000</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>23990000</v>
+        <v>35990000</v>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>-19%</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr"/>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ai-ag15-72p-54gy</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T17:24:34.893+07:00</t>
+          <t>2026-06-30T14:54:13.66+07:00</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:14</t>
+          <t>2026-09-20 11:54:31</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
+          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>20990000</v>
+        <v>48490000</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>21990000</v>
+        <v>52990000</v>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
-        </is>
-      </c>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr"/>
-      <c r="G149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: QHD (2560x1440) | Tần số quét: 165 Hz</t>
+        </is>
+      </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17T09:17:18.78+07:00</t>
+          <t>2026-09-10T14:49:48.046+07:00</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:19</t>
+          <t>2026-09-20 11:54:36</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-45P-R7Z3 (Ryzen 3 5400U/ 8GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>15990000</v>
+        <v>79990000</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>17590000</v>
+        <v>80990000</v>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
-      <c r="G150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+        </is>
+      </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-45p-r7z3</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T17:28:26.25+07:00</t>
+          <t>2026-06-30T15:43:38.331+07:00</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:24</t>
+          <t>2026-09-20 11:54:41</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR (Ryzen 5 3500U/ 8GB/ 512GB/ 14.0" FHD IPS)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>17990000</v>
-      </c>
-      <c r="C151" s="2" t="n">
-        <v>19990000</v>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
+        <v>85990000</v>
+      </c>
+      <c r="C151" s="2" t="inlineStr"/>
+      <c r="D151" s="2" t="inlineStr"/>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr"/>
-      <c r="G151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+        </is>
+      </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:14:52.788+07:00</t>
+          <t>2026-09-15T10:30:35.835+07:00</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:29</t>
+          <t>2026-09-20 11:54:46</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 16GB/ 512GB/ 14.0" FHD+ IPS)</t>
+          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>22990000</v>
+        <v>67690000</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>23990000</v>
+        <v>73990000</v>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
-        </is>
-      </c>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr"/>
-      <c r="G152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4060 | Kích thước màn hình: 16 inch</t>
+        </is>
+      </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T21:14:04.587+07:00</t>
+          <t>2026-01-27T14:36:44.954+07:00</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:34</t>
+          <t>2026-09-20 11:54:51</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-57P-54YV (Core 5 315/ 8GB/ 512GB)</t>
+          <t>Laptop GIGABYTE AERO X16 4WHN3VNC93AH (Ryzen AI 9 465/ RTX 5070 8GB/ 16GB/ 512GB/ 16" QHD+ 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>23990000</v>
-      </c>
-      <c r="C153" s="2" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
-        </is>
-      </c>
+        <v>54990000</v>
+      </c>
+      <c r="C153" s="2" t="inlineStr"/>
+      <c r="D153" s="2" t="inlineStr"/>
+      <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-54yv-core-5-315-8gb-512gb</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-x16-4whn3vnc93ah-ryzen-ai-9-465-rtx-5070-8gb-16gb-512gb-16-qhd-165hz-win-11</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T14:01:15.719+07:00</t>
+          <t>2026-09-18T13:49:41.514+07:00</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:39</t>
+          <t>2026-09-20 11:54:56</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14.0" FHD+ IPS)</t>
+          <t>Laptop GIGABYTE AORUS Master 16 6XJM4VNE64SH (Ryzen 9 9955HX3D/ RTX 5070 Ti 12GB/ 32GB/ 1TB/ 16" QHD+ OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="C154" s="2" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>86990000</v>
+      </c>
+      <c r="C154" s="2" t="inlineStr"/>
+      <c r="D154" s="2" t="inlineStr"/>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aorus-master-16-6xjm4vne64sh-ryzen-9-9955hx3d-rtx-5070-ti-12gb-32gb-1tb-16-qhd-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T15:07:04.792+07:00</t>
+          <t>2026-08-28T11:03:18.048+07:00</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:44</t>
+          <t>2026-09-20 11:55:01</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-57P-76KR (Core 7 350/ 8GB/ 512GB)</t>
+          <t>Laptop GIGABYTE Gaming A16 EVHS3VN893SH (Ultra 9-185H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>25990000</v>
+        <v>39990000</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>26990000</v>
+        <v>40990000</v>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
-        </is>
-      </c>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr"/>
       <c r="F155" s="2" t="inlineStr"/>
-      <c r="G155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+        </is>
+      </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-76kr-core-7-350-8gb-512gb</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-gaming-a16-evhs3vn893sh-ultra-9-185h-rtx-5060-8gb-16gb-512gb-16-fhd-165hz-win-11</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T12:03:11.649+07:00</t>
+          <t>2026-09-18T13:36:39.051+07:00</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:49</t>
+          <t>2026-09-20 11:55:06</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-36P-30TN (Core 3-N350/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop HP 15-fd1289TU C2CV8PA (Ultra 7-155H/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>16990000</v>
+        <v>24990000</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>18990000</v>
+        <v>25990000</v>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
-        </is>
-      </c>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr"/>
-      <c r="G156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al15-36p-30tn</t>
+          <t>https://gearvn.com/products/laptop-hp-15-fd1289tu-c2cv8pa-ultra-7-155h-16gb-512gb-15-6-fhd-ips-win-11</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:31:44.094+07:00</t>
+          <t>2026-09-10T13:33:44.001+07:00</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:54</t>
+          <t>2026-09-20 11:55:11</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop HP 250 G10 A06FDPT (I7-1355U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>17990000</v>
+        <v>23490000</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>19790000</v>
+        <v>25590000</v>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
-        </is>
-      </c>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr"/>
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
+          <t>https://gearvn.com/products/laptop-hp-250-g10-a06fdpt-i7-1355u-8gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T14:20:10.941+07:00</t>
+          <t>2026-09-10T13:31:30.682+07:00</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:59</t>
+          <t>2026-09-20 11:55:16</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop HP ProBook 450 G10 B73TPAT (I5-1334U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>19590000</v>
+        <v>23990000</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>21990000</v>
+        <v>24990000</v>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
-        </is>
-      </c>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr"/>
-      <c r="G158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Iris Xe Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
+          <t>https://gearvn.com/products/laptop-hp-probook-450-g10-b73tpat-i5-1334u-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11T14:50:36.616+07:00</t>
+          <t>2026-09-10T13:31:53.385+07:00</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:04</t>
+          <t>2026-09-20 11:55:21</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5 3500U/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 83RQ00DBVN (Core 3-304/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>17990000</v>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v>19990000</v>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
+        <v>24990000</v>
+      </c>
+      <c r="C159" s="2" t="inlineStr"/>
+      <c r="D159" s="2" t="inlineStr"/>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" s="2" t="inlineStr"/>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-14iwc11-83rq00dbvn-core-3-304-8gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T10:40:38.213+07:00</t>
+          <t>2026-09-07T10:16:44.995+07:00</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:09</t>
+          <t>2026-09-20 11:55:26</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-411P-R1CM (Ryzen 5 3500U/ 8GB/ 256GB)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB005YVN (Ryzen 5-125/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>17990000</v>
-      </c>
-      <c r="C160" s="2" t="n">
-        <v>18990000</v>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
+        <v>25990000</v>
+      </c>
+      <c r="C160" s="2" t="inlineStr"/>
+      <c r="D160" s="2" t="inlineStr"/>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r1cm-ryzen-5-3500u-8gb-256gb</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb005yvn-ryzen-5-125-8gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T14:26:56.746+07:00</t>
+          <t>2026-08-13T15:01:44.794+07:00</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:14</t>
+          <t>2026-09-20 11:55:31</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-411P-R7YP (Ryzen 3 3200U/ 8GB/ 256GB)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB0060VN (Ryzen 7-155/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>15990000</v>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v>16990000</v>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>27990000</v>
+      </c>
+      <c r="C161" s="2" t="inlineStr"/>
+      <c r="D161" s="2" t="inlineStr"/>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r7yp-ryzen-3-3200u-8gb-256gb</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb0060vn-ryzen-7-155-8gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T14:48:50.246+07:00</t>
+          <t>2026-08-13T14:35:59.897+07:00</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:19</t>
+          <t>2026-09-20 11:55:36</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-44P-R4UH (Ryzen 7 7730U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 83S1003GVN</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>21890000</v>
+        <v>44540000</v>
       </c>
       <c r="C162" s="2" t="n">
-        <v>23990000</v>
+        <v>47990000</v>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
-        </is>
-      </c>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr"/>
       <c r="F162" s="2" t="inlineStr"/>
-      <c r="G162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-44p-r4uh</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-83s1003gvn</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T17:27:57.208+07:00</t>
+          <t>2026-08-28T10:29:16.152+07:00</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:24</t>
+          <t>2026-09-20 11:55:41</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-46P-R73C (Ryzen 3 5400U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 OLED 83S1006RVN (Ryzen AI 7-445/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>15990000</v>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>16990000</v>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>32990000</v>
+      </c>
+      <c r="C163" s="2" t="inlineStr"/>
+      <c r="D163" s="2" t="inlineStr"/>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
-      <c r="G163" s="2" t="inlineStr"/>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-46p-r73c</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-oled-83s1006rvn-ryzen-ai-7-445-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T17:28:20.555+07:00</t>
+          <t>2026-08-13T11:54:44.05+07:00</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:29</t>
+          <t>2026-09-20 11:55:46</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R5MN (Ryzen 5 5625U/ 8GB/ 512GB/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00ABVN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>16490000</v>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>16990000</v>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr"/>
+        <v>30990000</v>
+      </c>
+      <c r="C164" s="2" t="inlineStr"/>
+      <c r="D164" s="2" t="inlineStr"/>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r5mn</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00abvn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30T16:07:13.447+07:00</t>
+          <t>2026-08-13T14:05:59.687+07:00</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:34</t>
+          <t>2026-09-20 11:55:51</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-48P-R86Q (Ryzen 7 5825U/ 8GB/ 512GB/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00F5VN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>18990000</v>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>20490000</v>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>34990000</v>
+      </c>
+      <c r="C165" s="2" t="inlineStr"/>
+      <c r="D165" s="2" t="inlineStr"/>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-48p-r86q-ryzen-7-5825u-8gb-512gb-windows-11-home-sl</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00f5vn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T17:26:23.345+07:00</t>
+          <t>2026-09-07T10:17:34.624+07:00</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:39</t>
+          <t>2026-09-20 11:55:56</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-49P-R6XX (Ryzen 5 7430U/ 8GB/ 512GB/15.6"/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002EVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>18590000</v>
-      </c>
-      <c r="C166" s="2" t="n">
-        <v>20990000</v>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
-      </c>
+        <v>55990000</v>
+      </c>
+      <c r="C166" s="2" t="inlineStr"/>
+      <c r="D166" s="2" t="inlineStr"/>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr"/>
-      <c r="G166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-49p-r6xx-ryzen-5-7430u-8gb-512gb-15-6-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002evn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T13:56:25.879+07:00</t>
+          <t>2026-08-13T10:21:35.763+07:00</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:44</t>
+          <t>2026-09-20 11:56:01</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56EC (Core 5-120U/ 16GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002FVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>21990000</v>
-      </c>
-      <c r="C167" s="2" t="n">
-        <v>23990000</v>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>-8%</t>
-        </is>
-      </c>
+        <v>55990000</v>
+      </c>
+      <c r="C167" s="2" t="inlineStr"/>
+      <c r="D167" s="2" t="inlineStr"/>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr"/>
-      <c r="G167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56ec-core-5-120u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002fvn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:36:16.413+07:00</t>
+          <t>2026-08-12T20:29:51.634+07:00</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:49</t>
+          <t>2026-09-20 11:56:06</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0075VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>18890000</v>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>-24%</t>
-        </is>
-      </c>
+        <v>46990000</v>
+      </c>
+      <c r="C168" s="2" t="inlineStr"/>
+      <c r="D168" s="2" t="inlineStr"/>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
-        </is>
-      </c>
+      <c r="G168" s="2" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0075vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T10:45:08.009+07:00</t>
+          <t>2026-09-07T10:19:34.771+07:00</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:54</t>
+          <t>2026-09-20 11:56:11</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0076VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
-      </c>
+        <v>46990000</v>
+      </c>
+      <c r="C169" s="2" t="inlineStr"/>
+      <c r="D169" s="2" t="inlineStr"/>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0076vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T15:19:10.843+07:00</t>
+          <t>2026-09-07T10:20:20.027+07:00</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:59</t>
+          <t>2026-09-20 11:56:16</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift 14 AI SF14-51-53P9 (Ultra 5-226V/ 16GB/ 1TB/ 14.0" 3K OLED/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK0015VN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>28990000</v>
-      </c>
-      <c r="C170" s="2" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>-17%</t>
-        </is>
-      </c>
+        <v>72990000</v>
+      </c>
+      <c r="C170" s="2" t="inlineStr"/>
+      <c r="D170" s="2" t="inlineStr"/>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ Graphics 130V | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-14-ai-sf14-51-53p9</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk0015vn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:46:36.845+07:00</t>
+          <t>2026-09-07T10:21:45.74+07:00</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:04</t>
+          <t>2026-09-20 11:56:21</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF (Core 3-304/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK006GVN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>21990000</v>
+        <v>72990000</v>
       </c>
       <c r="C171" s="2" t="inlineStr"/>
       <c r="D171" s="2" t="inlineStr"/>
@@ -7185,31 +7215,35 @@
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr"/>
-      <c r="G171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-34nf-core-3-304-12gb-512gb-14-fhd-ips-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk006gvn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T11:33:09.974+07:00</t>
+          <t>2026-09-07T10:23:05.36+07:00</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:09</t>
+          <t>2026-09-20 11:56:26</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV (Core 5-320/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 POLED 83QK009PVN (Ultra X9-378H/ 32GB/ 1TB/ 14" 2.8K WQXGA POLED Touch/ Win 11)</t>
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>24990000</v>
+        <v>70990000</v>
       </c>
       <c r="C172" s="2" t="inlineStr"/>
       <c r="D172" s="2" t="inlineStr"/>
@@ -7219,370 +7253,356 @@
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr"/>
-      <c r="G172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-52bv-core-5-320-12gb-512gb-14-wuxga-ips-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-poled-83qk009pvn-ultra-x9-378h-32gb-1tb-14-2-8k-wqxga-poled-touch-win-11</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T09:29:56.638+07:00</t>
+          <t>2026-08-12T20:11:25.828+07:00</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:14</t>
+          <t>2026-09-20 11:56:31</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Edge 14 AI SFE14-51T-52KD</t>
+          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="C173" s="2" t="inlineStr"/>
-      <c r="D173" s="2" t="inlineStr"/>
-      <c r="E173" s="2" t="inlineStr"/>
+        <v>33900000</v>
+      </c>
+      <c r="C173" s="2" t="n">
+        <v>34900000</v>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F173" s="2" t="inlineStr"/>
-      <c r="G173" s="2" t="inlineStr"/>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-edge-14-ai-sfe14-51t-52kd</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T11:08:27.137+07:00</t>
+          <t>2026-07-01T13:39:36.938+07:00</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:19</t>
+          <t>2026-09-20 11:56:36</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>29990000</v>
+        <v>36900000</v>
       </c>
       <c r="C174" s="2" t="n">
-        <v>30990000</v>
+        <v>37900000</v>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
           <t>-3%</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+      <c r="E174" s="2" t="inlineStr"/>
       <c r="F174" s="2" t="inlineStr"/>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T16:12:16.172+07:00</t>
+          <t>2026-07-01T13:34:21.041+07:00</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:24</t>
+          <t>2026-09-20 11:56:41</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>49990000</v>
+        <v>44900000</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>54990000</v>
+        <v>46490000</v>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr"/>
       <c r="F175" s="2" t="inlineStr"/>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel® Arc™ B390 GPU (đồ họa tích hợp) | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
-        </is>
-      </c>
+      <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T15:51:47.551+07:00</t>
+          <t>2026-07-01T13:43:00.949+07:00</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:29</t>
+          <t>2026-09-20 11:56:46</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI OLED SFG14-75-765M (Ultra 7-258V/ 32GB/ 512GB/ 14" FHD+ OLED/ Win11)</t>
+          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>39990000</v>
+        <v>23990000</v>
       </c>
       <c r="C176" s="2" t="n">
-        <v>40990000</v>
+        <v>24990000</v>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ Graphics 140V | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-ai-oled-sfg14-75-765m-14-fhd-oled-u7-258v-32lp-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T10:47:31.44+07:00</t>
+          <t>2026-07-01T13:36:48.562+07:00</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:34</t>
+          <t>2026-09-20 11:56:51</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>32999000</v>
-      </c>
-      <c r="C177" s="2" t="inlineStr"/>
-      <c r="D177" s="2" t="inlineStr"/>
+        <v>61990000</v>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>62990000</v>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr"/>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
+          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T14:38:31.288+07:00</t>
+          <t>2026-06-30T15:29:18.09+07:00</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:39</t>
+          <t>2026-09-20 11:56:56</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>31490000</v>
+        <v>33990000</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>32490000</v>
+        <v>37990000</v>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr"/>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel® Arc™ 130T Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
+          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:45:41.503+07:00</t>
+          <t>2026-08-28T10:03:31.114+07:00</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:44</t>
+          <t>2026-09-20 11:57:01</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" 2.8K OLED/ Win 11/ Office)</t>
+          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>35990000</v>
+        <v>25490000</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>45990000</v>
+        <v>25990000</v>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr"/>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6 | Kích thước màn hình: 14.5 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
-        </is>
-      </c>
+      <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:56:38.644+07:00</t>
+          <t>2026-06-25T15:41:40.106+07:00</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:49</t>
+          <t>2026-09-20 11:57:06</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
+          <t>Laptop MSI Modern 14S AI+ G3MG-050VN (Ultra 7-355/ 16GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>43990000</v>
-      </c>
-      <c r="C180" s="2" t="n">
-        <v>49490000</v>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
-      </c>
+        <v>36490000</v>
+      </c>
+      <c r="C180" s="2" t="inlineStr"/>
+      <c r="D180" s="2" t="inlineStr"/>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr"/>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: RTX 4060 | Kích thước màn hình: 14.5 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
-        </is>
-      </c>
+      <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-14s-ai-g3mg-050vn-ultra-7-355-16gb-1tb-14-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T15:10:56.836+07:00</t>
+          <t>2026-09-16T14:08:29.354+07:00</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:55</t>
+          <t>2026-09-20 11:57:11</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ExpertBook B1 BM1403CDA-S61611W (Ryzen 5-150/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>18800000</v>
+        <v>22190000</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>22490000</v>
+        <v>22690000</v>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -7593,40 +7613,40 @@
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon™ Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-b1-bm1403cda-s61611w</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T10:27:49.398+07:00</t>
+          <t>2026-07-09T15:28:04.144+07:00</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:00</t>
+          <t>2026-09-20 11:57:16</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H08-50W (Core 5-210H/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>19490000</v>
+        <v>43990000</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>21990000</v>
+        <v>44990000</v>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -7637,40 +7657,40 @@
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h08-50w</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T11:09:14.14+07:00</t>
+          <t>2026-06-25T15:49:42.234+07:00</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:05</t>
+          <t>2026-09-20 11:57:21</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1403CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>24290000</v>
+        <v>33990000</v>
       </c>
       <c r="C183" s="2" t="n">
-        <v>26990000</v>
+        <v>34990000</v>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -7681,40 +7701,40 @@
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 7 | Dung lượng SSD: 1024 GB | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h16-63ws-core-5-210h-16gb-512gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T15:06:02.246+07:00</t>
+          <t>2026-06-25T16:07:23.364+07:00</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:10</t>
+          <t>2026-09-20 11:57:26</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1403CVA-C7H16-50W (Core 7-240H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>28990000</v>
+        <v>37990000</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>30990000</v>
+        <v>39990000</v>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -7723,38 +7743,42 @@
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr"/>
-      <c r="G184" s="2" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 13.3 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c7h16-50w-core-7-240h-16gb-512gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T14:43:57.168+07:00</t>
+          <t>2026-08-17T11:20:56.718+07:00</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:15</t>
+          <t>2026-09-20 11:57:31</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1503CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN (Ultra 7-355/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>24290000</v>
+        <v>46990000</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>26990000</v>
+        <v>48990000</v>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -7765,128 +7789,104 @@
       <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® Arc™ graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1503cva-c5h16-63ws-core-5-210h-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T14:03:33.213+07:00</t>
+          <t>2026-08-31T14:41:10.864+07:00</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:20</t>
+          <t>2026-09-20 11:57:36</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1403CVA-C3U08-50W (Core 3-100U/ 8GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>15490000</v>
-      </c>
-      <c r="C186" s="2" t="n">
-        <v>17990000</v>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
-        <is>
-          <t>-14%</t>
-        </is>
-      </c>
+        <v>59990000</v>
+      </c>
+      <c r="C186" s="2" t="inlineStr"/>
+      <c r="D186" s="2" t="inlineStr"/>
       <c r="E186" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr"/>
-      <c r="G186" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
-        </is>
-      </c>
+      <c r="G186" s="2" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c3u08-50w</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T13:53:40.042+07:00</t>
+          <t>2026-06-30T09:54:52.677+07:00</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:25</t>
+          <t>2026-09-20 11:57:41</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>23390000</v>
-      </c>
-      <c r="C187" s="2" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
-        <is>
-          <t>-16%</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>59990000</v>
+      </c>
+      <c r="C187" s="2" t="inlineStr"/>
+      <c r="D187" s="2" t="inlineStr"/>
+      <c r="E187" s="2" t="inlineStr"/>
       <c r="F187" s="2" t="inlineStr"/>
-      <c r="G187" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G187" s="2" t="inlineStr"/>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T10:19:47.487+07:00</t>
+          <t>2026-06-30T10:17:43.984+07:00</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:30</t>
+          <t>2026-09-20 11:57:46</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U516S8W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/ RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>26390000</v>
+        <v>82990000</v>
       </c>
       <c r="C188" s="2" t="n">
-        <v>29990000</v>
+        <v>83990000</v>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -7895,42 +7895,38 @@
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr"/>
-      <c r="G188" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G188" s="2" t="inlineStr"/>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u516s8w-ultra-5-225h-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T11:57:56.626+07:00</t>
+          <t>2026-09-14T18:03:22.38+07:00</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:35</t>
+          <t>2026-09-20 11:57:51</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U716S8W (Ultra 7-255H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>30590000</v>
+        <v>86990000</v>
       </c>
       <c r="C189" s="2" t="n">
-        <v>34990000</v>
+        <v>87990000</v>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -7939,20 +7935,24 @@
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr"/>
-      <c r="G189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+        </is>
+      </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u716s8w-ultra-7-255h-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T13:46:08.673+07:00</t>
+          <t>2026-06-30T15:49:19.952+07:00</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:40</t>
+          <t>2026-09-20 11:57:56</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:41</t>
+          <t>2026-09-20 11:54:19</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:47</t>
+          <t>2026-09-20 11:54:25</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:52</t>
+          <t>2026-09-20 11:54:30</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:48:57</t>
+          <t>2026-09-20 11:54:35</t>
         </is>
       </c>
     </row>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:02</t>
+          <t>2026-09-20 11:54:40</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:07</t>
+          <t>2026-09-20 11:54:45</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:12</t>
+          <t>2026-09-20 11:54:50</t>
         </is>
       </c>
     </row>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:17</t>
+          <t>2026-09-20 11:54:55</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:22</t>
+          <t>2026-09-20 11:55:00</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:27</t>
+          <t>2026-09-20 11:55:05</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:32</t>
+          <t>2026-09-20 11:55:10</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:37</t>
+          <t>2026-09-20 11:55:15</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:42</t>
+          <t>2026-09-20 11:55:20</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:47</t>
+          <t>2026-09-20 11:55:25</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:53</t>
+          <t>2026-09-20 11:55:30</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:49:58</t>
+          <t>2026-09-20 11:55:35</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:03</t>
+          <t>2026-09-20 11:55:40</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:08</t>
+          <t>2026-09-20 11:55:45</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:13</t>
+          <t>2026-09-20 11:55:50</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:18</t>
+          <t>2026-09-20 11:55:55</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:23</t>
+          <t>2026-09-20 11:56:00</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:28</t>
+          <t>2026-09-20 11:56:05</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:33</t>
+          <t>2026-09-20 11:56:10</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:38</t>
+          <t>2026-09-20 11:56:15</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:43</t>
+          <t>2026-09-20 11:56:20</t>
         </is>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:48</t>
+          <t>2026-09-20 11:56:25</t>
         </is>
       </c>
     </row>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:53</t>
+          <t>2026-09-20 11:56:30</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:50:58</t>
+          <t>2026-09-20 11:56:35</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:03</t>
+          <t>2026-09-20 11:56:40</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:08</t>
+          <t>2026-09-20 11:56:45</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:13</t>
+          <t>2026-09-20 11:56:50</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:18</t>
+          <t>2026-09-20 11:56:55</t>
         </is>
       </c>
     </row>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:23</t>
+          <t>2026-09-20 11:57:00</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:28</t>
+          <t>2026-09-20 11:57:05</t>
         </is>
       </c>
     </row>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:33</t>
+          <t>2026-09-20 11:57:10</t>
         </is>
       </c>
     </row>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:38</t>
+          <t>2026-09-20 11:57:15</t>
         </is>
       </c>
     </row>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:43</t>
+          <t>2026-09-20 11:57:20</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:48</t>
+          <t>2026-09-20 11:57:25</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:53</t>
+          <t>2026-09-20 11:57:30</t>
         </is>
       </c>
     </row>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:51:58</t>
+          <t>2026-09-20 11:57:35</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:03</t>
+          <t>2026-09-20 11:57:40</t>
         </is>
       </c>
     </row>
@@ -9624,7 +9624,7 @@
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:08</t>
+          <t>2026-09-20 11:57:45</t>
         </is>
       </c>
     </row>
@@ -9635,14 +9635,14 @@
         </is>
       </c>
       <c r="B232" s="3" t="n">
-        <v>39590000</v>
+        <v>39490000</v>
       </c>
       <c r="C232" s="2" t="n">
         <v>40990000</v>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -9663,12 +9663,12 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:59:01.74+07:00</t>
+          <t>2026-09-19T16:43:38.321+07:00</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:13</t>
+          <t>2026-09-20 11:57:50</t>
         </is>
       </c>
     </row>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:18</t>
+          <t>2026-09-20 11:57:55</t>
         </is>
       </c>
     </row>
@@ -9751,12 +9751,12 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T16:48:14.974+07:00</t>
+          <t>2026-09-19T16:40:42.967+07:00</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:23</t>
+          <t>2026-09-20 11:58:00</t>
         </is>
       </c>
     </row>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:28</t>
+          <t>2026-09-20 11:58:05</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:33</t>
+          <t>2026-09-20 11:58:10</t>
         </is>
       </c>
     </row>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:52:38</t>
+          <t>2026-09-20 11:58:15</t>
         </is>
       </c>
     </row>

--- a/laptop_gearvn_all.xlsx
+++ b/laptop_gearvn_all.xlsx
@@ -503,11 +503,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU405AR-SY016W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB027W (Core 3/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>96990000</v>
+        <v>22990000</v>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
@@ -519,33 +519,33 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405ar-sy016w-ultra-9-rtx-5070-ti-32gb-1tb-14-3k-oled-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb027w-core-3-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:47:29.287+07:00</t>
+          <t>2026-08-18T16:52:41.33+07:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:27</t>
+          <t>2026-09-26 11:57:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU405AW-SY029W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB029W (Core 7/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>119990000</v>
+        <v>35490000</v>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr"/>
@@ -557,33 +557,33 @@
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405aw-sy029w-ultra-9-rtx-5080-32gb-1tb-14-3k-oled-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb029w-core-7-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:47:45.327+07:00</t>
+          <t>2026-08-20T15:05:22.575+07:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:33</t>
+          <t>2026-09-26 11:57:45</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR115W (Ultra 7-255H/ RTX 5070/ 16GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB219W (Core 5/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>74990000</v>
+        <v>26990000</v>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr"/>
@@ -593,35 +593,31 @@
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr115w-ultra-7-255h-rtx-5070-16gb-512gb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb219w-core-5-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:46:00.864+07:00</t>
+          <t>2026-08-28T13:46:08.34+07:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:38</t>
+          <t>2026-09-26 11:57:50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR141W (Ultra 7-255H/ RTX 5070/ 32GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB220W (Core 7/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>83990000</v>
+        <v>30490000</v>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr"/>
@@ -633,36 +629,42 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr141w-ultra-7-255h-rtx-5070-32gb-512gb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb220w-core-7-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:46:21.05+07:00</t>
+          <t>2026-08-20T11:43:31.989+07:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:43</t>
+          <t>2026-09-26 11:57:55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AR-TB027W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop Asus Vivobook 14 X1404V (Core 5-120U/ 8GB/ 256GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>99990000</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
+        <v>16590000</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>18990000</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -671,33 +673,33 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ar-tb027w-ultra-9-rtx-5070-ti-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404v-core-5-120u-8gb-256gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:10.531+07:00</t>
+          <t>2026-08-07T13:41:37.603+07:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:48</t>
+          <t>2026-09-26 11:58:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB052WS (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VA-EB355W (Core 7-150U/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>139990000</v>
+        <v>25990000</v>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr"/>
@@ -709,33 +711,33 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb052ws-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb355w-core-7-150u-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:28.879+07:00</t>
+          <t>2026-08-20T11:17:32.016+07:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:53</t>
+          <t>2026-09-26 11:58:05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB121W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VA-EB609W (Core 3-100U/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>124990000</v>
+        <v>21990000</v>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
@@ -747,36 +749,42 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb121w-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb609w-core-3-100u-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:44.227+07:00</t>
+          <t>2026-08-18T16:33:25.424+07:00</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:58</t>
+          <t>2026-09-26 11:58:10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AX-TB042WS (Ultra 9/ RTX 5090/ 64GB/ 2TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VAP-V14.C58256 (Core 5-120U/ 16GB/ 256GB/ 14" FHD IPS/ Win 11/ Quiet Blue)</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>169990000</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
+        <v>17890000</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>18990000</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -785,40 +793,40 @@
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ax-tb042ws-ultra-9-rtx-5090-64gb-2tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404vap-v14-c58256-core-5-120u-8gb-256gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:44:50.259+07:00</t>
+          <t>2026-09-14T17:42:34.369+07:00</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:03</t>
+          <t>2026-09-26 11:58:15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA 165Hz/ Win 11)</t>
+          <t>Laptop Asus VivoBook 14 X1407AA-LY360W (Ultra 5-325/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>57390000</v>
+        <v>26490000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>58990000</v>
+        <v>26990000</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -829,42 +837,36 @@
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407aa-ly360w-ultra-5-325-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:35:45.75+07:00</t>
+          <t>2026-08-07T15:46:33.275+07:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:08</t>
+          <t>2026-09-26 11:58:20</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN329W (Ryzen 7-8845HS/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1407CA-LY203W (Ultra 5-225H/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>27690000</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>37490000</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-26%</t>
-        </is>
-      </c>
+        <v>33490000</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -873,42 +875,36 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn329w-ryzen-7-8845hs-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407ca-ly203w-ultra-5-225h-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:04:13.749+07:00</t>
+          <t>2026-08-20T10:22:08.041+07:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:13</t>
+          <t>2026-09-26 11:58:25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN390W (Ryzen 7-155/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 15 X1504MA-BQ632W (Core 5-320/ 8GB/ 512GB/ 15" FHD IPS)</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>28990000</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>26990000</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -917,82 +913,74 @@
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn390w-ryzen-7-155-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq632w-core-5-320-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:05:26.118+07:00</t>
+          <t>2026-08-18T15:43:54.381+07:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:18</t>
+          <t>2026-09-26 11:58:30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUG-RL129W (Ryzen 7-7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 15 X1504MA-BQ633W (Core 7-350/ 8GB/ 512GB/ 15" FHD IPS)</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+        <v>30490000</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nug-rl129w-ryzen-7-7445hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq633w-core-7-350-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:41:09.162+07:00</t>
+          <t>2026-09-24T15:33:03.428+07:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:23</t>
+          <t>2026-09-26 11:58:34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUQ-RL007W (Ryzen 7-170/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 15 X1504VA-BQ165W (Core 5-120U/ 8GB/ 512GB/ 15" FHD IPS)</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>36290000</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
+        <v>20990000</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -1001,77 +989,73 @@
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nuq-rl007w-ryzen-7-170-rtx-4050-6gb-16gb-512gb-16-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504va-bq165w-core-5-120u-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:10:34.588+07:00</t>
+          <t>2026-08-18T16:12:00.028+07:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:28</t>
+          <t>2026-09-26 11:58:39</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop Asus Vivobook 16 X1605VA-MB1826W (I3-1315U/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>41260000</v>
+        <v>15390000</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>45390000</v>
+        <v>15990000</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 16 inch | Dòng CPU: i3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1605va-mb1826w-i3-1315u-8gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T14:06:48.719+07:00</t>
+          <t>2026-09-09T10:45:38.083+07:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:33</t>
+          <t>2026-09-26 11:58:44</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA401EA-RG041W (Ryzen AI Max+ 392/ 32GB/ 512GB/ 14" 2.5K/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 16 X1607CA-MB387W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD IPS)</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>59990000</v>
+        <v>33490000</v>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
@@ -1083,33 +1067,33 @@
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI MAX+ | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon 8060S | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401ea-rg041w-ryzen-ai-max-392-32gb-512gb-14-2-5k-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb387w-ultra-5-225h-16gb-512gb-16-fhd-ips</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T09:33:26.048+07:00</t>
+          <t>2026-08-20T16:08:06.906+07:00</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:38</t>
+          <t>2026-09-26 11:58:50</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA401UH-RG001W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 14" QHD/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 16 X1607CA-MB399W (Ultra 7-255H/ 16GB/ 512GB/ 16" FHD IPS)</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>49990000</v>
+        <v>36490000</v>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr"/>
@@ -1119,35 +1103,31 @@
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
-        </is>
-      </c>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401uh-rg001w-ryzen-7-260-rtx-5050-16gb-512gb-14-qhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb399w-ultra-7-255h-16gb-512gb-16-fhd-ips</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T10:36:20.499+07:00</t>
+          <t>2026-08-20T15:36:19.591+07:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:43</t>
+          <t>2026-09-26 11:58:55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA401UM-RG049W (Ryzen 7 260/ RTX 5060/ 32GB/ 512GB/ 14" QHD/ Win 11)</t>
+          <t>Laptop ASUS Vivobook Flip TP3407AA-SG029W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>64990000</v>
+        <v>41990000</v>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
@@ -1159,71 +1139,73 @@
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401um-rg049w-ryzen-7-260-rtx-5060-32gb-512gb-14-qhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-flip-tp3407aa-sg029w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T10:05:55.516+07:00</t>
+          <t>2026-08-18T14:55:40.249+07:00</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:48</t>
+          <t>2026-09-26 11:58:59</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA608UHI-TU121W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop Asus Vivobook Go 14 E1404FA-EB935W (Ryzen 5-7430U/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>48990000</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr"/>
+        <v>20490000</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>28490000</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>-28%</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608uhi-tu121w-ryzen-7-260-rtx-5050-16gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1404fa-eb935w-ryzen-5-7430u-16gb-512gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T11:22:30.725+07:00</t>
+          <t>2026-08-13T09:46:28.801+07:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:53</t>
+          <t>2026-09-26 11:59:04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA608UMI-TU162W (Ryzen 7 260/ RTX 5060/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ4821W (Ryzen 5/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>51990000</v>
+        <v>22990000</v>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1235,374 +1217,340 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608umi-tu162w-ryzen-7-260-rtx-5060-16gb-512gb-16-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1504fa-bq4821w-ryzen-5-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T11:01:50.971+07:00</t>
+          <t>2026-09-24T15:55:57.447+07:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:58</t>
+          <t>2026-09-26 11:59:09</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS V16 V3607VJ-TK189W (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 16" WUXGA 144Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ340W (Ryzen 5/ 16GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>26490000</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>28490000</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
-        </is>
-      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-v16-v3607vj-tk189w-core-5-210h-rtx-3050-6gb-16gb-512gb-16-wuxga-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-go-15-e1504fa-bq340w-ryzen-5-16gb-512gb-156-fhd-ips</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T16:26:14.526+07:00</t>
+          <t>2026-09-24T15:55:13.502+07:00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:03</t>
+          <t>2026-09-26 11:59:14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 M3407KA-SF034W (Ryzen AI 5-330/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>28790000</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>30790000</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>33990000</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-m3407ka-sf034w-ryzen-ai-5-330-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T11:00:26.909+07:00</t>
+          <t>2026-08-18T12:02:07.653+07:00</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:08</t>
+          <t>2026-09-26 11:59:19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming GIGABYTE A16 CVHI3MY893SH (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407AA-SF032W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>36990000</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
+        <v>40490000</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3my893sh</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf032w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T14:40:23.197+07:00</t>
+          <t>2026-08-18T10:00:42.045+07:00</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:13</t>
+          <t>2026-09-26 11:59:24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Laptop GIGABYTE Gaming A16 CVHI3VN893SH (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407AA-SF945W (Ultra 5-325/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+        <v>37490000</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 3 | Dung lượng RAM: 8 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon RX 6500M | Kích thước màn hình: 16 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf945w-ultra-5-325-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:10:12.472+07:00</t>
+          <t>2026-08-18T11:09:17.449+07:00</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:18</t>
+          <t>2026-09-26 11:59:29</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 A16-3THK3VN893SH (Ryzen 7 260/ RTX 5050 8GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407QA-SF043W (QC X126100/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>25990000</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-ga63h-3thk3vn893sh</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407qa-sf043w-qc-x126100-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30T09:54:12.234+07:00</t>
+          <t>2026-08-18T09:15:59.141+07:00</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:23</t>
+          <t>2026-09-26 11:59:34</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9LJR2VNF93SH (Ryzen 5 7533HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407VA-LY147W (Core 5-210H/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>34990000</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9ljr2vnf93sh-ryzen-5-7533hs-rtx-3050-6gb-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407va-ly147w-core-5-210h-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T15:10:54.55+07:00</t>
+          <t>2026-08-18T11:42:14.925+07:00</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:28</t>
+          <t>2026-09-26 11:59:39</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9MJR2VNF93SH (Ryzen 5 7533HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 16 S3607AA-SH042W (Ultra 5-325/ 16GB/ 512GB/ 16" FHD OLED)</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>34990000</v>
+        <v>37490000</v>
       </c>
       <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9mjr2vnf93sh-ryzen-5-7533hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-16-s3607aa-sh042w-ultra-5-325-16gb-512gb-16-fhd-oled</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:50:39.975+07:00</t>
+          <t>2026-08-18T10:44:16.77+07:00</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:33</t>
+          <t>2026-09-26 11:59:44</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CTHH3VN893SH (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 16 S3607CA-SH080W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD OLED)</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>33990000</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>36990000</v>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>-8%</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
+        <v>35990000</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-gaming-a16-cthh3vn893sh</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-16-s3607ca-sh080w-ultra-5-225h-16gb-512gb-16-fhd-oled</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:59.097+07:00</t>
+          <t>2026-08-18T10:21:29.428+07:00</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:38</t>
+          <t>2026-09-26 11:59:49</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS VivoBook S14 S3407CA-SF913W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>115990000</v>
+        <v>27890000</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>117990000</v>
+        <v>29990000</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1613,33 +1561,33 @@
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s14-s3407ca-sf913w-ultra-5-225h-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05T14:44:14.658+07:00</t>
+          <t>2026-09-08T17:02:01.429+07:00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:43</t>
+          <t>2026-09-26 11:59:54</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15AHP11 83TN0040VN (Ryzen 7-250/ RTX 5050 8GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UM3406GA-QD075W (Ryzen 7/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>43990000</v>
+        <v>39990000</v>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr"/>
@@ -1651,42 +1599,36 @@
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15ahp11-83tn0040vn-ryzen-7-250-rtx-5050-8gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ga-qd075w-ryzen-7-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T09:36:14.406+07:00</t>
+          <t>2026-08-17T16:03:07.024+07:00</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:48</t>
+          <t>2026-09-26 11:59:59</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1531W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED)</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>41990000</v>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>42990000</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -1695,40 +1637,40 @@
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1531w-ultra-9-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:38.199+07:00</t>
+          <t>2026-08-18T08:45:55.514+07:00</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:53</t>
+          <t>2026-09-26 12:00:04</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S0006RVN (Ryzen 7-7735HS/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1713W (Ultra 5-225H/ 16GB/ 512GB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
         <v>30990000</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>32990000</v>
+        <v>38990000</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1739,33 +1681,33 @@
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0006rvn-ryzen-7-7735hs-rtx-3050-6gb-16gb-1tb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1713w-ultra-5-225h-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T11:31:57.635+07:00</t>
+          <t>2026-09-25T10:16:16.703+07:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:58</t>
+          <t>2026-09-26 12:00:09</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S000DCVN (Ryzen 7-170/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST630W (Ultra 7-255H/ 16GB/ 512GB/ 14" 3K OLED)</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>32990000</v>
+        <v>40990000</v>
       </c>
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr"/>
@@ -1777,33 +1719,33 @@
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s000dcvn-ryzen-7-170-rtx-3050-6gb-16gb-1tb-15-6-fhd-ips-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st630w-ultra-7-255h-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T10:03:17.431+07:00</t>
+          <t>2026-08-17T15:05:39.807+07:00</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:03</t>
+          <t>2026-09-26 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003VVN (Core 5-205H/ RTX 3050 6GB/ 8GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3407NA-QD132WS (Snapdragon X2 Elite X2E-88-100/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>36990000</v>
+        <v>48990000</v>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr"/>
@@ -1815,33 +1757,33 @@
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 8 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003vvn-core-5-205h-rtx-3050-6gb-8gb-512gb-15-3-wuxga-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd132ws-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T19:41:42.305+07:00</t>
+          <t>2026-08-24T11:47:13.916+07:00</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:08</t>
+          <t>2026-09-26 12:00:19</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003WVN (Core 5-205H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
+          <t>Laptop ASUS Zenbook A14 UX3407NA-QD254W (Snapdragon X2 Elite X2E-88-100/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>41990000</v>
+        <v>63990000</v>
       </c>
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr"/>
@@ -1853,42 +1795,36 @@
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200)</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003wvn-core-5-205h-rtx-3050-6gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd254w-32gb-1tb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T16:50:55.152+07:00</t>
+          <t>2026-08-24T11:46:55.101+07:00</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:13</t>
+          <t>2026-09-26 12:00:24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRX10 83JE01AGVN (I7-13645HX/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook A16 UX3607OA-SQ137WS (Snapdragon X2 Elite Extreme X2E94100/ 24GB/ 512GB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>39490000</v>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>58990000</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -1897,42 +1833,36 @@
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 16 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 24 GB</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx10-83je01agvn</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-16-ux3607oa-sq137ws-24gb-512gb-16-3k-oled</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T16:43:38.321+07:00</t>
+          <t>2026-08-24T11:43:18.337+07:00</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:18</t>
+          <t>2026-09-26 12:00:29</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN138WS (Ultra X9/ 32GB/ 1TB/ 14" 3K OLED Touch 144Hz)</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>43990000</v>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>45990000</v>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>89990000</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -1941,42 +1871,36 @@
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn138ws-ultra-x9-32gb-1tb-14-3k-oled-touch-144hz</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T16:32:05.969+07:00</t>
+          <t>2026-08-17T12:04:03.945+07:00</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:23</t>
+          <t>2026-09-26 12:00:34</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0000DVN (Ryzen 5 7535HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN439WS (Ultra X7/ 32GB/ 512GB/ 14" 3K OLED Touch 144Hz)</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>26990000</v>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>82990000</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -1985,33 +1909,33 @@
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-essential-15arp10e-83s0000dvn</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn439ws-ultra-x7-32gb-512gb-14-3k-oled-touch-144hz</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T16:40:42.967+07:00</t>
+          <t>2026-08-17T11:44:06.982+07:00</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:28</t>
+          <t>2026-09-26 12:00:39</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS ProArt PX13 HN7306EA-LX050W (Ryzen AI Max+ 395/ 32GB/ 1TB/ 13.3" 3K OLED Touch)</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>33990000</v>
+        <v>76990000</v>
       </c>
       <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="inlineStr"/>
@@ -2023,33 +1947,33 @@
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 13.3 inch | Dòng CPU: Ryzen AI MAX+ | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-pro-art-hn7306ea-lx050w-ryzen-ai-max-395-32gb-1tb-13-3-3k-oled-touch</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:23:00.628+07:00</t>
+          <t>2026-09-24T15:58:08.111+07:00</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:33</t>
+          <t>2026-09-26 12:00:44</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook S 14 UX5406AA-SU348W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED Touch)</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>31990000</v>
+        <v>50990000</v>
       </c>
       <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr"/>
@@ -2061,42 +1985,36 @@
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-s-14-ux5406aa-su348w-ultra-9-16gb-512gb-14-3k-oled-touch</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:25:26.316+07:00</t>
+          <t>2026-08-17T10:26:19.879+07:00</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:38</t>
+          <t>2026-09-26 12:00:49</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook S 16 UM5606GA-SS441W (Ryzen AI 9 465/ 16GB/ 512GB/ 16" 3K OLED)</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>49490000</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2105,36 +2023,42 @@
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ryzen AI 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-s-15-um5606ga-ss441w-ryzen-ai-9-465-16gb-512gb-15-3k-oled</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:28:01.415+07:00</t>
+          <t>2026-09-24T16:22:14.948+07:00</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:43</t>
+          <t>2026-09-26 12:00:54</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Max C13WF-421VN (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop Dell 15 DC15250 - 71092480 (I7-1355U/ 16GB/ 512GB/ Win 11/ Office/ Microsoft 365)</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>44990000</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
+        <v>25390000</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>25990000</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2143,36 +2067,42 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13vf-421vn-i7-13620h-rtx-5060-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-dell-15-dc15250-71092480-i7-1355u-16gb-512gb-win-11-office-microsoft-365</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T16:26:05.15+07:00</t>
+          <t>2026-09-17T10:56:32.257+07:00</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:48</t>
+          <t>2026-09-26 12:00:58</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Max C13WE-422VN (I7-13620H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I3-100U/ 8GB/ 512GB/ 15.6" FHD 120Hz/DOS) - Nhập Khẩu Chính Hãng</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>42990000</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr"/>
+        <v>14390000</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>14990000</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2181,130 +2111,112 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn-i7-13620h-rtx-5050-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i3-100u-8gb-512gb-15-6-fhd-120hz</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:38:57.001+07:00</t>
+          <t>2026-08-21T10:44:17.994+07:00</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:53</t>
+          <t>2026-09-26 12:01:03</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU405AR-SY016W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>22990000</v>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>23990000</v>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>96990000</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Card đồ họa tích hợp - Qualcomm® Adreno™ | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405ar-sy016w-ultra-9-rtx-5070-ti-32gb-1tb-14-3k-oled-120hz-win-11</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T09:43:41.692+07:00</t>
+          <t>2026-09-06T15:47:29.287+07:00</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:34</t>
+          <t>2026-09-26 11:57:43</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU405AW-SY029W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>23990000</v>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>-8%</t>
-        </is>
-      </c>
+        <v>119990000</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® ARC™ Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405aw-sy029w-ultra-9-rtx-5080-32gb-1tb-14-3k-oled-120hz-win-11</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T15:00:45.83+07:00</t>
+          <t>2026-09-06T15:47:45.327+07:00</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:40</t>
+          <t>2026-09-26 11:57:48</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M (Ultra 9-185H/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR115W (Ultra 7-255H/ RTX 5070/ 16GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>29890000</v>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>-0%</t>
-        </is>
-      </c>
+        <v>74990000</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2313,645 +2225,597 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-16gb-512gb-14-fhd-ips-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr115w-ultra-7-255h-rtx-5070-16gb-512gb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:22:17.071+07:00</t>
+          <t>2026-09-06T15:46:00.864+07:00</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:45</t>
+          <t>2026-09-26 11:57:53</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR141W (Ultra 7-255H/ RTX 5070/ 32GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>22990000</v>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>83990000</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
+      <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr141w-ultra-7-255h-rtx-5070-32gb-512gb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T21:08:15.03+07:00</t>
+          <t>2026-09-06T15:46:21.05+07:00</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:50</t>
+          <t>2026-09-26 11:57:58</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AR-TB027W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>20990000</v>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>21990000</v>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
+        <v>99990000</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 680M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ar-tb027w-ultra-9-rtx-5070-ti-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17T09:17:18.78+07:00</t>
+          <t>2026-09-06T15:45:10.531+07:00</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:55</t>
+          <t>2026-09-26 11:58:03</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR (Ryzen 5-3500U/ 8GB/ 512GB/ 14" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB052WS (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>17990000</v>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>19990000</v>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
+        <v>139990000</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb052ws-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T20:43:49.815+07:00</t>
+          <t>2026-09-06T15:45:28.879+07:00</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:00</t>
+          <t>2026-09-26 11:58:08</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB121W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>22890000</v>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>23990000</v>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
+        <v>124990000</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb121w-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:44:03.513+07:00</t>
+          <t>2026-09-06T15:45:44.227+07:00</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:05</t>
+          <t>2026-09-26 11:58:14</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AX-TB042WS (Ultra 9/ RTX 5090/ 64GB/ 2TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>169990000</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ax-tb042ws-ultra-9-rtx-5090-64gb-2tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:20:56.552+07:00</t>
+          <t>2026-09-06T15:44:50.259+07:00</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:10</t>
+          <t>2026-09-26 11:58:19</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-76KR (Core 7-350/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>25990000</v>
+        <v>57390000</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>26990000</v>
+        <v>58990000</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen AI 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-76kr-core-7-350-8gb-512gb</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:44:29.405+07:00</t>
+          <t>2026-09-14T17:35:45.75+07:00</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:15</t>
+          <t>2026-09-26 11:58:24</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN329W (Ryzen 7-8845HS/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>17990000</v>
+        <v>27690000</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>19790000</v>
+        <v>37490000</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-26%</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn329w-ryzen-7-8845hs-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T09:51:43.721+07:00</t>
+          <t>2026-09-17T11:04:13.749+07:00</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:20</t>
+          <t>2026-09-26 11:58:29</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN390W (Ryzen 7-155/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>19590000</v>
+        <v>28990000</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>21990000</v>
+        <v>30990000</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn390w-ryzen-7-155-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T09:03:23.812+07:00</t>
+          <t>2026-09-17T11:05:26.118+07:00</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:25</t>
+          <t>2026-09-26 11:58:34</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5-3500U/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUG-RL129W (Ryzen 7-7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>17990000</v>
+        <v>29990000</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>19990000</v>
+        <v>30990000</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
-        </is>
-      </c>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nug-rl129w-ryzen-7-7445hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T08:51:32.5+07:00</t>
+          <t>2026-09-14T17:41:09.162+07:00</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:30</t>
+          <t>2026-09-26 11:58:39</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-411P-R1CM (Ryzen 5 3500U/ 8GB/ 256GB)</t>
+          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUQ-RL007W (Ryzen 7-170/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>17990000</v>
+        <v>36290000</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>18990000</v>
+        <v>39990000</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r1cm-ryzen-5-3500u-8gb-256gb</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nuq-rl007w-ryzen-7-170-rtx-4050-6gb-16gb-512gb-16-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T14:26:56.746+07:00</t>
+          <t>2026-09-25T10:10:34.588+07:00</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:35</t>
+          <t>2026-09-26 11:58:44</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-411P-R7YP (Ryzen 3 3200U/ 8GB/ 256GB)</t>
+          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>15990000</v>
+        <v>41260000</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>16990000</v>
+        <v>45390000</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r7yp-ryzen-3-3200u-8gb-256gb</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T14:48:50.246+07:00</t>
+          <t>2026-06-30T14:06:48.719+07:00</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:40</t>
+          <t>2026-09-26 11:58:49</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-49P-R6XX (Ryzen 5 7430U/ 8GB/ 512GB/15.6"/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA401EA-RG041W (Ryzen AI Max+ 392/ 32GB/ 512GB/ 14" 2.5K/ Win 11)</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>18590000</v>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>20990000</v>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
-      </c>
+        <v>59990000</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen AI MAX+ | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon 8060S | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-49p-r6xx-ryzen-5-7430u-8gb-512gb-15-6-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401ea-rg041w-ryzen-ai-max-392-32gb-512gb-14-2-5k-win-11</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T13:56:25.879+07:00</t>
+          <t>2026-08-14T09:33:26.048+07:00</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:45</t>
+          <t>2026-09-26 11:58:54</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA401UH-RG001W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 14" QHD/ Win 11)</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>18890000</v>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>-24%</t>
-        </is>
-      </c>
+        <v>49990000</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401uh-rg001w-ryzen-7-260-rtx-5050-16gb-512gb-14-qhd-win-11</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T10:45:08.009+07:00</t>
+          <t>2026-08-14T10:36:20.499+07:00</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:50</t>
+          <t>2026-09-26 11:58:59</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA401UM-RG049W (Ryzen 7 260/ RTX 5060/ 32GB/ 512GB/ 14" QHD/ Win 11)</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
-      </c>
+        <v>64990000</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401um-rg049w-ryzen-7-260-rtx-5060-32gb-512gb-14-qhd-win-11</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T15:19:10.843+07:00</t>
+          <t>2026-08-14T10:05:55.516+07:00</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:55</t>
+          <t>2026-09-26 11:59:04</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF (Core 3-304/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA608UHI-TU121W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>21990000</v>
+        <v>48990000</v>
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2963,33 +2827,33 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-34nf-core-3-304-12gb-512gb-14-fhd-ips-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608uhi-tu121w-ryzen-7-260-rtx-5050-16gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T13:32:07.536+07:00</t>
+          <t>2026-08-14T11:22:30.725+07:00</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:00</t>
+          <t>2026-09-26 11:59:09</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV (Core 5-320/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA608UMI-TU162W (Ryzen 7 260/ RTX 5060/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>24990000</v>
+        <v>51990000</v>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
@@ -3001,386 +2865,374 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-52bv-core-5-320-12gb-512gb-14-wuxga-ips-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608umi-tu162w-ryzen-7-260-rtx-5060-16gb-512gb-16-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T11:05:38.798+07:00</t>
+          <t>2026-08-14T11:01:50.971+07:00</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:05</t>
+          <t>2026-09-26 11:59:14</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming ASUS V16 V3607VJ-TK189W (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 16" WUXGA 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>29890000</v>
+        <v>26490000</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>30990000</v>
+        <v>29990000</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-v16-v3607vj-tk189w-core-5-210h-rtx-3050-6gb-16gb-512gb-16-wuxga-144hz-win-11</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:21:51.755+07:00</t>
+          <t>2026-09-15T16:26:14.526+07:00</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:10</t>
+          <t>2026-09-26 11:59:19</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>49990000</v>
+        <v>28790000</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>54990000</v>
+        <v>30790000</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ B390 GPU (đồ họa tích hợp) | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T15:51:47.551+07:00</t>
+          <t>2026-07-01T11:00:26.909+07:00</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:15</t>
+          <t>2026-09-26 11:59:23</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI OLED SFG14-75-765M (Ultra 7-258V/ 32GB/ 512GB/ 14" FHD+ OLED/ Win11)</t>
+          <t>Laptop gaming GIGABYTE A16 CVHI3MY893SH (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>39990000</v>
+        <v>36990000</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>40990000</v>
+        <v>38990000</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ Graphics 140V | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-ai-oled-sfg14-75-765m-14-fhd-oled-u7-258v-32lp-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3my893sh</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T10:47:31.44+07:00</t>
+          <t>2026-08-14T14:40:23.197+07:00</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:20</t>
+          <t>2026-09-26 11:59:29</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop GIGABYTE Gaming A16 CVHI3VN893SH (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>32999000</v>
-      </c>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>38990000</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 3 | Dung lượng RAM: 8 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon RX 6500M | Kích thước màn hình: 16 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T14:38:31.288+07:00</t>
+          <t>2026-09-17T11:10:12.472+07:00</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:25</t>
+          <t>2026-09-26 11:59:34</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 A16-3THK3VN893SH (Ryzen 7 260/ RTX 5050 8GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>31490000</v>
+        <v>35990000</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>32490000</v>
+        <v>40990000</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ 130T Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-ga63h-3thk3vn893sh</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T14:08:34.772+07:00</t>
+          <t>2026-07-30T09:54:12.234+07:00</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:30</t>
+          <t>2026-09-26 11:59:38</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" 2.8K OLED/ Win 11/ Office)</t>
+          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9LJR2VNF93SH (Ryzen 5 7533HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>35990000</v>
+        <v>29990000</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>45990000</v>
+        <v>30990000</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6 | Kích thước màn hình: 14.5 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9ljr2vnf93sh-ryzen-5-7533hs-rtx-3050-6gb-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:56:38.644+07:00</t>
+          <t>2026-07-31T15:10:54.55+07:00</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:35</t>
+          <t>2026-09-26 11:59:43</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
+          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9MJR2VNF93SH (Ryzen 5 7533HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>43990000</v>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>49490000</v>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>34990000</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: RTX 4060 | Kích thước màn hình: 14.5 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9mjr2vnf93sh-ryzen-5-7533hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T15:10:56.836+07:00</t>
+          <t>2026-09-18T13:50:39.975+07:00</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:40</t>
+          <t>2026-09-26 11:59:48</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H08-50W (Core 5-210H/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CTHH3VN893SH (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>19490000</v>
+        <v>33990000</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>21990000</v>
+        <v>36990000</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h08-50w</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-gaming-a16-cthh3vn893sh</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T11:09:14.14+07:00</t>
+          <t>2026-09-18T13:35:59.097+07:00</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:45</t>
+          <t>2026-09-26 11:59:53</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1403CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>24290000</v>
+        <v>115990000</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>26990000</v>
+        <v>117990000</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3391,80 +3243,78 @@
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h16-63ws-core-5-210h-16gb-512gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T15:06:02.246+07:00</t>
+          <t>2026-07-05T14:44:14.658+07:00</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:50</t>
+          <t>2026-09-26 11:59:58</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1403CVA-C7H16-50W (Core 7-240H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15AHP11 83TN0040VN (Ryzen 7-250/ RTX 5050 8GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>28990000</v>
-      </c>
-      <c r="C72" s="2" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>43990000</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c7h16-50w-core-7-240h-16gb-512gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15ahp11-83tn0040vn-ryzen-7-250-rtx-5050-8gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T14:43:57.168+07:00</t>
+          <t>2026-09-21T09:36:14.406+07:00</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:55</t>
+          <t>2026-09-26 12:00:03</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1503CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>24290000</v>
+        <v>38990000</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>26990000</v>
+        <v>41990000</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3475,40 +3325,40 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1503cva-c5h16-63ws-core-5-210h-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T14:03:33.213+07:00</t>
+          <t>2026-07-15T09:36:38.199+07:00</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:01</t>
+          <t>2026-09-26 12:00:08</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1403CVA-C3U08-50W (Core 3-100U/ 8GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S0006RVN (Ryzen 7-7735HS/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>15490000</v>
+        <v>30990000</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>17990000</v>
+        <v>32990000</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3519,42 +3369,36 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c3u08-50w</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0006rvn-ryzen-7-7735hs-rtx-3050-6gb-16gb-1tb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T13:53:40.042+07:00</t>
+          <t>2026-09-22T11:31:57.635+07:00</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:06</t>
+          <t>2026-09-26 12:00:13</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S000DCVN (Ryzen 7-170/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>23390000</v>
-      </c>
-      <c r="C75" s="2" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>-16%</t>
-        </is>
-      </c>
+        <v>32990000</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3563,42 +3407,36 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s000dcvn-ryzen-7-170-rtx-3050-6gb-16gb-1tb-15-6-fhd-ips-win-11</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T10:19:47.487+07:00</t>
+          <t>2026-09-21T10:03:17.431+07:00</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:11</t>
+          <t>2026-09-26 12:00:18</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U516S8W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003VVN (Core 5-205H/ RTX 3050 6GB/ 8GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>26390000</v>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>36990000</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3607,80 +3445,78 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 8 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u516s8w-ultra-5-225h-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003vvn-core-5-205h-rtx-3050-6gb-8gb-512gb-15-3-wuxga-165hz-win-11</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T11:57:56.626+07:00</t>
+          <t>2026-08-12T19:41:42.305+07:00</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:16</t>
+          <t>2026-09-26 12:00:23</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U716S8W (Ultra 7-255H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003WVN (Core 5-205H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>32990000</v>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>41990000</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr"/>
+      <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200)</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u716s8w-ultra-7-255h-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003wvn-core-5-205h-rtx-3050-6gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T13:46:08.673+07:00</t>
+          <t>2026-08-12T16:50:55.152+07:00</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:21</t>
+          <t>2026-09-26 12:00:28</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA / Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX10 83JE01AGVN (I7-13645HX/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>26390000</v>
+        <v>39490000</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>30490000</v>
+        <v>40990000</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3691,40 +3527,40 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx10-83je01agvn</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03T11:54:54.747+07:00</t>
+          <t>2026-09-19T16:43:38.321+07:00</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:26</t>
+          <t>2026-09-26 12:00:32</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>32990000</v>
+        <v>43990000</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>35990000</v>
+        <v>45990000</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3733,118 +3569,118 @@
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T08:56:23.461+07:00</t>
+          <t>2026-09-18T16:32:05.969+07:00</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:31</t>
+          <t>2026-09-26 12:00:37</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 G2 P5405CAA-NZ0223W (Ultra 7-356H/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>39190000</v>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>41990000</v>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>33990000</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-g2-p5405caa-nz0223w-ultra-7-356h-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T11:12:45.933+07:00</t>
+          <t>2026-06-30T15:23:00.628+07:00</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:36</t>
+          <t>2026-09-26 12:00:42</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0016W (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>28790000</v>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>31990000</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr"/>
+      <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0016w-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T10:54:41.9+07:00</t>
+          <t>2026-06-30T15:25:26.316+07:00</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:41</t>
+          <t>2026-09-26 12:00:47</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0017W (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>36290000</v>
+        <v>34990000</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>38990000</v>
+        <v>35990000</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3855,42 +3691,36 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: Arc | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0017w-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:51:05.888+07:00</t>
+          <t>2026-06-30T15:28:01.415+07:00</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:46</t>
+          <t>2026-09-26 12:00:52</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0442WS (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Max C13WF-421VN (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>37190000</v>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>44990000</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr"/>
+      <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3899,42 +3729,36 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc 140V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0442ws-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13vf-421vn-i7-13620h-rtx-5060-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T09:55:42.594+07:00</t>
+          <t>2026-09-23T16:26:05.15+07:00</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:51</t>
+          <t>2026-09-26 12:00:57</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0450WS (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Max C13WE-422VN (I7-13620H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>29790000</v>
-      </c>
-      <c r="C84" s="2" t="n">
-        <v>31990000</v>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>42990000</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr"/>
+      <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3943,36 +3767,42 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc 130V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0450ws-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn-i7-13620h-rtx-5050-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T09:56:18.911+07:00</t>
+          <t>2026-07-27T10:38:57.001+07:00</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:56</t>
+          <t>2026-09-26 12:01:02</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
+          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>199990000</v>
-      </c>
-      <c r="C85" s="2" t="inlineStr"/>
-      <c r="D85" s="2" t="inlineStr"/>
+        <v>34890000</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>35990000</v>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3981,124 +3811,128 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T11:12:30.954+07:00</t>
+          <t>2026-06-30T14:54:13.66+07:00</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:01:01</t>
+          <t>2026-09-26 12:01:07</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>34890000</v>
+        <v>22990000</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>35990000</v>
+        <v>23990000</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Card đồ họa tích hợp - Qualcomm® Adreno™ | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T14:54:13.66+07:00</t>
+          <t>2026-07-16T09:43:41.692+07:00</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:32</t>
+          <t>2026-09-26 11:57:40</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>48490000</v>
+        <v>23990000</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>52990000</v>
+        <v>25990000</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
           <t>-8%</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+        </is>
+      </c>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: QHD (2560x1440) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel® ARC™ Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T14:49:48.046+07:00</t>
+          <t>2026-07-16T15:00:45.83+07:00</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:37</t>
+          <t>2026-09-26 11:57:45</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M (Ultra 9-185H/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>79990000</v>
+        <v>29890000</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>80990000</v>
+        <v>29990000</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4109,334 +3943,394 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-16gb-512gb-14-fhd-ips-win-11</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:43:38.331+07:00</t>
+          <t>2026-09-25T10:22:17.071+07:00</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:43</t>
+          <t>2026-09-26 11:57:50</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>85990000</v>
-      </c>
-      <c r="C89" s="2" t="inlineStr"/>
-      <c r="D89" s="2" t="inlineStr"/>
+        <v>22990000</v>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>25990000</v>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T17:51:09.908+07:00</t>
+          <t>2026-09-11T21:08:15.03+07:00</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:48</t>
+          <t>2026-09-26 11:57:55</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>67690000</v>
+        <v>20990000</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>73990000</v>
+        <v>21990000</v>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
+          <t>-5%</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+        </is>
+      </c>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4060 | Kích thước màn hình: 16 inch</t>
+          <t>Card đồ họa: AMD Radeon 680M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27T14:36:44.954+07:00</t>
+          <t>2026-07-17T09:17:18.78+07:00</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:53</t>
+          <t>2026-09-26 11:58:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Laptop GIGABYTE AERO X16 4WHN3VNC93AH (Ryzen AI 9 465/ RTX 5070 8GB/ 16GB/ 512GB/ 16" QHD+ 165Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR (Ryzen 5-3500U/ 8GB/ 512GB/ 14" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>54990000</v>
-      </c>
-      <c r="C91" s="2" t="inlineStr"/>
-      <c r="D91" s="2" t="inlineStr"/>
-      <c r="E91" s="2" t="inlineStr"/>
+        <v>17990000</v>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>19990000</v>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+        </is>
+      </c>
       <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aero-x16-4whn3vnc93ah-ryzen-ai-9-465-rtx-5070-8gb-16gb-512gb-16-qhd-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:49:41.514+07:00</t>
+          <t>2026-09-24T20:43:49.815+07:00</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:58</t>
+          <t>2026-09-26 11:58:05</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming GIGABYTE AORUS Master 16 6XJM4VNE64SH (Ryzen 9 9955HX3D/ RTX 5070 Ti 12GB/ 32GB/ 1TB/ 16" QHD+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>86990000</v>
-      </c>
-      <c r="C92" s="2" t="inlineStr"/>
-      <c r="D92" s="2" t="inlineStr"/>
+        <v>22890000</v>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aorus-master-16-6xjm4vne64sh-ryzen-9-9955hx3d-rtx-5070-ti-12gb-32gb-1tb-16-qhd-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T11:46:50.068+07:00</t>
+          <t>2026-09-24T15:44:03.513+07:00</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:03</t>
+          <t>2026-09-26 11:58:10</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Laptop GIGABYTE Gaming A16 EVHS3VN893SH (Ultra 9-185H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>39990000</v>
+        <v>24990000</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>40990000</v>
+        <v>25990000</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr"/>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+        </is>
+      </c>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-gaming-a16-evhs3vn893sh-ultra-9-185h-rtx-5060-8gb-16gb-512gb-16-fhd-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:36:39.051+07:00</t>
+          <t>2026-09-25T10:20:56.552+07:00</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:08</t>
+          <t>2026-09-26 11:58:15</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 15-fd1289TU C2CV8PA (Ultra 7-155H/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-76KR (Core 7-350/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>24990000</v>
+        <v>25990000</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>25990000</v>
+        <v>26990000</v>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
           <t>-4%</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+        </is>
+      </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-hp-15-fd1289tu-c2cv8pa-ultra-7-155h-16gb-512gb-15-6-fhd-ips-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-76kr-core-7-350-8gb-512gb</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:33:44.001+07:00</t>
+          <t>2026-09-24T15:44:29.405+07:00</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:13</t>
+          <t>2026-09-26 11:58:20</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP 250 G10 A06FDPT (I7-1355U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>23490000</v>
+        <v>17990000</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>25590000</v>
+        <v>19790000</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr"/>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+        </is>
+      </c>
       <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-hp-250-g10-a06fdpt-i7-1355u-8gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:31:30.682+07:00</t>
+          <t>2026-09-24T09:51:43.721+07:00</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:19</t>
+          <t>2026-09-26 11:58:25</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop HP ProBook 450 G10 B73TPAT (I5-1334U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>23990000</v>
+        <v>19590000</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>24990000</v>
+        <v>21990000</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr"/>
+          <t>-11%</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+        </is>
+      </c>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Iris Xe Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-hp-probook-450-g10-b73tpat-i5-1334u-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:31:53.385+07:00</t>
+          <t>2026-09-25T09:03:23.812+07:00</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:24</t>
+          <t>2026-09-26 11:58:30</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 83RQ00DBVN (Core 3-304/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5-3500U/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="C97" s="2" t="inlineStr"/>
-      <c r="D97" s="2" t="inlineStr"/>
+        <v>16790000</v>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>19990000</v>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>-16%</t>
+        </is>
+      </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4445,217 +4339,249 @@
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-14iwc11-83rq00dbvn-core-3-304-8gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:16:44.995+07:00</t>
+          <t>2026-09-25T16:09:40.061+07:00</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:29</t>
+          <t>2026-09-26 11:58:35</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB005YVN (Ryzen 5-125/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-411P-R1CM (Ryzen 5 3500U/ 8GB/ 256GB)</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="C98" s="2" t="inlineStr"/>
-      <c r="D98" s="2" t="inlineStr"/>
+        <v>17990000</v>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>18990000</v>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb005yvn-ryzen-5-125-8gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r1cm-ryzen-5-3500u-8gb-256gb</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T15:01:44.794+07:00</t>
+          <t>2026-07-06T14:26:56.746+07:00</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:34</t>
+          <t>2026-09-26 11:58:40</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB0060VN (Ryzen 7-155/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-411P-R7YP (Ryzen 3 3200U/ 8GB/ 256GB)</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="C99" s="2" t="inlineStr"/>
-      <c r="D99" s="2" t="inlineStr"/>
+        <v>15990000</v>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>16990000</v>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb0060vn-ryzen-7-155-8gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r7yp-ryzen-3-3200u-8gb-256gb</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T14:35:59.897+07:00</t>
+          <t>2026-07-06T14:48:50.246+07:00</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:39</t>
+          <t>2026-09-26 11:58:45</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 83S1003GVN</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-49P-R6XX (Ryzen 5 7430U/ 8GB/ 512GB/15.6"/ Win 11)</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>44540000</v>
+        <v>18590000</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>47990000</v>
+        <v>20990000</v>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
+          <t>-11%</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-83s1003gvn</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-49p-r6xx-ryzen-5-7430u-8gb-512gb-15-6-win-11</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T10:29:16.152+07:00</t>
+          <t>2026-08-21T13:56:25.879+07:00</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:44</t>
+          <t>2026-09-26 11:58:50</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 OLED 83S1006RVN (Ryzen AI 7-445/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>32990000</v>
-      </c>
-      <c r="C101" s="2" t="inlineStr"/>
-      <c r="D101" s="2" t="inlineStr"/>
+        <v>18890000</v>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>24990000</v>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>-24%</t>
+        </is>
+      </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-oled-83s1006rvn-ryzen-ai-7-445-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T11:54:44.05+07:00</t>
+          <t>2026-08-24T10:45:08.009+07:00</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:49</t>
+          <t>2026-09-26 11:58:55</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00ABVN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="C102" s="2" t="inlineStr"/>
-      <c r="D102" s="2" t="inlineStr"/>
+        <v>24990000</v>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>27990000</v>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® Arc™ Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00abvn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T14:05:59.687+07:00</t>
+          <t>2026-07-16T15:19:10.843+07:00</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:54</t>
+          <t>2026-09-26 11:59:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00F5VN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF (Core 3-304/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>34990000</v>
+        <v>21990000</v>
       </c>
       <c r="C103" s="2" t="inlineStr"/>
       <c r="D103" s="2" t="inlineStr"/>
@@ -4667,36 +4593,42 @@
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00f5vn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-34nf-core-3-304-12gb-512gb-14-fhd-ips-120hz-win-11</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:17:34.624+07:00</t>
+          <t>2026-09-23T13:32:07.536+07:00</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:59</t>
+          <t>2026-09-26 11:59:05</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002EVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV (Core 5-320/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>55990000</v>
-      </c>
-      <c r="C104" s="2" t="inlineStr"/>
-      <c r="D104" s="2" t="inlineStr"/>
+        <v>23490000</v>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>24990000</v>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4705,108 +4637,130 @@
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002evn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-52bv-core-5-320-12gb-512gb-14-wuxga-ips-120hz-win-11</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T10:21:35.763+07:00</t>
+          <t>2026-09-25T16:09:22.19+07:00</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:04</t>
+          <t>2026-09-26 11:59:10</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002FVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>55990000</v>
-      </c>
-      <c r="C105" s="2" t="inlineStr"/>
-      <c r="D105" s="2" t="inlineStr"/>
+        <v>28990000</v>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002fvn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T20:29:51.634+07:00</t>
+          <t>2026-09-25T16:07:37.902+07:00</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:09</t>
+          <t>2026-09-26 11:59:15</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0075VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>46990000</v>
-      </c>
-      <c r="C106" s="2" t="inlineStr"/>
-      <c r="D106" s="2" t="inlineStr"/>
+        <v>49990000</v>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>54990000</v>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel® Arc™ B390 GPU (đồ họa tích hợp) | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0075vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:19:34.771+07:00</t>
+          <t>2026-08-28T15:51:47.551+07:00</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:14</t>
+          <t>2026-09-26 11:59:20</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0076VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Go AI OLED SFG14-75-765M (Ultra 7-258V/ 32GB/ 512GB/ 14" FHD+ OLED/ Win11)</t>
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>46990000</v>
-      </c>
-      <c r="C107" s="2" t="inlineStr"/>
-      <c r="D107" s="2" t="inlineStr"/>
+        <v>39990000</v>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>40990000</v>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4815,270 +4769,298 @@
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® Arc™ Graphics 140V | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0076vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-ai-oled-sfg14-75-765m-14-fhd-oled-u7-258v-32lp-512gb-win</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:20:20.027+07:00</t>
+          <t>2026-08-14T10:47:31.44+07:00</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:19</t>
+          <t>2026-09-26 11:59:25</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK0015VN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>72990000</v>
+        <v>32999000</v>
       </c>
       <c r="C108" s="2" t="inlineStr"/>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk0015vn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:21:45.74+07:00</t>
+          <t>2026-09-15T14:38:31.288+07:00</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:24</t>
+          <t>2026-09-26 11:59:30</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK006GVN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>72990000</v>
-      </c>
-      <c r="C109" s="2" t="inlineStr"/>
-      <c r="D109" s="2" t="inlineStr"/>
+        <v>31490000</v>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>32490000</v>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel® Arc™ 130T Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk006gvn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:23:05.36+07:00</t>
+          <t>2026-09-24T14:08:34.772+07:00</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:29</t>
+          <t>2026-09-26 11:59:35</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 POLED 83QK009PVN (Ultra X9-378H/ 32GB/ 1TB/ 14" 2.8K WQXGA POLED Touch/ Win 11)</t>
+          <t>Laptop Acer Swift X SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" 2.8K OLED/ Win 11/ Office)</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>70990000</v>
-      </c>
-      <c r="C110" s="2" t="inlineStr"/>
-      <c r="D110" s="2" t="inlineStr"/>
+        <v>35990000</v>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>45990000</v>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>-22%</t>
+        </is>
+      </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6 | Kích thước màn hình: 14.5 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-poled-83qk009pvn-ultra-x9-378h-32gb-1tb-14-2-8k-wqxga-poled-touch-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T20:11:25.828+07:00</t>
+          <t>2026-09-14T15:56:38.644+07:00</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:34</t>
+          <t>2026-09-26 11:59:40</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>33900000</v>
+        <v>43990000</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>34900000</v>
+        <v>49490000</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: RTX 4060 | Kích thước màn hình: 14.5 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:39:36.938+07:00</t>
+          <t>2026-07-03T15:10:56.836+07:00</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:39</t>
+          <t>2026-09-26 11:59:45</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H08-50W (Core 5-210H/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>36900000</v>
+        <v>19490000</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>37900000</v>
+        <v>21990000</v>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr"/>
+          <t>-11%</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h08-50w</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:34:21.041+07:00</t>
+          <t>2026-07-31T11:09:14.14+07:00</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:44</t>
+          <t>2026-09-26 11:59:51</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1 P1403CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>44900000</v>
+        <v>24290000</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>46490000</v>
+        <v>26990000</v>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr"/>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h16-63ws-core-5-210h-16gb-512gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:43:00.949+07:00</t>
+          <t>2026-08-03T15:06:02.246+07:00</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:49</t>
+          <t>2026-09-26 11:59:56</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1 P1403CVA-C7H16-50W (Core 7-240H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>23990000</v>
+        <v>28990000</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>24990000</v>
+        <v>30990000</v>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -5087,42 +5069,38 @@
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c7h16-50w-core-7-240h-16gb-512gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:36:48.562+07:00</t>
+          <t>2026-08-03T14:43:57.168+07:00</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:54</t>
+          <t>2026-09-26 12:00:01</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop Asus ExpertBook P1 P1503CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>61990000</v>
+        <v>24290000</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>62990000</v>
+        <v>26990000</v>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5133,40 +5111,40 @@
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1503cva-c5h16-63ws-core-5-210h-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T15:49:38.229+07:00</t>
+          <t>2026-08-03T14:03:33.213+07:00</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:59</t>
+          <t>2026-09-26 12:00:06</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
+          <t>Laptop Asus ExpertBook P1 P1403CVA-C3U08-50W (Core 3-100U/ 8GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>34690000</v>
+        <v>15490000</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>37990000</v>
+        <v>17990000</v>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -5177,40 +5155,40 @@
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c3u08-50w</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T10:28:18.636+07:00</t>
+          <t>2026-07-31T13:53:40.042+07:00</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:04</t>
+          <t>2026-09-26 12:00:11</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>25490000</v>
+        <v>23390000</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>25990000</v>
+        <v>27990000</v>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -5219,72 +5197,86 @@
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:41:40.106+07:00</t>
+          <t>2026-08-12T10:19:47.487+07:00</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:09</t>
+          <t>2026-09-26 12:00:16</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14S AI+ G3MG-050VN (Ultra 7-355/ 16GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U516S8W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>36490000</v>
-      </c>
-      <c r="C118" s="2" t="inlineStr"/>
-      <c r="D118" s="2" t="inlineStr"/>
+        <v>26390000</v>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>29990000</v>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14s-ai-g3mg-050vn-ultra-7-355-16gb-1tb-14-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u516s8w-ultra-5-225h-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T17:51:58.168+07:00</t>
+          <t>2026-08-03T11:57:56.626+07:00</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:14</t>
+          <t>2026-09-26 12:00:21</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
+          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U716S8W (Ultra 7-255H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>22190000</v>
+        <v>32990000</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>22690000</v>
+        <v>34990000</v>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -5293,42 +5285,38 @@
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u716s8w-ultra-7-255h-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T15:28:04.144+07:00</t>
+          <t>2026-09-06T13:46:08.673+07:00</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:19</t>
+          <t>2026-09-26 12:00:26</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA / Win 11)</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>43990000</v>
+        <v>26390000</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>44990000</v>
+        <v>30490000</v>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -5339,40 +5327,40 @@
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:49:42.234+07:00</t>
+          <t>2026-09-03T11:54:54.747+07:00</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:24</t>
+          <t>2026-09-26 12:00:31</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>33990000</v>
+        <v>32990000</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>34990000</v>
+        <v>35990000</v>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -5381,42 +5369,38 @@
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 7 | Dung lượng SSD: 1024 GB | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T16:07:23.364+07:00</t>
+          <t>2026-09-23T08:56:23.461+07:00</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:29</t>
+          <t>2026-09-26 12:00:36</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
+          <t>Laptop Asus ExpertBook P5 G2 P5405CAA-NZ0223W (Ultra 7-356H/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>37990000</v>
+        <v>39190000</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>39990000</v>
+        <v>41990000</v>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -5425,42 +5409,38 @@
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 13.3 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
-        </is>
-      </c>
+      <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-g2-p5405caa-nz0223w-ultra-7-356h-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T11:20:56.718+07:00</t>
+          <t>2026-08-03T11:12:45.933+07:00</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:34</t>
+          <t>2026-09-26 12:00:41</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN (Ultra 7-355/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0016W (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>46990000</v>
+        <v>28790000</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>48990000</v>
+        <v>30990000</v>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -5469,106 +5449,126 @@
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel® Arc™ graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
-        </is>
-      </c>
+      <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0016w-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31T14:41:10.864+07:00</t>
+          <t>2026-08-03T10:54:41.9+07:00</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:39</t>
+          <t>2026-09-26 12:00:46</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0017W (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>59990000</v>
-      </c>
-      <c r="C124" s="2" t="inlineStr"/>
-      <c r="D124" s="2" t="inlineStr"/>
+        <v>36290000</v>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>38990000</v>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: Arc | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 144 Hz</t>
+        </is>
+      </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0017w-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:54:52.677+07:00</t>
+          <t>2026-09-10T13:51:05.888+07:00</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:44</t>
+          <t>2026-09-26 12:00:51</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0442WS (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>59990000</v>
-      </c>
-      <c r="C125" s="2" t="inlineStr"/>
-      <c r="D125" s="2" t="inlineStr"/>
-      <c r="E125" s="2" t="inlineStr"/>
+        <v>37190000</v>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Arc 140V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0442ws-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T10:17:43.984+07:00</t>
+          <t>2026-08-03T09:55:42.594+07:00</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:49</t>
+          <t>2026-09-26 12:00:56</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/ RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0450WS (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>82990000</v>
+        <v>29790000</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>83990000</v>
+        <v>31990000</v>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -5579,42 +5579,36 @@
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Arc 130V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0450ws-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T15:48:57.837+07:00</t>
+          <t>2026-08-03T09:56:18.911+07:00</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:54</t>
+          <t>2026-09-26 12:01:01</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>86990000</v>
-      </c>
-      <c r="C127" s="2" t="n">
-        <v>87990000</v>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>-1%</t>
-        </is>
-      </c>
+        <v>199990000</v>
+      </c>
+      <c r="C127" s="2" t="inlineStr"/>
+      <c r="D127" s="2" t="inlineStr"/>
       <c r="E127" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5623,74 +5617,82 @@
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T17:54:02.495+07:00</t>
+          <t>2026-09-18T11:12:30.954+07:00</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:59</t>
+          <t>2026-09-26 12:01:06</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB027W (Core 3/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>22990000</v>
-      </c>
-      <c r="C128" s="2" t="inlineStr"/>
-      <c r="D128" s="2" t="inlineStr"/>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>48490000</v>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>52990000</v>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: QHD (2560x1440) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb027w-core-3-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:52:41.33+07:00</t>
+          <t>2026-09-10T14:49:48.046+07:00</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:21</t>
+          <t>2026-09-26 11:57:42</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB029W (Core 7/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>35490000</v>
-      </c>
-      <c r="C129" s="2" t="inlineStr"/>
-      <c r="D129" s="2" t="inlineStr"/>
+        <v>79990000</v>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>80990000</v>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5699,33 +5701,33 @@
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb029w-core-7-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T15:05:22.575+07:00</t>
+          <t>2026-06-30T15:43:38.331+07:00</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:26</t>
+          <t>2026-09-26 11:57:47</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB219W (Core 5/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>26990000</v>
+        <v>85990000</v>
       </c>
       <c r="C130" s="2" t="inlineStr"/>
       <c r="D130" s="2" t="inlineStr"/>
@@ -5735,315 +5737,295 @@
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
-      <c r="G130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+        </is>
+      </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb219w-core-5-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T13:46:08.34+07:00</t>
+          <t>2026-09-22T17:51:09.908+07:00</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:31</t>
+          <t>2026-09-26 11:57:52</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB220W (Core 7/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming MSI Stealth A16 AI+ A3XWHG 085VN</t>
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>30490000</v>
-      </c>
-      <c r="C131" s="2" t="inlineStr"/>
-      <c r="D131" s="2" t="inlineStr"/>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>67690000</v>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>73990000</v>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4060 | Kích thước màn hình: 16 inch</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb220w-core-7-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-a16-ai-a3xwhg-085vn</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:43:31.989+07:00</t>
+          <t>2026-01-27T14:36:44.954+07:00</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:36</t>
+          <t>2026-09-26 11:57:57</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1404V (Core 5-120U/ 8GB/ 256GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop GIGABYTE AERO X16 4WHN3VNC93AH (Ryzen AI 9 465/ RTX 5070 8GB/ 16GB/ 512GB/ 16" QHD+ 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>16590000</v>
-      </c>
-      <c r="C132" s="2" t="n">
-        <v>18990000</v>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>-13%</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>54990000</v>
+      </c>
+      <c r="C132" s="2" t="inlineStr"/>
+      <c r="D132" s="2" t="inlineStr"/>
+      <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
-        </is>
-      </c>
+      <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404v-core-5-120u-8gb-256gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aero-x16-4whn3vnc93ah-ryzen-ai-9-465-rtx-5070-8gb-16gb-512gb-16-qhd-165hz-win-11</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T13:41:37.603+07:00</t>
+          <t>2026-09-18T13:49:41.514+07:00</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:41</t>
+          <t>2026-09-26 11:58:02</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VA-EB355W (Core 7-150U/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming GIGABYTE AORUS Master 16 6XJM4VNE64SH (Ryzen 9 9955HX3D/ RTX 5070 Ti 12GB/ 32GB/ 1TB/ 16" QHD+ OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>25990000</v>
+        <v>86990000</v>
       </c>
       <c r="C133" s="2" t="inlineStr"/>
       <c r="D133" s="2" t="inlineStr"/>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb355w-core-7-150u-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aorus-master-16-6xjm4vne64sh-ryzen-9-9955hx3d-rtx-5070-ti-12gb-32gb-1tb-16-qhd-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:17:32.016+07:00</t>
+          <t>2026-09-24T11:46:50.068+07:00</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:46</t>
+          <t>2026-09-26 11:58:07</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VA-EB609W (Core 3-100U/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop GIGABYTE Gaming A16 EVHS3VN893SH (Ultra 9-185H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>21990000</v>
-      </c>
-      <c r="C134" s="2" t="inlineStr"/>
-      <c r="D134" s="2" t="inlineStr"/>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>39990000</v>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>40990000</v>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb609w-core-3-100u-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-gaming-a16-evhs3vn893sh-ultra-9-185h-rtx-5060-8gb-16gb-512gb-16-fhd-165hz-win-11</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:33:25.424+07:00</t>
+          <t>2026-09-18T13:36:39.051+07:00</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:51</t>
+          <t>2026-09-26 11:58:12</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VAP-V14.C58256 (Core 5-120U/ 16GB/ 256GB/ 14" FHD IPS/ Win 11/ Quiet Blue)</t>
+          <t>Laptop HP 15-fd1289TU C2CV8PA (Ultra 7-155H/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>17890000</v>
+        <v>24990000</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>18990000</v>
+        <v>25990000</v>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404vap-v14-c58256-core-5-120u-8gb-256gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-hp-15-fd1289tu-c2cv8pa-ultra-7-155h-16gb-512gb-15-6-fhd-ips-win-11</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:42:34.369+07:00</t>
+          <t>2026-09-10T13:33:44.001+07:00</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:56</t>
+          <t>2026-09-26 11:58:17</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus VivoBook 14 X1407AA-LY360W (Ultra 5-325/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop HP 250 G10 A06FDPT (I7-1355U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>26490000</v>
+        <v>23490000</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>26990000</v>
+        <v>25590000</v>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407aa-ly360w-ultra-5-325-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-hp-250-g10-a06fdpt-i7-1355u-8gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T15:46:33.275+07:00</t>
+          <t>2026-09-10T13:31:30.682+07:00</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:01</t>
+          <t>2026-09-26 11:58:22</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1407CA-LY203W (Ultra 5-225H/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop HP ProBook 450 G10 B73TPAT (I5-1334U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>33490000</v>
-      </c>
-      <c r="C137" s="2" t="inlineStr"/>
-      <c r="D137" s="2" t="inlineStr"/>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>23990000</v>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>24990000</v>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Iris Xe Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407ca-ly203w-ultra-5-225h-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-hp-probook-450-g10-b73tpat-i5-1334u-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T10:22:08.041+07:00</t>
+          <t>2026-09-10T13:31:53.385+07:00</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:06</t>
+          <t>2026-09-26 11:58:27</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504MA-BQ632W (Core 5-320/ 8GB/ 512GB/ 15" FHD IPS)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 83RQ00DBVN (Core 3-304/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>26990000</v>
+        <v>24990000</v>
       </c>
       <c r="C138" s="2" t="inlineStr"/>
       <c r="D138" s="2" t="inlineStr"/>
@@ -6055,33 +6037,33 @@
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq632w-core-5-320-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-14iwc11-83rq00dbvn-core-3-304-8gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T15:43:54.381+07:00</t>
+          <t>2026-09-07T10:16:44.995+07:00</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:11</t>
+          <t>2026-09-26 11:58:32</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504MA-BQ633W (Core 7-350/ 8GB/ 512GB/ 15" FHD IPS)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB005YVN (Ryzen 5-125/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>30490000</v>
+        <v>25990000</v>
       </c>
       <c r="C139" s="2" t="inlineStr"/>
       <c r="D139" s="2" t="inlineStr"/>
@@ -6091,35 +6073,31 @@
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
-        </is>
-      </c>
+      <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq633w-core-7-350-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb005yvn-ryzen-5-125-8gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:33:03.428+07:00</t>
+          <t>2026-08-13T15:01:44.794+07:00</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:17</t>
+          <t>2026-09-26 11:58:37</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504VA-BQ165W (Core 5-120U/ 8GB/ 512GB/ 15" FHD IPS)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB0060VN (Ryzen 7-155/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>20990000</v>
+        <v>27990000</v>
       </c>
       <c r="C140" s="2" t="inlineStr"/>
       <c r="D140" s="2" t="inlineStr"/>
@@ -6129,75 +6107,71 @@
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
-        </is>
-      </c>
+      <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504va-bq165w-core-5-120u-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb0060vn-ryzen-7-155-8gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:12:00.028+07:00</t>
+          <t>2026-08-13T14:35:59.897+07:00</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:22</t>
+          <t>2026-09-26 11:58:42</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 16 X1605VA-MB1826W (I3-1315U/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 83S1003GVN</t>
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>15390000</v>
+        <v>44540000</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>15990000</v>
+        <v>47990000</v>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 16 inch | Dòng CPU: i3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1605va-mb1826w-i3-1315u-8gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-83s1003gvn</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T10:45:38.083+07:00</t>
+          <t>2026-08-28T10:29:16.152+07:00</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:27</t>
+          <t>2026-09-26 11:58:47</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 16 X1607CA-MB387W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD IPS)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 OLED 83S1006RVN (Ryzen AI 7-445/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>33490000</v>
+        <v>32990000</v>
       </c>
       <c r="C142" s="2" t="inlineStr"/>
       <c r="D142" s="2" t="inlineStr"/>
@@ -6209,33 +6183,33 @@
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb387w-ultra-5-225h-16gb-512gb-16-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-oled-83s1006rvn-ryzen-ai-7-445-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T16:08:06.906+07:00</t>
+          <t>2026-08-13T11:54:44.05+07:00</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:32</t>
+          <t>2026-09-26 11:58:53</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 16 X1607CA-MB399W (Ultra 7-255H/ 16GB/ 512GB/ 16" FHD IPS)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00ABVN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>36490000</v>
+        <v>30990000</v>
       </c>
       <c r="C143" s="2" t="inlineStr"/>
       <c r="D143" s="2" t="inlineStr"/>
@@ -6245,31 +6219,35 @@
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb399w-ultra-7-255h-16gb-512gb-16-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00abvn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T15:36:19.591+07:00</t>
+          <t>2026-08-13T14:05:59.687+07:00</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:37</t>
+          <t>2026-09-26 11:58:58</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Flip TP3407AA-SG029W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00F5VN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>41990000</v>
+        <v>34990000</v>
       </c>
       <c r="C144" s="2" t="inlineStr"/>
       <c r="D144" s="2" t="inlineStr"/>
@@ -6281,73 +6259,71 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-flip-tp3407aa-sg029w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00f5vn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T14:55:40.249+07:00</t>
+          <t>2026-09-07T10:17:34.624+07:00</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:42</t>
+          <t>2026-09-26 11:59:03</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook Go 14 E1404FA-EB935W (Ryzen 5-7430U/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002EVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>20490000</v>
-      </c>
-      <c r="C145" s="2" t="n">
-        <v>28490000</v>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>-28%</t>
-        </is>
-      </c>
+        <v>55990000</v>
+      </c>
+      <c r="C145" s="2" t="inlineStr"/>
+      <c r="D145" s="2" t="inlineStr"/>
       <c r="E145" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
-      <c r="G145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1404fa-eb935w-ryzen-5-7430u-16gb-512gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002evn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T09:46:28.801+07:00</t>
+          <t>2026-08-13T10:21:35.763+07:00</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:47</t>
+          <t>2026-09-26 11:59:08</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ4821W (Ryzen 5/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002FVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>22990000</v>
+        <v>55990000</v>
       </c>
       <c r="C146" s="2" t="inlineStr"/>
       <c r="D146" s="2" t="inlineStr"/>
@@ -6359,33 +6335,33 @@
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1504fa-bq4821w-ryzen-5-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002fvn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:55:57.447+07:00</t>
+          <t>2026-08-12T20:29:51.634+07:00</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:52</t>
+          <t>2026-09-26 11:59:13</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ340W (Ryzen 5/ 16GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0075VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>28490000</v>
+        <v>46990000</v>
       </c>
       <c r="C147" s="2" t="inlineStr"/>
       <c r="D147" s="2" t="inlineStr"/>
@@ -6398,28 +6374,28 @@
       <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-go-15-e1504fa-bq340w-ryzen-5-16gb-512gb-156-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0075vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:55:13.502+07:00</t>
+          <t>2026-09-07T10:19:34.771+07:00</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:57</t>
+          <t>2026-09-26 11:59:18</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 M3407KA-SF034W (Ryzen AI 5-330/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0076VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>33990000</v>
+        <v>46990000</v>
       </c>
       <c r="C148" s="2" t="inlineStr"/>
       <c r="D148" s="2" t="inlineStr"/>
@@ -6431,33 +6407,33 @@
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-m3407ka-sf034w-ryzen-ai-5-330-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0076vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T12:02:07.653+07:00</t>
+          <t>2026-09-07T10:20:20.027+07:00</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:01</t>
+          <t>2026-09-26 11:59:23</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407AA-SF032W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK0015VN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>40490000</v>
+        <v>72990000</v>
       </c>
       <c r="C149" s="2" t="inlineStr"/>
       <c r="D149" s="2" t="inlineStr"/>
@@ -6469,33 +6445,33 @@
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf032w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk0015vn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T10:00:42.045+07:00</t>
+          <t>2026-09-07T10:21:45.74+07:00</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:07</t>
+          <t>2026-09-26 11:59:28</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407AA-SF945W (Ultra 5-325/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK006GVN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>37490000</v>
+        <v>72990000</v>
       </c>
       <c r="C150" s="2" t="inlineStr"/>
       <c r="D150" s="2" t="inlineStr"/>
@@ -6507,33 +6483,33 @@
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf945w-ultra-5-325-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk006gvn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T11:09:17.449+07:00</t>
+          <t>2026-09-07T10:23:05.36+07:00</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:12</t>
+          <t>2026-09-26 11:59:33</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407QA-SF043W (QC X126100/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 POLED 83QK009PVN (Ultra X9-378H/ 32GB/ 1TB/ 14" 2.8K WQXGA POLED Touch/ Win 11)</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>25990000</v>
+        <v>70990000</v>
       </c>
       <c r="C151" s="2" t="inlineStr"/>
       <c r="D151" s="2" t="inlineStr"/>
@@ -6545,36 +6521,42 @@
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407qa-sf043w-qc-x126100-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-poled-83qk009pvn-ultra-x9-378h-32gb-1tb-14-2-8k-wqxga-poled-touch-win-11</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T09:15:59.141+07:00</t>
+          <t>2026-08-12T20:11:25.828+07:00</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:17</t>
+          <t>2026-09-26 11:59:38</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407VA-LY147W (Core 5-210H/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="C152" s="2" t="inlineStr"/>
-      <c r="D152" s="2" t="inlineStr"/>
+        <v>33900000</v>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>34900000</v>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6583,116 +6565,112 @@
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407va-ly147w-core-5-210h-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T11:42:14.925+07:00</t>
+          <t>2026-07-01T13:39:36.938+07:00</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:22</t>
+          <t>2026-09-26 11:59:43</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 16 S3607AA-SH042W (Ultra 5-325/ 16GB/ 512GB/ 16" FHD OLED)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>37490000</v>
-      </c>
-      <c r="C153" s="2" t="inlineStr"/>
-      <c r="D153" s="2" t="inlineStr"/>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>36900000</v>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>37900000</v>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr"/>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-16-s3607aa-sh042w-ultra-5-325-16gb-512gb-16-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T10:44:16.77+07:00</t>
+          <t>2026-07-01T13:34:21.041+07:00</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:27</t>
+          <t>2026-09-26 11:59:48</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 16 S3607CA-SH080W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD OLED)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="C154" s="2" t="inlineStr"/>
-      <c r="D154" s="2" t="inlineStr"/>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>44900000</v>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>46490000</v>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr"/>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-16-s3607ca-sh080w-ultra-5-225h-16gb-512gb-16-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T10:21:29.428+07:00</t>
+          <t>2026-07-01T13:43:00.949+07:00</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:32</t>
+          <t>2026-09-26 11:59:53</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS VivoBook S14 S3407CA-SF913W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>27890000</v>
+        <v>23990000</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>29990000</v>
+        <v>24990000</v>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -6703,36 +6681,42 @@
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s14-s3407ca-sf913w-ultra-5-225h-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T17:02:01.429+07:00</t>
+          <t>2026-07-01T13:36:48.562+07:00</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:38</t>
+          <t>2026-09-26 11:59:58</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UM3406GA-QD075W (Ryzen 7/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop gaming MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="C156" s="2" t="inlineStr"/>
-      <c r="D156" s="2" t="inlineStr"/>
+        <v>61990000</v>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>62990000</v>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6741,36 +6725,42 @@
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ga-qd075w-ryzen-7-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T16:03:07.024+07:00</t>
+          <t>2026-09-23T15:49:38.229+07:00</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:43</t>
+          <t>2026-09-26 12:00:03</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1531W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>42990000</v>
-      </c>
-      <c r="C157" s="2" t="inlineStr"/>
-      <c r="D157" s="2" t="inlineStr"/>
+        <v>34690000</v>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>37990000</v>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6779,40 +6769,40 @@
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1531w-ultra-9-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T08:45:55.514+07:00</t>
+          <t>2026-09-21T10:28:18.636+07:00</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:48</t>
+          <t>2026-09-26 12:00:08</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1713W (Ultra 5-225H/ 16GB/ 512GB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>30990000</v>
+        <v>25490000</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>38990000</v>
+        <v>25990000</v>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -6821,35 +6811,31 @@
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr"/>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1713w-ultra-5-225h-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:16:16.703+07:00</t>
+          <t>2026-06-25T15:41:40.106+07:00</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:53</t>
+          <t>2026-09-26 12:00:13</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST630W (Ultra 7-255H/ 16GB/ 512GB/ 14" 3K OLED)</t>
+          <t>Laptop MSI Modern 14S AI+ G3MG-050VN (Ultra 7-355/ 16GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>40990000</v>
+        <v>36490000</v>
       </c>
       <c r="C159" s="2" t="inlineStr"/>
       <c r="D159" s="2" t="inlineStr"/>
@@ -6859,38 +6845,40 @@
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st630w-ultra-7-255h-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-14s-ai-g3mg-050vn-ultra-7-355-16gb-1tb-14-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T15:05:39.807+07:00</t>
+          <t>2026-09-22T17:51:58.168+07:00</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:58</t>
+          <t>2026-09-26 12:00:18</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3407NA-QD132WS (Snapdragon X2 Elite X2E-88-100/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>48990000</v>
-      </c>
-      <c r="C160" s="2" t="inlineStr"/>
-      <c r="D160" s="2" t="inlineStr"/>
+        <v>22190000</v>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>22690000</v>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6899,36 +6887,42 @@
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd132ws-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:47:13.916+07:00</t>
+          <t>2026-07-09T15:28:04.144+07:00</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:03</t>
+          <t>2026-09-26 12:00:23</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook A14 UX3407NA-QD254W (Snapdragon X2 Elite X2E-88-100/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>63990000</v>
-      </c>
-      <c r="C161" s="2" t="inlineStr"/>
-      <c r="D161" s="2" t="inlineStr"/>
+        <v>43990000</v>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>44990000</v>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6937,36 +6931,42 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd254w-32gb-1tb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:46:55.101+07:00</t>
+          <t>2026-06-25T15:49:42.234+07:00</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:08</t>
+          <t>2026-09-26 12:00:28</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook A16 UX3607OA-SQ137WS (Snapdragon X2 Elite Extreme X2E94100/ 24GB/ 512GB/ 16" 3K OLED/ Win 11)</t>
+          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>58990000</v>
-      </c>
-      <c r="C162" s="2" t="inlineStr"/>
-      <c r="D162" s="2" t="inlineStr"/>
+        <v>33990000</v>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>34990000</v>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6975,36 +6975,42 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 16 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 24 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 7 | Dung lượng SSD: 1024 GB | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-16-ux3607oa-sq137ws-24gb-512gb-16-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:43:18.337+07:00</t>
+          <t>2026-06-25T16:07:23.364+07:00</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:13</t>
+          <t>2026-09-26 12:00:33</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN138WS (Ultra X9/ 32GB/ 1TB/ 14" 3K OLED Touch 144Hz)</t>
+          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>89990000</v>
-      </c>
-      <c r="C163" s="2" t="inlineStr"/>
-      <c r="D163" s="2" t="inlineStr"/>
+        <v>37990000</v>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7013,36 +7019,42 @@
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 13.3 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn138ws-ultra-x9-32gb-1tb-14-3k-oled-touch-144hz</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T12:04:03.945+07:00</t>
+          <t>2026-08-17T11:20:56.718+07:00</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:18</t>
+          <t>2026-09-26 12:00:39</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN439WS (Ultra X7/ 32GB/ 512GB/ 14" 3K OLED Touch 144Hz)</t>
+          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN (Ultra 7-355/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>82990000</v>
-      </c>
-      <c r="C164" s="2" t="inlineStr"/>
-      <c r="D164" s="2" t="inlineStr"/>
+        <v>46990000</v>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>48990000</v>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7051,33 +7063,33 @@
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel® Arc™ graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn439ws-ultra-x7-32gb-512gb-14-3k-oled-touch-144hz</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T11:44:06.982+07:00</t>
+          <t>2026-08-31T14:41:10.864+07:00</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:23</t>
+          <t>2026-09-26 12:00:44</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ProArt PX13 HN7306EA-LX050W (Ryzen AI Max+ 395/ 32GB/ 1TB/ 13.3" 3K OLED Touch)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>76990000</v>
+        <v>59990000</v>
       </c>
       <c r="C165" s="2" t="inlineStr"/>
       <c r="D165" s="2" t="inlineStr"/>
@@ -7087,76 +7099,70 @@
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 13.3 inch | Dòng CPU: Ryzen AI MAX+ | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
-        </is>
-      </c>
+      <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-pro-art-hn7306ea-lx050w-ryzen-ai-max-395-32gb-1tb-13-3-3k-oled-touch</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:58:08.111+07:00</t>
+          <t>2026-06-30T09:54:52.677+07:00</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:28</t>
+          <t>2026-09-26 12:00:49</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook S 14 UX5406AA-SU348W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED Touch)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>50990000</v>
+        <v>59990000</v>
       </c>
       <c r="C166" s="2" t="inlineStr"/>
       <c r="D166" s="2" t="inlineStr"/>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+      <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr"/>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-s-14-ux5406aa-su348w-ultra-9-16gb-512gb-14-3k-oled-touch</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T10:26:19.879+07:00</t>
+          <t>2026-06-30T10:17:43.984+07:00</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:34</t>
+          <t>2026-09-26 12:00:54</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook S 16 UM5606GA-SS441W (Ryzen AI 9 465/ 16GB/ 512GB/ 16" 3K OLED)</t>
+          <t>Laptop gaming MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/ RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>49490000</v>
-      </c>
-      <c r="C167" s="2" t="inlineStr"/>
-      <c r="D167" s="2" t="inlineStr"/>
+        <v>82990000</v>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>83990000</v>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7165,40 +7171,40 @@
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ryzen AI 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-s-15-um5606ga-ss441w-ryzen-ai-9-465-16gb-512gb-15-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T16:22:14.948+07:00</t>
+          <t>2026-09-23T15:48:57.837+07:00</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:39</t>
+          <t>2026-09-26 12:00:59</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - 71092480 (I7-1355U/ 16GB/ 512GB/ Win 11/ Office/ Microsoft 365)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>25390000</v>
+        <v>86990000</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>25990000</v>
+        <v>87990000</v>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -7209,40 +7215,40 @@
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-15-dc15250-71092480-i7-1355u-16gb-512gb-win-11-office-microsoft-365</t>
+          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T10:56:32.257+07:00</t>
+          <t>2026-09-22T17:54:02.495+07:00</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:44</t>
+          <t>2026-09-26 12:01:04</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I3-100U/ 8GB/ 512GB/ 15.6" FHD 120Hz/DOS) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I5-1334U/ 8GB/ 512GB/ 15.6" FHD/DOS) - Nhập Khẩu Chính Hãng</t>
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>14390000</v>
+        <v>15990000</v>
       </c>
       <c r="C169" s="2" t="n">
-        <v>14990000</v>
+        <v>17490000</v>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -7253,40 +7259,40 @@
       <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i3-100u-8gb-512gb-15-6-fhd-120hz</t>
+          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i5-1334u-8gb-512gb-15-6-fhd</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T10:44:17.994+07:00</t>
+          <t>2026-09-17T11:07:57.107+07:00</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:49</t>
+          <t>2026-09-26 11:57:43</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I5-1334U/ 8GB/ 512GB/ 15.6" FHD/DOS) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop Dell 16 DC16251 (I5-120U/ 8GB/ 512GB/ 16" FHD+ Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>15990000</v>
+        <v>18390000</v>
       </c>
       <c r="C170" s="2" t="n">
-        <v>17490000</v>
+        <v>19990000</v>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -7297,40 +7303,40 @@
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i5-1334u-8gb-512gb-15-6-fhd</t>
+          <t>https://gearvn.com/products/laptop-dell-16-dc16251-i5-120u-8gb-512gb-16-fhd-touch-win-11</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:07:57.107+07:00</t>
+          <t>2026-08-12T13:45:33.424+07:00</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:36</t>
+          <t>2026-09-26 11:57:48</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 16 DC16251 (I5-120U/ 8GB/ 512GB/ 16" FHD+ Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop Dell DC15250-7982BLK H5YXJ (I7-1355U/ 16GB/ 1TB/ 15.6" FHD Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>18390000</v>
+        <v>22990000</v>
       </c>
       <c r="C171" s="2" t="n">
-        <v>19990000</v>
+        <v>23990000</v>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -7341,84 +7347,84 @@
       <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-16-dc16251-i5-120u-8gb-512gb-16-fhd-touch-win-11</t>
+          <t>https://gearvn.com/products/laptop-dell-dc15250-7982blk-h5yxj-i7-1355u-16gb-1tb-15-6-fhd-touch-win-11</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T13:45:33.424+07:00</t>
+          <t>2026-08-19T15:36:35.706+07:00</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:42</t>
+          <t>2026-09-26 11:57:53</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell DC15250-7982BLK H5YXJ (I7-1355U/ 16GB/ 1TB/ 15.6" FHD Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-53RH (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>22990000</v>
+        <v>29990000</v>
       </c>
       <c r="C172" s="2" t="n">
-        <v>23990000</v>
+        <v>32490000</v>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-dc15250-7982blk-h5yxj-i7-1355u-16gb-1tb-15-6-fhd-touch-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-53rh-core-5-210h-rtx-4050-6gb-16gb-512gb-15-6-fhd-ips-144hz</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19T15:36:35.706+07:00</t>
+          <t>2026-09-09T10:39:56.876+07:00</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:47</t>
+          <t>2026-09-26 11:57:59</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-53RH (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-59RD (Core 5-210H/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>29990000</v>
+        <v>24490000</v>
       </c>
       <c r="C173" s="2" t="n">
-        <v>32490000</v>
+        <v>27990000</v>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -7429,66 +7435,66 @@
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-53rh-core-5-210h-rtx-4050-6gb-16gb-512gb-15-6-fhd-ips-144hz</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T10:39:56.876+07:00</t>
+          <t>2026-09-25T16:06:18.096+07:00</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:52</t>
+          <t>2026-09-26 11:58:04</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-59RD (Core 5-210H/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R5F4 (Ryzen AI 7 350/ RTX 5060/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>25990000</v>
+        <v>48890000</v>
       </c>
       <c r="C174" s="2" t="n">
-        <v>27990000</v>
+        <v>50990000</v>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-gaming-nitro-v-propanel-an16s-61-r5f4</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T19:19:44.235+07:00</t>
+          <t>2026-09-09T15:11:02.875+07:00</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:57:57</t>
+          <t>2026-09-26 11:58:09</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7532,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:58:32</t>
+          <t>2026-09-26 11:58:14</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7570,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:06</t>
+          <t>2026-09-26 11:58:19</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7614,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:11</t>
+          <t>2026-09-26 11:58:24</t>
         </is>
       </c>
     </row>
@@ -7652,7 +7658,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:17</t>
+          <t>2026-09-26 11:58:29</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7702,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:22</t>
+          <t>2026-09-26 11:58:34</t>
         </is>
       </c>
     </row>
@@ -7740,7 +7746,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:27</t>
+          <t>2026-09-26 11:58:39</t>
         </is>
       </c>
     </row>
@@ -7784,7 +7790,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:32</t>
+          <t>2026-09-26 11:58:44</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7828,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:37</t>
+          <t>2026-09-26 11:58:49</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7866,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:42</t>
+          <t>2026-09-26 11:58:54</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7904,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:47</t>
+          <t>2026-09-26 11:58:59</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7948,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:52</t>
+          <t>2026-09-26 11:59:04</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7986,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 11:59:57</t>
+          <t>2026-09-26 11:59:09</t>
         </is>
       </c>
     </row>
@@ -7991,14 +7997,14 @@
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>33490000</v>
+        <v>30990000</v>
       </c>
       <c r="C187" s="2" t="n">
         <v>35990000</v>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -8019,12 +8025,12 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T11:28:25.12+07:00</t>
+          <t>2026-09-25T16:07:52.913+07:00</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:02</t>
+          <t>2026-09-26 11:59:14</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8074,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:07</t>
+          <t>2026-09-26 11:59:19</t>
         </is>
       </c>
     </row>
@@ -8079,14 +8085,14 @@
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>35890000</v>
+        <v>33490000</v>
       </c>
       <c r="C189" s="2" t="n">
         <v>37990000</v>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -8107,12 +8113,12 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T11:27:41.087+07:00</t>
+          <t>2026-09-25T16:08:20.8+07:00</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:12</t>
+          <t>2026-09-26 11:59:24</t>
         </is>
       </c>
     </row>
@@ -8156,7 +8162,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:17</t>
+          <t>2026-09-26 11:59:29</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8206,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:22</t>
+          <t>2026-09-26 11:59:34</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8250,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:27</t>
+          <t>2026-09-26 11:59:40</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8294,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:32</t>
+          <t>2026-09-26 11:59:45</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8338,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:37</t>
+          <t>2026-09-26 11:59:50</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8376,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:42</t>
+          <t>2026-09-26 11:59:55</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8414,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:48</t>
+          <t>2026-09-26 12:00:00</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8452,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:53</t>
+          <t>2026-09-26 12:00:05</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8490,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:00:58</t>
+          <t>2026-09-26 12:00:10</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8534,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:01:03</t>
+          <t>2026-09-26 12:00:15</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8572,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:01:08</t>
+          <t>2026-09-26 12:00:20</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8616,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:01:13</t>
+          <t>2026-09-26 12:00:25</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8654,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:01:18</t>
+          <t>2026-09-26 12:00:30</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8698,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:01:23</t>
+          <t>2026-09-26 12:00:35</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8738,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:01:28</t>
+          <t>2026-09-26 12:00:41</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8776,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:01:33</t>
+          <t>2026-09-26 12:00:46</t>
         </is>
       </c>
     </row>
@@ -8814,7 +8820,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:01:38</t>
+          <t>2026-09-26 12:00:51</t>
         </is>
       </c>
     </row>
@@ -8852,7 +8858,7 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:01:43</t>
+          <t>2026-09-26 12:00:56</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8902,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:01:48</t>
+          <t>2026-09-26 12:01:01</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8940,7 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:01:53</t>
+          <t>2026-09-26 12:01:06</t>
         </is>
       </c>
     </row>
@@ -8974,7 +8980,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:01:58</t>
+          <t>2026-09-26 12:01:11</t>
         </is>
       </c>
     </row>

--- a/laptop_gearvn_all.xlsx
+++ b/laptop_gearvn_all.xlsx
@@ -503,471 +503,447 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-59RD (Core 5-210H/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>24490000</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>-13%</t>
-        </is>
-      </c>
+        <v>199990000</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
+          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:06:18.096+07:00</t>
+          <t>2026-09-18T11:12:30.954+07:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:02</t>
+          <t>2026-09-28 12:23:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R5F4 (Ryzen AI 7 350/ RTX 5060/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB027W (Core 3/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>48890000</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>50990000</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>22990000</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-gaming-nitro-v-propanel-an16s-61-r5f4</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb027w-core-3-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T15:11:02.875+07:00</t>
+          <t>2026-08-18T16:52:41.33+07:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:07</t>
+          <t>2026-09-28 12:23:13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R7KQ (Ryzen AI 5 340/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD+/Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB029W (Core 7/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46990000</v>
+        <v>35490000</v>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-anv16s-61-r7kq</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb029w-core-7-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T10:11:28.855+07:00</t>
+          <t>2026-08-20T15:05:22.575+07:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:12</t>
+          <t>2026-09-28 12:23:18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R7ZJ (Ryzen AI 7 350/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB220W (Core 7/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>51990000</v>
+        <v>30490000</v>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-an16s-61-r7zj</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb220w-core-7-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T10:35:37.593+07:00</t>
+          <t>2026-08-20T11:43:31.989+07:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:17</t>
+          <t>2026-09-28 12:23:23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R0QM (Ryzen 5 7640HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus Vivobook 14 X1404V (Core 5-120U/ 8GB/ 256GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>32990000</v>
+        <v>16590000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>34990000</v>
+        <v>18990000</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r0qm</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404v-core-5-120u-8gb-256gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T14:12:10.19+07:00</t>
+          <t>2026-08-07T13:41:37.603+07:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:22</t>
+          <t>2026-09-28 12:23:28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R5EF (Ryzen 5 7640HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VA-EB355W (Core 7-150U/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>33390000</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
+        <v>25990000</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r5ef</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb355w-core-7-150u-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:23:17.905+07:00</t>
+          <t>2026-08-20T11:17:32.016+07:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:27</t>
+          <t>2026-09-28 12:23:33</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R9EH (Ryzen 7 7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VA-EB609W (Core 3-100U/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-8%</t>
-        </is>
-      </c>
+        <v>21990000</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r9eh</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb609w-core-3-100u-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T15:05:48.951+07:00</t>
+          <t>2026-08-18T16:33:25.424+07:00</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:32</t>
+          <t>2026-09-28 12:23:38</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-556L (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VAP-V14.C58256 (Core 5-120U/ 16GB/ 256GB/ 14" FHD IPS/ Win 11/ Quiet Blue)</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>38890000</v>
+        <v>17890000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>38990000</v>
+        <v>18990000</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Tay cầm Acer Nitro Controller NGR300 Wireless White (trị giá 1.200.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-556l</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404vap-v14-c58256-core-5-120u-8gb-256gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:27:47.558+07:00</t>
+          <t>2026-09-14T17:42:34.369+07:00</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:37</t>
+          <t>2026-09-28 12:23:43</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-78MD (Core 7-240H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus VivoBook 14 X1407AA-LY360W (Ultra 5-325/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>40890000</v>
+        <v>26490000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>40990000</v>
+        <v>26990000</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Tay cầm Acer Nitro Controller NGR300 Wireless White (trị giá 1.200.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-78md</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407aa-ly360w-ultra-5-325-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:28:06.595+07:00</t>
+          <t>2026-08-07T15:46:33.275+07:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:42</t>
+          <t>2026-09-28 12:23:48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-71T9 (Core 7-240H/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1407CA-LY203W (Ultra 5-225H/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>43990000</v>
+        <v>33490000</v>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-71t9</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407ca-ly203w-ultra-5-225h-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:29:41.759+07:00</t>
+          <t>2026-08-20T10:22:08.041+07:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:47</t>
+          <t>2026-09-28 12:23:53</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-782F (Core 7-240H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 15 X1504MA-BQ632W (Core 5-320/ 8GB/ 512GB/ 15" FHD IPS)</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>40990000</v>
+        <v>26990000</v>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-782f</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq632w-core-5-320-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T10:05:04.439+07:00</t>
+          <t>2026-08-18T15:43:54.381+07:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:52</t>
+          <t>2026-09-28 12:23:58</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-I51-71MF (Ultra 7-355/ RTX 5070 8GB/ 32GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 15 X1504MA-BQ633W (Core 7-350/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>76990000</v>
+        <v>30490000</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr"/>
@@ -979,867 +955,807 @@
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-i51-71mf-ultra-7-355-rtx-5070-8gb-32gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq633w-core-7-350-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T10:59:01.522+07:00</t>
+          <t>2026-09-26T12:47:34.397+07:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:56</t>
+          <t>2026-09-28 12:24:03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-71-58WQ (Core 5-210H/ RTX 5050/ 32GB/ 512GB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 15 X1504VA-BQ165W (Core 5-120U/ 8GB/ 512GB/ 15" FHD IPS)</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>44890000</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>45990000</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>20990000</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16s-71-58wq</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504va-bq165w-core-5-120u-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T10:25:14.809+07:00</t>
+          <t>2026-08-18T16:12:00.028+07:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:01</t>
+          <t>2026-09-28 12:24:08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R9CN (Ryzen AI 7 350/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop Asus Vivobook 16 X1605VA-MB1826W (I3-1315U/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>57990000</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
-        </is>
-      </c>
+        <v>15390000</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>15990000</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 16 inch | Dòng CPU: i3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-s-ai-propanel-an16s-61-r9cn</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1605va-mb1826w-i3-1315u-8gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T15:10:31.152+07:00</t>
+          <t>2026-09-09T10:45:38.083+07:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:06</t>
+          <t>2026-09-28 12:24:13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50RB (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 16 X1607CA-MB387W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD IPS)</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-14%</t>
-        </is>
-      </c>
+        <v>33490000</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50rb</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb387w-ultra-5-225h-16gb-512gb-16-fhd-ips</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T11:11:52.657+07:00</t>
+          <t>2026-08-20T16:08:06.906+07:00</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:11</t>
+          <t>2026-09-28 12:24:18</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50VA (Core 5-210H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 16 X1607CA-MB399W (Ultra 7-255H/ 16GB/ 512GB/ 16" FHD IPS)</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>28990000</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>33990000</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-15%</t>
-        </is>
-      </c>
+        <v>36490000</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50va</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb399w-ultra-7-255h-16gb-512gb-16-fhd-ips</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T11:03:23.184+07:00</t>
+          <t>2026-08-20T15:36:19.591+07:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:16</t>
+          <t>2026-09-28 12:24:23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-73Z8 (Core 7-240H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop ASUS Vivobook Flip TP3407AA-SG029W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>33490000</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>37990000</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>41990000</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-flip-tp3407aa-sg029w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:08:20.8+07:00</t>
+          <t>2026-08-18T14:55:40.249+07:00</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:21</t>
+          <t>2026-09-28 12:24:28</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
+          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ4821W (Ryzen 5/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>42590000</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>43990000</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>22990000</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1504fa-bq4821w-ryzen-5-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T11:01:07.66+07:00</t>
+          <t>2026-09-24T15:55:57.447+07:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:26</t>
+          <t>2026-09-28 12:24:33</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
+          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ340W (Ryzen 5/ 16GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>42990000</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>45990000</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>28490000</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-go-15-e1504fa-bq340w-ryzen-5-16gb-512gb-156-fhd-ips</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T09:31:41.277+07:00</t>
+          <t>2026-09-24T15:55:13.502+07:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:31</t>
+          <t>2026-09-28 12:24:38</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 M3407KA-SF034W (Ryzen AI 5-330/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>54990000</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>58690000</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>33990000</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-m3407ka-sf034w-ryzen-ai-5-330-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T10:40:22.072+07:00</t>
+          <t>2026-08-18T12:02:07.653+07:00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:36</t>
+          <t>2026-09-28 12:24:43</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407AA-SF945W (Ultra 5-325/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>32490000</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>36990000</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>37490000</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf945w-ultra-5-325-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T09:59:34.507+07:00</t>
+          <t>2026-08-18T11:09:17.449+07:00</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:41</t>
+          <t>2026-09-28 12:24:48</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios 18 AI PH18-I71-91UX (Ultra 9-290HX Plus/ RTX 5080 16GB/ 64GB/ 3TB/ 18" 2K+ Mini LED 250Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407VA-LY147W (Core 5-210H/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>179990000</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>181990000</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>-1%</t>
-        </is>
-      </c>
+        <v>34990000</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 3072 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 18 inch | Độ phân giải: 2K+ (2560x1600)</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-18-ai-ph18-i71-91ux-ultra-9-290hx-rtx-5080-16gb-16gb-3tb-18-2k-mini-led-250hz</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407va-ly147w-core-5-210h-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T13:30:49.416+07:00</t>
+          <t>2026-08-18T11:42:14.925+07:00</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:46</t>
+          <t>2026-09-28 12:24:53</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios 18 PH18-I71-975R (Ultra 9-290HX Plus/ RTX 5090 24GB/ 64GB/ 3TB/ 18" WQUXGA 4K IPS Mini LED 120Hz/ Win 11)</t>
+          <t>Laptop ASUS VivoBook S14 S3407CA-SF913W (Ultra 5-225H/ 16GB/ 512GB/ 14" OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>249990000</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
+        <v>27890000</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>29990000</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 3072 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 18 inch | Độ phân giải: UHD+ (3840x2400) | Tần số quét: 120 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-18-ai-ph18-i71-975r-ultra-9-290hx-rtx-5090-24gb-64gb-3tb-18-4k-mini-led-120hz</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s14-s3407ca-sf913w-ultra-5-225h-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:37:36.896+07:00</t>
+          <t>2026-09-26T13:01:54.572+07:00</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:51</t>
+          <t>2026-09-28 12:24:58</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo PHN16-I71-9779 (Ultra 9-290HX Plus/ RTX 5070 8GB/ 64GB/ 2TB/ 16" WQXGA IPS 180Hz/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UM3406GA-QD075W (Ryzen 7/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>109990000</v>
+        <v>39990000</v>
       </c>
       <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-ai-phn16-i71-9779-ultra-9-290hx-rtx-5070-8gb-64gb-2tb-16-2k-ips-180hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ga-qd075w-ryzen-7-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:35:07.531+07:00</t>
+          <t>2026-08-17T16:03:07.024+07:00</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:56</t>
+          <t>2026-09-28 12:25:03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo PHN16-I71-97VK (Ultra 9-290HX Plus/ RTX 5080 16GB/ 32GB/ 512GB/ 16" WQAGA 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1531W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED)</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>104990000</v>
+        <v>42990000</v>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-ai-phn16-i71-97vk-ultra-9-290hx-rtx-5080-16gb-16gb-512gb-16-2k-ips-240hz</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1531w-ultra-9-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:33:09.575+07:00</t>
+          <t>2026-08-18T08:45:55.514+07:00</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:01</t>
+          <t>2026-09-28 12:25:08</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-91K5 (I9-14900HX/ RTX 5070 8GB/ 32GB/ 1TB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1713W (Ultra 5-225H/ 16GB/ 512GB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>89990000</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr"/>
-      <c r="D27" s="2" t="inlineStr"/>
+        <v>30990000</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>38990000</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>-21%</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-91k5-i9-14900hx-rtx-5070-8gb-32gb-1tb-16-2k-ips-180hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1713w-ultra-5-225h-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T13:27:14.879+07:00</t>
+          <t>2026-09-25T10:16:16.703+07:00</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:06</t>
+          <t>2026-09-28 12:25:13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST630W (Ultra 7-255H/ 16GB/ 512GB/ 14" 3K OLED)</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>114990000</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>129900000</v>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
-      </c>
+        <v>40990000</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st630w-ultra-7-255h-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17T10:38:12.773+07:00</t>
+          <t>2026-08-17T15:05:39.807+07:00</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:11</t>
+          <t>2026-09-28 12:25:18</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 512GB/ 16" 2K+ OLED 165Hz/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3407NA-QD132WS (Snapdragon X2 Elite X2E-88-100/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>75990000</v>
+        <v>48990000</v>
       </c>
       <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd132ws-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:32:07.247+07:00</t>
+          <t>2026-08-24T11:47:13.916+07:00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:16</t>
+          <t>2026-09-28 12:25:23</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 32GB/ 512GB/ 16" 2K+ OLED 165Hz/ Win 11)</t>
+          <t>Laptop ASUS Zenbook A14 UX3407NA-QD254W (Snapdragon X2 Elite X2E-88-100/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>72990000</v>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>80290000</v>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
+        <v>63990000</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd254w-32gb-1tb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:31:06.752+07:00</t>
+          <t>2026-08-24T11:46:55.101+07:00</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:21</t>
+          <t>2026-09-28 12:25:28</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070 8GB/ 32GB/ 2TB/ 14.5" 2.8K+/ Win 11)</t>
+          <t>Laptop ASUS Zenbook A16 UX3607OA-SQ137WS (Snapdragon X2 Elite Extreme X2E94100/ 24GB/ 512GB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>93990000</v>
+        <v>58990000</v>
       </c>
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo gaming Acer Predator Robust PBG470 (trị giá 3.500.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 14.5 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 16 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 24 GB</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-16-ux3607oa-sq137ws-24gb-512gb-16-3k-oled</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:43:12.906+07:00</t>
+          <t>2026-08-24T11:43:18.337+07:00</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:26</t>
+          <t>2026-09-28 12:25:33</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Triton Neo 16 PTN16-51-78JQ (Ultra 7-155H/ RTX 4060/ 32GB/ 2TB/ 16.0" 2.5K/ Win 11)</t>
+          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN138WS (Ultra X9/ 32GB/ 1TB/ 14" 3K OLED Touch 144Hz)</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>49990000</v>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>52490000</v>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
+        <v>89990000</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 4060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-neo-16-ptn16-51-78jq</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn138ws-ultra-x9-32gb-1tb-14-3k-oled-touch-144hz</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T16:42:43.256+07:00</t>
+          <t>2026-08-17T12:04:03.945+07:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:31</t>
+          <t>2026-09-28 12:25:38</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN439WS (Ultra X7/ 32GB/ 512GB/ 14" 3K OLED Touch 144Hz)</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>27540000</v>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>30300000</v>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
+        <v>82990000</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn439ws-ultra-x7-32gb-512gb-14-3k-oled-touch-144hz</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12T11:35:32.312+07:00</t>
+          <t>2026-08-17T11:44:06.982+07:00</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:36</t>
+          <t>2026-09-28 12:25:43</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G G614PH-RV176W (Ryzen 9/ RTX 5050/ 16GB/ 512GB/ 16" FHD/ Win 11)</t>
+          <t>Laptop ASUS ProArt PX13 HN7306EA-LX050W (Ryzen AI Max+ 395/ 32GB/ 1TB/ 13.3" 3K OLED Touch)</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>49990000</v>
+        <v>76990000</v>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr"/>
@@ -1851,42 +1767,36 @@
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 13.3 inch | Dòng CPU: Ryzen AI MAX+ | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g-g614ph-rv176w-ryzen-9-rtx-5050-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-pro-art-hn7306ea-lx050w-ryzen-ai-max-395-32gb-1tb-13-3-3k-oled-touch</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:47:04.096+07:00</t>
+          <t>2026-09-24T15:58:08.111+07:00</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:41</t>
+          <t>2026-09-28 12:25:48</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G16 G614PH-S5101W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Zenbook S 14 UX5406AA-SU348W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED Touch)</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>47490000</v>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>53990000</v>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>50990000</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -1895,33 +1805,33 @@
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-s5101w</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-s-14-ux5406aa-su348w-ultra-9-16gb-512gb-14-3k-oled-touch</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T11:28:04.811+07:00</t>
+          <t>2026-08-17T10:26:19.879+07:00</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:46</t>
+          <t>2026-09-28 12:25:53</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G16 G614PH-TS118W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
+          <t>Laptop ASUS Zenbook S 16 UM5606GA-SS441W (Ryzen AI 9 465/ 16GB/ 512GB/ 16" 3K OLED)</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>52990000</v>
+        <v>49490000</v>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr"/>
@@ -1933,40 +1843,40 @@
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ryzen AI 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-ts118w</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-s-15-um5606ga-ss441w-ryzen-ai-9-465-16gb-512gb-15-3k-oled</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T11:49:35.857+07:00</t>
+          <t>2026-09-24T16:22:14.948+07:00</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:51</t>
+          <t>2026-09-28 12:25:58</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G16 G614PM-TS147W (Ryzen 9-8940HX/ RTX 5060 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
+          <t>Laptop Dell 15 DC15250 - 71092480 (I7-1355U/ 16GB/ 512GB/ Win 11/ Office/ Microsoft 365)</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>54690000</v>
+        <v>25390000</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>59990000</v>
+        <v>25990000</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1977,36 +1887,42 @@
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614pm-ts147w</t>
+          <t>https://gearvn.com/products/laptop-dell-15-dc15250-71092480-i7-1355u-16gb-512gb-win-11-office-microsoft-365</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:15:11.541+07:00</t>
+          <t>2026-09-17T10:56:32.257+07:00</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:56</t>
+          <t>2026-09-28 12:26:03</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix SCAR G835LXG-TQ473W (Ultra 9-290HX Plus/ RTX 5090/ 64GB/ 2TB/ 18" Mini LED 240Hz/ Win 11)</t>
+          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I3-100U/ 8GB/ 512GB/ 15.6" FHD 120Hz/DOS) - Nhập Khẩu Chính Hãng</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>179990000</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
+        <v>14390000</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>14990000</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2015,76 +1931,86 @@
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 18 inch | Độ phân giải: UHD+ (3840x2400) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-scar-g835lxg-tq473w-ultra-9-290hx-plus-rtx-5090-64gb-2tb-18-qhd-mini-led-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i3-100u-8gb-512gb-15-6-fhd-120hz</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:58:23.481+07:00</t>
+          <t>2026-08-21T10:44:17.994+07:00</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:22:01</t>
+          <t>2026-09-28 12:26:08</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus G14 GA403WW QS136WS</t>
+          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I5-1334U/ 8GB/ 512GB/ 15.6" FHD/DOS) - Nhập Khẩu Chính Hãng</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>84990000</v>
+        <v>15990000</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>89490000</v>
+        <v>17490000</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-g14-ga403ww-qs136ws</t>
+          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i5-1334u-8gb-512gb-15-6-fhd</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08T18:04:20.593+07:00</t>
+          <t>2026-09-17T11:07:57.107+07:00</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:22:06</t>
+          <t>2026-09-28 12:26:13</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU405AR-SY016W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop Dell 16 DC16251 (I5-120U/ 8GB/ 512GB/ 16" FHD+ Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>96990000</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
+        <v>18390000</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>19990000</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2093,36 +2019,42 @@
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405ar-sy016w-ultra-9-rtx-5070-ti-32gb-1tb-14-3k-oled-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-dell-16-dc16251-i5-120u-8gb-512gb-16-fhd-touch-win-11</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:47:29.287+07:00</t>
+          <t>2026-08-12T13:45:33.424+07:00</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:22:11</t>
+          <t>2026-09-28 12:26:18</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU405AW-SY029W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop Dell DC15250-7982BLK H5YXJ (I7-1355U/ 16GB/ 1TB/ 15.6" FHD Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>119990000</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr"/>
-      <c r="D41" s="2" t="inlineStr"/>
+        <v>22990000</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2131,150 +2063,174 @@
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405aw-sy029w-ultra-9-rtx-5080-32gb-1tb-14-3k-oled-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-dell-dc15250-7982blk-h5yxj-i7-1355u-16gb-1tb-15-6-fhd-touch-win-11</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:47:45.327+07:00</t>
+          <t>2026-08-19T15:36:35.706+07:00</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:22:16</t>
+          <t>2026-09-28 12:26:23</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR115W (Ultra 7-255H/ RTX 5070/ 16GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-53RH (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>74990000</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
+        <v>29990000</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>32490000</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr115w-ultra-7-255h-rtx-5070-16gb-512gb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-53rh-core-5-210h-rtx-4050-6gb-16gb-512gb-15-6-fhd-ips-144hz</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:46:00.864+07:00</t>
+          <t>2026-09-09T10:39:56.876+07:00</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:22:21</t>
+          <t>2026-09-28 12:26:28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR141W (Ultra 7-255H/ RTX 5070/ 32GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>83990000</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr"/>
+        <v>22990000</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Card đồ họa tích hợp - Qualcomm® Adreno™ | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr141w-ultra-7-255h-rtx-5070-32gb-512gb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:46:21.05+07:00</t>
+          <t>2026-07-16T09:43:41.692+07:00</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:30</t>
+          <t>2026-09-28 12:23:12</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AR-TB027W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>99990000</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
+        <v>23990000</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>25990000</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel® ARC™ Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ar-tb027w-ultra-9-rtx-5070-ti-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:10.531+07:00</t>
+          <t>2026-07-16T15:00:45.83+07:00</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:35</t>
+          <t>2026-09-28 12:23:18</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB052WS (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M (Ultra 9-185H/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>139990000</v>
-      </c>
-      <c r="C45" s="2" t="inlineStr"/>
-      <c r="D45" s="2" t="inlineStr"/>
+        <v>29890000</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>29990000</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>-0%</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2283,284 +2239,300 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb052ws-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-16gb-512gb-14-fhd-ips-win-11</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:28.879+07:00</t>
+          <t>2026-09-25T10:22:17.071+07:00</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:40</t>
+          <t>2026-09-28 12:23:23</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB121W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>124990000</v>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr"/>
+        <v>22990000</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>25990000</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb121w-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:44.227+07:00</t>
+          <t>2026-09-11T21:08:15.03+07:00</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:45</t>
+          <t>2026-09-28 12:23:29</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AX-TB042WS (Ultra 9/ RTX 5090/ 64GB/ 2TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>169990000</v>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
-      <c r="D47" s="2" t="inlineStr"/>
+        <v>20990000</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>21990000</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: AMD Radeon 680M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ax-tb042ws-ultra-9-rtx-5090-64gb-2tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:44:50.259+07:00</t>
+          <t>2026-07-17T09:17:18.78+07:00</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:50</t>
+          <t>2026-09-28 12:23:34</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA 165Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR (Ryzen 5-3500U/ 8GB/ 512GB/ 14" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>57390000</v>
+        <v>17990000</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>58990000</v>
+        <v>19990000</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:35:45.75+07:00</t>
+          <t>2026-09-24T20:43:49.815+07:00</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:55</t>
+          <t>2026-09-28 12:23:39</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN329W (Ryzen 7-8845HS/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>27690000</v>
+        <v>22890000</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>37490000</v>
+        <v>23990000</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn329w-ryzen-7-8845hs-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:04:13.749+07:00</t>
+          <t>2026-09-24T15:44:03.513+07:00</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:00</t>
+          <t>2026-09-28 12:23:44</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN390W (Ryzen 7-155/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>28990000</v>
+        <v>24990000</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>30990000</v>
+        <v>25990000</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn390w-ryzen-7-155-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:05:26.118+07:00</t>
+          <t>2026-09-25T10:20:56.552+07:00</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:05</t>
+          <t>2026-09-28 12:23:50</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUG-RL129W (Ryzen 7-7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-76KR (Core 7-350/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>29990000</v>
+        <v>25990000</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>30990000</v>
+        <v>26990000</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr"/>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+        </is>
+      </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nug-rl129w-ryzen-7-7445hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-76kr-core-7-350-8gb-512gb</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:41:09.162+07:00</t>
+          <t>2026-09-24T15:44:29.405+07:00</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:10</t>
+          <t>2026-09-28 12:23:55</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUQ-RL007W (Ryzen 7-170/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>36290000</v>
+        <v>17990000</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>39990000</v>
+        <v>19790000</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
@@ -2569,696 +2541,738 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nuq-rl007w-ryzen-7-170-rtx-4050-6gb-16gb-512gb-16-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:10:34.588+07:00</t>
+          <t>2026-09-24T09:51:43.721+07:00</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:15</t>
+          <t>2026-09-28 12:24:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>41260000</v>
+        <v>19590000</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>45390000</v>
+        <v>21990000</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T14:06:48.719+07:00</t>
+          <t>2026-09-25T09:03:23.812+07:00</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:21</t>
+          <t>2026-09-28 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA401EA-RG041W (Ryzen AI Max+ 392/ 32GB/ 512GB/ 14" 2.5K/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5-3500U/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>59990000</v>
-      </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr"/>
+        <v>16790000</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>19990000</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>-16%</t>
+        </is>
+      </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI MAX+ | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon 8060S | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401ea-rg041w-ryzen-ai-max-392-32gb-512gb-14-2-5k-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T09:33:26.048+07:00</t>
+          <t>2026-09-25T16:09:40.061+07:00</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:26</t>
+          <t>2026-09-28 12:24:10</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA401UH-RG001W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-411P-R1CM (Ryzen 5 3500U/ 8GB/ 256GB)</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>49990000</v>
-      </c>
-      <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="inlineStr"/>
+        <v>17990000</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>18990000</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401uh-rg001w-ryzen-7-260-rtx-5050-16gb-512gb-14-qhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r1cm-ryzen-5-3500u-8gb-256gb</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:59:55.007+07:00</t>
+          <t>2026-07-06T14:26:56.746+07:00</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:31</t>
+          <t>2026-09-28 12:24:15</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA401UM-RG049W (Ryzen 7 260/ RTX 5060/ 32GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-411P-R7YP (Ryzen 3 3200U/ 8GB/ 256GB)</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>64990000</v>
-      </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr"/>
+        <v>15990000</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>16990000</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 3 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401um-rg049w-ryzen-7-260-rtx-5060-32gb-512gb-14-qhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r7yp-ryzen-3-3200u-8gb-256gb</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T13:00:47.55+07:00</t>
+          <t>2026-07-06T14:48:50.246+07:00</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:36</t>
+          <t>2026-09-28 12:24:20</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA608UHI-TU121W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-49P-R6XX (Ryzen 5 7430U/ 8GB/ 512GB/15.6"/ Win 11)</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>48990000</v>
-      </c>
-      <c r="C57" s="2" t="inlineStr"/>
-      <c r="D57" s="2" t="inlineStr"/>
+        <v>18590000</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>20990000</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608uhi-tu121w-ryzen-7-260-rtx-5050-16gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-49p-r6xx-ryzen-5-7430u-8gb-512gb-15-6-win-11</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T11:22:30.725+07:00</t>
+          <t>2026-08-21T13:56:25.879+07:00</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:41</t>
+          <t>2026-09-28 12:24:25</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA608UMI-TU162W (Ryzen 7 260/ RTX 5060/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>51990000</v>
-      </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr"/>
+        <v>18890000</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>24990000</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>-24%</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608umi-tu162w-ryzen-7-260-rtx-5060-16gb-512gb-16-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T11:01:50.971+07:00</t>
+          <t>2026-08-24T10:45:08.009+07:00</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:46</t>
+          <t>2026-09-28 12:24:30</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS V16 V3607VJ-TK189W (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 16" WUXGA 144Hz/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>26490000</v>
+        <v>24990000</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>29990000</v>
+        <v>27990000</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel® Arc™ Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-v16-v3607vj-tk189w-core-5-210h-rtx-3050-6gb-16gb-512gb-16-wuxga-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T16:26:14.526+07:00</t>
+          <t>2026-07-16T15:19:10.843+07:00</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:51</t>
+          <t>2026-09-28 12:24:35</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF (Core 3-304/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>28790000</v>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>30790000</v>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>21990000</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-34nf-core-3-304-12gb-512gb-14-fhd-ips-120hz-win-11</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T11:00:26.909+07:00</t>
+          <t>2026-09-23T13:32:07.536+07:00</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:56</t>
+          <t>2026-09-28 12:24:40</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming GIGABYTE A16 CVHI3MY893SH (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV (Core 5-320/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>36990000</v>
+        <v>23490000</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>38990000</v>
+        <v>24990000</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3my893sh</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-52bv-core-5-320-12gb-512gb-14-wuxga-ips-120hz-win-11</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T14:40:23.197+07:00</t>
+          <t>2026-09-25T16:09:22.19+07:00</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:01</t>
+          <t>2026-09-28 12:24:45</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop GIGABYTE Gaming A16 CVHI3VN893SH (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>38990000</v>
+        <v>28990000</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>39990000</v>
+        <v>30990000</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+          <t>-6%</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 3 | Dung lượng RAM: 8 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon RX 6500M | Kích thước màn hình: 16 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:10:12.472+07:00</t>
+          <t>2026-09-25T16:07:37.902+07:00</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:06</t>
+          <t>2026-09-28 12:24:50</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 A16-3THK3VN893SH (Ryzen 7 260/ RTX 5050 8GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>35990000</v>
+        <v>49990000</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>40990000</v>
+        <v>54990000</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel® Arc™ B390 GPU (đồ họa tích hợp) | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-ga63h-3thk3vn893sh</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30T09:54:12.234+07:00</t>
+          <t>2026-08-28T15:51:47.551+07:00</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:11</t>
+          <t>2026-09-28 12:24:55</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9LJR2VNF93SH (Ryzen 5 7533HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop Acer Swift Go AI OLED SFG14-75-765M (Ultra 7-258V/ 32GB/ 512GB/ 14" FHD+ OLED/ Win11)</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>29990000</v>
+        <v>39990000</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>30990000</v>
+        <v>40990000</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel® Arc™ Graphics 140V | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9ljr2vnf93sh-ryzen-5-7533hs-rtx-3050-6gb-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-ai-oled-sfg14-75-765m-14-fhd-oled-u7-258v-32lp-512gb-win</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T15:10:54.55+07:00</t>
+          <t>2026-08-14T10:47:31.44+07:00</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:16</t>
+          <t>2026-09-28 12:25:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9MJR2VNF93SH (Ryzen 5 7533HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>34990000</v>
+        <v>32999000</v>
       </c>
       <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9mjr2vnf93sh-ryzen-5-7533hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:50:39.975+07:00</t>
+          <t>2026-09-15T14:38:31.288+07:00</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:21</t>
+          <t>2026-09-28 12:25:05</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CTHH3VN893SH (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>33990000</v>
+        <v>31490000</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>36990000</v>
+        <v>32490000</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr"/>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel® Arc™ 130T Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-gaming-a16-cthh3vn893sh</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:59.097+07:00</t>
+          <t>2026-09-24T14:08:34.772+07:00</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:26</t>
+          <t>2026-09-28 12:25:10</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
+          <t>Laptop Acer Swift X SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" 2.8K OLED/ Win 11/ Office)</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>115990000</v>
+        <v>35990000</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>117990000</v>
+        <v>45990000</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6 | Kích thước màn hình: 14.5 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05T14:44:14.658+07:00</t>
+          <t>2026-09-14T15:56:38.644+07:00</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:31</t>
+          <t>2026-09-28 12:25:15</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15AHP11 83TN0040VN (Ryzen 7-250/ RTX 5050 8GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
+          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
         <v>43990000</v>
       </c>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="n">
+        <v>49490000</v>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: RTX 4060 | Kích thước màn hình: 14.5 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15ahp11-83tn0040vn-ryzen-7-250-rtx-5050-8gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T09:36:14.406+07:00</t>
+          <t>2026-07-03T15:10:56.836+07:00</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:36</t>
+          <t>2026-09-28 12:25:20</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H08-50W (Core 5-210H/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>38990000</v>
+        <v>19490000</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>41990000</v>
+        <v>21990000</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3269,40 +3283,40 @@
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h08-50w</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:38.199+07:00</t>
+          <t>2026-07-31T11:09:14.14+07:00</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:41</t>
+          <t>2026-09-28 12:25:25</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S0006RVN (Ryzen 7-7735HS/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1 P1403CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>30990000</v>
+        <v>24290000</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>32990000</v>
+        <v>26990000</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3313,74 +3327,82 @@
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0006rvn-ryzen-7-7735hs-rtx-3050-6gb-16gb-1tb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h16-63ws-core-5-210h-16gb-512gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T11:31:57.635+07:00</t>
+          <t>2026-08-03T15:06:02.246+07:00</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:46</t>
+          <t>2026-09-28 12:25:30</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S000DCVN (Ryzen 7-170/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1 P1403CVA-C7H16-50W (Core 7-240H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>32990000</v>
-      </c>
-      <c r="C71" s="2" t="inlineStr"/>
-      <c r="D71" s="2" t="inlineStr"/>
+        <v>28990000</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
-        </is>
-      </c>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s000dcvn-ryzen-7-170-rtx-3050-6gb-16gb-1tb-15-6-fhd-ips-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c7h16-50w-core-7-240h-16gb-512gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T10:03:17.431+07:00</t>
+          <t>2026-08-03T14:43:57.168+07:00</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:51</t>
+          <t>2026-09-28 12:25:35</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003VVN (Core 5-205H/ RTX 3050 6GB/ 8GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1 P1503CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>36990000</v>
-      </c>
-      <c r="C72" s="2" t="inlineStr"/>
-      <c r="D72" s="2" t="inlineStr"/>
+        <v>24290000</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>26990000</v>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3389,36 +3411,42 @@
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 8 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003vvn-core-5-205h-rtx-3050-6gb-8gb-512gb-15-3-wuxga-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1503cva-c5h16-63ws-core-5-210h-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T19:41:42.305+07:00</t>
+          <t>2026-08-03T14:03:33.213+07:00</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:56</t>
+          <t>2026-09-28 12:25:40</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003WVN (Core 5-205H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1 P1403CVA-C3U08-50W (Core 3-100U/ 8GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>41990000</v>
-      </c>
-      <c r="C73" s="2" t="inlineStr"/>
-      <c r="D73" s="2" t="inlineStr"/>
+        <v>15490000</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>17990000</v>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3427,40 +3455,40 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200)</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003wvn-core-5-205h-rtx-3050-6gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c3u08-50w</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T16:50:55.152+07:00</t>
+          <t>2026-07-31T13:53:40.042+07:00</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:01</t>
+          <t>2026-09-28 12:25:45</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRX10 83JE01AGVN (I7-13645HX/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>39490000</v>
+        <v>23390000</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>40990000</v>
+        <v>27990000</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3471,40 +3499,40 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx10-83je01agvn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T16:43:38.321+07:00</t>
+          <t>2026-08-12T10:19:47.487+07:00</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:06</t>
+          <t>2026-09-28 12:25:50</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U516S8W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>43990000</v>
+        <v>26390000</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>45990000</v>
+        <v>29990000</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3515,74 +3543,82 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u516s8w-ultra-5-225h-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T16:32:05.969+07:00</t>
+          <t>2026-08-03T11:57:56.626+07:00</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:11</t>
+          <t>2026-09-28 12:25:55</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U716S8W (Ultra 7-255H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>33990000</v>
-      </c>
-      <c r="C76" s="2" t="inlineStr"/>
-      <c r="D76" s="2" t="inlineStr"/>
+        <v>32990000</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>34990000</v>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
-        </is>
-      </c>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u716s8w-ultra-7-255h-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:23:00.628+07:00</t>
+          <t>2026-09-06T13:46:08.673+07:00</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:16</t>
+          <t>2026-09-28 12:26:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA / Win 11)</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>31990000</v>
-      </c>
-      <c r="C77" s="2" t="inlineStr"/>
-      <c r="D77" s="2" t="inlineStr"/>
+        <v>26390000</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>30490000</v>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3591,40 +3627,40 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:25:26.316+07:00</t>
+          <t>2026-09-03T11:54:54.747+07:00</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:21</t>
+          <t>2026-09-28 12:26:06</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>34990000</v>
+        <v>32990000</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>35990000</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3633,118 +3669,118 @@
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
-        </is>
-      </c>
+      <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:28:01.415+07:00</t>
+          <t>2026-09-23T08:56:23.461+07:00</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:26</t>
+          <t>2026-09-28 12:26:11</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Max C13WF-421VN (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 G2 P5405CAA-NZ0223W (Ultra 7-356H/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>44990000</v>
-      </c>
-      <c r="C79" s="2" t="inlineStr"/>
-      <c r="D79" s="2" t="inlineStr"/>
+        <v>39190000</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>41990000</v>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
-        </is>
-      </c>
+      <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13vf-421vn-i7-13620h-rtx-5060-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-g2-p5405caa-nz0223w-ultra-7-356h-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T16:26:05.15+07:00</t>
+          <t>2026-08-03T11:12:45.933+07:00</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:31</t>
+          <t>2026-09-28 12:26:16</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Max C13WE-422VN (I7-13620H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0016W (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>42990000</v>
-      </c>
-      <c r="C80" s="2" t="inlineStr"/>
-      <c r="D80" s="2" t="inlineStr"/>
+        <v>28790000</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
-        </is>
-      </c>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn-i7-13620h-rtx-5050-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0016w-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:38:57.001+07:00</t>
+          <t>2026-08-03T10:54:41.9+07:00</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:36</t>
+          <t>2026-09-28 12:26:21</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0017W (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>34890000</v>
+        <v>36290000</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>35990000</v>
+        <v>38990000</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3755,80 +3791,84 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: Arc | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0017w-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T14:54:13.66+07:00</t>
+          <t>2026-09-10T13:51:05.888+07:00</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:41</t>
+          <t>2026-09-28 12:26:26</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0442WS (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>48490000</v>
+        <v>37190000</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>52990000</v>
+        <v>39990000</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: QHD (2560x1440) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Arc 140V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0442ws-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T14:49:48.046+07:00</t>
+          <t>2026-08-03T09:55:42.594+07:00</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:45</t>
+          <t>2026-09-28 12:26:31</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0450WS (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>79990000</v>
+        <v>29790000</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>80990000</v>
+        <v>31990000</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3839,33 +3879,33 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Arc 130V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0450ws-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:43:38.331+07:00</t>
+          <t>2026-08-03T09:56:18.911+07:00</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:51</t>
+          <t>2026-09-28 12:26:36</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR141W (Ultra 7-255H/ RTX 5070/ 32GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>199990000</v>
+        <v>83990000</v>
       </c>
       <c r="C84" s="2" t="inlineStr"/>
       <c r="D84" s="2" t="inlineStr"/>
@@ -3877,33 +3917,33 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr141w-ultra-7-255h-rtx-5070-32gb-512gb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T11:12:30.954+07:00</t>
+          <t>2026-09-06T15:46:21.05+07:00</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:36</t>
+          <t>2026-09-28 12:23:12</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB027W (Core 3/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AR-TB027W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>22990000</v>
+        <v>99990000</v>
       </c>
       <c r="C85" s="2" t="inlineStr"/>
       <c r="D85" s="2" t="inlineStr"/>
@@ -3915,33 +3955,33 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb027w-core-3-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ar-tb027w-ultra-9-rtx-5070-ti-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:52:41.33+07:00</t>
+          <t>2026-09-06T15:45:10.531+07:00</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:41</t>
+          <t>2026-09-28 12:23:17</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB029W (Core 7/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB052WS (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>35490000</v>
+        <v>139990000</v>
       </c>
       <c r="C86" s="2" t="inlineStr"/>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3953,33 +3993,33 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb029w-core-7-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb052ws-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T15:05:22.575+07:00</t>
+          <t>2026-09-06T15:45:28.879+07:00</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:47</t>
+          <t>2026-09-28 12:23:23</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB220W (Core 7/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB121W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>30490000</v>
+        <v>124990000</v>
       </c>
       <c r="C87" s="2" t="inlineStr"/>
       <c r="D87" s="2" t="inlineStr"/>
@@ -3991,42 +4031,36 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb220w-core-7-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb121w-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:43:31.989+07:00</t>
+          <t>2026-09-06T15:45:44.227+07:00</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:52</t>
+          <t>2026-09-28 12:23:28</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1404V (Core 5-120U/ 8GB/ 256GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AX-TB042WS (Ultra 9/ RTX 5090/ 64GB/ 2TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>16590000</v>
-      </c>
-      <c r="C88" s="2" t="n">
-        <v>18990000</v>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>-13%</t>
-        </is>
-      </c>
+        <v>169990000</v>
+      </c>
+      <c r="C88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4035,36 +4069,42 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404v-core-5-120u-8gb-256gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ax-tb042ws-ultra-9-rtx-5090-64gb-2tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T13:41:37.603+07:00</t>
+          <t>2026-09-06T15:44:50.259+07:00</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:57</t>
+          <t>2026-09-28 12:23:33</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VA-EB355W (Core 7-150U/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming ASUS TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="C89" s="2" t="inlineStr"/>
-      <c r="D89" s="2" t="inlineStr"/>
+        <v>57390000</v>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>58990000</v>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4073,36 +4113,42 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen AI 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb355w-core-7-150u-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:17:32.016+07:00</t>
+          <t>2026-09-14T17:35:45.75+07:00</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:02</t>
+          <t>2026-09-28 12:23:38</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VA-EB609W (Core 3-100U/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN329W (Ryzen 7-8845HS/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>21990000</v>
-      </c>
-      <c r="C90" s="2" t="inlineStr"/>
-      <c r="D90" s="2" t="inlineStr"/>
+        <v>27690000</v>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>37490000</v>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>-26%</t>
+        </is>
+      </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4111,36 +4157,36 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb609w-core-3-100u-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn329w-ryzen-7-8845hs-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:33:25.424+07:00</t>
+          <t>2026-09-17T11:04:13.749+07:00</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:07</t>
+          <t>2026-09-28 12:23:43</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VAP-V14.C58256 (Core 5-120U/ 16GB/ 256GB/ 14" FHD IPS/ Win 11/ Quiet Blue)</t>
+          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN390W (Ryzen 7-155/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>17890000</v>
+        <v>28990000</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>18990000</v>
+        <v>30990000</v>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
@@ -4155,80 +4201,82 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404vap-v14-c58256-core-5-120u-8gb-256gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn390w-ryzen-7-155-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:42:34.369+07:00</t>
+          <t>2026-09-17T11:05:26.118+07:00</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:12</t>
+          <t>2026-09-28 12:23:48</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus VivoBook 14 X1407AA-LY360W (Ultra 5-325/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUG-RL129W (Ryzen 7-7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>26490000</v>
+        <v>29990000</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>26990000</v>
+        <v>30990000</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407aa-ly360w-ultra-5-325-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nug-rl129w-ryzen-7-7445hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T15:46:33.275+07:00</t>
+          <t>2026-09-14T17:41:09.162+07:00</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:17</t>
+          <t>2026-09-28 12:23:53</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1407CA-LY203W (Ultra 5-225H/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUQ-RL007W (Ryzen 7-170/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>33490000</v>
-      </c>
-      <c r="C93" s="2" t="inlineStr"/>
-      <c r="D93" s="2" t="inlineStr"/>
+        <v>36290000</v>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4237,36 +4285,42 @@
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407ca-ly203w-ultra-5-225h-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nuq-rl007w-ryzen-7-170-rtx-4050-6gb-16gb-512gb-16-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T10:22:08.041+07:00</t>
+          <t>2026-09-25T10:10:34.588+07:00</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:22</t>
+          <t>2026-09-28 12:23:58</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504MA-BQ632W (Core 5-320/ 8GB/ 512GB/ 15" FHD IPS)</t>
+          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>26990000</v>
-      </c>
-      <c r="C94" s="2" t="inlineStr"/>
-      <c r="D94" s="2" t="inlineStr"/>
+        <v>41260000</v>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>45390000</v>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4275,33 +4329,33 @@
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq632w-core-5-320-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T15:43:54.381+07:00</t>
+          <t>2026-06-30T14:06:48.719+07:00</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:27</t>
+          <t>2026-09-28 12:24:03</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504MA-BQ633W (Core 7-350/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA401EA-RG041W (Ryzen AI Max+ 392/ 32GB/ 512GB/ 14" 2.5K/ Win 11)</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>30490000</v>
+        <v>59990000</v>
       </c>
       <c r="C95" s="2" t="inlineStr"/>
       <c r="D95" s="2" t="inlineStr"/>
@@ -4313,33 +4367,33 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen AI MAX+ | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon 8060S | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq633w-core-7-350-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401ea-rg041w-ryzen-ai-max-392-32gb-512gb-14-2-5k-win-11</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:47:34.397+07:00</t>
+          <t>2026-08-14T09:33:26.048+07:00</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:32</t>
+          <t>2026-09-28 12:24:08</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504VA-BQ165W (Core 5-120U/ 8GB/ 512GB/ 15" FHD IPS)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA401UH-RG001W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>20990000</v>
+        <v>49990000</v>
       </c>
       <c r="C96" s="2" t="inlineStr"/>
       <c r="D96" s="2" t="inlineStr"/>
@@ -4351,73 +4405,71 @@
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504va-bq165w-core-5-120u-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401uh-rg001w-ryzen-7-260-rtx-5050-16gb-512gb-14-qhd-win-11</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:12:00.028+07:00</t>
+          <t>2026-09-26T12:59:55.007+07:00</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:37</t>
+          <t>2026-09-28 12:24:13</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 16 X1605VA-MB1826W (I3-1315U/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA401UM-RG049W (Ryzen 7 260/ RTX 5060/ 32GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>15390000</v>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v>15990000</v>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr"/>
+        <v>64990000</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr"/>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 16 inch | Dòng CPU: i3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1605va-mb1826w-i3-1315u-8gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401um-rg049w-ryzen-7-260-rtx-5060-32gb-512gb-14-qhd-win-11</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T10:45:38.083+07:00</t>
+          <t>2026-09-26T13:00:47.55+07:00</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:42</t>
+          <t>2026-09-28 12:24:18</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 16 X1607CA-MB387W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD IPS)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA608UHI-TU121W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>33490000</v>
+        <v>48990000</v>
       </c>
       <c r="C98" s="2" t="inlineStr"/>
       <c r="D98" s="2" t="inlineStr"/>
@@ -4429,33 +4481,33 @@
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb387w-ultra-5-225h-16gb-512gb-16-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608uhi-tu121w-ryzen-7-260-rtx-5050-16gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T16:08:06.906+07:00</t>
+          <t>2026-08-14T11:22:30.725+07:00</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:47</t>
+          <t>2026-09-28 12:24:23</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 16 X1607CA-MB399W (Ultra 7-255H/ 16GB/ 512GB/ 16" FHD IPS)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA608UMI-TU162W (Ryzen 7 260/ RTX 5060/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>36490000</v>
+        <v>51990000</v>
       </c>
       <c r="C99" s="2" t="inlineStr"/>
       <c r="D99" s="2" t="inlineStr"/>
@@ -4467,36 +4519,42 @@
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb399w-ultra-7-255h-16gb-512gb-16-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608umi-tu162w-ryzen-7-260-rtx-5060-16gb-512gb-16-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T15:36:19.591+07:00</t>
+          <t>2026-08-14T11:01:50.971+07:00</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:52</t>
+          <t>2026-09-28 12:24:28</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Flip TP3407AA-SG029W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop gaming ASUS V16 V3607VJ-TK189W (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 16" WUXGA 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>41990000</v>
-      </c>
-      <c r="C100" s="2" t="inlineStr"/>
-      <c r="D100" s="2" t="inlineStr"/>
+        <v>26490000</v>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>29990000</v>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4505,308 +4563,332 @@
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-flip-tp3407aa-sg029w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-v16-v3607vj-tk189w-core-5-210h-rtx-3050-6gb-16gb-512gb-16-wuxga-144hz-win-11</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T14:55:40.249+07:00</t>
+          <t>2026-09-15T16:26:14.526+07:00</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:57</t>
+          <t>2026-09-28 12:24:33</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ4821W (Ryzen 5/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>22990000</v>
-      </c>
-      <c r="C101" s="2" t="inlineStr"/>
-      <c r="D101" s="2" t="inlineStr"/>
+        <v>28790000</v>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>30790000</v>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1504fa-bq4821w-ryzen-5-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:55:57.447+07:00</t>
+          <t>2026-07-01T11:00:26.909+07:00</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:02</t>
+          <t>2026-09-28 12:24:38</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ340W (Ryzen 5/ 16GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop gaming GIGABYTE A16 CVHI3MY893SH (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>28490000</v>
-      </c>
-      <c r="C102" s="2" t="inlineStr"/>
-      <c r="D102" s="2" t="inlineStr"/>
+        <v>36990000</v>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>38990000</v>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-go-15-e1504fa-bq340w-ryzen-5-16gb-512gb-156-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3my893sh</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:55:13.502+07:00</t>
+          <t>2026-08-14T14:40:23.197+07:00</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:07</t>
+          <t>2026-09-28 12:24:43</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 M3407KA-SF034W (Ryzen AI 5-330/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop GIGABYTE Gaming A16 CVHI3VN893SH (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>33990000</v>
-      </c>
-      <c r="C103" s="2" t="inlineStr"/>
-      <c r="D103" s="2" t="inlineStr"/>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>38990000</v>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 3 | Dung lượng RAM: 8 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon RX 6500M | Kích thước màn hình: 16 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-m3407ka-sf034w-ryzen-ai-5-330-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3vn893sh</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T12:02:07.653+07:00</t>
+          <t>2026-09-17T11:10:12.472+07:00</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:12</t>
+          <t>2026-09-28 12:24:48</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407AA-SF945W (Ultra 5-325/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop gaming Gigabyte A16 A16-3THK3VN893SH (Ryzen 7 260/ RTX 5050 8GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>37490000</v>
-      </c>
-      <c r="C104" s="2" t="inlineStr"/>
-      <c r="D104" s="2" t="inlineStr"/>
+        <v>35990000</v>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>40990000</v>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf945w-ultra-5-325-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-ga63h-3thk3vn893sh</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T11:09:17.449+07:00</t>
+          <t>2026-07-30T09:54:12.234+07:00</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:17</t>
+          <t>2026-09-28 12:24:53</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407VA-LY147W (Core 5-210H/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9LJR2VNF93SH (Ryzen 5 7533HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="C105" s="2" t="inlineStr"/>
-      <c r="D105" s="2" t="inlineStr"/>
+        <v>29990000</v>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407va-ly147w-core-5-210h-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9ljr2vnf93sh-ryzen-5-7533hs-rtx-3050-6gb-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T11:42:14.925+07:00</t>
+          <t>2026-07-31T15:10:54.55+07:00</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:22</t>
+          <t>2026-09-28 12:24:58</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS VivoBook S14 S3407CA-SF913W (Ultra 5-225H/ 16GB/ 512GB/ 14" OLED/ Win 11)</t>
+          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9MJR2VNF93SH (Ryzen 5 7533HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>27890000</v>
-      </c>
-      <c r="C106" s="2" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>34990000</v>
+      </c>
+      <c r="C106" s="2" t="inlineStr"/>
+      <c r="D106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s14-s3407ca-sf913w-ultra-5-225h-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9mjr2vnf93sh-ryzen-5-7533hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T13:01:54.572+07:00</t>
+          <t>2026-09-18T13:50:39.975+07:00</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:27</t>
+          <t>2026-09-28 12:25:03</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UM3406GA-QD075W (Ryzen 7/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop gaming Gigabyte A16 CTHH3VN893SH (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="C107" s="2" t="inlineStr"/>
-      <c r="D107" s="2" t="inlineStr"/>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>33990000</v>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>36990000</v>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ga-qd075w-ryzen-7-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-gaming-a16-cthh3vn893sh</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T16:03:07.024+07:00</t>
+          <t>2026-09-18T13:35:59.097+07:00</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:32</t>
+          <t>2026-09-28 12:25:08</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1531W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED)</t>
+          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>42990000</v>
-      </c>
-      <c r="C108" s="2" t="inlineStr"/>
-      <c r="D108" s="2" t="inlineStr"/>
+        <v>115990000</v>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>117990000</v>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4815,42 +4897,36 @@
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1531w-ultra-9-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T08:45:55.514+07:00</t>
+          <t>2026-07-05T14:44:14.658+07:00</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:37</t>
+          <t>2026-09-28 12:25:13</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1713W (Ultra 5-225H/ 16GB/ 512GB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15AHP11 83TN0040VN (Ryzen 7-250/ RTX 5050 8GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="C109" s="2" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>-21%</t>
-        </is>
-      </c>
+        <v>43990000</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr"/>
+      <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4859,36 +4935,42 @@
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1713w-ultra-5-225h-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15ahp11-83tn0040vn-ryzen-7-250-rtx-5050-8gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:16:16.703+07:00</t>
+          <t>2026-09-21T09:36:14.406+07:00</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:42</t>
+          <t>2026-09-28 12:25:18</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST630W (Ultra 7-255H/ 16GB/ 512GB/ 14" 3K OLED)</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="C110" s="2" t="inlineStr"/>
-      <c r="D110" s="2" t="inlineStr"/>
+        <v>38990000</v>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>41990000</v>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4897,36 +4979,42 @@
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st630w-ultra-7-255h-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T15:05:39.807+07:00</t>
+          <t>2026-07-15T09:36:38.199+07:00</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:47</t>
+          <t>2026-09-28 12:25:23</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3407NA-QD132WS (Snapdragon X2 Elite X2E-88-100/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S0006RVN (Ryzen 7-7735HS/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>48990000</v>
-      </c>
-      <c r="C111" s="2" t="inlineStr"/>
-      <c r="D111" s="2" t="inlineStr"/>
+        <v>30990000</v>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>32990000</v>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4935,33 +5023,33 @@
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd132ws-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0006rvn-ryzen-7-7735hs-rtx-3050-6gb-16gb-1tb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:47:13.916+07:00</t>
+          <t>2026-09-22T11:31:57.635+07:00</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:52</t>
+          <t>2026-09-28 12:25:28</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook A14 UX3407NA-QD254W (Snapdragon X2 Elite X2E-88-100/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S000DCVN (Ryzen 7-170/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>63990000</v>
+        <v>32990000</v>
       </c>
       <c r="C112" s="2" t="inlineStr"/>
       <c r="D112" s="2" t="inlineStr"/>
@@ -4973,33 +5061,33 @@
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd254w-32gb-1tb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s000dcvn-ryzen-7-170-rtx-3050-6gb-16gb-1tb-15-6-fhd-ips-win-11</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:46:55.101+07:00</t>
+          <t>2026-09-21T10:03:17.431+07:00</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:57</t>
+          <t>2026-09-28 12:25:33</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook A16 UX3607OA-SQ137WS (Snapdragon X2 Elite Extreme X2E94100/ 24GB/ 512GB/ 16" 3K OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003VVN (Core 5-205H/ RTX 3050 6GB/ 8GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>58990000</v>
+        <v>36990000</v>
       </c>
       <c r="C113" s="2" t="inlineStr"/>
       <c r="D113" s="2" t="inlineStr"/>
@@ -5011,33 +5099,33 @@
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 16 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 24 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 8 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-16-ux3607oa-sq137ws-24gb-512gb-16-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003vvn-core-5-205h-rtx-3050-6gb-8gb-512gb-15-3-wuxga-165hz-win-11</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:43:18.337+07:00</t>
+          <t>2026-08-12T19:41:42.305+07:00</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:02</t>
+          <t>2026-09-28 12:25:38</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN138WS (Ultra X9/ 32GB/ 1TB/ 14" 3K OLED Touch 144Hz)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003WVN (Core 5-205H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>89990000</v>
+        <v>41990000</v>
       </c>
       <c r="C114" s="2" t="inlineStr"/>
       <c r="D114" s="2" t="inlineStr"/>
@@ -5049,36 +5137,42 @@
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200)</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn138ws-ultra-x9-32gb-1tb-14-3k-oled-touch-144hz</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003wvn-core-5-205h-rtx-3050-6gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T12:04:03.945+07:00</t>
+          <t>2026-08-12T16:50:55.152+07:00</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:07</t>
+          <t>2026-09-28 12:25:43</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN439WS (Ultra X7/ 32GB/ 512GB/ 14" 3K OLED Touch 144Hz)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX10 83JE01AGVN (I7-13645HX/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>82990000</v>
-      </c>
-      <c r="C115" s="2" t="inlineStr"/>
-      <c r="D115" s="2" t="inlineStr"/>
+        <v>39490000</v>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>40990000</v>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5087,36 +5181,42 @@
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn439ws-ultra-x7-32gb-512gb-14-3k-oled-touch-144hz</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx10-83je01agvn</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T11:44:06.982+07:00</t>
+          <t>2026-09-19T16:43:38.321+07:00</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:12</t>
+          <t>2026-09-28 12:25:48</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ProArt PX13 HN7306EA-LX050W (Ryzen AI Max+ 395/ 32GB/ 1TB/ 13.3" 3K OLED Touch)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>76990000</v>
-      </c>
-      <c r="C116" s="2" t="inlineStr"/>
-      <c r="D116" s="2" t="inlineStr"/>
+        <v>43990000</v>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>45990000</v>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5125,33 +5225,33 @@
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 13.3 inch | Dòng CPU: Ryzen AI MAX+ | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-pro-art-hn7306ea-lx050w-ryzen-ai-max-395-32gb-1tb-13-3-3k-oled-touch</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:58:08.111+07:00</t>
+          <t>2026-09-18T16:32:05.969+07:00</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:17</t>
+          <t>2026-09-28 12:25:53</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook S 14 UX5406AA-SU348W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED Touch)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>50990000</v>
+        <v>33990000</v>
       </c>
       <c r="C117" s="2" t="inlineStr"/>
       <c r="D117" s="2" t="inlineStr"/>
@@ -5163,33 +5263,33 @@
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-s-14-ux5406aa-su348w-ultra-9-16gb-512gb-14-3k-oled-touch</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T10:26:19.879+07:00</t>
+          <t>2026-06-30T15:23:00.628+07:00</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:22</t>
+          <t>2026-09-28 12:25:58</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook S 16 UM5606GA-SS441W (Ryzen AI 9 465/ 16GB/ 512GB/ 16" 3K OLED)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>49490000</v>
+        <v>31990000</v>
       </c>
       <c r="C118" s="2" t="inlineStr"/>
       <c r="D118" s="2" t="inlineStr"/>
@@ -5201,40 +5301,40 @@
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ryzen AI 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-s-15-um5606ga-ss441w-ryzen-ai-9-465-16gb-512gb-15-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T16:22:14.948+07:00</t>
+          <t>2026-06-30T15:25:26.316+07:00</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:27</t>
+          <t>2026-09-28 12:26:03</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - 71092480 (I7-1355U/ 16GB/ 512GB/ Win 11/ Office/ Microsoft 365)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>25390000</v>
+        <v>34990000</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>25990000</v>
+        <v>35990000</v>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -5245,42 +5345,36 @@
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-15-dc15250-71092480-i7-1355u-16gb-512gb-win-11-office-microsoft-365</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T10:56:32.257+07:00</t>
+          <t>2026-06-30T15:28:01.415+07:00</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:32</t>
+          <t>2026-09-28 12:26:08</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I3-100U/ 8GB/ 512GB/ 15.6" FHD 120Hz/DOS) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop gaming MSI Cyborg 15 Max C13WF-421VN (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>14390000</v>
-      </c>
-      <c r="C120" s="2" t="n">
-        <v>14990000</v>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>44990000</v>
+      </c>
+      <c r="C120" s="2" t="inlineStr"/>
+      <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5289,42 +5383,36 @@
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i3-100u-8gb-512gb-15-6-fhd-120hz</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13vf-421vn-i7-13620h-rtx-5060-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T10:44:17.994+07:00</t>
+          <t>2026-09-23T16:26:05.15+07:00</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:37</t>
+          <t>2026-09-28 12:26:13</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I5-1334U/ 8GB/ 512GB/ 15.6" FHD/DOS) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop gaming MSI Cyborg 15 Max C13WE-422VN (I7-13620H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>15990000</v>
-      </c>
-      <c r="C121" s="2" t="n">
-        <v>17490000</v>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
+        <v>42990000</v>
+      </c>
+      <c r="C121" s="2" t="inlineStr"/>
+      <c r="D121" s="2" t="inlineStr"/>
       <c r="E121" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5333,40 +5421,40 @@
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i5-1334u-8gb-512gb-15-6-fhd</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn-i7-13620h-rtx-5050-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:07:57.107+07:00</t>
+          <t>2026-07-27T10:38:57.001+07:00</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:42</t>
+          <t>2026-09-28 12:26:18</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 16 DC16251 (I5-120U/ 8GB/ 512GB/ 16" FHD+ Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>18390000</v>
+        <v>34890000</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>19990000</v>
+        <v>35990000</v>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -5377,954 +5465,914 @@
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-16-dc16251-i5-120u-8gb-512gb-16-fhd-touch-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T13:45:33.424+07:00</t>
+          <t>2026-06-30T14:54:13.66+07:00</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:47</t>
+          <t>2026-09-28 12:26:23</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell DC15250-7982BLK H5YXJ (I7-1355U/ 16GB/ 1TB/ 15.6" FHD Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop gaming MSI Katana 15 HX B14WEK-027VN (I7-14650HX/ RTX 5050 8GB/ 32GB/ 512GB/ 15.6" QHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>22990000</v>
+        <v>48490000</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>23990000</v>
+        <v>52990000</v>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: QHD (2560x1440) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-dc15250-7982blk-h5yxj-i7-1355u-16gb-1tb-15-6-fhd-touch-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-hx-b14wek-027vn</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19T15:36:35.706+07:00</t>
+          <t>2026-09-10T14:49:48.046+07:00</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:52</t>
+          <t>2026-09-28 12:26:28</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-53RH (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>29990000</v>
+        <v>79990000</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>32490000</v>
+        <v>80990000</v>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-53rh-core-5-210h-rtx-4050-6gb-16gb-512gb-15-6-fhd-ips-144hz</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T10:39:56.876+07:00</t>
+          <t>2026-06-30T15:43:38.331+07:00</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:57</t>
+          <t>2026-09-28 12:26:33</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-59RD (Core 5-210H/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>22990000</v>
+        <v>24490000</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>23990000</v>
+        <v>27990000</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Card đồ họa tích hợp - Qualcomm® Adreno™ | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T09:43:41.692+07:00</t>
+          <t>2026-09-25T16:06:18.096+07:00</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:25</t>
+          <t>2026-09-28 12:23:14</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R5F4 (Ryzen AI 7 350/ RTX 5060/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>23990000</v>
+        <v>48890000</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>25990000</v>
+        <v>50990000</v>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® ARC™ Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-gaming-nitro-v-propanel-an16s-61-r5f4</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T15:00:45.83+07:00</t>
+          <t>2026-09-09T15:11:02.875+07:00</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:30</t>
+          <t>2026-09-28 12:23:19</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M (Ultra 9-185H/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R7KQ (Ryzen AI 5 340/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD+/Win 11)</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>29890000</v>
-      </c>
-      <c r="C127" s="2" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>-0%</t>
-        </is>
-      </c>
+        <v>46990000</v>
+      </c>
+      <c r="C127" s="2" t="inlineStr"/>
+      <c r="D127" s="2" t="inlineStr"/>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen AI 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-16gb-512gb-14-fhd-ips-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-anv16s-61-r7kq</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:22:17.071+07:00</t>
+          <t>2026-09-11T10:11:28.855+07:00</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:35</t>
+          <t>2026-09-28 12:23:24</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R7ZJ (Ryzen AI 7 350/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>22990000</v>
-      </c>
-      <c r="C128" s="2" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>51990000</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr"/>
+      <c r="D128" s="2" t="inlineStr"/>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-an16s-61-r7zj</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T21:08:15.03+07:00</t>
+          <t>2026-09-24T10:35:37.593+07:00</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:40</t>
+          <t>2026-09-28 12:23:29</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R0QM (Ryzen 5 7640HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>20990000</v>
+        <v>32990000</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>21990000</v>
+        <v>34990000</v>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 680M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r0qm</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17T09:17:18.78+07:00</t>
+          <t>2026-08-07T14:12:10.19+07:00</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:45</t>
+          <t>2026-09-28 12:23:34</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR (Ryzen 5-3500U/ 8GB/ 512GB/ 14" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R5EF (Ryzen 5 7640HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>17990000</v>
+        <v>33390000</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>19990000</v>
+        <v>34990000</v>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r5ef</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T20:43:49.815+07:00</t>
+          <t>2026-09-25T10:23:17.905+07:00</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:49</t>
+          <t>2026-09-28 12:23:39</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R9EH (Ryzen 7 7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>22890000</v>
+        <v>35990000</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>23990000</v>
+        <v>38990000</v>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r9eh</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:44:03.513+07:00</t>
+          <t>2026-08-21T15:05:48.951+07:00</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:54</t>
+          <t>2026-09-28 12:23:44</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-556L (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>24990000</v>
+        <v>38890000</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>25990000</v>
+        <v>38990000</v>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Tay cầm Acer Nitro Controller NGR300 Wireless White (trị giá 1.200.000đ)</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-556l</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:20:56.552+07:00</t>
+          <t>2026-09-25T10:27:47.558+07:00</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:59</t>
+          <t>2026-09-28 12:23:49</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-76KR (Core 7-350/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-78MD (Core 7-240H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>25990000</v>
+        <v>40890000</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>26990000</v>
+        <v>40990000</v>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Tay cầm Acer Nitro Controller NGR300 Wireless White (trị giá 1.200.000đ)</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-76kr-core-7-350-8gb-512gb</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-78md</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:44:29.405+07:00</t>
+          <t>2026-09-25T10:28:06.595+07:00</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:04</t>
+          <t>2026-09-28 12:23:54</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-71T9 (Core 7-240H/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>17990000</v>
-      </c>
-      <c r="C134" s="2" t="n">
-        <v>19790000</v>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
+        <v>43990000</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr"/>
+      <c r="D134" s="2" t="inlineStr"/>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-71t9</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T09:51:43.721+07:00</t>
+          <t>2026-09-25T10:29:41.759+07:00</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:09</t>
+          <t>2026-09-28 12:23:59</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-782F (Core 7-240H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>19590000</v>
-      </c>
-      <c r="C135" s="2" t="n">
-        <v>21990000</v>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
-      </c>
+        <v>40990000</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr"/>
+      <c r="D135" s="2" t="inlineStr"/>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-782f</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T09:03:23.812+07:00</t>
+          <t>2026-09-11T10:05:04.439+07:00</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:14</t>
+          <t>2026-09-28 12:24:04</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5-3500U/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-I51-71MF (Ultra 7-355/ RTX 5070 8GB/ 32GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>16790000</v>
-      </c>
-      <c r="C136" s="2" t="n">
-        <v>19990000</v>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>-16%</t>
-        </is>
-      </c>
+        <v>76990000</v>
+      </c>
+      <c r="C136" s="2" t="inlineStr"/>
+      <c r="D136" s="2" t="inlineStr"/>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-i51-71mf-ultra-7-355-rtx-5070-8gb-32gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:09:40.061+07:00</t>
+          <t>2026-09-18T10:59:01.522+07:00</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:19</t>
+          <t>2026-09-28 12:24:09</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-411P-R1CM (Ryzen 5 3500U/ 8GB/ 256GB)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-71-58WQ (Core 5-210H/ RTX 5050/ 32GB/ 512GB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>17990000</v>
+        <v>44890000</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>18990000</v>
+        <v>45990000</v>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r1cm-ryzen-5-3500u-8gb-256gb</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16s-71-58wq</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T14:26:56.746+07:00</t>
+          <t>2026-09-18T10:25:14.809+07:00</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:24</t>
+          <t>2026-09-28 12:24:14</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-411P-R7YP (Ryzen 3 3200U/ 8GB/ 256GB)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R9CN (Ryzen AI 7 350/ RTX 5070 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>15990000</v>
-      </c>
-      <c r="C138" s="2" t="n">
-        <v>16990000</v>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>57990000</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr"/>
+      <c r="D138" s="2" t="inlineStr"/>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 3 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r7yp-ryzen-3-3200u-8gb-256gb</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-s-ai-propanel-an16s-61-r9cn</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T14:48:50.246+07:00</t>
+          <t>2026-09-09T15:10:31.152+07:00</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:28</t>
+          <t>2026-09-28 12:24:19</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-49P-R6XX (Ryzen 5 7430U/ 8GB/ 512GB/15.6"/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50RB (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>18590000</v>
+        <v>30990000</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>20990000</v>
+        <v>35990000</v>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-49p-r6xx-ryzen-5-7430u-8gb-512gb-15-6-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50rb</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T13:56:25.879+07:00</t>
+          <t>2026-09-27T11:11:52.657+07:00</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:33</t>
+          <t>2026-09-28 12:24:25</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50VA (Core 5-210H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>18890000</v>
+        <v>28990000</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>24990000</v>
+        <v>33990000</v>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>-24%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50va</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T10:45:08.009+07:00</t>
+          <t>2026-09-25T11:03:23.184+07:00</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:39</t>
+          <t>2026-09-28 12:24:30</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-73Z8 (Core 7-240H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>24990000</v>
+        <v>33490000</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>27990000</v>
+        <v>37990000</v>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T15:19:10.843+07:00</t>
+          <t>2026-09-25T16:08:20.8+07:00</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:44</t>
+          <t>2026-09-28 12:24:35</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF (Core 3-304/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>21990000</v>
+        <v>43990000</v>
       </c>
       <c r="C142" s="2" t="inlineStr"/>
       <c r="D142" s="2" t="inlineStr"/>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-34nf-core-3-304-12gb-512gb-14-fhd-ips-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T13:32:07.536+07:00</t>
+          <t>2026-09-28T09:10:13.793+07:00</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:49</t>
+          <t>2026-09-28 12:24:40</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV (Core 5-320/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>23490000</v>
+        <v>42990000</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>24990000</v>
+        <v>45990000</v>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
+          <t>Dòng CPU: Ryzen AI 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-52bv-core-5-320-12gb-512gb-14-wuxga-ips-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:09:22.19+07:00</t>
+          <t>2026-09-08T09:31:41.277+07:00</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:54</t>
+          <t>2026-09-28 12:24:45</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>28990000</v>
+        <v>54990000</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>30990000</v>
+        <v>58690000</v>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
@@ -6333,300 +6381,282 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:07:37.902+07:00</t>
+          <t>2026-09-18T10:40:22.072+07:00</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:58</t>
+          <t>2026-09-28 12:24:50</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>49990000</v>
+        <v>32490000</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>54990000</v>
+        <v>36990000</v>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ B390 GPU (đồ họa tích hợp) | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T15:51:47.551+07:00</t>
+          <t>2026-09-11T09:59:34.507+07:00</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:03</t>
+          <t>2026-09-28 12:24:55</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI OLED SFG14-75-765M (Ultra 7-258V/ 32GB/ 512GB/ 14" FHD+ OLED/ Win11)</t>
+          <t>Laptop gaming Acer Predator Helios 18 AI PH18-I71-91UX (Ultra 9-290HX Plus/ RTX 5080 16GB/ 64GB/ 3TB/ 18" 2K+ Mini LED 250Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>39990000</v>
+        <v>179990000</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>40990000</v>
+        <v>181990000</v>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ Graphics 140V | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 3072 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 18 inch | Độ phân giải: 2K+ (2560x1600)</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-ai-oled-sfg14-75-765m-14-fhd-oled-u7-258v-32lp-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-18-ai-ph18-i71-91ux-ultra-9-290hx-rtx-5080-16gb-16gb-3tb-18-2k-mini-led-250hz</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T10:47:31.44+07:00</t>
+          <t>2026-09-17T13:30:49.416+07:00</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:08</t>
+          <t>2026-09-28 12:25:00</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios 18 PH18-I71-975R (Ultra 9-290HX Plus/ RTX 5090 24GB/ 64GB/ 3TB/ 18" WQUXGA 4K IPS Mini LED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>32999000</v>
+        <v>249990000</v>
       </c>
       <c r="C147" s="2" t="inlineStr"/>
       <c r="D147" s="2" t="inlineStr"/>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 3072 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 18 inch | Độ phân giải: UHD+ (3840x2400) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-18-ai-ph18-i71-975r-ultra-9-290hx-rtx-5090-24gb-64gb-3tb-18-4k-mini-led-120hz</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T14:38:31.288+07:00</t>
+          <t>2026-09-14T15:37:36.896+07:00</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:13</t>
+          <t>2026-09-28 12:25:05</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo PHN16-I71-9779 (Ultra 9-290HX Plus/ RTX 5070 8GB/ 64GB/ 2TB/ 16" WQXGA IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>31490000</v>
-      </c>
-      <c r="C148" s="2" t="n">
-        <v>32490000</v>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>109990000</v>
+      </c>
+      <c r="C148" s="2" t="inlineStr"/>
+      <c r="D148" s="2" t="inlineStr"/>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ 130T Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-ai-phn16-i71-9779-ultra-9-290hx-rtx-5070-8gb-64gb-2tb-16-2k-ips-180hz-win-11</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T14:08:34.772+07:00</t>
+          <t>2026-09-14T15:35:07.531+07:00</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:18</t>
+          <t>2026-09-28 12:25:10</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" 2.8K OLED/ Win 11/ Office)</t>
+          <t>Laptop gaming Acer Predator Helios Neo PHN16-I71-97VK (Ultra 9-290HX Plus/ RTX 5080 16GB/ 32GB/ 512GB/ 16" WQAGA 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="C149" s="2" t="n">
-        <v>45990000</v>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>-22%</t>
-        </is>
-      </c>
+        <v>104990000</v>
+      </c>
+      <c r="C149" s="2" t="inlineStr"/>
+      <c r="D149" s="2" t="inlineStr"/>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6 | Kích thước màn hình: 14.5 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-ai-phn16-i71-97vk-ultra-9-290hx-rtx-5080-16gb-16gb-512gb-16-2k-ips-240hz</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:56:38.644+07:00</t>
+          <t>2026-09-14T15:33:09.575+07:00</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:23</t>
+          <t>2026-09-28 12:25:15</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-91K5 (I9-14900HX/ RTX 5070 8GB/ 32GB/ 1TB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>43990000</v>
-      </c>
-      <c r="C150" s="2" t="n">
-        <v>49490000</v>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
-      </c>
+        <v>89990000</v>
+      </c>
+      <c r="C150" s="2" t="inlineStr"/>
+      <c r="D150" s="2" t="inlineStr"/>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: RTX 4060 | Kích thước màn hình: 14.5 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: i9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-91k5-i9-14900hx-rtx-5070-8gb-32gb-1tb-16-2k-ips-180hz-win-11</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T15:10:56.836+07:00</t>
+          <t>2026-09-17T13:27:14.879+07:00</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:28</t>
+          <t>2026-09-28 12:25:20</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H08-50W (Core 5-210H/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>19490000</v>
+        <v>114990000</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>21990000</v>
+        <v>129900000</v>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
@@ -6635,264 +6665,246 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h08-50w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T11:09:14.14+07:00</t>
+          <t>2026-07-17T10:38:12.773+07:00</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:33</t>
+          <t>2026-09-28 12:25:25</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1403CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 512GB/ 16" 2K+ OLED 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>24290000</v>
-      </c>
-      <c r="C152" s="2" t="n">
-        <v>26990000</v>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
+        <v>75990000</v>
+      </c>
+      <c r="C152" s="2" t="inlineStr"/>
+      <c r="D152" s="2" t="inlineStr"/>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h16-63ws-core-5-210h-16gb-512gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T15:06:02.246+07:00</t>
+          <t>2026-09-14T15:32:07.247+07:00</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:38</t>
+          <t>2026-09-28 12:25:31</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1403CVA-C7H16-50W (Core 7-240H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 32GB/ 512GB/ 16" 2K+ OLED 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>28990000</v>
+        <v>72990000</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>30990000</v>
+        <v>80290000</v>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr"/>
-      <c r="G153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+        </is>
+      </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c7h16-50w-core-7-240h-16gb-512gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T14:43:57.168+07:00</t>
+          <t>2026-09-14T15:31:06.752+07:00</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:43</t>
+          <t>2026-09-28 12:25:36</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1503CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070 8GB/ 32GB/ 2TB/ 14.5" 2.8K+/ Win 11)</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>24290000</v>
-      </c>
-      <c r="C154" s="2" t="n">
-        <v>26990000</v>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
+        <v>93990000</v>
+      </c>
+      <c r="C154" s="2" t="inlineStr"/>
+      <c r="D154" s="2" t="inlineStr"/>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo gaming Acer Predator Robust PBG470 (trị giá 3.500.000đ)</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 14.5 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1503cva-c5h16-63ws-core-5-210h-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T14:03:33.213+07:00</t>
+          <t>2026-09-14T15:43:12.906+07:00</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:48</t>
+          <t>2026-09-28 12:25:41</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1403CVA-C3U08-50W (Core 3-100U/ 8GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton Neo 16 PTN16-51-78JQ (Ultra 7-155H/ RTX 4060/ 32GB/ 2TB/ 16.0" 2.5K/ Win 11)</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>15490000</v>
+        <v>49990000</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>17990000</v>
+        <v>52490000</v>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 4060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c3u08-50w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-neo-16-ptn16-51-78jq</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T13:53:40.042+07:00</t>
+          <t>2026-09-22T16:42:43.256+07:00</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:53</t>
+          <t>2026-09-28 12:25:46</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>23390000</v>
+        <v>27540000</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>27990000</v>
+        <v>30300000</v>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T10:19:47.487+07:00</t>
+          <t>2026-07-12T11:35:32.312+07:00</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:58</t>
+          <t>2026-09-28 12:25:51</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U516S8W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix G G614PH-RV176W (Ryzen 9/ RTX 5050/ 16GB/ 512GB/ 16" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>26390000</v>
-      </c>
-      <c r="C157" s="2" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>49990000</v>
+      </c>
+      <c r="C157" s="2" t="inlineStr"/>
+      <c r="D157" s="2" t="inlineStr"/>
       <c r="E157" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6901,40 +6913,40 @@
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u516s8w-ultra-5-225h-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g-g614ph-rv176w-ryzen-9-rtx-5050-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T11:57:56.626+07:00</t>
+          <t>2026-09-06T15:47:04.096+07:00</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:03</t>
+          <t>2026-09-28 12:25:56</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U716S8W (Ultra 7-255H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix G16 G614PH-S5101W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>32990000</v>
+        <v>47490000</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>34990000</v>
+        <v>53990000</v>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -6943,40 +6955,38 @@
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr"/>
-      <c r="G158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+        </is>
+      </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u716s8w-ultra-7-255h-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-s5101w</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T13:46:08.673+07:00</t>
+          <t>2026-09-10T11:28:04.811+07:00</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:08</t>
+          <t>2026-09-28 12:26:01</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA / Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix G16 G614PH-TS118W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>26390000</v>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v>30490000</v>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>-13%</t>
-        </is>
-      </c>
+        <v>52990000</v>
+      </c>
+      <c r="C159" s="2" t="inlineStr"/>
+      <c r="D159" s="2" t="inlineStr"/>
       <c r="E159" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6985,40 +6995,40 @@
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-ts118w</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03T11:54:54.747+07:00</t>
+          <t>2026-08-13T11:49:35.857+07:00</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:13</t>
+          <t>2026-09-28 12:26:06</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix G16 G614PM-TS147W (Ryzen 9-8940HX/ RTX 5060 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>32990000</v>
+        <v>54690000</v>
       </c>
       <c r="C160" s="2" t="n">
-        <v>35990000</v>
+        <v>59990000</v>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -7027,120 +7037,116 @@
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
-      <c r="G160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
+        </is>
+      </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614pm-ts147w</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T08:56:23.461+07:00</t>
+          <t>2026-09-07T10:15:11.541+07:00</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:18</t>
+          <t>2026-09-28 12:26:11</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 G2 P5405CAA-NZ0223W (Ultra 7-356H/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix SCAR G835LXG-TQ473W (Ultra 9-290HX Plus/ RTX 5090/ 64GB/ 2TB/ 18" Mini LED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>39190000</v>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v>41990000</v>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>179990000</v>
+      </c>
+      <c r="C161" s="2" t="inlineStr"/>
+      <c r="D161" s="2" t="inlineStr"/>
       <c r="E161" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
-      <c r="G161" s="2" t="inlineStr"/>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 18 inch | Độ phân giải: UHD+ (3840x2400) | Tần số quét: 240 Hz</t>
+        </is>
+      </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-g2-p5405caa-nz0223w-ultra-7-356h-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-scar-g835lxg-tq473w-ultra-9-290hx-plus-rtx-5090-64gb-2tb-18-qhd-mini-led-240hz-win-11</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T11:12:45.933+07:00</t>
+          <t>2026-09-26T12:58:23.481+07:00</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:23</t>
+          <t>2026-09-28 12:26:16</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0016W (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus G14 GA403WW QS136WS</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>28790000</v>
+        <v>84990000</v>
       </c>
       <c r="C162" s="2" t="n">
-        <v>30990000</v>
+        <v>89490000</v>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-5%</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr"/>
       <c r="F162" s="2" t="inlineStr"/>
-      <c r="G162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ryzen AI 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+        </is>
+      </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0016w-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-g14-ga403ww-qs136ws</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T10:54:41.9+07:00</t>
+          <t>2026-07-08T18:04:20.593+07:00</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:27</t>
+          <t>2026-09-28 12:26:21</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0017W (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU405AR-SY016W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>36290000</v>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>96990000</v>
+      </c>
+      <c r="C163" s="2" t="inlineStr"/>
+      <c r="D163" s="2" t="inlineStr"/>
       <c r="E163" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7149,42 +7155,36 @@
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: Arc | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0017w-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405ar-sy016w-ultra-9-rtx-5070-ti-32gb-1tb-14-3k-oled-120hz-win-11</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:51:05.888+07:00</t>
+          <t>2026-09-06T15:47:29.287+07:00</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:32</t>
+          <t>2026-09-28 12:26:26</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0442WS (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU405AW-SY029W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>37190000</v>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>119990000</v>
+      </c>
+      <c r="C164" s="2" t="inlineStr"/>
+      <c r="D164" s="2" t="inlineStr"/>
       <c r="E164" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7193,42 +7193,36 @@
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc 140V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0442ws-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405aw-sy029w-ultra-9-rtx-5080-32gb-1tb-14-3k-oled-120hz-win-11</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T09:55:42.594+07:00</t>
+          <t>2026-09-06T15:47:45.327+07:00</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:37</t>
+          <t>2026-09-28 12:26:31</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0450WS (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR115W (Ultra 7-255H/ RTX 5070/ 16GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>29790000</v>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>31990000</v>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>74990000</v>
+      </c>
+      <c r="C165" s="2" t="inlineStr"/>
+      <c r="D165" s="2" t="inlineStr"/>
       <c r="E165" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7237,22 +7231,22 @@
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc 130V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0450ws-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr115w-ultra-7-255h-rtx-5070-16gb-512gb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T09:56:18.911+07:00</t>
+          <t>2026-09-06T15:46:00.864+07:00</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:42</t>
+          <t>2026-09-28 12:26:37</t>
         </is>
       </c>
     </row>
@@ -7290,7 +7284,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:37</t>
+          <t>2026-09-28 12:23:16</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7324,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:42</t>
+          <t>2026-09-28 12:23:21</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7354,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:48</t>
+          <t>2026-09-28 12:23:26</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7392,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:52</t>
+          <t>2026-09-28 12:23:31</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7432,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:18:57</t>
+          <t>2026-09-28 12:23:37</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7472,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:02</t>
+          <t>2026-09-28 12:23:42</t>
         </is>
       </c>
     </row>
@@ -7514,7 +7508,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:07</t>
+          <t>2026-09-28 12:23:47</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7548,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:12</t>
+          <t>2026-09-28 12:23:52</t>
         </is>
       </c>
     </row>
@@ -7592,7 +7586,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:17</t>
+          <t>2026-09-28 12:23:57</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7620,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:22</t>
+          <t>2026-09-28 12:24:02</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7654,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:27</t>
+          <t>2026-09-28 12:24:07</t>
         </is>
       </c>
     </row>
@@ -7700,7 +7694,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:32</t>
+          <t>2026-09-28 12:24:13</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7732,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:37</t>
+          <t>2026-09-28 12:24:18</t>
         </is>
       </c>
     </row>
@@ -7776,7 +7770,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:42</t>
+          <t>2026-09-28 12:24:23</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7808,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:47</t>
+          <t>2026-09-28 12:24:28</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7846,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:52</t>
+          <t>2026-09-28 12:24:33</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7884,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:19:57</t>
+          <t>2026-09-28 12:24:38</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7918,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:02</t>
+          <t>2026-09-28 12:24:43</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7956,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:07</t>
+          <t>2026-09-28 12:24:48</t>
         </is>
       </c>
     </row>
@@ -8000,7 +7994,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:12</t>
+          <t>2026-09-28 12:24:53</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8032,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:16</t>
+          <t>2026-09-28 12:24:58</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8070,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:21</t>
+          <t>2026-09-28 12:25:03</t>
         </is>
       </c>
     </row>
@@ -8120,7 +8114,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:26</t>
+          <t>2026-09-28 12:25:09</t>
         </is>
       </c>
     </row>
@@ -8156,7 +8150,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:31</t>
+          <t>2026-09-28 12:25:14</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8186,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:36</t>
+          <t>2026-09-28 12:25:19</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8230,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:41</t>
+          <t>2026-09-28 12:25:24</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8274,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:46</t>
+          <t>2026-09-28 12:25:29</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8318,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:51</t>
+          <t>2026-09-28 12:25:34</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8358,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:20:56</t>
+          <t>2026-09-28 12:25:39</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8396,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:01</t>
+          <t>2026-09-28 12:25:44</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8440,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:06</t>
+          <t>2026-09-28 12:25:49</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8484,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:11</t>
+          <t>2026-09-28 12:25:54</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8528,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:16</t>
+          <t>2026-09-28 12:25:59</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8572,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:21</t>
+          <t>2026-09-28 12:26:04</t>
         </is>
       </c>
     </row>
@@ -8589,14 +8583,14 @@
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>46990000</v>
+        <v>44490000</v>
       </c>
       <c r="C200" s="2" t="n">
         <v>48990000</v>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -8622,7 +8616,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:26</t>
+          <t>2026-09-28 12:26:09</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8650,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:31</t>
+          <t>2026-09-28 12:26:14</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8680,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:36</t>
+          <t>2026-09-28 12:26:19</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8724,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:41</t>
+          <t>2026-09-28 12:26:24</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8768,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:21:46</t>
+          <t>2026-09-28 12:26:30</t>
         </is>
       </c>
     </row>

--- a/laptop_gearvn_all.xlsx
+++ b/laptop_gearvn_all.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J193"/>
+  <dimension ref="A1:J197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Dell DC15250-7982BLK H5YXJ (I7-1355U/ 16GB/ 1TB/ 15.6" FHD Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -519,42 +519,42 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Card đồ họa tích hợp - Qualcomm® Adreno™ | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
+          <t>https://gearvn.com/products/laptop-dell-dc15250-7982blk-h5yxj-i7-1355u-16gb-1tb-15-6-fhd-touch-win-11</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T09:43:41.692+07:00</t>
+          <t>2026-08-19T15:36:35.706+07:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:43:53</t>
+          <t>2026-09-30 12:32:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-53RH (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>23990000</v>
+        <v>29990000</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>25990000</v>
+        <v>32490000</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -563,1598 +563,1514 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® ARC™ Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-53rh-core-5-210h-rtx-4050-6gb-16gb-512gb-15-6-fhd-ips-144hz</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T15:00:45.83+07:00</t>
+          <t>2026-09-09T10:39:56.876+07:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:43:58</t>
+          <t>2026-09-30 12:32:17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M (Ultra 9-185H/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-59RD (Core 5-210H/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>29890000</v>
+        <v>24490000</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>29990000</v>
+        <v>27990000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-16gb-512gb-14-fhd-ips-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:22:17.071+07:00</t>
+          <t>2026-09-25T16:06:18.096+07:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:03</t>
+          <t>2026-09-30 12:32:22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R5F4 (Ryzen AI 7 350/ RTX 5060/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>22990000</v>
+        <v>48890000</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>25990000</v>
+        <v>50990000</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-gaming-nitro-v-propanel-an16s-61-r5f4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T21:08:15.03+07:00</t>
+          <t>2026-09-09T15:11:02.875+07:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:08</t>
+          <t>2026-09-30 12:32:28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R7KQ (Ryzen AI 5 340/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD+/Win 11)</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>20990000</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>21990000</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
+        <v>46990000</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 680M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen AI 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-anv16s-61-r7kq</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17T09:17:18.78+07:00</t>
+          <t>2026-09-11T10:11:28.855+07:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:13</t>
+          <t>2026-09-30 12:32:33</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR (Ryzen 5-3500U/ 8GB/ 512GB/ 14" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R7ZJ (Ryzen AI 7 350/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>17990000</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>19990000</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
+        <v>51990000</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-an16s-61-r7zj</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T20:43:49.815+07:00</t>
+          <t>2026-09-24T10:35:37.593+07:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:18</t>
+          <t>2026-09-30 12:32:38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R0QM (Ryzen 5 7640HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>22890000</v>
+        <v>32990000</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>23990000</v>
+        <v>34990000</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r0qm</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:44:03.513+07:00</t>
+          <t>2026-08-07T14:12:10.19+07:00</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:23</t>
+          <t>2026-09-30 12:32:43</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R5EF (Ryzen 5 7640HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>24990000</v>
+        <v>33390000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>25990000</v>
+        <v>34990000</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r5ef</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:20:56.552+07:00</t>
+          <t>2026-09-25T10:23:17.905+07:00</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:28</t>
+          <t>2026-09-30 12:32:48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-76KR (Core 7-350/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R9EH (Ryzen 7 7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>25990000</v>
+        <v>35990000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>26990000</v>
+        <v>38990000</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-76kr-core-7-350-8gb-512gb</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r9eh</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:44:29.405+07:00</t>
+          <t>2026-08-21T15:05:48.951+07:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:33</t>
+          <t>2026-09-30 12:32:53</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-556L (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>17990000</v>
+        <v>38890000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>19790000</v>
+        <v>38990000</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Tay cầm Acer Nitro Controller NGR300 Wireless White (trị giá 1.200.000đ)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-556l</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T09:51:43.721+07:00</t>
+          <t>2026-09-25T10:27:47.558+07:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:38</t>
+          <t>2026-09-30 12:32:58</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-78MD (Core 7-240H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>19590000</v>
+        <v>40890000</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>21990000</v>
+        <v>40990000</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Tay cầm Acer Nitro Controller NGR300 Wireless White (trị giá 1.200.000đ)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-78md</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T09:03:23.812+07:00</t>
+          <t>2026-09-25T10:28:06.595+07:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:43</t>
+          <t>2026-09-30 12:33:03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5-3500U/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-71T9 (Core 7-240H/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>16790000</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>19990000</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-16%</t>
-        </is>
-      </c>
+        <v>43990000</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-71t9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:09:40.061+07:00</t>
+          <t>2026-09-25T10:29:41.759+07:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:48</t>
+          <t>2026-09-30 12:33:08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-411P-R1CM (Ryzen 5 3500U/ 8GB/ 256GB)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-782F (Core 7-240H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>17990000</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>18990000</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
+        <v>40990000</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r1cm-ryzen-5-3500u-8gb-256gb</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-782f</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T14:26:56.746+07:00</t>
+          <t>2026-09-11T10:05:04.439+07:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:53</t>
+          <t>2026-09-30 12:33:13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-411P-R7YP (Ryzen 3 3200U/ 8GB/ 256GB)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-A71-R7Z6 (Ryzen AI 9 465/ RTX 5070 8GB/ 32GB/ 512GB/ 16" FHD+ IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>15990000</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>16990000</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>77990000</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 3 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
-        </is>
-      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r7yp-ryzen-3-3200u-8gb-256gb</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-a71-r7z6-ryzen-ai-9-465-rtx-5070-8gb-32gb-512gb-16-fhd-ips-180hz-win-11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T14:48:50.246+07:00</t>
+          <t>2026-09-30T11:39:31.454+07:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:58</t>
+          <t>2026-09-30 12:33:19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-49P-R6XX (Ryzen 5 7430U/ 8GB/ 512GB/15.6"/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-I12-53VH (Core 5-205H/ RTX 3050 4GB/ 16GB/ 512GB/ 16" FHD 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>18590000</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>20990000</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
-      </c>
+        <v>30990000</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
-        </is>
-      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-49p-r6xx-ryzen-5-7430u-8gb-512gb-15-6-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-i12-53vh-core-5-205h-rtx-3050-4gb-16gb-512gb-16-fhd-165hz-win-11</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T13:56:25.879+07:00</t>
+          <t>2026-09-30T11:06:22.406+07:00</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:03</t>
+          <t>2026-09-30 12:33:24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-I12-72G0 (Core 7-230H/ RTX 3050 4GB/ 16GB/ 512GB/ 16" FHD 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>18890000</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-24%</t>
-        </is>
-      </c>
+        <v>33990000</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
-        </is>
-      </c>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-i12-72g0-core-7-230h-rtx-3050-4gb-16gb-512gb-16-fhd-165hz-win-11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T10:45:08.009+07:00</t>
+          <t>2026-09-30T10:45:24.015+07:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:08</t>
+          <t>2026-09-30 12:33:29</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-I51-71MF (Ultra 7-355/ RTX 5070 8GB/ 32GB/ 512GB/ 16" FHD+ IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>24990000</v>
+        <v>74990000</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>27990000</v>
+        <v>76990000</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-i51-71mf-ultra-7-355-rtx-5070-8gb-32gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T15:19:10.843+07:00</t>
+          <t>2026-09-29T11:40:49.662+07:00</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:13</t>
+          <t>2026-09-30 12:33:34</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF (Core 3-304/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-71-58WQ (Core 5-210H/ RTX 5050/ 32GB/ 512GB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>21990000</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr"/>
+        <v>44890000</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>45990000</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-34nf-core-3-304-12gb-512gb-14-fhd-ips-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16s-71-58wq</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T13:32:07.536+07:00</t>
+          <t>2026-09-18T10:25:14.809+07:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:18</t>
+          <t>2026-09-30 12:33:40</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV (Core 5-320/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R9CN (Ryzen AI 7 350/ RTX 5070 8GB/ 32GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>23490000</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>62990000</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
+          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-52bv-core-5-320-12gb-512gb-14-wuxga-ips-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-s-ai-propanel-an16s-61-r9cn</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:09:22.19+07:00</t>
+          <t>2026-09-29T09:15:37.613+07:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:23</t>
+          <t>2026-09-30 12:33:45</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50RB (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>28990000</v>
+        <v>30990000</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>30990000</v>
+        <v>35990000</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50rb</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:07:37.902+07:00</t>
+          <t>2026-09-27T11:11:52.657+07:00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:28</t>
+          <t>2026-09-30 12:33:50</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50VA (Core 5-210H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>49990000</v>
+        <v>28990000</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>54990000</v>
+        <v>33990000</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-15%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ B390 GPU (đồ họa tích hợp) | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50va</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T15:51:47.551+07:00</t>
+          <t>2026-09-25T11:03:23.184+07:00</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:33</t>
+          <t>2026-09-30 12:33:55</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI OLED SFG14-75-765M (Ultra 7-258V/ 32GB/ 512GB/ 14" FHD+ OLED/ Win11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-73Z8 (Core 7-240H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>39990000</v>
+        <v>33490000</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>40990000</v>
+        <v>37990000</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ Graphics 140V | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-ai-oled-sfg14-75-765m-14-fhd-oled-u7-258v-32lp-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T10:47:31.44+07:00</t>
+          <t>2026-09-25T16:08:20.8+07:00</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:38</t>
+          <t>2026-09-30 12:34:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>32999000</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
+        <v>42590000</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>43990000</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T14:38:31.288+07:00</t>
+          <t>2026-09-28T19:07:42.806+07:00</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:43</t>
+          <t>2026-09-30 12:34:05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>31490000</v>
+        <v>42990000</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>32490000</v>
+        <v>45990000</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ 130T Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen AI 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T14:08:34.772+07:00</t>
+          <t>2026-09-08T09:31:41.277+07:00</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:48</t>
+          <t>2026-09-30 12:34:11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" 2.8K OLED/ Win 11/ Office)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>35990000</v>
+        <v>54990000</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>45990000</v>
+        <v>58690000</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6 | Kích thước màn hình: 14.5 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:56:38.644+07:00</t>
+          <t>2026-09-18T10:40:22.072+07:00</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:53</t>
+          <t>2026-09-30 12:34:16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>43990000</v>
+        <v>32490000</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>49490000</v>
+        <v>36990000</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: RTX 4060 | Kích thước màn hình: 14.5 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T15:10:56.836+07:00</t>
+          <t>2026-09-11T09:59:34.507+07:00</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:58</t>
+          <t>2026-09-30 12:34:21</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H08-50W (Core 5-210H/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios 18 AI PH18-I71-91UX (Ultra 9-290HX Plus/ RTX 5080 16GB/ 64GB/ 3TB/ 18" 2K+ Mini LED 250Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>19490000</v>
+        <v>179990000</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>21990000</v>
+        <v>181990000</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 3072 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 18 inch | Độ phân giải: 2K+ (2560x1600)</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h08-50w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-18-ai-ph18-i71-91ux-ultra-9-290hx-rtx-5080-16gb-16gb-3tb-18-2k-mini-led-250hz</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T11:09:14.14+07:00</t>
+          <t>2026-09-17T13:30:49.416+07:00</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:03</t>
+          <t>2026-09-30 12:34:26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1403CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios 18 PH18-I71-975R (Ultra 9-290HX Plus/ RTX 5090 24GB/ 64GB/ 3TB/ 18" 4K+ Mini LED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>24290000</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>26990000</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
+        <v>249990000</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 3072 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 18 inch | Độ phân giải: UHD+ (3840x2400) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h16-63ws-core-5-210h-16gb-512gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-18-ai-ph18-i71-975r-ultra-9-290hx-rtx-5090-24gb-64gb-3tb-18-4k-mini-led-120hz</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T15:06:02.246+07:00</t>
+          <t>2026-09-29T11:56:13.749+07:00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:08</t>
+          <t>2026-09-30 12:34:32</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1403CVA-C7H16-50W (Core 7-240H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo PHN16-I71-9779 (Ultra 9-290HX Plus/ RTX 5070 8GB/ 64GB/ 2TB/ 16" WQXGA IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>28990000</v>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>109990000</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c7h16-50w-core-7-240h-16gb-512gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-ai-phn16-i71-9779-ultra-9-290hx-rtx-5070-8gb-64gb-2tb-16-2k-ips-180hz-win-11</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T14:43:57.168+07:00</t>
+          <t>2026-09-14T15:35:07.531+07:00</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:13</t>
+          <t>2026-09-30 12:34:37</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1503CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo PHN16-I71-97VK (Ultra 9-290HX Plus/ RTX 5080 16GB/ 32GB/ 512GB/ 16" WQAGA 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>24290000</v>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>26990000</v>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
+        <v>104990000</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1503cva-c5h16-63ws-core-5-210h-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-ai-phn16-i71-97vk-ultra-9-290hx-rtx-5080-16gb-16gb-512gb-16-2k-ips-240hz</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T14:03:33.213+07:00</t>
+          <t>2026-09-14T15:33:09.575+07:00</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:17</t>
+          <t>2026-09-30 12:34:42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1403CVA-C3U08-50W (Core 3-100U/ 8GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-74MN (I7-14650HX/ RTX 5050/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>15490000</v>
+        <v>54990000</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>17990000</v>
+        <v>64990000</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c3u08-50w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-74mn</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T13:53:40.042+07:00</t>
+          <t>2026-09-29T14:23:25.919+07:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:22</t>
+          <t>2026-09-30 12:34:47</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-91K5 (I9-14900HX/ RTX 5070 8GB/ 32GB/ 1TB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>23390000</v>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>27990000</v>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>-16%</t>
-        </is>
-      </c>
+        <v>89990000</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-91k5-i9-14900hx-rtx-5070-8gb-32gb-1tb-16-2k-ips-180hz-win-11</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T10:19:47.487+07:00</t>
+          <t>2026-09-17T13:27:14.879+07:00</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:27</t>
+          <t>2026-09-30 12:34:52</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U516S8W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>26390000</v>
+        <v>114990000</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>29990000</v>
+        <v>129900000</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u516s8w-ultra-5-225h-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T11:57:56.626+07:00</t>
+          <t>2026-07-17T10:38:12.773+07:00</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:32</t>
+          <t>2026-09-30 12:34:57</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U716S8W (Ultra 7-255H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 512GB/ 16" 2K+ OLED 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>32990000</v>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>80990000</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u716s8w-ultra-7-255h-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T13:46:08.673+07:00</t>
+          <t>2026-09-29T11:50:52.42+07:00</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:37</t>
+          <t>2026-09-30 12:35:03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA / Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 32GB/ 512GB/ 16" 2K+ OLED 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>26390000</v>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>30490000</v>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>-13%</t>
-        </is>
-      </c>
+        <v>77990000</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03T11:54:54.747+07:00</t>
+          <t>2026-09-29T11:52:22.882+07:00</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:42</t>
+          <t>2026-09-30 12:35:08</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070 8GB/ 32GB/ 2TB/ 14.5" 2.8K+/ Win 11)</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>32990000</v>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>-8%</t>
-        </is>
-      </c>
+        <v>93990000</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo gaming Acer Predator Robust PBG470 (trị giá 3.500.000đ)</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 14.5 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T08:56:23.461+07:00</t>
+          <t>2026-09-14T15:43:12.906+07:00</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:47</t>
+          <t>2026-09-30 12:35:13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 G2 P5405CAA-NZ0223W (Ultra 7-356H/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>39190000</v>
+        <v>27540000</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>41990000</v>
+        <v>30300000</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-g2-p5405caa-nz0223w-ultra-7-356h-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T11:12:45.933+07:00</t>
+          <t>2026-07-12T11:35:32.312+07:00</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:52</t>
+          <t>2026-09-30 12:35:18</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0016W (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix G G614PH-RV176W (Ryzen 9/ RTX 5050/ 16GB/ 512GB/ 16" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>28790000</v>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>49990000</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0016w-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g-g614ph-rv176w-ryzen-9-rtx-5050-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T10:54:41.9+07:00</t>
+          <t>2026-09-06T15:47:04.096+07:00</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:57</t>
+          <t>2026-09-30 12:35:24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0017W (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix G16 G614PH-S5101W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>36290000</v>
+        <v>47490000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>38990000</v>
+        <v>53990000</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2165,33 +2081,33 @@
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: Arc | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0017w-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-s5101w</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:51:05.888+07:00</t>
+          <t>2026-09-10T11:28:04.811+07:00</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:47:02</t>
+          <t>2026-09-30 12:35:29</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Max C13WE-422VN (I7-13620H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix G16 G614PH-TS118W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>42990000</v>
+        <v>52990000</v>
       </c>
       <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr"/>
@@ -2203,40 +2119,40 @@
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn-i7-13620h-rtx-5050-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-ts118w</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:38:57.001+07:00</t>
+          <t>2026-08-13T11:49:35.857+07:00</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:43:55</t>
+          <t>2026-09-30 12:35:34</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix G16 G614PM-TS147W (Ryzen 9-8940HX/ RTX 5060 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>34890000</v>
+        <v>54690000</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>35990000</v>
+        <v>59990000</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2247,42 +2163,36 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614pm-ts147w</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T14:54:13.66+07:00</t>
+          <t>2026-09-07T10:15:11.541+07:00</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:00</t>
+          <t>2026-09-30 12:32:04</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix SCAR G835LXG-TQ473W (Ultra 9-290HX Plus/ RTX 5090/ 64GB/ 2TB/ 18" Mini LED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>79990000</v>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>80990000</v>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>-1%</t>
-        </is>
-      </c>
+        <v>179990000</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2291,33 +2201,33 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 18 inch | Độ phân giải: UHD+ (3840x2400) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-scar-g835lxg-tq473w-ultra-9-290hx-plus-rtx-5090-64gb-2tb-18-qhd-mini-led-240hz-win-11</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:43:38.331+07:00</t>
+          <t>2026-09-26T12:58:23.481+07:00</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:05</t>
+          <t>2026-09-30 12:32:10</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU405AR-SY016W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>85990000</v>
+        <v>96990000</v>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr"/>
@@ -2329,71 +2239,71 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405ar-sy016w-ultra-9-rtx-5070-ti-32gb-1tb-14-3k-oled-120hz-win-11</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T17:51:09.908+07:00</t>
+          <t>2026-09-06T15:47:29.287+07:00</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:10</t>
+          <t>2026-09-30 12:32:15</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming GIGABYTE AORUS Master 16 6XJM4VNE64SH (Ryzen 9 9955HX3D/ RTX 5070 Ti 12GB/ 32GB/ 1TB/ 16" QHD+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU405AW-SY029W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>86990000</v>
+        <v>119990000</v>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aorus-master-16-6xjm4vne64sh-ryzen-9-9955hx3d-rtx-5070-ti-12gb-32gb-1tb-16-qhd-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405aw-sy029w-ultra-9-rtx-5080-32gb-1tb-14-3k-oled-120hz-win-11</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T11:46:50.068+07:00</t>
+          <t>2026-09-06T15:47:45.327+07:00</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:15</t>
+          <t>2026-09-30 12:32:20</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 83RQ00DBVN (Core 3-304/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR115W (Ultra 7-255H/ RTX 5070/ 16GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>24990000</v>
+        <v>74990000</v>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2405,33 +2315,33 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-14iwc11-83rq00dbvn-core-3-304-8gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr115w-ultra-7-255h-rtx-5070-16gb-512gb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:16:44.995+07:00</t>
+          <t>2026-09-06T15:46:00.864+07:00</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:20</t>
+          <t>2026-09-30 12:32:25</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB005YVN (Ryzen 5-125/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR141W (Ultra 7-255H/ RTX 5070/ 32GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>25990000</v>
+        <v>83990000</v>
       </c>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2441,31 +2351,35 @@
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb005yvn-ryzen-5-125-8gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr141w-ultra-7-255h-rtx-5070-32gb-512gb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T15:01:44.794+07:00</t>
+          <t>2026-09-06T15:46:21.05+07:00</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:25</t>
+          <t>2026-09-30 12:32:30</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB0060VN (Ryzen 7-155/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AR-TB027W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>27990000</v>
+        <v>99990000</v>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2475,71 +2389,73 @@
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb0060vn-ryzen-7-155-8gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ar-tb027w-ultra-9-rtx-5070-ti-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T14:35:59.897+07:00</t>
+          <t>2026-09-06T15:45:10.531+07:00</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:30</t>
+          <t>2026-09-30 12:32:35</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 83S1003GVN</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB052WS (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>44540000</v>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>47990000</v>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr"/>
+        <v>139990000</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-83s1003gvn</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb052ws-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T10:29:16.152+07:00</t>
+          <t>2026-09-06T15:45:28.879+07:00</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:35</t>
+          <t>2026-09-30 12:32:40</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 OLED 83S1006RVN (Ryzen AI 7-445/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB121W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>32990000</v>
+        <v>124990000</v>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2551,33 +2467,33 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-oled-83s1006rvn-ryzen-ai-7-445-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb121w-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T11:54:44.05+07:00</t>
+          <t>2026-09-06T15:45:44.227+07:00</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:40</t>
+          <t>2026-09-30 12:32:45</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00ABVN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AX-TB042WS (Ultra 9/ RTX 5090/ 64GB/ 2TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>30990000</v>
+        <v>169990000</v>
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2589,36 +2505,42 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00abvn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ax-tb042ws-ultra-9-rtx-5090-64gb-2tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T14:05:59.687+07:00</t>
+          <t>2026-09-06T15:44:50.259+07:00</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:45</t>
+          <t>2026-09-30 12:32:50</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00F5VN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr"/>
+        <v>57390000</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>58990000</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2627,36 +2549,42 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen AI 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00f5vn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:17:34.624+07:00</t>
+          <t>2026-09-14T17:35:45.75+07:00</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:50</t>
+          <t>2026-09-30 12:32:55</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002EVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN329W (Ryzen 7-8845HS/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>55990000</v>
-      </c>
-      <c r="C53" s="2" t="inlineStr"/>
-      <c r="D53" s="2" t="inlineStr"/>
+        <v>27690000</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>37490000</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>-26%</t>
+        </is>
+      </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2665,36 +2593,42 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002evn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn329w-ryzen-7-8845hs-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T10:21:35.763+07:00</t>
+          <t>2026-09-17T11:04:13.749+07:00</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:55</t>
+          <t>2026-09-30 12:33:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002FVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN390W (Ryzen 7-155/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>55990000</v>
-      </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr"/>
+        <v>28990000</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2703,70 +2637,82 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002fvn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn390w-ryzen-7-155-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T20:29:51.634+07:00</t>
+          <t>2026-09-17T11:05:26.118+07:00</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:00</t>
+          <t>2026-09-30 12:33:05</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0075VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUG-RL129W (Ryzen 7-7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>46990000</v>
-      </c>
-      <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>29990000</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+        </is>
+      </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0075vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nug-rl129w-ryzen-7-7445hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:19:34.771+07:00</t>
+          <t>2026-09-14T17:41:09.162+07:00</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:06</t>
+          <t>2026-09-30 12:33:10</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0076VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUQ-RL007W (Ryzen 7-170/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>46990000</v>
-      </c>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr"/>
+        <v>36290000</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2775,36 +2721,42 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0076vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nuq-rl007w-ryzen-7-170-rtx-4050-6gb-16gb-512gb-16-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:20:20.027+07:00</t>
+          <t>2026-09-25T10:10:34.588+07:00</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:11</t>
+          <t>2026-09-30 12:33:15</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK0015VN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>72990000</v>
-      </c>
-      <c r="C57" s="2" t="inlineStr"/>
-      <c r="D57" s="2" t="inlineStr"/>
+        <v>41260000</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>45390000</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2813,33 +2765,33 @@
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk0015vn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:21:45.74+07:00</t>
+          <t>2026-06-30T14:06:48.719+07:00</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:16</t>
+          <t>2026-09-30 12:33:20</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK006GVN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA401EA-RG041W (Ryzen AI Max+ 392/ 32GB/ 512GB/ 14" 2.5K/ Win 11)</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>72990000</v>
+        <v>59990000</v>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr"/>
@@ -2851,33 +2803,33 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ryzen AI MAX+ | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon 8060S | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk006gvn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401ea-rg041w-ryzen-ai-max-392-32gb-512gb-14-2-5k-win-11</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:23:05.36+07:00</t>
+          <t>2026-08-14T09:33:26.048+07:00</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:21</t>
+          <t>2026-09-30 12:33:25</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 POLED 83QK009PVN (Ultra X9-378H/ 32GB/ 1TB/ 14" 2.8K WQXGA POLED Touch/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA401UH-RG001W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>70990000</v>
+        <v>49990000</v>
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr"/>
@@ -2889,42 +2841,36 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-poled-83qk009pvn-ultra-x9-378h-32gb-1tb-14-2-8k-wqxga-poled-touch-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401uh-rg001w-ryzen-7-260-rtx-5050-16gb-512gb-14-qhd-win-11</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T20:11:25.828+07:00</t>
+          <t>2026-09-26T12:59:55.007+07:00</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:26</t>
+          <t>2026-09-30 12:33:30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA401UM-RG049W (Ryzen 7 260/ RTX 5060/ 32GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>33900000</v>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>34900000</v>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>64990000</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2933,112 +2879,116 @@
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401um-rg049w-ryzen-7-260-rtx-5060-32gb-512gb-14-qhd-win-11</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:39:36.938+07:00</t>
+          <t>2026-09-26T13:00:47.55+07:00</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:31</t>
+          <t>2026-09-30 12:33:35</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA608UHI-TU121W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>36900000</v>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>37900000</v>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
+        <v>48990000</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608uhi-tu121w-ryzen-7-260-rtx-5050-16gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:34:21.041+07:00</t>
+          <t>2026-08-14T11:22:30.725+07:00</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:36</t>
+          <t>2026-09-30 12:33:40</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA608UMI-TU162W (Ryzen 7 260/ RTX 5060/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>44900000</v>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>46490000</v>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+        <v>51990000</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608umi-tu162w-ryzen-7-260-rtx-5060-16gb-512gb-16-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:43:00.949+07:00</t>
+          <t>2026-08-14T11:01:50.971+07:00</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:41</t>
+          <t>2026-09-30 12:33:45</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming ASUS V16 V3607VJ-TK189W (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 16" WUXGA 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>23990000</v>
+        <v>26490000</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>24990000</v>
+        <v>29990000</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3049,36 +2999,36 @@
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-v16-v3607vj-tk189w-core-5-210h-rtx-3050-6gb-16gb-512gb-16-wuxga-144hz-win-11</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:36:48.562+07:00</t>
+          <t>2026-09-15T16:26:14.526+07:00</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:46</t>
+          <t>2026-09-30 12:33:50</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>61990000</v>
+        <v>31990000</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>62990000</v>
+        <v>32790000</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
@@ -3087,208 +3037,208 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T15:49:38.229+07:00</t>
+          <t>2026-09-30T11:59:37.483+07:00</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:52</t>
+          <t>2026-09-30 12:33:55</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
+          <t>Laptop gaming GIGABYTE A16 CVHI3MY893SH (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>34690000</v>
+        <v>36990000</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>37990000</v>
+        <v>38990000</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3my893sh</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T10:28:18.636+07:00</t>
+          <t>2026-08-14T14:40:23.197+07:00</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:57</t>
+          <t>2026-09-30 12:34:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
+          <t>Laptop gaming Gigabyte A16 A16-3THK3VN893SH (Ryzen 7 260/ RTX 5050 8GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>25490000</v>
+        <v>35990000</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>25990000</v>
+        <v>40990000</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-ga63h-3thk3vn893sh</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:41:40.106+07:00</t>
+          <t>2026-07-30T09:54:12.234+07:00</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:02</t>
+          <t>2026-09-30 12:34:05</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14S AI+ G3MG-050VN (Ultra 7-355/ 16GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9LJR2VNF93SH (Ryzen 5 7533HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>36490000</v>
-      </c>
-      <c r="C67" s="2" t="inlineStr"/>
-      <c r="D67" s="2" t="inlineStr"/>
+        <v>29990000</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14s-ai-g3mg-050vn-ultra-7-355-16gb-1tb-14-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9ljr2vnf93sh-ryzen-5-7533hs-rtx-3050-6gb-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T17:51:58.168+07:00</t>
+          <t>2026-07-31T15:10:54.55+07:00</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:07</t>
+          <t>2026-09-30 12:34:10</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
+          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9MJR2VNF93SH (Ryzen 5 7533HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>22190000</v>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>22690000</v>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>34990000</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9mjr2vnf93sh-ryzen-5-7533hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T15:28:04.144+07:00</t>
+          <t>2026-09-18T13:50:39.975+07:00</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:12</t>
+          <t>2026-09-30 12:34:15</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>43990000</v>
+        <v>115990000</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>44990000</v>
+        <v>117990000</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
@@ -3303,42 +3253,36 @@
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:49:42.234+07:00</t>
+          <t>2026-07-05T14:44:14.658+07:00</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:17</t>
+          <t>2026-09-30 12:34:20</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15AHP11 83TN0040VN (Ryzen 7-250/ RTX 5050 8GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>33990000</v>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>43990000</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3347,40 +3291,40 @@
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 7 | Dung lượng SSD: 1024 GB | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15ahp11-83tn0040vn-ryzen-7-250-rtx-5050-8gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T16:07:23.364+07:00</t>
+          <t>2026-09-21T09:36:14.406+07:00</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:22</t>
+          <t>2026-09-30 12:34:25</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>37990000</v>
+        <v>38990000</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>39990000</v>
+        <v>41990000</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3391,40 +3335,40 @@
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 13.3 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T11:20:56.718+07:00</t>
+          <t>2026-07-15T09:36:38.199+07:00</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:27</t>
+          <t>2026-09-30 12:34:30</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN (Ultra 7-355/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S0006RVN (Ryzen 7-7735HS/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>44490000</v>
+        <v>30990000</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>48990000</v>
+        <v>32990000</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3435,33 +3379,33 @@
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0006rvn-ryzen-7-7735hs-rtx-3050-6gb-16gb-1tb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T10:53:12.84+07:00</t>
+          <t>2026-09-22T11:31:57.635+07:00</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:32</t>
+          <t>2026-09-30 12:34:35</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S000DCVN (Ryzen 7-170/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>59990000</v>
+        <v>32990000</v>
       </c>
       <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="inlineStr"/>
@@ -3471,70 +3415,76 @@
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s000dcvn-ryzen-7-170-rtx-3050-6gb-16gb-1tb-15-6-fhd-ips-win-11</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:54:52.677+07:00</t>
+          <t>2026-09-21T10:03:17.431+07:00</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:38</t>
+          <t>2026-09-30 12:34:40</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003VVN (Core 5-205H/ RTX 3050 6GB/ 8GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>59990000</v>
+        <v>36990000</v>
       </c>
       <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="inlineStr"/>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 8 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003vvn-core-5-205h-rtx-3050-6gb-8gb-512gb-15-3-wuxga-165hz-win-11</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T10:17:43.984+07:00</t>
+          <t>2026-08-12T19:41:42.305+07:00</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:43</t>
+          <t>2026-09-30 12:34:45</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/ RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003WVN (Core 5-205H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>82990000</v>
-      </c>
-      <c r="C75" s="2" t="n">
-        <v>83990000</v>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>-1%</t>
-        </is>
-      </c>
+        <v>41990000</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3543,40 +3493,40 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200)</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003wvn-core-5-205h-rtx-3050-6gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T15:48:57.837+07:00</t>
+          <t>2026-08-12T16:50:55.152+07:00</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:48</t>
+          <t>2026-09-30 12:34:50</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX10 83JE01AGVN (I7-13645HX/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>86990000</v>
+        <v>39490000</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>87990000</v>
+        <v>40990000</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3587,40 +3537,40 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx10-83je01agvn</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T17:54:02.495+07:00</t>
+          <t>2026-09-19T16:43:38.321+07:00</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:53</t>
+          <t>2026-09-30 12:34:55</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 16 DC16251 (I5-120U/ 8GB/ 512GB/ 16" FHD+ Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>18390000</v>
+        <v>43990000</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>19990000</v>
+        <v>45990000</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3631,42 +3581,36 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-16-dc16251-i5-120u-8gb-512gb-16-fhd-touch-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T13:45:33.424+07:00</t>
+          <t>2026-09-18T16:32:05.969+07:00</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:06</t>
+          <t>2026-09-30 12:35:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell DC15250-7982BLK H5YXJ (I7-1355U/ 16GB/ 1TB/ 15.6" FHD Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>22990000</v>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>23990000</v>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>33990000</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3675,537 +3619,501 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-dc15250-7982blk-h5yxj-i7-1355u-16gb-1tb-15-6-fhd-touch-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19T15:36:35.706+07:00</t>
+          <t>2026-06-30T15:23:00.628+07:00</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:12</t>
+          <t>2026-09-30 12:35:05</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-53RH (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>32490000</v>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>-8%</t>
-        </is>
-      </c>
+        <v>31990000</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-53rh-core-5-210h-rtx-4050-6gb-16gb-512gb-15-6-fhd-ips-144hz</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T10:39:56.876+07:00</t>
+          <t>2026-06-30T15:25:26.316+07:00</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:18</t>
+          <t>2026-09-30 12:35:10</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-59RD (Core 5-210H/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>24490000</v>
+        <v>34990000</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>27990000</v>
+        <v>35990000</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:06:18.096+07:00</t>
+          <t>2026-06-30T15:28:01.415+07:00</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:24</t>
+          <t>2026-09-30 12:35:15</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R5F4 (Ryzen AI 7 350/ RTX 5060/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Max C13WF-421VN (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>48890000</v>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>50990000</v>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>44990000</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr"/>
+      <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-gaming-nitro-v-propanel-an16s-61-r5f4</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13vf-421vn-i7-13620h-rtx-5060-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T15:11:02.875+07:00</t>
+          <t>2026-09-23T16:26:05.15+07:00</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:29</t>
+          <t>2026-09-30 12:35:20</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R7KQ (Ryzen AI 5 340/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD+/Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Max C13WE-422VN (I7-13620H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>46990000</v>
+        <v>42990000</v>
       </c>
       <c r="C82" s="2" t="inlineStr"/>
       <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-anv16s-61-r7kq</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn-i7-13620h-rtx-5050-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T10:11:28.855+07:00</t>
+          <t>2026-07-27T10:38:57.001+07:00</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:34</t>
+          <t>2026-09-30 12:32:18</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R7ZJ (Ryzen AI 7 350/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>51990000</v>
-      </c>
-      <c r="C83" s="2" t="inlineStr"/>
-      <c r="D83" s="2" t="inlineStr"/>
+        <v>34890000</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>35990000</v>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-an16s-61-r7zj</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T10:35:37.593+07:00</t>
+          <t>2026-06-30T14:54:13.66+07:00</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:39</t>
+          <t>2026-09-30 12:32:23</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R0QM (Ryzen 5 7640HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>32990000</v>
+        <v>79990000</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>34990000</v>
+        <v>80990000</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r0qm</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T14:12:10.19+07:00</t>
+          <t>2026-06-30T15:43:38.331+07:00</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:44</t>
+          <t>2026-09-30 12:32:29</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R5EF (Ryzen 5 7640HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>33390000</v>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
+        <v>85990000</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr"/>
+      <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r5ef</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:23:17.905+07:00</t>
+          <t>2026-09-22T17:51:09.908+07:00</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:49</t>
+          <t>2026-09-30 12:32:34</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R9EH (Ryzen 7 7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming GIGABYTE AORUS Master 16 6XJM4VNE64SH (Ryzen 9 9955HX3D/ RTX 5070 Ti 12GB/ 32GB/ 1TB/ 16" QHD+ OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="C86" s="2" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>-8%</t>
-        </is>
-      </c>
+        <v>86990000</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r9eh</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aorus-master-16-6xjm4vne64sh-ryzen-9-9955hx3d-rtx-5070-ti-12gb-32gb-1tb-16-qhd-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T15:05:48.951+07:00</t>
+          <t>2026-09-24T11:46:50.068+07:00</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:54</t>
+          <t>2026-09-30 12:32:39</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-556L (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 83RQ00DBVN (Core 3-304/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>38890000</v>
-      </c>
-      <c r="C87" s="2" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>-0%</t>
-        </is>
-      </c>
+        <v>24990000</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr"/>
+      <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Tay cầm Acer Nitro Controller NGR300 Wireless White (trị giá 1.200.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-556l</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-14iwc11-83rq00dbvn-core-3-304-8gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:27:47.558+07:00</t>
+          <t>2026-09-07T10:16:44.995+07:00</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:59</t>
+          <t>2026-09-30 12:32:44</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-78MD (Core 7-240H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB005YVN (Ryzen 5-125/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>40890000</v>
-      </c>
-      <c r="C88" s="2" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>-0%</t>
-        </is>
-      </c>
+        <v>25990000</v>
+      </c>
+      <c r="C88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Tay cầm Acer Nitro Controller NGR300 Wireless White (trị giá 1.200.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
-        </is>
-      </c>
+      <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-78md</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb005yvn-ryzen-5-125-8gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:28:06.595+07:00</t>
+          <t>2026-08-13T15:01:44.794+07:00</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:04</t>
+          <t>2026-09-30 12:32:49</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-71T9 (Core 7-240H/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB0060VN (Ryzen 7-155/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>43990000</v>
+        <v>27990000</v>
       </c>
       <c r="C89" s="2" t="inlineStr"/>
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
-        </is>
-      </c>
+      <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-71t9</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb0060vn-ryzen-7-155-8gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:29:41.759+07:00</t>
+          <t>2026-08-13T14:35:59.897+07:00</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:09</t>
+          <t>2026-09-30 12:32:54</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-782F (Core 7-240H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 83S1003GVN</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="C90" s="2" t="inlineStr"/>
-      <c r="D90" s="2" t="inlineStr"/>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
-        </is>
-      </c>
+        <v>44540000</v>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>47990000</v>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-782f</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-83s1003gvn</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T10:05:04.439+07:00</t>
+          <t>2026-08-28T10:29:16.152+07:00</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:14</t>
+          <t>2026-09-30 12:32:59</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-I51-71MF (Ultra 7-355/ RTX 5070 8GB/ 32GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 OLED 83S1006RVN (Ryzen AI 7-445/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>76990000</v>
+        <v>32990000</v>
       </c>
       <c r="C91" s="2" t="inlineStr"/>
       <c r="D91" s="2" t="inlineStr"/>
@@ -4217,864 +4125,838 @@
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-i51-71mf-ultra-7-355-rtx-5070-8gb-32gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-oled-83s1006rvn-ryzen-ai-7-445-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T11:40:49.662+07:00</t>
+          <t>2026-08-13T11:54:44.05+07:00</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:20</t>
+          <t>2026-09-30 12:33:04</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-71-58WQ (Core 5-210H/ RTX 5050/ 32GB/ 512GB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00ABVN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>44890000</v>
-      </c>
-      <c r="C92" s="2" t="n">
-        <v>45990000</v>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>30990000</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr"/>
+      <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16s-71-58wq</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00abvn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T10:25:14.809+07:00</t>
+          <t>2026-08-13T14:05:59.687+07:00</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:25</t>
+          <t>2026-09-30 12:33:09</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R9CN (Ryzen AI 7 350/ RTX 5070 8GB/ 32GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00F5VN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>62990000</v>
+        <v>34990000</v>
       </c>
       <c r="C93" s="2" t="inlineStr"/>
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-s-ai-propanel-an16s-61-r9cn</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00f5vn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T09:15:37.613+07:00</t>
+          <t>2026-09-07T10:17:34.624+07:00</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:30</t>
+          <t>2026-09-30 12:33:14</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50RB (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002EVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="C94" s="2" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>-14%</t>
-        </is>
-      </c>
+        <v>55990000</v>
+      </c>
+      <c r="C94" s="2" t="inlineStr"/>
+      <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50rb</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002evn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T11:11:52.657+07:00</t>
+          <t>2026-08-13T10:21:35.763+07:00</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:35</t>
+          <t>2026-09-30 12:33:20</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50VA (Core 5-210H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002FVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>28990000</v>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v>33990000</v>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>-15%</t>
-        </is>
-      </c>
+        <v>55990000</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr"/>
+      <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50va</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002fvn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T11:03:23.184+07:00</t>
+          <t>2026-08-12T20:29:51.634+07:00</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:40</t>
+          <t>2026-09-30 12:33:25</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-73Z8 (Core 7-240H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0075VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>33490000</v>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v>37990000</v>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>46990000</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr"/>
+      <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
-        </is>
-      </c>
+      <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0075vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:08:20.8+07:00</t>
+          <t>2026-09-07T10:19:34.771+07:00</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:45</t>
+          <t>2026-09-30 12:33:30</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0076VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>42590000</v>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v>43990000</v>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>46990000</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr"/>
+      <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0076vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T19:07:42.806+07:00</t>
+          <t>2026-09-07T10:20:20.027+07:00</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:50</t>
+          <t>2026-09-30 12:33:36</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK0015VN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>42990000</v>
-      </c>
-      <c r="C98" s="2" t="n">
-        <v>45990000</v>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>72990000</v>
+      </c>
+      <c r="C98" s="2" t="inlineStr"/>
+      <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk0015vn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T09:31:41.277+07:00</t>
+          <t>2026-09-07T10:21:45.74+07:00</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:55</t>
+          <t>2026-09-30 12:33:41</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK006GVN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>54990000</v>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v>58690000</v>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>72990000</v>
+      </c>
+      <c r="C99" s="2" t="inlineStr"/>
+      <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk006gvn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T10:40:22.072+07:00</t>
+          <t>2026-09-07T10:23:05.36+07:00</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:00</t>
+          <t>2026-09-30 12:33:46</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 POLED 83QK009PVN (Ultra X9-378H/ 32GB/ 1TB/ 14" 2.8K WQXGA POLED Touch/ Win 11)</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>32490000</v>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v>36990000</v>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>70990000</v>
+      </c>
+      <c r="C100" s="2" t="inlineStr"/>
+      <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-poled-83qk009pvn-ultra-x9-378h-32gb-1tb-14-2-8k-wqxga-poled-touch-win-11</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T09:59:34.507+07:00</t>
+          <t>2026-08-12T20:11:25.828+07:00</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:05</t>
+          <t>2026-09-30 12:33:51</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios 18 AI PH18-I71-91UX (Ultra 9-290HX Plus/ RTX 5080 16GB/ 64GB/ 3TB/ 18" 2K+ Mini LED 250Hz/ Win 11)</t>
+          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>179990000</v>
+        <v>33900000</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>181990000</v>
+        <v>34900000</v>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 3072 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 18 inch | Độ phân giải: 2K+ (2560x1600)</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-18-ai-ph18-i71-91ux-ultra-9-290hx-rtx-5080-16gb-16gb-3tb-18-2k-mini-led-250hz</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T13:30:49.416+07:00</t>
+          <t>2026-07-01T13:39:36.938+07:00</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:10</t>
+          <t>2026-09-30 12:33:56</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios 18 PH18-I71-975R (Ultra 9-290HX Plus/ RTX 5090 24GB/ 64GB/ 3TB/ 18" 4K+ Mini LED 120Hz/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>249990000</v>
-      </c>
-      <c r="C102" s="2" t="inlineStr"/>
-      <c r="D102" s="2" t="inlineStr"/>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
-        </is>
-      </c>
+        <v>36900000</v>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>37900000</v>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 3072 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 18 inch | Độ phân giải: UHD+ (3840x2400) | Tần số quét: 120 Hz</t>
-        </is>
-      </c>
+      <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-18-ai-ph18-i71-975r-ultra-9-290hx-rtx-5090-24gb-64gb-3tb-18-4k-mini-led-120hz</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T11:56:13.749+07:00</t>
+          <t>2026-07-01T13:34:21.041+07:00</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:15</t>
+          <t>2026-09-30 12:34:01</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo PHN16-I71-9779 (Ultra 9-290HX Plus/ RTX 5070 8GB/ 64GB/ 2TB/ 16" WQXGA IPS 180Hz/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>109990000</v>
-      </c>
-      <c r="C103" s="2" t="inlineStr"/>
-      <c r="D103" s="2" t="inlineStr"/>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
-        </is>
-      </c>
+        <v>44900000</v>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>46490000</v>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
-        </is>
-      </c>
+      <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-ai-phn16-i71-9779-ultra-9-290hx-rtx-5070-8gb-64gb-2tb-16-2k-ips-180hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:35:07.531+07:00</t>
+          <t>2026-07-01T13:43:00.949+07:00</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:20</t>
+          <t>2026-09-30 12:34:06</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo PHN16-I71-97VK (Ultra 9-290HX Plus/ RTX 5080 16GB/ 32GB/ 512GB/ 16" WQAGA 240Hz/ Win 11)</t>
+          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>104990000</v>
-      </c>
-      <c r="C104" s="2" t="inlineStr"/>
-      <c r="D104" s="2" t="inlineStr"/>
+        <v>23990000</v>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>24990000</v>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-ai-phn16-i71-97vk-ultra-9-290hx-rtx-5080-16gb-16gb-512gb-16-2k-ips-240hz</t>
+          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:33:09.575+07:00</t>
+          <t>2026-07-01T13:36:48.562+07:00</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:25</t>
+          <t>2026-09-30 12:34:12</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-91K5 (I9-14900HX/ RTX 5070 8GB/ 32GB/ 1TB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
+          <t>Laptop gaming MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>89990000</v>
-      </c>
-      <c r="C105" s="2" t="inlineStr"/>
-      <c r="D105" s="2" t="inlineStr"/>
+        <v>61990000</v>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>62990000</v>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: i9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-91k5-i9-14900hx-rtx-5070-8gb-32gb-1tb-16-2k-ips-180hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T13:27:14.879+07:00</t>
+          <t>2026-09-23T15:49:38.229+07:00</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:30</t>
+          <t>2026-09-30 12:34:17</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>114990000</v>
+        <v>34690000</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>129900000</v>
+        <v>37990000</v>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
+          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17T10:38:12.773+07:00</t>
+          <t>2026-09-21T10:28:18.636+07:00</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:35</t>
+          <t>2026-09-30 12:34:22</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 512GB/ 16" 2K+ OLED 165Hz/ Win 11)</t>
+          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>80990000</v>
-      </c>
-      <c r="C107" s="2" t="inlineStr"/>
-      <c r="D107" s="2" t="inlineStr"/>
+        <v>25490000</v>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>25990000</v>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
-        </is>
-      </c>
+      <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T11:50:52.42+07:00</t>
+          <t>2026-06-25T15:41:40.106+07:00</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:41</t>
+          <t>2026-09-30 12:34:28</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 32GB/ 512GB/ 16" 2K+ OLED 165Hz/ Win 11)</t>
+          <t>Laptop MSI Modern 14S AI+ G3MG-050VN (Ultra 7-355/ 16GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>77990000</v>
+        <v>36490000</v>
       </c>
       <c r="C108" s="2" t="inlineStr"/>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-14s-ai-g3mg-050vn-ultra-7-355-16gb-1tb-14-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T11:52:22.882+07:00</t>
+          <t>2026-09-22T17:51:58.168+07:00</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:46</t>
+          <t>2026-09-30 12:34:33</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070 8GB/ 32GB/ 2TB/ 14.5" 2.8K+/ Win 11)</t>
+          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>93990000</v>
-      </c>
-      <c r="C109" s="2" t="inlineStr"/>
-      <c r="D109" s="2" t="inlineStr"/>
+        <v>22190000</v>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>22690000</v>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo gaming Acer Predator Robust PBG470 (trị giá 3.500.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 14.5 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:43:12.906+07:00</t>
+          <t>2026-07-09T15:28:04.144+07:00</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:51</t>
+          <t>2026-09-30 12:34:38</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Triton Neo 16 PTN16-51-78JQ (Ultra 7-155H/ RTX 4060/ 32GB/ 2TB/ 16.0" 2.5K/ Win 11)</t>
+          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>49990000</v>
+        <v>43990000</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>52490000</v>
+        <v>44990000</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 4060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-neo-16-ptn16-51-78jq</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T16:42:43.256+07:00</t>
+          <t>2026-06-25T15:49:42.234+07:00</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:56</t>
+          <t>2026-09-30 12:34:43</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>27540000</v>
+        <v>33990000</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>30300000</v>
+        <v>34990000</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr"/>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 7 | Dung lượng SSD: 1024 GB | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12T11:35:32.312+07:00</t>
+          <t>2026-06-25T16:07:23.364+07:00</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:47:01</t>
+          <t>2026-09-30 12:34:48</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G G614PH-RV176W (Ryzen 9/ RTX 5050/ 16GB/ 512GB/ 16" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>49990000</v>
-      </c>
-      <c r="C112" s="2" t="inlineStr"/>
-      <c r="D112" s="2" t="inlineStr"/>
+        <v>37990000</v>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5083,40 +4965,40 @@
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 13.3 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g-g614ph-rv176w-ryzen-9-rtx-5050-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:47:04.096+07:00</t>
+          <t>2026-08-17T11:20:56.718+07:00</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:47:06</t>
+          <t>2026-09-30 12:34:53</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G16 G614PH-S5101W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 240Hz/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN (Ultra 7-355/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>47490000</v>
+        <v>44490000</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>53990000</v>
+        <v>48990000</v>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5127,33 +5009,33 @@
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel® Arc™ graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-s5101w</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T11:28:04.811+07:00</t>
+          <t>2026-09-28T10:53:12.84+07:00</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:47:11</t>
+          <t>2026-09-30 12:34:58</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G16 G614PH-TS118W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>52990000</v>
+        <v>59990000</v>
       </c>
       <c r="C114" s="2" t="inlineStr"/>
       <c r="D114" s="2" t="inlineStr"/>
@@ -5163,86 +5045,68 @@
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
-        </is>
-      </c>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-ts118w</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T11:49:35.857+07:00</t>
+          <t>2026-06-30T09:54:52.677+07:00</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:47:16</t>
+          <t>2026-09-30 12:35:03</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G16 G614PM-TS147W (Ryzen 9-8940HX/ RTX 5060 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>54690000</v>
-      </c>
-      <c r="C115" s="2" t="n">
         <v>59990000</v>
       </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+      <c r="C115" s="2" t="inlineStr"/>
+      <c r="D115" s="2" t="inlineStr"/>
+      <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
-        </is>
-      </c>
+      <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614pm-ts147w</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:15:11.541+07:00</t>
+          <t>2026-06-30T10:17:43.984+07:00</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:47:21</t>
+          <t>2026-09-30 12:35:09</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0442WS (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/ RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>37190000</v>
+        <v>82990000</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>39990000</v>
+        <v>83990000</v>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -5253,40 +5117,40 @@
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc 140V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0442ws-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T09:55:42.594+07:00</t>
+          <t>2026-09-23T15:48:57.837+07:00</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:43:44</t>
+          <t>2026-09-30 12:35:14</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0450WS (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>29790000</v>
+        <v>86990000</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>31990000</v>
+        <v>87990000</v>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -5297,697 +5161,781 @@
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc 130V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0450ws-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T09:56:18.911+07:00</t>
+          <t>2026-09-22T17:54:02.495+07:00</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:43:49</t>
+          <t>2026-09-30 12:35:19</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>199990000</v>
-      </c>
-      <c r="C118" s="2" t="inlineStr"/>
-      <c r="D118" s="2" t="inlineStr"/>
+        <v>22990000</v>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Card đồ họa: Card đồ họa tích hợp - Qualcomm® Adreno™ | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T11:12:30.954+07:00</t>
+          <t>2026-07-16T09:43:41.692+07:00</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:43:54</t>
+          <t>2026-09-30 12:32:24</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB027W (Core 3/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>22990000</v>
-      </c>
-      <c r="C119" s="2" t="inlineStr"/>
-      <c r="D119" s="2" t="inlineStr"/>
+        <v>23990000</v>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>25990000</v>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel® ARC™ Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb027w-core-3-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:52:41.33+07:00</t>
+          <t>2026-07-16T15:00:45.83+07:00</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:43:59</t>
+          <t>2026-09-30 12:32:29</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB029W (Core 7/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M (Ultra 9-185H/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>35490000</v>
-      </c>
-      <c r="C120" s="2" t="inlineStr"/>
-      <c r="D120" s="2" t="inlineStr"/>
+        <v>29890000</v>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>29990000</v>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>-0%</t>
+        </is>
+      </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb029w-core-7-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-16gb-512gb-14-fhd-ips-win-11</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T15:05:22.575+07:00</t>
+          <t>2026-09-25T10:22:17.071+07:00</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:04</t>
+          <t>2026-09-30 12:32:35</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB220W (Core 7/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>30490000</v>
-      </c>
-      <c r="C121" s="2" t="inlineStr"/>
-      <c r="D121" s="2" t="inlineStr"/>
+        <v>22990000</v>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>25990000</v>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb220w-core-7-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:43:31.989+07:00</t>
+          <t>2026-09-11T21:08:15.03+07:00</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:09</t>
+          <t>2026-09-30 12:32:41</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1404V (Core 5-120U/ 8GB/ 256GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>16590000</v>
+        <v>20990000</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>18990000</v>
+        <v>21990000</v>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon 680M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404v-core-5-120u-8gb-256gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T13:41:37.603+07:00</t>
+          <t>2026-07-17T09:17:18.78+07:00</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:14</t>
+          <t>2026-09-30 12:32:46</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VA-EB355W (Core 7-150U/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR (Ryzen 5-3500U/ 8GB/ 512GB/ 14" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="C123" s="2" t="inlineStr"/>
-      <c r="D123" s="2" t="inlineStr"/>
+        <v>17990000</v>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>19990000</v>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb355w-core-7-150u-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:17:32.016+07:00</t>
+          <t>2026-09-24T20:43:49.815+07:00</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:19</t>
+          <t>2026-09-30 12:32:51</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VA-EB609W (Core 3-100U/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>21990000</v>
-      </c>
-      <c r="C124" s="2" t="inlineStr"/>
-      <c r="D124" s="2" t="inlineStr"/>
+        <v>22890000</v>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>23990000</v>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb609w-core-3-100u-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:33:25.424+07:00</t>
+          <t>2026-09-24T15:44:03.513+07:00</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:24</t>
+          <t>2026-09-30 12:32:56</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VAP-V14.C58256 (Core 5-120U/ 16GB/ 256GB/ 14" FHD IPS/ Win 11/ Quiet Blue)</t>
+          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>17890000</v>
+        <v>24990000</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>18990000</v>
+        <v>25990000</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404vap-v14-c58256-core-5-120u-8gb-256gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:42:34.369+07:00</t>
+          <t>2026-09-25T10:20:56.552+07:00</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:29</t>
+          <t>2026-09-30 12:33:01</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus VivoBook 14 X1407AA-LY360W (Ultra 5-325/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-76KR (Core 7-350/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>26490000</v>
+        <v>25990000</v>
       </c>
       <c r="C126" s="2" t="n">
         <v>26990000</v>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407aa-ly360w-ultra-5-325-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-76kr-core-7-350-8gb-512gb</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T15:46:33.275+07:00</t>
+          <t>2026-09-24T15:44:29.405+07:00</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:34</t>
+          <t>2026-09-30 12:33:06</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1407CA-LY203W (Ultra 5-225H/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>33490000</v>
-      </c>
-      <c r="C127" s="2" t="inlineStr"/>
-      <c r="D127" s="2" t="inlineStr"/>
+        <v>17990000</v>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407ca-ly203w-ultra-5-225h-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T10:22:08.041+07:00</t>
+          <t>2026-09-24T09:51:43.721+07:00</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:39</t>
+          <t>2026-09-30 12:33:12</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504MA-BQ632W (Core 5-320/ 8GB/ 512GB/ 15" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>26990000</v>
-      </c>
-      <c r="C128" s="2" t="inlineStr"/>
-      <c r="D128" s="2" t="inlineStr"/>
+        <v>19590000</v>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>21990000</v>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq632w-core-5-320-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T15:43:54.381+07:00</t>
+          <t>2026-09-25T09:03:23.812+07:00</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:44</t>
+          <t>2026-09-30 12:33:17</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504MA-BQ633W (Core 7-350/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5-3500U/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>30490000</v>
-      </c>
-      <c r="C129" s="2" t="inlineStr"/>
-      <c r="D129" s="2" t="inlineStr"/>
+        <v>16790000</v>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>19990000</v>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>-16%</t>
+        </is>
+      </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq633w-core-7-350-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:47:34.397+07:00</t>
+          <t>2026-09-25T16:09:40.061+07:00</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:49</t>
+          <t>2026-09-30 12:33:22</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504VA-BQ165W (Core 5-120U/ 8GB/ 512GB/ 15" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-411P-R1CM (Ryzen 5 3500U/ 8GB/ 256GB)</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>20990000</v>
-      </c>
-      <c r="C130" s="2" t="inlineStr"/>
-      <c r="D130" s="2" t="inlineStr"/>
+        <v>17990000</v>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>18990000</v>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504va-bq165w-core-5-120u-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r1cm-ryzen-5-3500u-8gb-256gb</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:12:00.028+07:00</t>
+          <t>2026-07-06T14:26:56.746+07:00</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:54</t>
+          <t>2026-09-30 12:33:27</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 16 X1607CA-MB387W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-411P-R7YP (Ryzen 3 3200U/ 8GB/ 256GB)</t>
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>33490000</v>
-      </c>
-      <c r="C131" s="2" t="inlineStr"/>
-      <c r="D131" s="2" t="inlineStr"/>
+        <v>15990000</v>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>16990000</v>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 3 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb387w-ultra-5-225h-16gb-512gb-16-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r7yp-ryzen-3-3200u-8gb-256gb</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T16:08:06.906+07:00</t>
+          <t>2026-07-06T14:48:50.246+07:00</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:59</t>
+          <t>2026-09-30 12:33:32</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 16 X1607CA-MB399W (Ultra 7-255H/ 16GB/ 512GB/ 16" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-49P-R6XX (Ryzen 5 7430U/ 8GB/ 512GB/15.6"/ Win 11)</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>36490000</v>
-      </c>
-      <c r="C132" s="2" t="inlineStr"/>
-      <c r="D132" s="2" t="inlineStr"/>
+        <v>18590000</v>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>20990000</v>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb399w-ultra-7-255h-16gb-512gb-16-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-49p-r6xx-ryzen-5-7430u-8gb-512gb-15-6-win-11</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T15:36:19.591+07:00</t>
+          <t>2026-08-21T13:56:25.879+07:00</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:04</t>
+          <t>2026-09-30 12:33:38</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Flip TP3407AA-SG029W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>41990000</v>
-      </c>
-      <c r="C133" s="2" t="inlineStr"/>
-      <c r="D133" s="2" t="inlineStr"/>
+        <v>18890000</v>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>24990000</v>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>-24%</t>
+        </is>
+      </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-flip-tp3407aa-sg029w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T14:55:40.249+07:00</t>
+          <t>2026-08-24T10:45:08.009+07:00</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:09</t>
+          <t>2026-09-30 12:33:43</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ4821W (Ryzen 5/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>22990000</v>
-      </c>
-      <c r="C134" s="2" t="inlineStr"/>
-      <c r="D134" s="2" t="inlineStr"/>
+        <v>24990000</v>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>27990000</v>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel® Arc™ Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1504fa-bq4821w-ryzen-5-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:55:57.447+07:00</t>
+          <t>2026-07-16T15:19:10.843+07:00</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:14</t>
+          <t>2026-09-30 12:33:48</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ340W (Ryzen 5/ 16GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop Acer Swift Air 14 AI SFA14-I31-54A2 (Core 5-320/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Blue/ Win 11)</t>
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>28490000</v>
+        <v>24990000</v>
       </c>
       <c r="C135" s="2" t="inlineStr"/>
       <c r="D135" s="2" t="inlineStr"/>
@@ -5997,392 +5945,424 @@
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-go-15-e1504fa-bq340w-ryzen-5-16gb-512gb-156-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-air-14-ai-sfa14-i31-54a2-core-5-320-12gb-512gb-14-fhd-ips-120hz-blue-win-11</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:55:13.502+07:00</t>
+          <t>2026-09-30T10:04:26.762+07:00</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:20</t>
+          <t>2026-09-30 12:33:53</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 M3407KA-SF034W (Ryzen AI 5-330/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF (Core 3-304/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>33990000</v>
+        <v>21990000</v>
       </c>
       <c r="C136" s="2" t="inlineStr"/>
       <c r="D136" s="2" t="inlineStr"/>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-m3407ka-sf034w-ryzen-ai-5-330-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-34nf-core-3-304-12gb-512gb-14-fhd-ips-120hz-win-11</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T12:02:07.653+07:00</t>
+          <t>2026-09-23T13:32:07.536+07:00</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:25</t>
+          <t>2026-09-30 12:33:58</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407AA-SF945W (Ultra 5-325/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV (Core 5-320/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>37490000</v>
-      </c>
-      <c r="C137" s="2" t="inlineStr"/>
-      <c r="D137" s="2" t="inlineStr"/>
+        <v>23490000</v>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>24990000</v>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf945w-ultra-5-325-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-52bv-core-5-320-12gb-512gb-14-wuxga-ips-120hz-win-11</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T11:09:17.449+07:00</t>
+          <t>2026-09-25T16:09:22.19+07:00</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:30</t>
+          <t>2026-09-30 12:34:03</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407VA-LY147W (Core 5-210H/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="C138" s="2" t="inlineStr"/>
-      <c r="D138" s="2" t="inlineStr"/>
+        <v>28990000</v>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407va-ly147w-core-5-210h-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T11:42:14.925+07:00</t>
+          <t>2026-09-25T16:07:37.902+07:00</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:35</t>
+          <t>2026-09-30 12:34:08</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS VivoBook S14 S3407CA-SF913W (Ultra 5-225H/ 16GB/ 512GB/ 14" OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>27890000</v>
+        <v>49990000</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>29990000</v>
+        <v>54990000</v>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® Arc™ B390 GPU (đồ họa tích hợp) | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s14-s3407ca-sf913w-ultra-5-225h-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T13:01:54.572+07:00</t>
+          <t>2026-08-28T15:51:47.551+07:00</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:40</t>
+          <t>2026-09-30 12:34:13</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UM3406GA-QD075W (Ryzen 7/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Acer Swift Go AI OLED SFG14-75-765M (Ultra 7-258V/ 32GB/ 512GB/ 14" FHD+ OLED/ Win11)</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
         <v>39990000</v>
       </c>
-      <c r="C140" s="2" t="inlineStr"/>
-      <c r="D140" s="2" t="inlineStr"/>
+      <c r="C140" s="2" t="n">
+        <v>40990000</v>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® Arc™ Graphics 140V | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ga-qd075w-ryzen-7-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-ai-oled-sfg14-75-765m-14-fhd-oled-u7-258v-32lp-512gb-win</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T16:03:07.024+07:00</t>
+          <t>2026-08-14T10:47:31.44+07:00</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:45</t>
+          <t>2026-09-30 12:34:19</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1531W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED)</t>
+          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>42990000</v>
+        <v>32999000</v>
       </c>
       <c r="C141" s="2" t="inlineStr"/>
       <c r="D141" s="2" t="inlineStr"/>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1531w-ultra-9-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T08:45:55.514+07:00</t>
+          <t>2026-09-15T14:38:31.288+07:00</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:50</t>
+          <t>2026-09-30 12:34:24</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1713W (Ultra 5-225H/ 16GB/ 512GB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>30990000</v>
+        <v>31490000</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>38990000</v>
+        <v>32490000</v>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® Arc™ 130T Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1713w-ultra-5-225h-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:16:16.703+07:00</t>
+          <t>2026-09-24T14:08:34.772+07:00</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:55</t>
+          <t>2026-09-30 12:34:29</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST630W (Ultra 7-255H/ 16GB/ 512GB/ 14" 3K OLED)</t>
+          <t>Laptop Acer Swift X SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" 2.8K OLED/ Win 11/ Office)</t>
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="C143" s="2" t="inlineStr"/>
-      <c r="D143" s="2" t="inlineStr"/>
+        <v>35990000</v>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>45990000</v>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>-22%</t>
+        </is>
+      </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6 | Kích thước màn hình: 14.5 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st630w-ultra-7-255h-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T15:05:39.807+07:00</t>
+          <t>2026-09-14T15:56:38.644+07:00</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:00</t>
+          <t>2026-09-30 12:34:34</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3407NA-QD132WS (Snapdragon X2 Elite X2E-88-100/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>48990000</v>
-      </c>
-      <c r="C144" s="2" t="inlineStr"/>
-      <c r="D144" s="2" t="inlineStr"/>
+        <v>43990000</v>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>49490000</v>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: RTX 4060 | Kích thước màn hình: 14.5 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd132ws-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:47:13.916+07:00</t>
+          <t>2026-07-03T15:10:56.836+07:00</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:05</t>
+          <t>2026-09-30 12:34:39</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook A14 UX3407NA-QD254W (Snapdragon X2 Elite X2E-88-100/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H08-50W (Core 5-210H/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>63990000</v>
-      </c>
-      <c r="C145" s="2" t="inlineStr"/>
-      <c r="D145" s="2" t="inlineStr"/>
+        <v>19490000</v>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>21990000</v>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6391,36 +6371,42 @@
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd254w-32gb-1tb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h08-50w</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:46:55.101+07:00</t>
+          <t>2026-07-31T11:09:14.14+07:00</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:10</t>
+          <t>2026-09-30 12:34:44</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook A16 UX3607OA-SQ137WS (Snapdragon X2 Elite Extreme X2E94100/ 24GB/ 512GB/ 16" 3K OLED/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1 P1403CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>58990000</v>
-      </c>
-      <c r="C146" s="2" t="inlineStr"/>
-      <c r="D146" s="2" t="inlineStr"/>
+        <v>24290000</v>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>26990000</v>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6429,74 +6415,82 @@
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 16 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 24 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-16-ux3607oa-sq137ws-24gb-512gb-16-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h16-63ws-core-5-210h-16gb-512gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:43:18.337+07:00</t>
+          <t>2026-08-03T15:06:02.246+07:00</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:15</t>
+          <t>2026-09-30 12:34:49</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN138WS (Ultra X9/ 32GB/ 1TB/ 14" 3K OLED Touch 144Hz)</t>
+          <t>Laptop Asus ExpertBook P1 P1403CVA-C7H16-50W (Core 7-240H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>89990000</v>
-      </c>
-      <c r="C147" s="2" t="inlineStr"/>
-      <c r="D147" s="2" t="inlineStr"/>
+        <v>28990000</v>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
-        </is>
-      </c>
+      <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn138ws-ultra-x9-32gb-1tb-14-3k-oled-touch-144hz</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c7h16-50w-core-7-240h-16gb-512gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T12:04:03.945+07:00</t>
+          <t>2026-08-03T14:43:57.168+07:00</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:20</t>
+          <t>2026-09-30 12:34:54</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN439WS (Ultra X7/ 32GB/ 512GB/ 14" 3K OLED Touch 144Hz)</t>
+          <t>Laptop Asus ExpertBook P1 P1503CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>82990000</v>
-      </c>
-      <c r="C148" s="2" t="inlineStr"/>
-      <c r="D148" s="2" t="inlineStr"/>
+        <v>24290000</v>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>26990000</v>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6505,36 +6499,42 @@
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn439ws-ultra-x7-32gb-512gb-14-3k-oled-touch-144hz</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1503cva-c5h16-63ws-core-5-210h-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T11:44:06.982+07:00</t>
+          <t>2026-08-03T14:03:33.213+07:00</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:25</t>
+          <t>2026-09-30 12:35:00</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ProArt PX13 HN7306EA-LX050W (Ryzen AI Max+ 395/ 32GB/ 1TB/ 13.3" 3K OLED Touch)</t>
+          <t>Laptop Asus ExpertBook P1 P1403CVA-C3U08-50W (Core 3-100U/ 8GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>76990000</v>
-      </c>
-      <c r="C149" s="2" t="inlineStr"/>
-      <c r="D149" s="2" t="inlineStr"/>
+        <v>15490000</v>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>17990000</v>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6543,36 +6543,42 @@
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 13.3 inch | Dòng CPU: Ryzen AI MAX+ | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-pro-art-hn7306ea-lx050w-ryzen-ai-max-395-32gb-1tb-13-3-3k-oled-touch</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c3u08-50w</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:58:08.111+07:00</t>
+          <t>2026-07-31T13:53:40.042+07:00</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:30</t>
+          <t>2026-09-30 12:35:05</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook S 14 UX5406AA-SU348W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED Touch)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>50990000</v>
-      </c>
-      <c r="C150" s="2" t="inlineStr"/>
-      <c r="D150" s="2" t="inlineStr"/>
+        <v>23390000</v>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>27990000</v>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>-16%</t>
+        </is>
+      </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6581,36 +6587,42 @@
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-s-14-ux5406aa-su348w-ultra-9-16gb-512gb-14-3k-oled-touch</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T10:26:19.879+07:00</t>
+          <t>2026-08-12T10:19:47.487+07:00</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:35</t>
+          <t>2026-09-30 12:35:10</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook S 16 UM5606GA-SS441W (Ryzen AI 9 465/ 16GB/ 512GB/ 16" 3K OLED)</t>
+          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U516S8W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>49490000</v>
-      </c>
-      <c r="C151" s="2" t="inlineStr"/>
-      <c r="D151" s="2" t="inlineStr"/>
+        <v>26390000</v>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>29990000</v>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6619,40 +6631,40 @@
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ryzen AI 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-s-15-um5606ga-ss441w-ryzen-ai-9-465-16gb-512gb-15-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u516s8w-ultra-5-225h-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T16:22:14.948+07:00</t>
+          <t>2026-08-03T11:57:56.626+07:00</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:40</t>
+          <t>2026-09-30 12:35:15</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - 71092480 (I7-1355U/ 16GB/ 512GB/ Win 11/ Office/ Microsoft 365)</t>
+          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U716S8W (Ultra 7-255H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>25390000</v>
+        <v>32990000</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>25990000</v>
+        <v>34990000</v>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -6661,42 +6673,38 @@
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr"/>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-15-dc15250-71092480-i7-1355u-16gb-512gb-win-11-office-microsoft-365</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u716s8w-ultra-7-255h-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T10:56:32.257+07:00</t>
+          <t>2026-09-06T13:46:08.673+07:00</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:45</t>
+          <t>2026-09-30 12:35:20</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I3-100U/ 8GB/ 512GB/ 15.6" FHD 120Hz/DOS) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA / Win 11)</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>14390000</v>
+        <v>26390000</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>14990000</v>
+        <v>30490000</v>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -6707,40 +6715,40 @@
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i3-100u-8gb-512gb-15-6-fhd-120hz</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T10:44:17.994+07:00</t>
+          <t>2026-09-03T11:54:54.747+07:00</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:50</t>
+          <t>2026-09-30 12:35:25</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I5-1334U/ 8GB/ 512GB/ 15.6" FHD/DOS) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>15990000</v>
+        <v>32990000</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>17490000</v>
+        <v>35990000</v>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -6749,114 +6757,120 @@
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr"/>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
-        </is>
-      </c>
+      <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i5-1334u-8gb-512gb-15-6-fhd</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:07:57.107+07:00</t>
+          <t>2026-09-23T08:56:23.461+07:00</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:55</t>
+          <t>2026-09-30 12:35:30</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix SCAR G835LXG-TQ473W (Ultra 9-290HX Plus/ RTX 5090/ 64GB/ 2TB/ 18" Mini LED 240Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 G2 P5405CAA-NZ0223W (Ultra 7-356H/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>179990000</v>
-      </c>
-      <c r="C155" s="2" t="inlineStr"/>
-      <c r="D155" s="2" t="inlineStr"/>
+        <v>39190000</v>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>41990000</v>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr"/>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 18 inch | Độ phân giải: UHD+ (3840x2400) | Tần số quét: 240 Hz</t>
-        </is>
-      </c>
+      <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-scar-g835lxg-tq473w-ultra-9-290hx-plus-rtx-5090-64gb-2tb-18-qhd-mini-led-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-g2-p5405caa-nz0223w-ultra-7-356h-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:58:23.481+07:00</t>
+          <t>2026-08-03T11:12:45.933+07:00</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:43:53</t>
+          <t>2026-09-30 12:35:35</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU405AR-SY016W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0016W (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>96990000</v>
-      </c>
-      <c r="C156" s="2" t="inlineStr"/>
-      <c r="D156" s="2" t="inlineStr"/>
+        <v>28790000</v>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr"/>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
-        </is>
-      </c>
+      <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405ar-sy016w-ultra-9-rtx-5070-ti-32gb-1tb-14-3k-oled-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0016w-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:47:29.287+07:00</t>
+          <t>2026-08-03T10:54:41.9+07:00</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:43:58</t>
+          <t>2026-09-30 12:35:40</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU405AW-SY029W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0017W (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>119990000</v>
-      </c>
-      <c r="C157" s="2" t="inlineStr"/>
-      <c r="D157" s="2" t="inlineStr"/>
+        <v>36290000</v>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>38990000</v>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6865,36 +6879,42 @@
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: Arc | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405aw-sy029w-ultra-9-rtx-5080-32gb-1tb-14-3k-oled-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0017w-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:47:45.327+07:00</t>
+          <t>2026-09-10T13:51:05.888+07:00</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:04</t>
+          <t>2026-09-30 12:35:45</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR115W (Ultra 7-255H/ RTX 5070/ 16GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0442WS (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>74990000</v>
-      </c>
-      <c r="C158" s="2" t="inlineStr"/>
-      <c r="D158" s="2" t="inlineStr"/>
+        <v>37190000</v>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6903,36 +6923,42 @@
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Arc 140V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr115w-ultra-7-255h-rtx-5070-16gb-512gb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0442ws-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:46:00.864+07:00</t>
+          <t>2026-08-03T09:55:42.594+07:00</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:09</t>
+          <t>2026-09-30 12:32:10</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR141W (Ultra 7-255H/ RTX 5070/ 32GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0450WS (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>83990000</v>
-      </c>
-      <c r="C159" s="2" t="inlineStr"/>
-      <c r="D159" s="2" t="inlineStr"/>
+        <v>29790000</v>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>31990000</v>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6941,33 +6967,33 @@
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Arc 130V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr141w-ultra-7-255h-rtx-5070-32gb-512gb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0450ws-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:46:21.05+07:00</t>
+          <t>2026-08-03T09:56:18.911+07:00</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:14</t>
+          <t>2026-09-30 12:32:15</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AR-TB027W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>99990000</v>
+        <v>199990000</v>
       </c>
       <c r="C160" s="2" t="inlineStr"/>
       <c r="D160" s="2" t="inlineStr"/>
@@ -6979,33 +7005,33 @@
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ar-tb027w-ultra-9-rtx-5070-ti-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:10.531+07:00</t>
+          <t>2026-09-18T11:12:30.954+07:00</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:19</t>
+          <t>2026-09-30 12:32:21</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB052WS (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB027W (Core 3/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>139990000</v>
+        <v>22990000</v>
       </c>
       <c r="C161" s="2" t="inlineStr"/>
       <c r="D161" s="2" t="inlineStr"/>
@@ -7017,33 +7043,33 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb052ws-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb027w-core-3-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:28.879+07:00</t>
+          <t>2026-08-18T16:52:41.33+07:00</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:23</t>
+          <t>2026-09-30 12:32:26</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB121W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB029W (Core 7/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>124990000</v>
+        <v>35490000</v>
       </c>
       <c r="C162" s="2" t="inlineStr"/>
       <c r="D162" s="2" t="inlineStr"/>
@@ -7055,33 +7081,33 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb121w-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb029w-core-7-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:44.227+07:00</t>
+          <t>2026-08-20T15:05:22.575+07:00</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:28</t>
+          <t>2026-09-30 12:32:31</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AX-TB042WS (Ultra 9/ RTX 5090/ 64GB/ 2TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB220W (Core 7/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>169990000</v>
+        <v>30490000</v>
       </c>
       <c r="C163" s="2" t="inlineStr"/>
       <c r="D163" s="2" t="inlineStr"/>
@@ -7093,40 +7119,40 @@
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ax-tb042ws-ultra-9-rtx-5090-64gb-2tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb220w-core-7-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:44:50.259+07:00</t>
+          <t>2026-08-20T11:43:31.989+07:00</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:33</t>
+          <t>2026-09-30 12:32:36</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA 165Hz/ Win 11)</t>
+          <t>Laptop Asus Vivobook 14 X1404V (Core 5-120U/ 8GB/ 256GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>57390000</v>
+        <v>16590000</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>58990000</v>
+        <v>18990000</v>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -7137,42 +7163,36 @@
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404v-core-5-120u-8gb-256gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:35:45.75+07:00</t>
+          <t>2026-08-07T13:41:37.603+07:00</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:38</t>
+          <t>2026-09-30 12:32:41</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN329W (Ryzen 7-8845HS/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VA-EB355W (Core 7-150U/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>27690000</v>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>37490000</v>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>-26%</t>
-        </is>
-      </c>
+        <v>25990000</v>
+      </c>
+      <c r="C165" s="2" t="inlineStr"/>
+      <c r="D165" s="2" t="inlineStr"/>
       <c r="E165" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7181,42 +7201,36 @@
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn329w-ryzen-7-8845hs-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb355w-core-7-150u-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:04:13.749+07:00</t>
+          <t>2026-08-20T11:17:32.016+07:00</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:43</t>
+          <t>2026-09-30 12:32:46</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN390W (Ryzen 7-155/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VA-EB609W (Core 3-100U/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>28990000</v>
-      </c>
-      <c r="C166" s="2" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>21990000</v>
+      </c>
+      <c r="C166" s="2" t="inlineStr"/>
+      <c r="D166" s="2" t="inlineStr"/>
       <c r="E166" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7225,80 +7239,84 @@
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn390w-ryzen-7-155-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb609w-core-3-100u-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:05:26.118+07:00</t>
+          <t>2026-08-18T16:33:25.424+07:00</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:48</t>
+          <t>2026-09-30 12:32:51</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUG-RL129W (Ryzen 7-7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VAP-V14.C58256 (Core 5-120U/ 16GB/ 256GB/ 14" FHD IPS/ Win 11/ Quiet Blue)</t>
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>29990000</v>
+        <v>17890000</v>
       </c>
       <c r="C167" s="2" t="n">
-        <v>30990000</v>
+        <v>18990000</v>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr"/>
+          <t>-6%</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nug-rl129w-ryzen-7-7445hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404vap-v14-c58256-core-5-120u-8gb-256gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:41:09.162+07:00</t>
+          <t>2026-09-14T17:42:34.369+07:00</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:53</t>
+          <t>2026-09-30 12:32:56</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUQ-RL007W (Ryzen 7-170/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
+          <t>Laptop Asus VivoBook 14 X1407AA-LY360W (Ultra 5-325/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>36290000</v>
+        <v>26490000</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>39990000</v>
+        <v>26990000</v>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -7309,42 +7327,36 @@
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nuq-rl007w-ryzen-7-170-rtx-4050-6gb-16gb-512gb-16-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407aa-ly360w-ultra-5-325-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:10:34.588+07:00</t>
+          <t>2026-08-07T15:46:33.275+07:00</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:44:58</t>
+          <t>2026-09-30 12:33:01</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1407CA-LY203W (Ultra 5-225H/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>41260000</v>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v>45390000</v>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
+        <v>33490000</v>
+      </c>
+      <c r="C169" s="2" t="inlineStr"/>
+      <c r="D169" s="2" t="inlineStr"/>
       <c r="E169" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7353,33 +7365,33 @@
       <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407ca-ly203w-ultra-5-225h-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T14:06:48.719+07:00</t>
+          <t>2026-08-20T10:22:08.041+07:00</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:03</t>
+          <t>2026-09-30 12:33:06</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA401EA-RG041W (Ryzen AI Max+ 392/ 32GB/ 512GB/ 14" 2.5K/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 15 X1504MA-BQ632W (Core 5-320/ 8GB/ 512GB/ 15" FHD IPS)</t>
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>59990000</v>
+        <v>26990000</v>
       </c>
       <c r="C170" s="2" t="inlineStr"/>
       <c r="D170" s="2" t="inlineStr"/>
@@ -7391,33 +7403,33 @@
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI MAX+ | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon 8060S | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401ea-rg041w-ryzen-ai-max-392-32gb-512gb-14-2-5k-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq632w-core-5-320-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T09:33:26.048+07:00</t>
+          <t>2026-08-18T15:43:54.381+07:00</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:09</t>
+          <t>2026-09-30 12:33:11</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA401UH-RG001W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 15 X1504MA-BQ633W (Core 7-350/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>49990000</v>
+        <v>30490000</v>
       </c>
       <c r="C171" s="2" t="inlineStr"/>
       <c r="D171" s="2" t="inlineStr"/>
@@ -7429,33 +7441,33 @@
       <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401uh-rg001w-ryzen-7-260-rtx-5050-16gb-512gb-14-qhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq633w-core-7-350-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:59:55.007+07:00</t>
+          <t>2026-09-26T12:47:34.397+07:00</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:14</t>
+          <t>2026-09-30 12:33:17</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA401UM-RG049W (Ryzen 7 260/ RTX 5060/ 32GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 15 X1504VA-BQ165W (Core 5-120U/ 8GB/ 512GB/ 15" FHD IPS)</t>
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>64990000</v>
+        <v>20990000</v>
       </c>
       <c r="C172" s="2" t="inlineStr"/>
       <c r="D172" s="2" t="inlineStr"/>
@@ -7467,33 +7479,33 @@
       <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401um-rg049w-ryzen-7-260-rtx-5060-32gb-512gb-14-qhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504va-bq165w-core-5-120u-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T13:00:47.55+07:00</t>
+          <t>2026-08-18T16:12:00.028+07:00</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:19</t>
+          <t>2026-09-30 12:33:22</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA608UHI-TU121W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 16 X1607CA-MB387W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD IPS)</t>
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>48990000</v>
+        <v>33490000</v>
       </c>
       <c r="C173" s="2" t="inlineStr"/>
       <c r="D173" s="2" t="inlineStr"/>
@@ -7505,33 +7517,33 @@
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608uhi-tu121w-ryzen-7-260-rtx-5050-16gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb387w-ultra-5-225h-16gb-512gb-16-fhd-ips</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T11:22:30.725+07:00</t>
+          <t>2026-08-20T16:08:06.906+07:00</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:24</t>
+          <t>2026-09-30 12:33:27</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA608UMI-TU162W (Ryzen 7 260/ RTX 5060/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 16 X1607CA-MB399W (Ultra 7-255H/ 16GB/ 512GB/ 16" FHD IPS)</t>
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>51990000</v>
+        <v>36490000</v>
       </c>
       <c r="C174" s="2" t="inlineStr"/>
       <c r="D174" s="2" t="inlineStr"/>
@@ -7543,42 +7555,36 @@
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608umi-tu162w-ryzen-7-260-rtx-5060-16gb-512gb-16-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb399w-ultra-7-255h-16gb-512gb-16-fhd-ips</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T11:01:50.971+07:00</t>
+          <t>2026-08-20T15:36:19.591+07:00</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:29</t>
+          <t>2026-09-30 12:33:32</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS V16 V3607VJ-TK189W (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 16" WUXGA 144Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook Flip TP3407AA-SG029W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>26490000</v>
-      </c>
-      <c r="C175" s="2" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>41990000</v>
+      </c>
+      <c r="C175" s="2" t="inlineStr"/>
+      <c r="D175" s="2" t="inlineStr"/>
       <c r="E175" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7587,205 +7593,181 @@
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-v16-v3607vj-tk189w-core-5-210h-rtx-3050-6gb-16gb-512gb-16-wuxga-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-flip-tp3407aa-sg029w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T16:26:14.526+07:00</t>
+          <t>2026-08-18T14:55:40.249+07:00</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:34</t>
+          <t>2026-09-30 12:33:37</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ4821W (Ryzen 5/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>28790000</v>
-      </c>
-      <c r="C176" s="2" t="n">
-        <v>30790000</v>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>22990000</v>
+      </c>
+      <c r="C176" s="2" t="inlineStr"/>
+      <c r="D176" s="2" t="inlineStr"/>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1504fa-bq4821w-ryzen-5-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T11:00:26.909+07:00</t>
+          <t>2026-09-24T15:55:57.447+07:00</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:39</t>
+          <t>2026-09-30 12:33:42</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming GIGABYTE A16 CVHI3MY893SH (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ340W (Ryzen 5/ 16GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>36990000</v>
-      </c>
-      <c r="C177" s="2" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
+        <v>28490000</v>
+      </c>
+      <c r="C177" s="2" t="inlineStr"/>
+      <c r="D177" s="2" t="inlineStr"/>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3my893sh</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-go-15-e1504fa-bq340w-ryzen-5-16gb-512gb-156-fhd-ips</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T14:40:23.197+07:00</t>
+          <t>2026-09-24T15:55:13.502+07:00</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:44</t>
+          <t>2026-09-30 12:33:47</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 A16-3THK3VN893SH (Ryzen 7 260/ RTX 5050 8GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 M3407KA-SF034W (Ryzen AI 5-330/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="C178" s="2" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>33990000</v>
+      </c>
+      <c r="C178" s="2" t="inlineStr"/>
+      <c r="D178" s="2" t="inlineStr"/>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-ga63h-3thk3vn893sh</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-m3407ka-sf034w-ryzen-ai-5-330-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30T09:54:12.234+07:00</t>
+          <t>2026-08-18T12:02:07.653+07:00</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:49</t>
+          <t>2026-09-30 12:33:52</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9LJR2VNF93SH (Ryzen 5 7533HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407AA-SF945W (Ultra 5-325/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="C179" s="2" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>37490000</v>
+      </c>
+      <c r="C179" s="2" t="inlineStr"/>
+      <c r="D179" s="2" t="inlineStr"/>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr"/>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9ljr2vnf93sh-ryzen-5-7533hs-rtx-3050-6gb-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf945w-ultra-5-325-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T15:10:54.55+07:00</t>
+          <t>2026-08-18T11:09:17.449+07:00</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:54</t>
+          <t>2026-09-30 12:33:57</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9MJR2VNF93SH (Ryzen 5 7533HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407VA-LY147W (Core 5-210H/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B180" s="3" t="n">
@@ -7793,44 +7775,48 @@
       </c>
       <c r="C180" s="2" t="inlineStr"/>
       <c r="D180" s="2" t="inlineStr"/>
-      <c r="E180" s="2" t="inlineStr"/>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9mjr2vnf93sh-ryzen-5-7533hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407va-ly147w-core-5-210h-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:50:39.975+07:00</t>
+          <t>2026-08-18T11:42:14.925+07:00</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45:59</t>
+          <t>2026-09-30 12:34:02</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS VivoBook S14 S3407CA-SF913W (Ultra 5-225H/ 16GB/ 512GB/ 14" OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>115990000</v>
+        <v>27890000</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>117990000</v>
+        <v>29990000</v>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -7841,33 +7827,33 @@
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s14-s3407ca-sf913w-ultra-5-225h-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05T14:44:14.658+07:00</t>
+          <t>2026-09-26T13:01:54.572+07:00</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:04</t>
+          <t>2026-09-30 12:34:07</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15AHP11 83TN0040VN (Ryzen 7-250/ RTX 5050 8GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UM3406GA-QD075W (Ryzen 7/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>43990000</v>
+        <v>39990000</v>
       </c>
       <c r="C182" s="2" t="inlineStr"/>
       <c r="D182" s="2" t="inlineStr"/>
@@ -7879,42 +7865,36 @@
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15ahp11-83tn0040vn-ryzen-7-250-rtx-5050-8gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ga-qd075w-ryzen-7-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T09:36:14.406+07:00</t>
+          <t>2026-08-17T16:03:07.024+07:00</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:09</t>
+          <t>2026-09-30 12:34:12</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1531W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED)</t>
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="C183" s="2" t="n">
-        <v>41990000</v>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>42990000</v>
+      </c>
+      <c r="C183" s="2" t="inlineStr"/>
+      <c r="D183" s="2" t="inlineStr"/>
       <c r="E183" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7923,40 +7903,40 @@
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1531w-ultra-9-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:38.199+07:00</t>
+          <t>2026-08-18T08:45:55.514+07:00</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:14</t>
+          <t>2026-09-30 12:34:17</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S0006RVN (Ryzen 7-7735HS/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1713W (Ultra 5-225H/ 16GB/ 512GB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B184" s="3" t="n">
         <v>30990000</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>32990000</v>
+        <v>38990000</v>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -7967,33 +7947,33 @@
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0006rvn-ryzen-7-7735hs-rtx-3050-6gb-16gb-1tb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1713w-ultra-5-225h-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T11:31:57.635+07:00</t>
+          <t>2026-09-25T10:16:16.703+07:00</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:19</t>
+          <t>2026-09-30 12:34:22</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S000DCVN (Ryzen 7-170/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST630W (Ultra 7-255H/ 16GB/ 512GB/ 14" 3K OLED)</t>
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>32990000</v>
+        <v>40990000</v>
       </c>
       <c r="C185" s="2" t="inlineStr"/>
       <c r="D185" s="2" t="inlineStr"/>
@@ -8005,33 +7985,33 @@
       <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s000dcvn-ryzen-7-170-rtx-3050-6gb-16gb-1tb-15-6-fhd-ips-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st630w-ultra-7-255h-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T10:03:17.431+07:00</t>
+          <t>2026-08-17T15:05:39.807+07:00</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:24</t>
+          <t>2026-09-30 12:34:27</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003VVN (Core 5-205H/ RTX 3050 6GB/ 8GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3407NA-QD132WS (Snapdragon X2 Elite X2E-88-100/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>36990000</v>
+        <v>48990000</v>
       </c>
       <c r="C186" s="2" t="inlineStr"/>
       <c r="D186" s="2" t="inlineStr"/>
@@ -8043,33 +8023,33 @@
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 8 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003vvn-core-5-205h-rtx-3050-6gb-8gb-512gb-15-3-wuxga-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd132ws-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T19:41:42.305+07:00</t>
+          <t>2026-08-24T11:47:13.916+07:00</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:29</t>
+          <t>2026-09-30 12:34:32</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003WVN (Core 5-205H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
+          <t>Laptop ASUS Zenbook A14 UX3407NA-QD254W (Snapdragon X2 Elite X2E-88-100/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>41990000</v>
+        <v>63990000</v>
       </c>
       <c r="C187" s="2" t="inlineStr"/>
       <c r="D187" s="2" t="inlineStr"/>
@@ -8081,42 +8061,36 @@
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200)</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003wvn-core-5-205h-rtx-3050-6gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd254w-32gb-1tb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T16:50:55.152+07:00</t>
+          <t>2026-08-24T11:46:55.101+07:00</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:34</t>
+          <t>2026-09-30 12:34:37</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRX10 83JE01AGVN (I7-13645HX/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook A16 UX3607OA-SQ137WS (Snapdragon X2 Elite Extreme X2E94100/ 24GB/ 512GB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>39490000</v>
-      </c>
-      <c r="C188" s="2" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>58990000</v>
+      </c>
+      <c r="C188" s="2" t="inlineStr"/>
+      <c r="D188" s="2" t="inlineStr"/>
       <c r="E188" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -8125,42 +8099,36 @@
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 16 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 24 GB</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx10-83je01agvn</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-16-ux3607oa-sq137ws-24gb-512gb-16-3k-oled</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T16:43:38.321+07:00</t>
+          <t>2026-08-24T11:43:18.337+07:00</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:39</t>
+          <t>2026-09-30 12:34:42</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN138WS (Ultra X9/ 32GB/ 1TB/ 14" 3K OLED Touch 144Hz)</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>43990000</v>
-      </c>
-      <c r="C189" s="2" t="n">
-        <v>45990000</v>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>89990000</v>
+      </c>
+      <c r="C189" s="2" t="inlineStr"/>
+      <c r="D189" s="2" t="inlineStr"/>
       <c r="E189" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -8169,33 +8137,33 @@
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn138ws-ultra-x9-32gb-1tb-14-3k-oled-touch-144hz</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T16:32:05.969+07:00</t>
+          <t>2026-08-17T12:04:03.945+07:00</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:44</t>
+          <t>2026-09-30 12:34:47</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN439WS (Ultra X7/ 32GB/ 512GB/ 14" 3K OLED Touch 144Hz)</t>
         </is>
       </c>
       <c r="B190" s="3" t="n">
-        <v>33990000</v>
+        <v>82990000</v>
       </c>
       <c r="C190" s="2" t="inlineStr"/>
       <c r="D190" s="2" t="inlineStr"/>
@@ -8207,33 +8175,33 @@
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn439ws-ultra-x7-32gb-512gb-14-3k-oled-touch-144hz</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:23:00.628+07:00</t>
+          <t>2026-08-17T11:44:06.982+07:00</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:49</t>
+          <t>2026-09-30 12:34:52</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS ProArt PX13 HN7306EA-LX050W (Ryzen AI Max+ 395/ 32GB/ 1TB/ 13.3" 3K OLED Touch)</t>
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>31990000</v>
+        <v>76990000</v>
       </c>
       <c r="C191" s="2" t="inlineStr"/>
       <c r="D191" s="2" t="inlineStr"/>
@@ -8245,42 +8213,36 @@
       <c r="F191" s="2" t="inlineStr"/>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 13.3 inch | Dòng CPU: Ryzen AI MAX+ | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-pro-art-hn7306ea-lx050w-ryzen-ai-max-395-32gb-1tb-13-3-3k-oled-touch</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:25:26.316+07:00</t>
+          <t>2026-09-24T15:58:08.111+07:00</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:54</t>
+          <t>2026-09-30 12:34:57</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook S 14 UX5406AA-SU348W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED Touch)</t>
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="C192" s="2" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>50990000</v>
+      </c>
+      <c r="C192" s="2" t="inlineStr"/>
+      <c r="D192" s="2" t="inlineStr"/>
       <c r="E192" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -8289,33 +8251,33 @@
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-s-14-ux5406aa-su348w-ultra-9-16gb-512gb-14-3k-oled-touch</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:28:01.415+07:00</t>
+          <t>2026-08-17T10:26:19.879+07:00</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:59</t>
+          <t>2026-09-30 12:35:02</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Max C13WF-421VN (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop ASUS Zenbook S 16 UM5606GA-SS441W (Ryzen AI 9 465/ 16GB/ 512GB/ 16" 3K OLED)</t>
         </is>
       </c>
       <c r="B193" s="3" t="n">
-        <v>44990000</v>
+        <v>49490000</v>
       </c>
       <c r="C193" s="2" t="inlineStr"/>
       <c r="D193" s="2" t="inlineStr"/>
@@ -8327,22 +8289,198 @@
       <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ryzen AI 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13vf-421vn-i7-13620h-rtx-5060-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-s-15-um5606ga-ss441w-ryzen-ai-9-465-16gb-512gb-15-3k-oled</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T16:26:05.15+07:00</t>
+          <t>2026-09-24T16:22:14.948+07:00</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:47:04</t>
+          <t>2026-09-30 12:35:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Dell 15 DC15250 - 71092480 (I7-1355U/ 16GB/ 512GB/ Win 11/ Office/ Microsoft 365)</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="n">
+        <v>25390000</v>
+      </c>
+      <c r="C194" s="2" t="n">
+        <v>25990000</v>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr"/>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-dell-15-dc15250-71092480-i7-1355u-16gb-512gb-win-11-office-microsoft-365</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T10:56:32.257+07:00</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:35:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I3-100U/ 8GB/ 512GB/ 15.6" FHD 120Hz/DOS) - Nhập Khẩu Chính Hãng</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="n">
+        <v>14390000</v>
+      </c>
+      <c r="C195" s="2" t="n">
+        <v>14990000</v>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i3-100u-8gb-512gb-15-6-fhd-120hz</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21T10:44:17.994+07:00</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:35:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I5-1334U/ 8GB/ 512GB/ 15.6" FHD/DOS) - Nhập Khẩu Chính Hãng</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="n">
+        <v>15990000</v>
+      </c>
+      <c r="C196" s="2" t="n">
+        <v>17490000</v>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr"/>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i5-1334u-8gb-512gb-15-6-fhd</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:07:57.107+07:00</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:35:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Dell 16 DC16251 (I5-120U/ 8GB/ 512GB/ 16" FHD+ Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="n">
+        <v>18390000</v>
+      </c>
+      <c r="C197" s="2" t="n">
+        <v>19990000</v>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-dell-16-dc16251-i5-120u-8gb-512gb-16-fhd-touch-win-11</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T13:45:33.424+07:00</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:35:27</t>
         </is>
       </c>
     </row>

--- a/laptop_gearvn_all.xlsx
+++ b/laptop_gearvn_all.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J197"/>
+  <dimension ref="A1:J199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -503,18 +503,18 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell DC15250-7982BLK H5YXJ (I7-1355U/ 16GB/ 1TB/ 15.6" FHD Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I5-1334U/ 8GB/ 512GB/ 15.6" FHD/DOS) - Nhập Khẩu Chính Hãng</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>22990000</v>
+        <v>15990000</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>23990000</v>
+        <v>17490000</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -525,36 +525,36 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-dc15250-7982blk-h5yxj-i7-1355u-16gb-1tb-15-6-fhd-touch-win-11</t>
+          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i5-1334u-8gb-512gb-15-6-fhd</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19T15:36:35.706+07:00</t>
+          <t>2026-09-17T11:07:57.107+07:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:11</t>
+          <t>2026-10-01 12:51:06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-53RH (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop Dell 16 DC16251 (I5-120U/ 8GB/ 512GB/ 16" FHD+ Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>29990000</v>
+        <v>18390000</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>32490000</v>
+        <v>19990000</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -563,168 +563,180 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-53rh-core-5-210h-rtx-4050-6gb-16gb-512gb-15-6-fhd-ips-144hz</t>
+          <t>https://gearvn.com/products/laptop-dell-16-dc16251-i5-120u-8gb-512gb-16-fhd-touch-win-11</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T10:39:56.876+07:00</t>
+          <t>2026-08-12T13:45:33.424+07:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:17</t>
+          <t>2026-10-01 12:51:11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Aspire 7 A715-59G-59RD (Core 5-210H/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Dell DC15250-7982BLK H5YXJ (I7-1355U/ 16GB/ 1TB/ 15.6" FHD Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>24490000</v>
+        <v>22990000</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>27990000</v>
+        <v>23990000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
+          <t>https://gearvn.com/products/laptop-dell-dc15250-7982blk-h5yxj-i7-1355u-16gb-1tb-15-6-fhd-touch-win-11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:06:18.096+07:00</t>
+          <t>2026-08-19T15:36:35.706+07:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:22</t>
+          <t>2026-10-01 12:51:17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R5F4 (Ryzen AI 7 350/ RTX 5060/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-53RH (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>48890000</v>
+        <v>29990000</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>50990000</v>
+        <v>32490000</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-gaming-nitro-v-propanel-an16s-61-r5f4</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-53rh-core-5-210h-rtx-4050-6gb-16gb-512gb-15-6-fhd-ips-144hz</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09T15:11:02.875+07:00</t>
+          <t>2026-10-01T12:38:22.817+07:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:28</t>
+          <t>2026-10-01 12:51:22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R7KQ (Ryzen AI 5 340/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD+/Win 11)</t>
+          <t>Laptop gaming Acer Aspire 7 A715-59G-59RD (Core 5-210H/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46990000</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
+        <v>25990000</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>27990000</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-anv16s-61-r7kq</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-aspire-7-a715-59g-59rd</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T10:11:28.855+07:00</t>
+          <t>2026-10-01T07:27:58.022+07:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:33</t>
+          <t>2026-10-01 12:51:27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R7ZJ (Ryzen AI 7 350/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R5F4 (Ryzen AI 7 350/ RTX 5060/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>51990000</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
+        <v>48890000</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>50990000</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -733,128 +745,122 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-an16s-61-r7zj</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-gaming-nitro-v-propanel-an16s-61-r5f4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T10:35:37.593+07:00</t>
+          <t>2026-09-09T15:11:02.875+07:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:38</t>
+          <t>2026-10-01 12:51:32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R0QM (Ryzen 5 7640HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R7KQ (Ryzen AI 5 340/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD+/Win 11)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>32990000</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>46990000</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Ryzen AI 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r0qm</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-anv16s-61-r7kq</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T14:12:10.19+07:00</t>
+          <t>2026-09-11T10:11:28.855+07:00</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:43</t>
+          <t>2026-10-01 12:51:37</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R5EF (Ryzen 5 7640HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R7ZJ (Ryzen AI 7 350/ RTX 5060 8GB/ 16GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>33390000</v>
+        <v>49990000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>34990000</v>
+        <v>51990000</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r5ef</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-an16s-61-r7zj</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:23:17.905+07:00</t>
+          <t>2026-10-01T09:32:20.877+07:00</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:48</t>
+          <t>2026-10-01 12:51:42</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R9EH (Ryzen 7 7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R0QM (Ryzen 5 7640HS/ RTX 3050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>35990000</v>
+        <v>32990000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>38990000</v>
+        <v>34990000</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -865,265 +871,285 @@
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r9eh</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r0qm</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T15:05:48.951+07:00</t>
+          <t>2026-08-07T14:12:10.19+07:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:53</t>
+          <t>2026-10-01 12:51:47</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-556L (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R5EF (Ryzen 5 7640HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>38890000</v>
+        <v>33390000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>38990000</v>
+        <v>34990000</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Tay cầm Acer Nitro Controller NGR300 Wireless White (trị giá 1.200.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-556l</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r5ef</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:27:47.558+07:00</t>
+          <t>2026-09-25T10:23:17.905+07:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:58</t>
+          <t>2026-10-01 12:51:52</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-78MD (Core 7-240H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-42-R9EH (Ryzen 7 7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>40890000</v>
+        <v>35990000</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>40990000</v>
+        <v>38990000</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Tay cầm Acer Nitro Controller NGR300 Wireless White (trị giá 1.200.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-78md</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-42-r9eh</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:28:06.595+07:00</t>
+          <t>2026-08-21T15:05:48.951+07:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:03</t>
+          <t>2026-10-01 12:51:58</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-71T9 (Core 7-240H/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-556L (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>43990000</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr"/>
+        <v>38890000</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>38990000</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>-0%</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Tay cầm Acer Nitro Controller NGR300 Wireless White (trị giá 1.200.000đ)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-71t9</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-556l</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:29:41.759+07:00</t>
+          <t>2026-09-25T10:27:47.558+07:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:08</t>
+          <t>2026-10-01 12:52:03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-782F (Core 7-240H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-78MD (Core 7-240H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>40890000</v>
+      </c>
+      <c r="C14" s="2" t="n">
         <v>40990000</v>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-0%</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Tay cầm Acer Nitro Controller NGR300 Wireless White (trị giá 1.200.000đ)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-782f</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv15-52-78md</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T10:05:04.439+07:00</t>
+          <t>2026-09-25T10:28:06.595+07:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:13</t>
+          <t>2026-10-01 12:52:08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-A71-R7Z6 (Ryzen AI 9 465/ RTX 5070 8GB/ 32GB/ 512GB/ 16" FHD+ IPS 180Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-71T9 (Core 7-240H/ RTX 5060/ 16GB/ 512GB/ 16.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>77990000</v>
+        <v>43990000</v>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-a71-r7z6-ryzen-ai-9-465-rtx-5070-8gb-32gb-512gb-16-fhd-ips-180hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-71t9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T11:39:31.454+07:00</t>
+          <t>2026-09-25T10:29:41.759+07:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:19</t>
+          <t>2026-10-01 12:52:13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-I12-53VH (Core 5-205H/ RTX 3050 4GB/ 16GB/ 512GB/ 16" FHD 165Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-72-782F (Core 7-240H/ RTX 5050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>30990000</v>
+        <v>40990000</v>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | Tặng ngay 1 x Chuột Logitech G304 Wireless (trị giá 725.000đ)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-i12-53vh-core-5-205h-rtx-3050-4gb-16gb-512gb-16-fhd-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-72-782f</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T11:06:22.406+07:00</t>
+          <t>2026-09-11T10:05:04.439+07:00</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:24</t>
+          <t>2026-10-01 12:52:18</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-I12-72G0 (Core 7-230H/ RTX 3050 4GB/ 16GB/ 512GB/ 16" FHD 165Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-A71-R7Z6 (Ryzen AI 9 465/ RTX 5070 8GB/ 32GB/ 512GB/ 16" FHD+ IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>33990000</v>
+        <v>77990000</v>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr"/>
@@ -1136,249 +1162,229 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-i12-72g0-core-7-230h-rtx-3050-4gb-16gb-512gb-16-fhd-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-a71-r7z6-ryzen-ai-9-465-rtx-5070-8gb-32gb-512gb-16-fhd-ips-180hz-win-11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T10:45:24.015+07:00</t>
+          <t>2026-09-30T20:59:22.108+07:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:29</t>
+          <t>2026-10-01 12:52:23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16-I51-71MF (Ultra 7-355/ RTX 5070 8GB/ 32GB/ 512GB/ 16" FHD+ IPS 180Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-I12-53VH (Core 5-205H/ RTX 3050 4GB/ 16GB/ 512GB/ 16" FHD 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>74990000</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>76990000</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>30990000</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
-        </is>
-      </c>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-i51-71mf-ultra-7-355-rtx-5070-8gb-32gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-i12-53vh-core-5-205h-rtx-3050-4gb-16gb-512gb-16-fhd-165hz-win-11</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T11:40:49.662+07:00</t>
+          <t>2026-09-30T11:06:22.406+07:00</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:34</t>
+          <t>2026-10-01 12:52:28</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-71-58WQ (Core 5-210H/ RTX 5050/ 32GB/ 512GB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-I12-72G0 (Core 7-230H/ RTX 3050 4GB/ 16GB/ 512GB/ 16" FHD 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>44890000</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>45990000</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>33990000</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16s-71-58wq</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-i12-72g0-core-7-230h-rtx-3050-4gb-16gb-512gb-16-fhd-165hz-win-11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T10:25:14.809+07:00</t>
+          <t>2026-09-30T10:45:24.015+07:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:40</t>
+          <t>2026-10-01 12:52:33</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R9CN (Ryzen AI 7 350/ RTX 5070 8GB/ 32GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16-I51-71MF (Ultra 7-355/ RTX 5070 8GB/ 32GB/ 512GB/ 16" FHD+ IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>62990000</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
+        <v>74990000</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>76990000</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-s-ai-propanel-an16s-61-r9cn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16-i51-71mf-ultra-7-355-rtx-5070-8gb-32gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T09:15:37.613+07:00</t>
+          <t>2026-09-30T20:58:30.543+07:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:45</t>
+          <t>2026-10-01 12:52:38</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50RB (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-71-58WQ (Core 5-210H/ RTX 5050/ 32GB/ 512GB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>30990000</v>
+        <v>44890000</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>35990000</v>
+        <v>45990000</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50rb</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-propanel-anv16s-71-58wq</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27T11:11:52.657+07:00</t>
+          <t>2026-09-18T10:25:14.809+07:00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:50</t>
+          <t>2026-10-01 12:52:43</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50VA (Core 5-210H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel AN16S-61-R9CN (Ryzen AI 7 350/ RTX 5070 8GB/ 32GB/ 512GB/ 16.0" 2K+/ Win 11)</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>28990000</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>33990000</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-15%</t>
-        </is>
-      </c>
+        <v>62990000</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50va</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-s-ai-propanel-an16s-61-r9cn</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T11:03:23.184+07:00</t>
+          <t>2026-09-30T20:56:33.919+07:00</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:55</t>
+          <t>2026-10-01 12:52:48</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-73Z8 (Core 7-240H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50RB (Core 5-210H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
         <v>33490000</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>37990000</v>
+        <v>35990000</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1389,128 +1395,128 @@
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50rb</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:08:20.8+07:00</t>
+          <t>2026-10-01T07:30:06.192+07:00</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:00</t>
+          <t>2026-10-01 12:52:53</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-50VA (Core 5-210H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>42590000</v>
+        <v>29490000</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>43990000</v>
+        <v>33990000</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-50va</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T19:07:42.806+07:00</t>
+          <t>2026-10-01T07:37:03.916+07:00</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:05</t>
+          <t>2026-10-01 12:52:58</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-73Z8 (Core 7-240H/ RTX 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>42990000</v>
+        <v>35990000</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>45990000</v>
+        <v>37990000</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-15-propanel-anv15-52-73z8</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T09:31:41.277+07:00</t>
+          <t>2026-10-01T07:30:30.681+07:00</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:11</t>
+          <t>2026-10-01 12:53:03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-41-R337 (Ryzen 7 260/ RTX 5050/ 16GB/ 1TB/ 16.0" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>54990000</v>
+        <v>42590000</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>58690000</v>
+        <v>43990000</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1521,511 +1527,521 @@
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-41-r337</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T10:40:22.072+07:00</t>
+          <t>2026-09-28T19:07:42.806+07:00</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:16</t>
+          <t>2026-10-01 12:53:08</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R0B8 (Ryzen AI 5 340/ RTX 5050 8GB/ 16GB/ 512GB/ 16.0" FHD+/ Win11)</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>32490000</v>
+        <v>42990000</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>36990000</v>
+        <v>45990000</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Ryzen AI 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r0b8</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T09:59:34.507+07:00</t>
+          <t>2026-09-08T09:31:41.277+07:00</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:21</t>
+          <t>2026-10-01 12:53:13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios 18 AI PH18-I71-91UX (Ultra 9-290HX Plus/ RTX 5080 16GB/ 64GB/ 3TB/ 18" 2K+ Mini LED 250Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV16S-61-R9ZV (Ryzen AI 7 350/ RTX 5060 8GB/ 32GB/ 1TB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>179990000</v>
+        <v>54990000</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>181990000</v>
+        <v>58690000</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>Tặng ngay 1 x Màn hình Acer KG241Y-X1 24" IPS 200Hz Gsync chuyên game (trị giá 2.590.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 3072 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 18 inch | Độ phân giải: 2K+ (2560x1600)</t>
+          <t>Dòng CPU: Ryzen AI 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-18-ai-ph18-i71-91ux-ultra-9-290hx-rtx-5080-16gb-16gb-3tb-18-2k-mini-led-250hz</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-16s-propanel-anv16s-61-r9zv</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T13:30:49.416+07:00</t>
+          <t>2026-09-18T10:40:22.072+07:00</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:26</t>
+          <t>2026-10-01 12:53:18</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios 18 PH18-I71-975R (Ultra 9-290HX Plus/ RTX 5090 24GB/ 64GB/ 3TB/ 18" 4K+ Mini LED 120Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Nitro ProPanel ANV15-52-74UM (Core 7-240H/ RTX 3050/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>249990000</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="inlineStr"/>
+        <v>32490000</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>36990000</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 3072 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 18 inch | Độ phân giải: UHD+ (3840x2400) | Tần số quét: 120 Hz</t>
+          <t>Dòng CPU: Core 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-18-ai-ph18-i71-975r-ultra-9-290hx-rtx-5090-24gb-64gb-3tb-18-4k-mini-led-120hz</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-nitro-v-propanel-anv15-52-74um</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T11:56:13.749+07:00</t>
+          <t>2026-09-11T09:59:34.507+07:00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:32</t>
+          <t>2026-10-01 12:53:23</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo PHN16-I71-9779 (Ultra 9-290HX Plus/ RTX 5070 8GB/ 64GB/ 2TB/ 16" WQXGA IPS 180Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios 18 AI PH18-I71-91UX (Ultra 9-290HX Plus/ RTX 5080 16GB/ 64GB/ 3TB/ 18" 2K+ Mini LED 250Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>109990000</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
+        <v>179990000</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>181990000</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 3072 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 18 inch | Độ phân giải: 2K+ (2560x1600)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-ai-phn16-i71-9779-ultra-9-290hx-rtx-5070-8gb-64gb-2tb-16-2k-ips-180hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-18-ai-ph18-i71-91ux-ultra-9-290hx-rtx-5080-16gb-16gb-3tb-18-2k-mini-led-250hz</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:35:07.531+07:00</t>
+          <t>2026-09-17T13:30:49.416+07:00</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:37</t>
+          <t>2026-10-01 12:53:29</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo PHN16-I71-97VK (Ultra 9-290HX Plus/ RTX 5080 16GB/ 32GB/ 512GB/ 16" WQAGA 240Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios 18 PH18-I71-975R (Ultra 9-290HX Plus/ RTX 5090 24GB/ 64GB/ 3TB/ 18" 4K+ Mini LED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>104990000</v>
+        <v>249990000</v>
       </c>
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 3072 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 18 inch | Độ phân giải: UHD+ (3840x2400) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-ai-phn16-i71-97vk-ultra-9-290hx-rtx-5080-16gb-16gb-512gb-16-2k-ips-240hz</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-18-ai-ph18-i71-975r-ultra-9-290hx-rtx-5090-24gb-64gb-3tb-18-4k-mini-led-120hz</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:33:09.575+07:00</t>
+          <t>2026-09-29T11:56:13.749+07:00</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:42</t>
+          <t>2026-10-01 12:53:34</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-74MN (I7-14650HX/ RTX 5050/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo PHN16-I71-9779 (Ultra 9-290HX Plus/ RTX 5070 8GB/ 64GB/ 2TB/ 16" WQXGA IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>54990000</v>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>64990000</v>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>-15%</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
+        <v>109990000</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-74mn</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-ai-phn16-i71-9779-ultra-9-290hx-rtx-5070-8gb-64gb-2tb-16-2k-ips-180hz-win-11</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T14:23:25.919+07:00</t>
+          <t>2026-09-14T15:35:07.531+07:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:47</t>
+          <t>2026-10-01 12:53:39</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-91K5 (I9-14900HX/ RTX 5070 8GB/ 32GB/ 1TB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo PHN16-I71-97VK (Ultra 9-290HX Plus/ RTX 5080 16GB/ 32GB/ 512GB/ 16" WQAGA 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>89990000</v>
+        <v>104990000</v>
       </c>
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-91k5-i9-14900hx-rtx-5070-8gb-32gb-1tb-16-2k-ips-180hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-ai-phn16-i71-97vk-ultra-9-290hx-rtx-5080-16gb-16gb-512gb-16-2k-ips-240hz</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T13:27:14.879+07:00</t>
+          <t>2026-09-14T15:33:09.575+07:00</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:52</t>
+          <t>2026-10-01 12:53:44</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-74MN (I7-14650HX/ RTX 5050/ 32GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>114990000</v>
+        <v>54990000</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>129900000</v>
+        <v>64990000</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
-        </is>
-      </c>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-74mn</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17T10:38:12.773+07:00</t>
+          <t>2026-09-29T14:23:25.919+07:00</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:57</t>
+          <t>2026-10-01 12:53:49</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 512GB/ 16" 2K+ OLED 165Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16 PHN16-I31-91K5 (I9-14900HX/ RTX 5070 8GB/ 32GB/ 1TB/ 16" 2K+ IPS 180Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>80990000</v>
+        <v>89990000</v>
       </c>
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: i9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 180 Hz</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16-phn16-i31-91k5-i9-14900hx-rtx-5070-8gb-32gb-1tb-16-2k-ips-180hz-win-11</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T11:50:52.42+07:00</t>
+          <t>2026-09-17T13:27:14.879+07:00</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:03</t>
+          <t>2026-10-01 12:53:54</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Helios Neo PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 32GB/ 512GB/ 16" 2K+ OLED 165Hz/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo 16S PHN16S-71-95MS (Ultra 9-275HX/ RTX 5070 Ti 12GB/ 64GB/ 2TB/ 16.0" 2K+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>77990000</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
+        <v>114990000</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>129900000</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-71-95ms-2</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29T11:52:22.882+07:00</t>
+          <t>2026-07-17T10:38:12.773+07:00</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:08</t>
+          <t>2026-10-01 12:53:59</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070 8GB/ 32GB/ 2TB/ 14.5" 2.8K+/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo PHN16S-I51-97T9 (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 512GB/ 16" 2K+ OLED 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>93990000</v>
+        <v>80990000</v>
       </c>
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Ghế Acer Predator Gaming PGC331 Black (trị giá 8.990.000đ) | Tặng ngay 1 x Balo gaming Acer Predator Robust PBG470 (trị giá 3.500.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 14.5 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-97t9</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:43:12.906+07:00</t>
+          <t>2026-09-30T20:53:45.08+07:00</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:13</t>
+          <t>2026-10-01 12:54:04</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Helios Neo PHN16S-I51-98CX (Ultra 9-386H/ RTX 5060 8GB/ 32GB/ 512GB/ 16" 2K+ OLED 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>27540000</v>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>30300000</v>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
+        <v>77990000</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Balo Acer Predator SUV (trị giá 2.000.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-helios-neo-16s-phn16s-i51-98cx</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12T11:35:32.312+07:00</t>
+          <t>2026-09-30T20:55:07.782+07:00</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:18</t>
+          <t>2026-10-01 12:54:09</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G G614PH-RV176W (Ryzen 9/ RTX 5050/ 16GB/ 512GB/ 16" FHD/ Win 11)</t>
+          <t>Laptop gaming Acer Predator Triton 14 AI PT14-52T-99TU (Ultra 9-288V/ RTX 5070 8GB/ 32GB/ 2TB/ 14.5" 2.8K+/ Win 11)</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>49990000</v>
+        <v>93990000</v>
       </c>
       <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="inlineStr"/>
@@ -2037,77 +2053,73 @@
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 14.5 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g-g614ph-rv176w-ryzen-9-rtx-5050-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-acer-predator-triton-14-ai-pt14-52t-99tu</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:47:04.096+07:00</t>
+          <t>2026-09-14T15:43:12.906+07:00</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:24</t>
+          <t>2026-10-01 12:54:14</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G16 G614PH-S5101W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 240Hz/ Win 11)</t>
+          <t>Laptop gaming Asus V16 V3607VH-RP084W (Core 5-210H/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>47490000</v>
+        <v>27540000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>53990000</v>
+        <v>30300000</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-s5101w</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-gaming-v16-v3607vh-rp084w</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T11:28:04.811+07:00</t>
+          <t>2026-07-12T11:35:32.312+07:00</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:29</t>
+          <t>2026-10-01 12:54:19</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G16 G614PH-TS118W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix G G614PH-RV176W (Ryzen 9/ RTX 5050/ 16GB/ 512GB/ 16" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>52990000</v>
+        <v>49990000</v>
       </c>
       <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr"/>
@@ -2119,40 +2131,40 @@
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-ts118w</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g-g614ph-rv176w-ryzen-9-rtx-5050-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T11:49:35.857+07:00</t>
+          <t>2026-09-06T15:47:04.096+07:00</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:34</t>
+          <t>2026-10-01 12:54:24</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G16 G614PM-TS147W (Ryzen 9-8940HX/ RTX 5060 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix G16 G614PH-S5101W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>54690000</v>
+        <v>47490000</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>59990000</v>
+        <v>53990000</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2163,33 +2175,33 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614pm-ts147w</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-s5101w</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:15:11.541+07:00</t>
+          <t>2026-09-10T11:28:04.811+07:00</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:04</t>
+          <t>2026-10-01 12:50:56</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix SCAR G835LXG-TQ473W (Ultra 9-290HX Plus/ RTX 5090/ 64GB/ 2TB/ 18" Mini LED 240Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix G16 G614PH-TS118W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>179990000</v>
+        <v>52990000</v>
       </c>
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr"/>
@@ -2201,36 +2213,42 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 18 inch | Độ phân giải: UHD+ (3840x2400) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-scar-g835lxg-tq473w-ultra-9-290hx-plus-rtx-5090-64gb-2tb-18-qhd-mini-led-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-ts118w</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:58:23.481+07:00</t>
+          <t>2026-08-13T11:49:35.857+07:00</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:10</t>
+          <t>2026-10-01 12:51:01</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU405AR-SY016W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix G16 G614PM-TS147W (Ryzen 9-8940HX/ RTX 5060 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>96990000</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
+        <v>54690000</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>59990000</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2239,33 +2257,33 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405ar-sy016w-ultra-9-rtx-5070-ti-32gb-1tb-14-3k-oled-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614pm-ts147w</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:47:29.287+07:00</t>
+          <t>2026-09-07T10:15:11.541+07:00</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:15</t>
+          <t>2026-10-01 12:51:06</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU405AW-SY029W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix SCAR G835LXG-TQ473W (Ultra 9-290HX Plus/ RTX 5090/ 64GB/ 2TB/ 18" Mini LED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>119990000</v>
+        <v>179990000</v>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr"/>
@@ -2277,33 +2295,33 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 18 inch | Độ phân giải: UHD+ (3840x2400) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405aw-sy029w-ultra-9-rtx-5080-32gb-1tb-14-3k-oled-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-scar-g835lxg-tq473w-ultra-9-290hx-plus-rtx-5090-64gb-2tb-18-qhd-mini-led-240hz-win-11</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:47:45.327+07:00</t>
+          <t>2026-09-26T12:58:23.481+07:00</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:20</t>
+          <t>2026-10-01 12:51:11</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR115W (Ultra 7-255H/ RTX 5070/ 16GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU405AR-SY016W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>74990000</v>
+        <v>96990000</v>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2315,33 +2333,33 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr115w-ultra-7-255h-rtx-5070-16gb-512gb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405ar-sy016w-ultra-9-rtx-5070-ti-32gb-1tb-14-3k-oled-120hz-win-11</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:46:00.864+07:00</t>
+          <t>2026-09-06T15:47:29.287+07:00</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:25</t>
+          <t>2026-10-01 12:51:16</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR141W (Ultra 7-255H/ RTX 5070/ 32GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU405AW-SY029W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>83990000</v>
+        <v>119990000</v>
       </c>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2353,33 +2371,33 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr141w-ultra-7-255h-rtx-5070-32gb-512gb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405aw-sy029w-ultra-9-rtx-5080-32gb-1tb-14-3k-oled-120hz-win-11</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:46:21.05+07:00</t>
+          <t>2026-09-06T15:47:45.327+07:00</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:30</t>
+          <t>2026-10-01 12:51:21</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AR-TB027W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR115W (Ultra 7-255H/ RTX 5070/ 16GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>99990000</v>
+        <v>74990000</v>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2391,33 +2409,33 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ar-tb027w-ultra-9-rtx-5070-ti-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr115w-ultra-7-255h-rtx-5070-16gb-512gb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:10.531+07:00</t>
+          <t>2026-09-06T15:46:00.864+07:00</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:35</t>
+          <t>2026-10-01 12:51:26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB052WS (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR141W (Ultra 7-255H/ RTX 5070/ 32GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>139990000</v>
+        <v>83990000</v>
       </c>
       <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2429,33 +2447,33 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb052ws-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr141w-ultra-7-255h-rtx-5070-32gb-512gb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:28.879+07:00</t>
+          <t>2026-09-06T15:46:21.05+07:00</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:40</t>
+          <t>2026-10-01 12:51:31</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB121W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AR-TB027W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>124990000</v>
+        <v>99990000</v>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2467,33 +2485,33 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb121w-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ar-tb027w-ultra-9-rtx-5070-ti-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:44.227+07:00</t>
+          <t>2026-09-06T15:45:10.531+07:00</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:45</t>
+          <t>2026-10-01 12:51:36</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AX-TB042WS (Ultra 9/ RTX 5090/ 64GB/ 2TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB052WS (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>169990000</v>
+        <v>139990000</v>
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2505,42 +2523,36 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ax-tb042ws-ultra-9-rtx-5090-64gb-2tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb052ws-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:44:50.259+07:00</t>
+          <t>2026-09-06T15:45:28.879+07:00</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:50</t>
+          <t>2026-10-01 12:51:41</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA 165Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB121W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>57390000</v>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>58990000</v>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>124990000</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2549,42 +2561,36 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb121w-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:35:45.75+07:00</t>
+          <t>2026-09-06T15:45:44.227+07:00</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:55</t>
+          <t>2026-10-01 12:51:46</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN329W (Ryzen 7-8845HS/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AX-TB042WS (Ultra 9/ RTX 5090/ 64GB/ 2TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>27690000</v>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>37490000</v>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>-26%</t>
-        </is>
-      </c>
+        <v>169990000</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2593,40 +2599,40 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn329w-ryzen-7-8845hs-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ax-tb042ws-ultra-9-rtx-5090-64gb-2tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:04:13.749+07:00</t>
+          <t>2026-09-06T15:44:50.259+07:00</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:00</t>
+          <t>2026-10-01 12:51:51</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN390W (Ryzen 7-155/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>28990000</v>
+        <v>57390000</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>30990000</v>
+        <v>58990000</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2637,80 +2643,84 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ryzen AI 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn390w-ryzen-7-155-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:05:26.118+07:00</t>
+          <t>2026-09-14T17:35:45.75+07:00</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:05</t>
+          <t>2026-10-01 12:51:56</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUG-RL129W (Ryzen 7-7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN329W (Ryzen 7-8845HS/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>29990000</v>
+        <v>27690000</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>30990000</v>
+        <v>37490000</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
+          <t>-26%</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nug-rl129w-ryzen-7-7445hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn329w-ryzen-7-8845hs-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:41:09.162+07:00</t>
+          <t>2026-09-17T11:04:13.749+07:00</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:10</t>
+          <t>2026-10-01 12:52:02</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUQ-RL007W (Ryzen 7-170/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN390W (Ryzen 7-155/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>36290000</v>
+        <v>28990000</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>39990000</v>
+        <v>30990000</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2721,80 +2731,82 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nuq-rl007w-ryzen-7-170-rtx-4050-6gb-16gb-512gb-16-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn390w-ryzen-7-155-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:10:34.588+07:00</t>
+          <t>2026-09-17T11:05:26.118+07:00</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:15</t>
+          <t>2026-10-01 12:52:07</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUG-RL129W (Ryzen 7-7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>41260000</v>
+        <v>29990000</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>45390000</v>
+        <v>30990000</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nug-rl129w-ryzen-7-7445hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T14:06:48.719+07:00</t>
+          <t>2026-09-14T17:41:09.162+07:00</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:20</t>
+          <t>2026-10-01 12:52:12</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA401EA-RG041W (Ryzen AI Max+ 392/ 32GB/ 512GB/ 14" 2.5K/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUQ-RL007W (Ryzen 7-170/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>59990000</v>
-      </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr"/>
+        <v>36290000</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2803,36 +2815,42 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI MAX+ | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon 8060S | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401ea-rg041w-ryzen-ai-max-392-32gb-512gb-14-2-5k-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nuq-rl007w-ryzen-7-170-rtx-4050-6gb-16gb-512gb-16-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T09:33:26.048+07:00</t>
+          <t>2026-09-25T10:10:34.588+07:00</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:25</t>
+          <t>2026-10-01 12:52:17</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA401UH-RG001W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
+          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>49990000</v>
-      </c>
-      <c r="C59" s="2" t="inlineStr"/>
-      <c r="D59" s="2" t="inlineStr"/>
+        <v>41260000</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>45390000</v>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2841,33 +2859,33 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401uh-rg001w-ryzen-7-260-rtx-5050-16gb-512gb-14-qhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:59:55.007+07:00</t>
+          <t>2026-06-30T14:06:48.719+07:00</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:30</t>
+          <t>2026-10-01 12:52:22</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA401UM-RG049W (Ryzen 7 260/ RTX 5060/ 32GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA401EA-RG041W (Ryzen AI Max+ 392/ 32GB/ 512GB/ 14" 2.5K/ Win 11)</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>64990000</v>
+        <v>59990000</v>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr"/>
@@ -2879,33 +2897,33 @@
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: Ryzen AI MAX+ | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon 8060S | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401um-rg049w-ryzen-7-260-rtx-5060-32gb-512gb-14-qhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401ea-rg041w-ryzen-ai-max-392-32gb-512gb-14-2-5k-win-11</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T13:00:47.55+07:00</t>
+          <t>2026-08-14T09:33:26.048+07:00</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:35</t>
+          <t>2026-10-01 12:52:27</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA608UHI-TU121W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA401UH-RG001W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>48990000</v>
+        <v>49990000</v>
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2917,33 +2935,33 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608uhi-tu121w-ryzen-7-260-rtx-5050-16gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401uh-rg001w-ryzen-7-260-rtx-5050-16gb-512gb-14-qhd-win-11</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T11:22:30.725+07:00</t>
+          <t>2026-09-26T12:59:55.007+07:00</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:40</t>
+          <t>2026-10-01 12:52:33</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA608UMI-TU162W (Ryzen 7 260/ RTX 5060/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA401UM-RG049W (Ryzen 7 260/ RTX 5060/ 32GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>51990000</v>
+        <v>64990000</v>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
@@ -2955,42 +2973,36 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608umi-tu162w-ryzen-7-260-rtx-5060-16gb-512gb-16-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401um-rg049w-ryzen-7-260-rtx-5060-32gb-512gb-14-qhd-win-11</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T11:01:50.971+07:00</t>
+          <t>2026-09-26T13:00:47.55+07:00</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:45</t>
+          <t>2026-10-01 12:52:38</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS V16 V3607VJ-TK189W (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 16" WUXGA 144Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA608UHI-TU121W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>26490000</v>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>48990000</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -2999,128 +3011,122 @@
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-v16-v3607vj-tk189w-core-5-210h-rtx-3050-6gb-16gb-512gb-16-wuxga-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608uhi-tu121w-ryzen-7-260-rtx-5050-16gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T16:26:14.526+07:00</t>
+          <t>2026-08-14T11:22:30.725+07:00</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:50</t>
+          <t>2026-10-01 12:52:43</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA608UMI-TU162W (Ryzen 7 260/ RTX 5060/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>31990000</v>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>32790000</v>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>51990000</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608umi-tu162w-ryzen-7-260-rtx-5060-16gb-512gb-16-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T11:59:37.483+07:00</t>
+          <t>2026-08-14T11:01:50.971+07:00</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:55</t>
+          <t>2026-10-01 12:52:48</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming GIGABYTE A16 CVHI3MY893SH (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
+          <t>Laptop gaming ASUS V16 V3607VJ-TK189W (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 16" WUXGA 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>36990000</v>
+        <v>26490000</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>38990000</v>
+        <v>29990000</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3my893sh</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-v16-v3607vj-tk189w-core-5-210h-rtx-3050-6gb-16gb-512gb-16-wuxga-144hz-win-11</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T14:40:23.197+07:00</t>
+          <t>2026-09-15T16:26:14.526+07:00</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:00</t>
+          <t>2026-10-01 12:52:53</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 A16-3THK3VN893SH (Ryzen 7 260/ RTX 5050 8GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>35990000</v>
+        <v>31990000</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>40990000</v>
+        <v>32790000</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3131,40 +3137,40 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-ga63h-3thk3vn893sh</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30T09:54:12.234+07:00</t>
+          <t>2026-09-30T11:59:37.483+07:00</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:05</t>
+          <t>2026-10-01 12:52:58</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9LJR2VNF93SH (Ryzen 5 7533HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop gaming GIGABYTE A16 CVHI3MY893SH (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>29990000</v>
+        <v>36990000</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>30990000</v>
+        <v>38990000</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3175,156 +3181,162 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9ljr2vnf93sh-ryzen-5-7533hs-rtx-3050-6gb-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3my893sh</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T15:10:54.55+07:00</t>
+          <t>2026-08-14T14:40:23.197+07:00</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:10</t>
+          <t>2026-10-01 12:53:03</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9MJR2VNF93SH (Ryzen 5 7533HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 A16-3THK3VN893SH (Ryzen 7 260/ RTX 5050 8GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr"/>
+        <v>35990000</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>40990000</v>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9mjr2vnf93sh-ryzen-5-7533hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-ga63h-3thk3vn893sh</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:50:39.975+07:00</t>
+          <t>2026-07-30T09:54:12.234+07:00</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:15</t>
+          <t>2026-10-01 12:53:08</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9LJR2VNF93SH (Ryzen 5 7533HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>115990000</v>
+        <v>29990000</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>117990000</v>
+        <v>30990000</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9ljr2vnf93sh-ryzen-5-7533hs-rtx-3050-6gb-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05T14:44:14.658+07:00</t>
+          <t>2026-07-31T15:10:54.55+07:00</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:20</t>
+          <t>2026-10-01 12:53:13</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15AHP11 83TN0040VN (Ryzen 7-250/ RTX 5050 8GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
+          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9MJR2VNF93SH (Ryzen 5 7533HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>43990000</v>
+        <v>34990000</v>
       </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+      <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15ahp11-83tn0040vn-ryzen-7-250-rtx-5050-8gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9mjr2vnf93sh-ryzen-5-7533hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T09:36:14.406+07:00</t>
+          <t>2026-09-18T13:50:39.975+07:00</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:25</t>
+          <t>2026-10-01 12:53:18</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>38990000</v>
+        <v>115990000</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>41990000</v>
+        <v>117990000</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3335,42 +3347,36 @@
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:38.199+07:00</t>
+          <t>2026-07-05T14:44:14.658+07:00</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:30</t>
+          <t>2026-10-01 12:53:24</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S0006RVN (Ryzen 7-7735HS/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15AHP11 83TN0040VN (Ryzen 7-250/ RTX 5050 8GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="C72" s="2" t="n">
-        <v>32990000</v>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>43990000</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3379,36 +3385,42 @@
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0006rvn-ryzen-7-7735hs-rtx-3050-6gb-16gb-1tb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15ahp11-83tn0040vn-ryzen-7-250-rtx-5050-8gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T11:31:57.635+07:00</t>
+          <t>2026-09-21T09:36:14.406+07:00</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:35</t>
+          <t>2026-10-01 12:53:29</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S000DCVN (Ryzen 7-170/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>32990000</v>
-      </c>
-      <c r="C73" s="2" t="inlineStr"/>
-      <c r="D73" s="2" t="inlineStr"/>
+        <v>38990000</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>41990000</v>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3417,36 +3429,42 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s000dcvn-ryzen-7-170-rtx-3050-6gb-16gb-1tb-15-6-fhd-ips-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T10:03:17.431+07:00</t>
+          <t>2026-07-15T09:36:38.199+07:00</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:40</t>
+          <t>2026-10-01 12:53:34</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003VVN (Core 5-205H/ RTX 3050 6GB/ 8GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S0006RVN (Ryzen 7-7735HS/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>36990000</v>
-      </c>
-      <c r="C74" s="2" t="inlineStr"/>
-      <c r="D74" s="2" t="inlineStr"/>
+        <v>30990000</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>32990000</v>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3455,33 +3473,33 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 8 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003vvn-core-5-205h-rtx-3050-6gb-8gb-512gb-15-3-wuxga-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0006rvn-ryzen-7-7735hs-rtx-3050-6gb-16gb-1tb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T19:41:42.305+07:00</t>
+          <t>2026-09-22T11:31:57.635+07:00</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:45</t>
+          <t>2026-10-01 12:53:39</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003WVN (Core 5-205H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S000DCVN (Ryzen 7-170/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>41990000</v>
+        <v>32990000</v>
       </c>
       <c r="C75" s="2" t="inlineStr"/>
       <c r="D75" s="2" t="inlineStr"/>
@@ -3493,42 +3511,36 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200)</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003wvn-core-5-205h-rtx-3050-6gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s000dcvn-ryzen-7-170-rtx-3050-6gb-16gb-1tb-15-6-fhd-ips-win-11</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T16:50:55.152+07:00</t>
+          <t>2026-09-21T10:03:17.431+07:00</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:50</t>
+          <t>2026-10-01 12:53:44</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRX10 83JE01AGVN (I7-13645HX/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003VVN (Core 5-205H/ RTX 3050 6GB/ 8GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>39490000</v>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>36990000</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3537,42 +3549,36 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 8 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx10-83je01agvn</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003vvn-core-5-205h-rtx-3050-6gb-8gb-512gb-15-3-wuxga-165hz-win-11</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T16:43:38.321+07:00</t>
+          <t>2026-08-12T19:41:42.305+07:00</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:55</t>
+          <t>2026-10-01 12:53:49</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003WVN (Core 5-205H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>43990000</v>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>45990000</v>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>41990000</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr"/>
+      <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3581,36 +3587,42 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200)</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003wvn-core-5-205h-rtx-3050-6gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T16:32:05.969+07:00</t>
+          <t>2026-08-12T16:50:55.152+07:00</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:00</t>
+          <t>2026-10-01 12:53:54</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX10 83JE01AGVN (I7-13645HX/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>33990000</v>
-      </c>
-      <c r="C78" s="2" t="inlineStr"/>
-      <c r="D78" s="2" t="inlineStr"/>
+        <v>39490000</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>40990000</v>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3619,36 +3631,42 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx10-83je01agvn</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:23:00.628+07:00</t>
+          <t>2026-09-19T16:43:38.321+07:00</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:05</t>
+          <t>2026-10-01 12:53:59</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>31990000</v>
-      </c>
-      <c r="C79" s="2" t="inlineStr"/>
-      <c r="D79" s="2" t="inlineStr"/>
+        <v>43990000</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>45990000</v>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3657,42 +3675,36 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:25:26.316+07:00</t>
+          <t>2026-09-18T16:32:05.969+07:00</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:10</t>
+          <t>2026-10-01 12:54:04</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>33990000</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3701,33 +3713,33 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:28:01.415+07:00</t>
+          <t>2026-06-30T15:23:00.628+07:00</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:15</t>
+          <t>2026-10-01 12:54:09</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Max C13WF-421VN (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>44990000</v>
+        <v>31990000</v>
       </c>
       <c r="C81" s="2" t="inlineStr"/>
       <c r="D81" s="2" t="inlineStr"/>
@@ -3739,36 +3751,42 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13vf-421vn-i7-13620h-rtx-5060-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T16:26:05.15+07:00</t>
+          <t>2026-06-30T15:25:26.316+07:00</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:20</t>
+          <t>2026-10-01 12:54:14</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Max C13WE-422VN (I7-13620H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>42990000</v>
-      </c>
-      <c r="C82" s="2" t="inlineStr"/>
-      <c r="D82" s="2" t="inlineStr"/>
+        <v>34990000</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>35990000</v>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3777,42 +3795,36 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn-i7-13620h-rtx-5050-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:38:57.001+07:00</t>
+          <t>2026-06-30T15:28:01.415+07:00</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:18</t>
+          <t>2026-10-01 12:50:59</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Max C13WF-421VN (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>34890000</v>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>44990000</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr"/>
+      <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3821,42 +3833,36 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13vf-421vn-i7-13620h-rtx-5060-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T14:54:13.66+07:00</t>
+          <t>2026-09-23T16:26:05.15+07:00</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:23</t>
+          <t>2026-10-01 12:51:04</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Max C13WE-422VN (I7-13620H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>79990000</v>
-      </c>
-      <c r="C84" s="2" t="n">
-        <v>80990000</v>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>-1%</t>
-        </is>
-      </c>
+        <v>42990000</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr"/>
+      <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3865,36 +3871,42 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn-i7-13620h-rtx-5050-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:43:38.331+07:00</t>
+          <t>2026-07-27T10:38:57.001+07:00</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:29</t>
+          <t>2026-10-01 12:51:09</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>85990000</v>
-      </c>
-      <c r="C85" s="2" t="inlineStr"/>
-      <c r="D85" s="2" t="inlineStr"/>
+        <v>34890000</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>35990000</v>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3903,71 +3915,77 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T17:51:09.908+07:00</t>
+          <t>2026-06-30T14:54:13.66+07:00</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:34</t>
+          <t>2026-10-01 12:51:14</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming GIGABYTE AORUS Master 16 6XJM4VNE64SH (Ryzen 9 9955HX3D/ RTX 5070 Ti 12GB/ 32GB/ 1TB/ 16" QHD+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>86990000</v>
-      </c>
-      <c r="C86" s="2" t="inlineStr"/>
-      <c r="D86" s="2" t="inlineStr"/>
+        <v>79990000</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>80990000</v>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aorus-master-16-6xjm4vne64sh-ryzen-9-9955hx3d-rtx-5070-ti-12gb-32gb-1tb-16-qhd-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T11:46:50.068+07:00</t>
+          <t>2026-06-30T15:43:38.331+07:00</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:39</t>
+          <t>2026-10-01 12:51:19</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 83RQ00DBVN (Core 3-304/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>24990000</v>
+        <v>85990000</v>
       </c>
       <c r="C87" s="2" t="inlineStr"/>
       <c r="D87" s="2" t="inlineStr"/>
@@ -3979,67 +3997,71 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-14iwc11-83rq00dbvn-core-3-304-8gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:16:44.995+07:00</t>
+          <t>2026-09-22T17:51:09.908+07:00</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:44</t>
+          <t>2026-10-01 12:51:24</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB005YVN (Ryzen 5-125/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop gaming GIGABYTE AORUS Master 16 6XJM4VNE64SH (Ryzen 9 9955HX3D/ RTX 5070 Ti 12GB/ 32GB/ 1TB/ 16" QHD+ OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>25990000</v>
+        <v>86990000</v>
       </c>
       <c r="C88" s="2" t="inlineStr"/>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb005yvn-ryzen-5-125-8gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aorus-master-16-6xjm4vne64sh-ryzen-9-9955hx3d-rtx-5070-ti-12gb-32gb-1tb-16-qhd-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T15:01:44.794+07:00</t>
+          <t>2026-09-24T11:46:50.068+07:00</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:49</t>
+          <t>2026-10-01 12:51:29</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB0060VN (Ryzen 7-155/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 83RQ00DBVN (Core 3-304/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>27990000</v>
+        <v>24990000</v>
       </c>
       <c r="C89" s="2" t="inlineStr"/>
       <c r="D89" s="2" t="inlineStr"/>
@@ -4049,71 +4071,69 @@
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb0060vn-ryzen-7-155-8gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-14iwc11-83rq00dbvn-core-3-304-8gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T14:35:59.897+07:00</t>
+          <t>2026-09-07T10:16:44.995+07:00</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:54</t>
+          <t>2026-10-01 12:51:34</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 83S1003GVN</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB005YVN (Ryzen 5-125/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>44540000</v>
-      </c>
-      <c r="C90" s="2" t="n">
-        <v>47990000</v>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
+        <v>25990000</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr"/>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
-        </is>
-      </c>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-83s1003gvn</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb005yvn-ryzen-5-125-8gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T10:29:16.152+07:00</t>
+          <t>2026-08-13T15:01:44.794+07:00</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:59</t>
+          <t>2026-10-01 12:51:39</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 OLED 83S1006RVN (Ryzen AI 7-445/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB0060VN (Ryzen 7-155/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>32990000</v>
+        <v>27990000</v>
       </c>
       <c r="C91" s="2" t="inlineStr"/>
       <c r="D91" s="2" t="inlineStr"/>
@@ -4123,73 +4143,71 @@
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-oled-83s1006rvn-ryzen-ai-7-445-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb0060vn-ryzen-7-155-8gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T11:54:44.05+07:00</t>
+          <t>2026-08-13T14:35:59.897+07:00</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:04</t>
+          <t>2026-10-01 12:51:43</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00ABVN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 83S1003GVN</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="C92" s="2" t="inlineStr"/>
-      <c r="D92" s="2" t="inlineStr"/>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>44540000</v>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>47990000</v>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00abvn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-83s1003gvn</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T14:05:59.687+07:00</t>
+          <t>2026-08-28T10:29:16.152+07:00</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:09</t>
+          <t>2026-10-01 12:51:48</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00F5VN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 OLED 83S1006RVN (Ryzen AI 7-445/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>34990000</v>
+        <v>32990000</v>
       </c>
       <c r="C93" s="2" t="inlineStr"/>
       <c r="D93" s="2" t="inlineStr"/>
@@ -4201,33 +4219,33 @@
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00f5vn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-oled-83s1006rvn-ryzen-ai-7-445-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:17:34.624+07:00</t>
+          <t>2026-08-13T11:54:44.05+07:00</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:14</t>
+          <t>2026-10-01 12:51:53</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002EVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00ABVN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>55990000</v>
+        <v>30990000</v>
       </c>
       <c r="C94" s="2" t="inlineStr"/>
       <c r="D94" s="2" t="inlineStr"/>
@@ -4239,33 +4257,33 @@
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002evn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00abvn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T10:21:35.763+07:00</t>
+          <t>2026-08-13T14:05:59.687+07:00</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:20</t>
+          <t>2026-10-01 12:51:58</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002FVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00F5VN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>55990000</v>
+        <v>34990000</v>
       </c>
       <c r="C95" s="2" t="inlineStr"/>
       <c r="D95" s="2" t="inlineStr"/>
@@ -4277,33 +4295,33 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002fvn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00f5vn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T20:29:51.634+07:00</t>
+          <t>2026-09-07T10:17:34.624+07:00</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:25</t>
+          <t>2026-10-01 12:52:03</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0075VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002EVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>46990000</v>
+        <v>55990000</v>
       </c>
       <c r="C96" s="2" t="inlineStr"/>
       <c r="D96" s="2" t="inlineStr"/>
@@ -4313,31 +4331,35 @@
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0075vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002evn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:19:34.771+07:00</t>
+          <t>2026-08-13T10:21:35.763+07:00</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:30</t>
+          <t>2026-10-01 12:52:08</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0076VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002FVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>46990000</v>
+        <v>55990000</v>
       </c>
       <c r="C97" s="2" t="inlineStr"/>
       <c r="D97" s="2" t="inlineStr"/>
@@ -4349,33 +4371,33 @@
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0076vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002fvn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:20:20.027+07:00</t>
+          <t>2026-08-12T20:29:51.634+07:00</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:36</t>
+          <t>2026-10-01 12:52:13</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK0015VN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0075VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>72990000</v>
+        <v>46990000</v>
       </c>
       <c r="C98" s="2" t="inlineStr"/>
       <c r="D98" s="2" t="inlineStr"/>
@@ -4385,35 +4407,31 @@
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
-        </is>
-      </c>
+      <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk0015vn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0075vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:21:45.74+07:00</t>
+          <t>2026-09-07T10:19:34.771+07:00</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:41</t>
+          <t>2026-10-01 12:52:18</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK006GVN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0076VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>72990000</v>
+        <v>46990000</v>
       </c>
       <c r="C99" s="2" t="inlineStr"/>
       <c r="D99" s="2" t="inlineStr"/>
@@ -4425,33 +4443,33 @@
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk006gvn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0076vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:23:05.36+07:00</t>
+          <t>2026-09-07T10:20:20.027+07:00</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:46</t>
+          <t>2026-10-01 12:52:23</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 POLED 83QK009PVN (Ultra X9-378H/ 32GB/ 1TB/ 14" 2.8K WQXGA POLED Touch/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK0015VN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>70990000</v>
+        <v>72990000</v>
       </c>
       <c r="C100" s="2" t="inlineStr"/>
       <c r="D100" s="2" t="inlineStr"/>
@@ -4463,42 +4481,36 @@
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-poled-83qk009pvn-ultra-x9-378h-32gb-1tb-14-2-8k-wqxga-poled-touch-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk0015vn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T20:11:25.828+07:00</t>
+          <t>2026-09-07T10:21:45.74+07:00</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:51</t>
+          <t>2026-10-01 12:52:28</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK006GVN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>33900000</v>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v>34900000</v>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>72990000</v>
+      </c>
+      <c r="C101" s="2" t="inlineStr"/>
+      <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4507,200 +4519,194 @@
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk006gvn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:39:36.938+07:00</t>
+          <t>2026-09-07T10:23:05.36+07:00</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:56</t>
+          <t>2026-10-01 12:52:33</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 POLED 83QK009PVN (Ultra X9-378H/ 32GB/ 1TB/ 14" 2.8K WQXGA POLED Touch/ Win 11)</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>36900000</v>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v>37900000</v>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
+        <v>70990000</v>
+      </c>
+      <c r="C102" s="2" t="inlineStr"/>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-poled-83qk009pvn-ultra-x9-378h-32gb-1tb-14-2-8k-wqxga-poled-touch-win-11</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:34:21.041+07:00</t>
+          <t>2026-08-12T20:11:25.828+07:00</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:01</t>
+          <t>2026-10-01 12:52:38</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>44900000</v>
+        <v>33900000</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>46490000</v>
+        <v>34900000</v>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
           <t>-3%</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:43:00.949+07:00</t>
+          <t>2026-07-01T13:39:36.938+07:00</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:06</t>
+          <t>2026-10-01 12:52:43</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>23990000</v>
+        <v>36900000</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>24990000</v>
+        <v>37900000</v>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:36:48.562+07:00</t>
+          <t>2026-07-01T13:34:21.041+07:00</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:12</t>
+          <t>2026-10-01 12:52:48</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>61990000</v>
+        <v>44900000</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>62990000</v>
+        <v>46490000</v>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: i9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
-        </is>
-      </c>
+      <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T15:49:38.229+07:00</t>
+          <t>2026-07-01T13:43:00.949+07:00</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:17</t>
+          <t>2026-10-01 12:52:53</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
+          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>34690000</v>
+        <v>23990000</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>37990000</v>
+        <v>24990000</v>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -4711,36 +4717,36 @@
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
+          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T10:28:18.636+07:00</t>
+          <t>2026-07-01T13:36:48.562+07:00</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:22</t>
+          <t>2026-10-01 12:52:58</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
+          <t>Laptop gaming MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>25490000</v>
+        <v>61990000</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>25990000</v>
+        <v>62990000</v>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
@@ -4753,34 +4759,44 @@
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: i9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+        </is>
+      </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:41:40.106+07:00</t>
+          <t>2026-09-23T15:49:38.229+07:00</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:28</t>
+          <t>2026-10-01 12:53:03</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14S AI+ G3MG-050VN (Ultra 7-355/ 16GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>36490000</v>
-      </c>
-      <c r="C108" s="2" t="inlineStr"/>
-      <c r="D108" s="2" t="inlineStr"/>
+        <v>34690000</v>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>37990000</v>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4789,36 +4805,36 @@
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14s-ai-g3mg-050vn-ultra-7-355-16gb-1tb-14-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T17:51:58.168+07:00</t>
+          <t>2026-09-21T10:28:18.636+07:00</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:33</t>
+          <t>2026-10-01 12:53:08</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
+          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>22190000</v>
+        <v>25490000</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>22690000</v>
+        <v>25990000</v>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
@@ -4831,44 +4847,34 @@
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T15:28:04.144+07:00</t>
+          <t>2026-06-25T15:41:40.106+07:00</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:38</t>
+          <t>2026-10-01 12:53:13</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
+          <t>Laptop MSI Modern 14S AI+ G3MG-050VN (Ultra 7-355/ 16GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>43990000</v>
-      </c>
-      <c r="C110" s="2" t="n">
-        <v>44990000</v>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>36490000</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr"/>
+      <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4877,40 +4883,40 @@
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-14s-ai-g3mg-050vn-ultra-7-355-16gb-1tb-14-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:49:42.234+07:00</t>
+          <t>2026-09-22T17:51:58.168+07:00</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:43</t>
+          <t>2026-10-01 12:53:18</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
+          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>33990000</v>
+        <v>22190000</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>34990000</v>
+        <v>22690000</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -4921,40 +4927,40 @@
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 7 | Dung lượng SSD: 1024 GB | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T16:07:23.364+07:00</t>
+          <t>2026-07-09T15:28:04.144+07:00</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:48</t>
+          <t>2026-10-01 12:53:23</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
+          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>37990000</v>
+        <v>43990000</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>39990000</v>
+        <v>44990000</v>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -4965,40 +4971,40 @@
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 13.3 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T11:20:56.718+07:00</t>
+          <t>2026-06-25T15:49:42.234+07:00</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:53</t>
+          <t>2026-10-01 12:53:28</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN (Ultra 7-355/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>44490000</v>
+        <v>33990000</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>48990000</v>
+        <v>34990000</v>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5009,324 +5015,324 @@
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 7 | Dung lượng SSD: 1024 GB | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T10:53:12.84+07:00</t>
+          <t>2026-06-25T16:07:23.364+07:00</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:58</t>
+          <t>2026-10-01 12:53:33</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>59990000</v>
-      </c>
-      <c r="C114" s="2" t="inlineStr"/>
-      <c r="D114" s="2" t="inlineStr"/>
+        <v>37990000</v>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 13.3 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:54:52.677+07:00</t>
+          <t>2026-08-17T11:20:56.718+07:00</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:03</t>
+          <t>2026-10-01 12:53:38</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN (Ultra 7-355/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>59990000</v>
-      </c>
-      <c r="C115" s="2" t="inlineStr"/>
-      <c r="D115" s="2" t="inlineStr"/>
-      <c r="E115" s="2" t="inlineStr"/>
+        <v>44490000</v>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>48990000</v>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel® Arc™ graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T10:17:43.984+07:00</t>
+          <t>2026-09-28T10:53:12.84+07:00</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:09</t>
+          <t>2026-10-01 12:53:42</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/ RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>82990000</v>
-      </c>
-      <c r="C116" s="2" t="n">
-        <v>83990000</v>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>-1%</t>
-        </is>
-      </c>
+        <v>59990000</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr"/>
+      <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
-        </is>
-      </c>
+      <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T15:48:57.837+07:00</t>
+          <t>2026-06-30T09:54:52.677+07:00</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:14</t>
+          <t>2026-10-01 12:53:48</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>86990000</v>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v>87990000</v>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>-1%</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>59990000</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr"/>
+      <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
-        </is>
-      </c>
+      <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T17:54:02.495+07:00</t>
+          <t>2026-06-30T10:17:43.984+07:00</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:19</t>
+          <t>2026-10-01 12:53:53</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop gaming MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/ RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>22990000</v>
+        <v>82990000</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>23990000</v>
+        <v>83990000</v>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Card đồ họa tích hợp - Qualcomm® Adreno™ | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
+          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T09:43:41.692+07:00</t>
+          <t>2026-09-23T15:48:57.837+07:00</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:24</t>
+          <t>2026-10-01 12:53:57</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>23990000</v>
+        <v>86990000</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>25990000</v>
+        <v>87990000</v>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® ARC™ Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
+          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T15:00:45.83+07:00</t>
+          <t>2026-09-22T17:54:02.495+07:00</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:29</t>
+          <t>2026-10-01 12:54:02</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M (Ultra 9-185H/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
+          <t>Laptop Acer Aspire 14 AI A14-11M-X8FP (Snapdragon X X1-26-100/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>29890000</v>
+        <v>22990000</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>29990000</v>
+        <v>23990000</v>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>-0%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Card đồ họa tích hợp - Qualcomm® Adreno™ | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-16gb-512gb-14-fhd-ips-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-14-al-a14-11m-x8fp</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:22:17.071+07:00</t>
+          <t>2026-07-16T09:43:41.692+07:00</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:35</t>
+          <t>2026-10-01 12:51:00</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-50AL (Ultra 5-125H/ 16GB/ 512GB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>22990000</v>
+        <v>23990000</v>
       </c>
       <c r="C121" s="2" t="n">
         <v>25990000</v>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -5337,84 +5343,84 @@
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® ARC™ Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-50al</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T21:08:15.03+07:00</t>
+          <t>2026-07-16T15:00:45.83+07:00</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:41</t>
+          <t>2026-10-01 12:51:05</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 14 AI AG14-I71M-977M (Ultra 9-185H/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>20990000</v>
+        <v>29890000</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>21990000</v>
+        <v>29990000</v>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-0%</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 680M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-14-ai-ag14-i71m-977m-ultra-9-185h-16gb-512gb-14-fhd-ips-win-11</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17T09:17:18.78+07:00</t>
+          <t>2026-09-30T13:26:12.266+07:00</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:46</t>
+          <t>2026-10-01 12:51:10</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR (Ryzen 5-3500U/ 8GB/ 512GB/ 14" FHD IPS/ Win 11)</t>
+          <t>Laptop Acer Aspire Go 15 AG15-72P-776J (Core 7-150U/ 16GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>17990000</v>
+        <v>22990000</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>19990000</v>
+        <v>25990000</v>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -5425,36 +5431,36 @@
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-go-15-ag15-72p-776j-15-6-fhdips-c7-150u-1-16gb-512gb-win</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T20:43:49.815+07:00</t>
+          <t>2026-09-11T21:08:15.03+07:00</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:51</t>
+          <t>2026-10-01 12:51:15</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-44P-R0SP (Ryzen 7 7730U/ 8GB/ 512GB/ 14.5" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>22890000</v>
+        <v>20990000</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>23990000</v>
+        <v>21990000</v>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
@@ -5469,40 +5475,40 @@
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon 680M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-44p-r0sp</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:44:03.513+07:00</t>
+          <t>2026-07-17T09:17:18.78+07:00</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:56</t>
+          <t>2026-10-01 12:51:20</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-47P-R0TR (Ryzen 5-3500U/ 8GB/ 512GB/ 14" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>24990000</v>
+        <v>17990000</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>25990000</v>
+        <v>19990000</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -5513,40 +5519,40 @@
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-47p-r0tr-ryzen-5-3500u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:20:56.552+07:00</t>
+          <t>2026-09-24T20:43:49.815+07:00</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:01</t>
+          <t>2026-10-01 12:51:25</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-76KR (Core 7-350/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AL14-53M-53E8 (Core 5-120U/ 16GB/ 512GB/ 14" FHD+ IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>25990000</v>
+        <v>21990000</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>26990000</v>
+        <v>23990000</v>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -5557,40 +5563,40 @@
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-76kr-core-7-350-8gb-512gb</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-53m-53e8-core-5-120u-8gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:44:29.405+07:00</t>
+          <t>2026-10-01T10:51:51.763+07:00</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:06</t>
+          <t>2026-10-01 12:51:30</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-59HB (Core 5-320/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>17990000</v>
+        <v>24990000</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>19790000</v>
+        <v>25990000</v>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -5601,40 +5607,40 @@
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-59hb-core-5-320-16gb-512gb-14-0-fhd-ips</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T09:51:43.721+07:00</t>
+          <t>2026-09-25T10:20:56.552+07:00</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:12</t>
+          <t>2026-10-01 12:51:35</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 14 AI AL14-57P-76KR (Core 7-350/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>19590000</v>
+        <v>25990000</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>21990000</v>
+        <v>26990000</v>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -5645,40 +5651,40 @@
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-14-al14-57p-76kr-core-7-350-8gb-512gb</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T09:03:23.812+07:00</t>
+          <t>2026-09-24T15:44:29.405+07:00</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:17</t>
+          <t>2026-10-01 12:51:40</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5-3500U/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R87W (Ryzen 3 30/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>16790000</v>
+        <v>17990000</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>19990000</v>
+        <v>19790000</v>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -5689,40 +5695,40 @@
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r87w</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:09:40.061+07:00</t>
+          <t>2026-09-24T09:51:43.721+07:00</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:22</t>
+          <t>2026-10-01 12:51:45</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-411P-R1CM (Ryzen 5 3500U/ 8GB/ 256GB)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-21P-R91W (Ryzen 5 40/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>17990000</v>
+        <v>19590000</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>18990000</v>
+        <v>21990000</v>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -5733,40 +5739,40 @@
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r1cm-ryzen-5-3500u-8gb-256gb</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-21p-r91w</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T14:26:56.746+07:00</t>
+          <t>2026-09-25T09:03:23.812+07:00</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:27</t>
+          <t>2026-10-01 12:51:50</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-411P-R7YP (Ryzen 3 3200U/ 8GB/ 256GB)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-410P-R1W8 (Ryzen 5-3500U/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>15990000</v>
+        <v>17990000</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>16990000</v>
+        <v>19990000</v>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -5777,40 +5783,40 @@
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 3 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon Vega Mobile Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r7yp-ryzen-3-3200u-8gb-256gb</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-410p-r1w8-ryzen-5-3500u-8gb-512gb-15-6-fhd-ips</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06T14:48:50.246+07:00</t>
+          <t>2026-10-01T07:32:42.016+07:00</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:32</t>
+          <t>2026-10-01 12:51:55</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-49P-R6XX (Ryzen 5 7430U/ 8GB/ 512GB/15.6"/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-411P-R1CM (Ryzen 5 3500U/ 8GB/ 256GB)</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>18590000</v>
+        <v>17990000</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>20990000</v>
+        <v>18990000</v>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -5821,40 +5827,40 @@
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-49p-r6xx-ryzen-5-7430u-8gb-512gb-15-6-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r1cm-ryzen-5-3500u-8gb-256gb</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T13:56:25.879+07:00</t>
+          <t>2026-07-06T14:26:56.746+07:00</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:38</t>
+          <t>2026-10-01 12:52:00</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-411P-R7YP (Ryzen 3 3200U/ 8GB/ 256GB)</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>18890000</v>
+        <v>15990000</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>24990000</v>
+        <v>16990000</v>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>-24%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -5865,36 +5871,36 @@
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 3 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-411p-r7yp-ryzen-3-3200u-8gb-256gb</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T10:45:08.009+07:00</t>
+          <t>2026-07-06T14:48:50.246+07:00</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:43</t>
+          <t>2026-10-01 12:52:05</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-49P-R6XX (Ryzen 5 7430U/ 8GB/ 512GB/15.6"/ Win 11)</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>24990000</v>
+        <v>18590000</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>27990000</v>
+        <v>20990000</v>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
@@ -5909,281 +5915,261 @@
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-49p-r6xx-ryzen-5-7430u-8gb-512gb-15-6-win-11</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16T15:19:10.843+07:00</t>
+          <t>2026-08-21T13:56:25.879+07:00</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:48</t>
+          <t>2026-10-01 12:52:11</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 AI SFA14-I31-54A2 (Core 5-320/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Blue/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 15 AL15-53P-56QH (Core 5-120U/ 8GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B135" s="3" t="n">
+        <v>18890000</v>
+      </c>
+      <c r="C135" s="2" t="n">
         <v>24990000</v>
       </c>
-      <c r="C135" s="2" t="inlineStr"/>
-      <c r="D135" s="2" t="inlineStr"/>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>-24%</t>
+        </is>
+      </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-air-14-ai-sfa14-i31-54a2-core-5-320-12gb-512gb-14-fhd-ips-120hz-blue-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-15-al15-53p-56qh</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T10:04:26.762+07:00</t>
+          <t>2026-08-24T10:45:08.009+07:00</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:53</t>
+          <t>2026-10-01 12:52:16</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF (Core 3-304/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
+          <t>Laptop Acer Aspire Lite 16 AI AL16-71P-582Q (Ultra 5-125H/ 16GB/ 512GB/ 16.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>21990000</v>
-      </c>
-      <c r="C136" s="2" t="inlineStr"/>
-      <c r="D136" s="2" t="inlineStr"/>
+        <v>24990000</v>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>27990000</v>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
+          <t>Card đồ họa: Intel® Arc™ Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-34nf-core-3-304-12gb-512gb-14-fhd-ips-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-aspire-lite-16-ai-al16-71p-582q</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T13:32:07.536+07:00</t>
+          <t>2026-09-30T12:07:23.843+07:00</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:58</t>
+          <t>2026-10-01 12:52:21</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV (Core 5-320/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
+          <t>Laptop Acer Swift Air 14 AI SFA14-I31-36GM (Core 3-304/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Pink/ Win 11)</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>23490000</v>
-      </c>
-      <c r="C137" s="2" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>21990000</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr"/>
+      <c r="D137" s="2" t="inlineStr"/>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
-        </is>
-      </c>
+      <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-52bv-core-5-320-12gb-512gb-14-wuxga-ips-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-air-14-ai-sfa14-i31-36gm-core-3-304-12gb-512gb-14-fhd-ips-120hz-pink-win-11</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:09:22.19+07:00</t>
+          <t>2026-10-01T10:59:03.125+07:00</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:03</t>
+          <t>2026-10-01 12:52:26</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Air 14 AI SFA14-I31-54A2 (Core 5-320/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Blue/ Win 11)</t>
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>28990000</v>
-      </c>
-      <c r="C138" s="2" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>24990000</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr"/>
+      <c r="D138" s="2" t="inlineStr"/>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-air-14-ai-sfa14-i31-54a2-core-5-320-12gb-512gb-14-fhd-ips-120hz-blue-win-11</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T16:07:37.902+07:00</t>
+          <t>2026-09-30T10:04:26.762+07:00</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:08</t>
+          <t>2026-10-01 12:52:31</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Air 14 AI SFA14-I31-55NR (Core 5-320/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Pink/ Win 11)</t>
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>49990000</v>
-      </c>
-      <c r="C139" s="2" t="n">
-        <v>54990000</v>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
+        <v>24990000</v>
+      </c>
+      <c r="C139" s="2" t="inlineStr"/>
+      <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel® Arc™ B390 GPU (đồ họa tích hợp) | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
-        </is>
-      </c>
+      <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-air-14-ai-sfa14-i31-55nr-core-5-320-12gb-512gb-14-fhd-ips-120hz-pink-win-11</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T15:51:47.551+07:00</t>
+          <t>2026-10-01T10:22:23.976+07:00</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:13</t>
+          <t>2026-10-01 12:52:36</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go AI OLED SFG14-75-765M (Ultra 7-258V/ 32GB/ 512GB/ 14" FHD+ OLED/ Win11)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-34NF (Core 3-304/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="C140" s="2" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>21990000</v>
+      </c>
+      <c r="C140" s="2" t="inlineStr"/>
+      <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
+          <t>Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ Graphics 140V | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-ai-oled-sfg14-75-765m-14-fhd-oled-u7-258v-32lp-512gb-win</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-34nf-core-3-304-12gb-512gb-14-fhd-ips-120hz-win-11</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T10:47:31.44+07:00</t>
+          <t>2026-09-30T13:29:57.791+07:00</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:19</t>
+          <t>2026-10-01 12:52:41</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop Acer Swift Air 14 SFA14-I31-52BV (Core 5-320/ 12GB/ 512GB/ 14" FHD+ IPS 120Hz/ Green/ Win 11)</t>
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>32999000</v>
+        <v>24990000</v>
       </c>
       <c r="C141" s="2" t="inlineStr"/>
       <c r="D141" s="2" t="inlineStr"/>
@@ -6195,36 +6181,36 @@
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 12 GB</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-air-14-sfa14-i31-52bv-core-5-320-12gb-512gb-14-wuxga-ips-120hz-win-11</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T14:38:31.288+07:00</t>
+          <t>2026-10-01T07:26:46.913+07:00</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:24</t>
+          <t>2026-10-01 12:52:46</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-75-5264 (Ultra 5-226V/ 16GB/ 512GB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>31490000</v>
+        <v>29990000</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>32490000</v>
+        <v>30990000</v>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
@@ -6239,40 +6225,40 @@
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ 130T Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-75-5264</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T14:08:34.772+07:00</t>
+          <t>2026-10-01T07:28:23.313+07:00</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:29</t>
+          <t>2026-10-01 12:52:51</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" 2.8K OLED/ Win 11/ Office)</t>
+          <t>Laptop Acer Swift Go 14 AI SFG14-I71-70RP (Ultra 7-358H/ 32GB/ 1TB/ 14.0" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>35990000</v>
+        <v>49990000</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>45990000</v>
+        <v>54990000</v>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>-22%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -6283,40 +6269,40 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6 | Kích thước màn hình: 14.5 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel® Arc™ B390 GPU (đồ họa tích hợp) | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-14-ai-sfg14-i71-70rp</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:56:38.644+07:00</t>
+          <t>2026-08-28T15:51:47.551+07:00</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:34</t>
+          <t>2026-10-01 12:52:56</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
+          <t>Laptop Acer Swift Go AI OLED SFG14-75-765M (Ultra 7-258V/ 32GB/ 512GB/ 14" FHD+ OLED/ Win11)</t>
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>43990000</v>
+        <v>39990000</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>49490000</v>
+        <v>40990000</v>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>-11%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -6327,212 +6313,210 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: RTX 4060 | Kích thước màn hình: 14.5 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel® Arc™ Graphics 140V | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-ai-oled-sfg14-75-765m-14-fhd-oled-u7-258v-32lp-512gb-win</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03T15:10:56.836+07:00</t>
+          <t>2026-09-30T13:30:56.068+07:00</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:39</t>
+          <t>2026-10-01 12:53:01</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H08-50W (Core 5-210H/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74-58FJ (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>19490000</v>
-      </c>
-      <c r="C145" s="2" t="n">
-        <v>21990000</v>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
-      </c>
+        <v>32999000</v>
+      </c>
+      <c r="C145" s="2" t="inlineStr"/>
+      <c r="D145" s="2" t="inlineStr"/>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h08-50w</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74-58fj</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T11:09:14.14+07:00</t>
+          <t>2026-09-15T14:38:31.288+07:00</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:44</t>
+          <t>2026-10-01 12:53:06</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1403CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift Go SFG14-74T-55HD (Ultra 5-225H/ 16GB/ 1TB/ 14.0" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>24290000</v>
+        <v>31490000</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>26990000</v>
+        <v>32490000</v>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel® Arc™ 130T Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 5 | Dung lượng SSD: 1024 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h16-63ws-core-5-210h-16gb-512gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-go-sfg14-74t-55hd</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T15:06:02.246+07:00</t>
+          <t>2026-09-24T14:08:34.772+07:00</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:49</t>
+          <t>2026-10-01 12:53:11</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1403CVA-C7H16-50W (Core 7-240H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift X SFX14-71G-78SY (I7-13700H/ RTX 4050 6GB/ 32GB/ 1TB/ 14.5" 2.8K OLED/ Win 11/ Office)</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>28990000</v>
+        <v>35990000</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>30990000</v>
+        <v>45990000</v>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-22%</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
-      <c r="G147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: NVIDIA® GeForce RTX™ 4050 6GB GDDR6 | Kích thước màn hình: 14.5 inch | Dòng CPU: i7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+        </is>
+      </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c7h16-50w-core-7-240h-16gb-512gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-71g-78sy</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T14:43:57.168+07:00</t>
+          <t>2026-09-14T15:56:38.644+07:00</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:54</t>
+          <t>2026-10-01 12:53:16</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1503CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Acer Swift X14 SFX14 72G 708X</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>24290000</v>
+        <v>43990000</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>26990000</v>
+        <v>49490000</v>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Chuột không dây Logitech M331 Silent Black (trị giá 360.000đ) | Tặng ngay 1 x Balo Acer Office (trị giá 49.000đ)</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: RTX 4060 | Kích thước màn hình: 14.5 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1503cva-c5h16-63ws-core-5-210h-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-acer-swift-x14-sfx14-72g-708x</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T14:03:33.213+07:00</t>
+          <t>2026-07-03T15:10:56.836+07:00</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:00</t>
+          <t>2026-10-01 12:53:22</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1 P1403CVA-C3U08-50W (Core 3-100U/ 8GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H08-50W (Core 5-210H/ 8GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>15490000</v>
+        <v>19490000</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>17990000</v>
+        <v>21990000</v>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>-14%</t>
+          <t>-11%</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -6543,40 +6527,40 @@
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c3u08-50w</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h08-50w</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T13:53:40.042+07:00</t>
+          <t>2026-07-31T11:09:14.14+07:00</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:05</t>
+          <t>2026-10-01 12:53:27</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1 P1403CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>23390000</v>
+        <v>24290000</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>27990000</v>
+        <v>26990000</v>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>-16%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -6587,40 +6571,40 @@
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c5h16-63ws-core-5-210h-16gb-512gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T10:19:47.487+07:00</t>
+          <t>2026-08-03T15:06:02.246+07:00</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:10</t>
+          <t>2026-10-01 12:53:32</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U516S8W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1 P1403CVA-C7H16-50W (Core 7-240H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>26390000</v>
+        <v>28990000</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>29990000</v>
+        <v>30990000</v>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -6629,42 +6613,38 @@
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr"/>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u516s8w-ultra-5-225h-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1403cva-c7h16-50w-core-7-240h-16gb-512gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T11:57:56.626+07:00</t>
+          <t>2026-08-03T14:43:57.168+07:00</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:15</t>
+          <t>2026-10-01 12:53:37</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U716S8W (Ultra 7-255H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1 P1503CVA-C5H16-63WS (Core 5-210H/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>32990000</v>
+        <v>24290000</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>34990000</v>
+        <v>26990000</v>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -6673,38 +6653,42 @@
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr"/>
-      <c r="G152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u716s8w-ultra-7-255h-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1-p1503cva-c5h16-63ws-core-5-210h-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T13:46:08.673+07:00</t>
+          <t>2026-08-03T14:03:33.213+07:00</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:20</t>
+          <t>2026-10-01 12:53:42</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA / Win 11)</t>
+          <t>Laptop Asus ExpertBook P1 P1403CVA-C3U08-50W (Core 3-100U/ 8GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>26390000</v>
+        <v>15490000</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>30490000</v>
+        <v>17990000</v>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>-13%</t>
+          <t>-14%</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -6715,40 +6699,40 @@
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c3u08-50w</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03T11:54:54.747+07:00</t>
+          <t>2026-07-31T13:53:40.042+07:00</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:25</t>
+          <t>2026-10-01 12:53:47</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P1403CVA-C5H16-50W (Core 5-210H/ 16GB/ 512GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>32990000</v>
+        <v>23390000</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>35990000</v>
+        <v>27990000</v>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>-8%</t>
+          <t>-16%</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -6757,34 +6741,38 @@
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr"/>
-      <c r="G154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel® UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p1403cva-c5h16-50w</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T08:56:23.461+07:00</t>
+          <t>2026-08-12T10:19:47.487+07:00</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:30</t>
+          <t>2026-10-01 12:53:52</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 G2 P5405CAA-NZ0223W (Ultra 7-356H/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U516S8W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>39190000</v>
+        <v>27990000</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>41990000</v>
+        <v>29990000</v>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
@@ -6797,38 +6785,42 @@
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr"/>
-      <c r="G155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-g2-p5405caa-nz0223w-ultra-7-356h-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u516s8w-ultra-5-225h-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T11:12:45.933+07:00</t>
+          <t>2026-09-30T15:47:23.345+07:00</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:35</t>
+          <t>2026-10-01 12:53:57</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0016W (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 G1 P3406CCAP-U716S8W (Ultra 7-255H/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>28790000</v>
+        <v>32990000</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>30990000</v>
+        <v>34990000</v>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -6840,31 +6832,31 @@
       <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0016w-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-g1-p3406ccap-u716s8w-ultra-7-255h-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T10:54:41.9+07:00</t>
+          <t>2026-09-06T13:46:08.673+07:00</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:40</t>
+          <t>2026-10-01 12:54:02</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0017W (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U516W (Ultra 5-225H/ 16GB/ 512GB/ 14" WUXGA / Win 11)</t>
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>36290000</v>
+        <v>27990000</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>38990000</v>
+        <v>29990000</v>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
@@ -6879,40 +6871,40 @@
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: Arc | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0017w-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u516w-14-ips-60hz-intel-core-ultra-5-225h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:51:05.888+07:00</t>
+          <t>2026-09-30T15:47:52.431+07:00</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:45</t>
+          <t>2026-10-01 12:54:07</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0442WS (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P3 P3406CCAP-U716W (Ultra 7-255H/ 16GB/ 512GB/ 14.0" IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>37190000</v>
+        <v>32990000</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>39990000</v>
+        <v>35990000</v>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-8%</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -6921,38 +6913,34 @@
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr"/>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc 140V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 32 GB</t>
-        </is>
-      </c>
+      <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0442ws-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p3-p3406ccap-u716w-14-ips-60hz-intel-core-ultra-7-255h-16gb-512gb-windows-11</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T09:55:42.594+07:00</t>
+          <t>2026-09-23T08:56:23.461+07:00</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:10</t>
+          <t>2026-10-01 12:54:12</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0450WS (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 G2 P5405CAA-NZ0223W (Ultra 7-356H/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>29790000</v>
+        <v>39190000</v>
       </c>
       <c r="C159" s="2" t="n">
-        <v>31990000</v>
+        <v>41990000</v>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
@@ -6965,76 +6953,80 @@
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>Card đồ họa: Intel Arc 130V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 16 GB</t>
-        </is>
-      </c>
+      <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0450ws-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-g2-p5405caa-nz0223w-ultra-7-356h-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T09:56:18.911+07:00</t>
+          <t>2026-08-03T11:12:45.933+07:00</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:15</t>
+          <t>2026-10-01 12:54:17</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0016W (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>199990000</v>
-      </c>
-      <c r="C160" s="2" t="inlineStr"/>
-      <c r="D160" s="2" t="inlineStr"/>
+        <v>28790000</v>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
-        </is>
-      </c>
+      <c r="G160" s="2" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0016w-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T11:12:30.954+07:00</t>
+          <t>2026-08-03T10:54:41.9+07:00</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:21</t>
+          <t>2026-10-01 12:51:02</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB027W (Core 3/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0017W (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>22990000</v>
-      </c>
-      <c r="C161" s="2" t="inlineStr"/>
-      <c r="D161" s="2" t="inlineStr"/>
+        <v>36290000</v>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>38990000</v>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7043,36 +7035,42 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: Arc | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb027w-core-3-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0017w-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:52:41.33+07:00</t>
+          <t>2026-09-10T13:51:05.888+07:00</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:26</t>
+          <t>2026-10-01 12:51:07</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB029W (Core 7/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0442WS (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>35490000</v>
-      </c>
-      <c r="C162" s="2" t="inlineStr"/>
-      <c r="D162" s="2" t="inlineStr"/>
+        <v>37190000</v>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7081,36 +7079,42 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Arc 140V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb029w-core-7-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0442ws-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T15:05:22.575+07:00</t>
+          <t>2026-08-03T09:55:42.594+07:00</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:31</t>
+          <t>2026-10-01 12:51:12</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB220W (Core 7/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0450WS (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>30490000</v>
-      </c>
-      <c r="C163" s="2" t="inlineStr"/>
-      <c r="D163" s="2" t="inlineStr"/>
+        <v>29790000</v>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>31990000</v>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7119,42 +7123,36 @@
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel Arc 130V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb220w-core-7-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0450ws-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:43:31.989+07:00</t>
+          <t>2026-08-03T09:56:18.911+07:00</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:36</t>
+          <t>2026-10-01 12:51:17</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1404V (Core 5-120U/ 8GB/ 256GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>16590000</v>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>18990000</v>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>-13%</t>
-        </is>
-      </c>
+        <v>199990000</v>
+      </c>
+      <c r="C164" s="2" t="inlineStr"/>
+      <c r="D164" s="2" t="inlineStr"/>
       <c r="E164" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7163,33 +7161,33 @@
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404v-core-5-120u-8gb-256gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T13:41:37.603+07:00</t>
+          <t>2026-09-18T11:12:30.954+07:00</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:41</t>
+          <t>2026-10-01 12:51:22</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VA-EB355W (Core 7-150U/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB027W (Core 3/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>25990000</v>
+        <v>22990000</v>
       </c>
       <c r="C165" s="2" t="inlineStr"/>
       <c r="D165" s="2" t="inlineStr"/>
@@ -7201,33 +7199,33 @@
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb355w-core-7-150u-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb027w-core-3-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:17:32.016+07:00</t>
+          <t>2026-08-18T16:52:41.33+07:00</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:46</t>
+          <t>2026-10-01 12:51:28</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VA-EB609W (Core 3-100U/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB029W (Core 7/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>21990000</v>
+        <v>35490000</v>
       </c>
       <c r="C166" s="2" t="inlineStr"/>
       <c r="D166" s="2" t="inlineStr"/>
@@ -7239,42 +7237,36 @@
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb609w-core-3-100u-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb029w-core-7-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:33:25.424+07:00</t>
+          <t>2026-08-20T15:05:22.575+07:00</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:51</t>
+          <t>2026-10-01 12:51:33</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VAP-V14.C58256 (Core 5-120U/ 16GB/ 256GB/ 14" FHD IPS/ Win 11/ Quiet Blue)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB220W (Core 7/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>17890000</v>
-      </c>
-      <c r="C167" s="2" t="n">
-        <v>18990000</v>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>30490000</v>
+      </c>
+      <c r="C167" s="2" t="inlineStr"/>
+      <c r="D167" s="2" t="inlineStr"/>
       <c r="E167" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7283,40 +7275,40 @@
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404vap-v14-c58256-core-5-120u-8gb-256gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb220w-core-7-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:42:34.369+07:00</t>
+          <t>2026-08-20T11:43:31.989+07:00</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:56</t>
+          <t>2026-10-01 12:51:38</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus VivoBook 14 X1407AA-LY360W (Ultra 5-325/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop Asus Vivobook 14 X1404V (Core 5-120U/ 8GB/ 256GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>26490000</v>
+        <v>16590000</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>26990000</v>
+        <v>18990000</v>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-13%</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -7327,33 +7319,33 @@
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407aa-ly360w-ultra-5-325-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404v-core-5-120u-8gb-256gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T15:46:33.275+07:00</t>
+          <t>2026-08-07T13:41:37.603+07:00</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:01</t>
+          <t>2026-10-01 12:51:43</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1407CA-LY203W (Ultra 5-225H/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VA-EB355W (Core 7-150U/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>33490000</v>
+        <v>25990000</v>
       </c>
       <c r="C169" s="2" t="inlineStr"/>
       <c r="D169" s="2" t="inlineStr"/>
@@ -7365,33 +7357,33 @@
       <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407ca-ly203w-ultra-5-225h-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb355w-core-7-150u-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T10:22:08.041+07:00</t>
+          <t>2026-08-20T11:17:32.016+07:00</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:06</t>
+          <t>2026-10-01 12:51:48</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504MA-BQ632W (Core 5-320/ 8GB/ 512GB/ 15" FHD IPS)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VA-EB609W (Core 3-100U/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>26990000</v>
+        <v>21990000</v>
       </c>
       <c r="C170" s="2" t="inlineStr"/>
       <c r="D170" s="2" t="inlineStr"/>
@@ -7403,36 +7395,42 @@
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq632w-core-5-320-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb609w-core-3-100u-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T15:43:54.381+07:00</t>
+          <t>2026-08-18T16:33:25.424+07:00</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:11</t>
+          <t>2026-10-01 12:51:53</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504MA-BQ633W (Core 7-350/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VAP-V14.C58256 (Core 5-120U/ 16GB/ 256GB/ 14" FHD IPS/ Win 11/ Quiet Blue)</t>
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>30490000</v>
-      </c>
-      <c r="C171" s="2" t="inlineStr"/>
-      <c r="D171" s="2" t="inlineStr"/>
+        <v>17890000</v>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>18990000</v>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7441,36 +7439,42 @@
       <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq633w-core-7-350-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404vap-v14-c58256-core-5-120u-8gb-256gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:47:34.397+07:00</t>
+          <t>2026-09-14T17:42:34.369+07:00</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:17</t>
+          <t>2026-10-01 12:51:58</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504VA-BQ165W (Core 5-120U/ 8GB/ 512GB/ 15" FHD IPS)</t>
+          <t>Laptop Asus VivoBook 14 X1407AA-LY360W (Ultra 5-325/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>20990000</v>
-      </c>
-      <c r="C172" s="2" t="inlineStr"/>
-      <c r="D172" s="2" t="inlineStr"/>
+        <v>26490000</v>
+      </c>
+      <c r="C172" s="2" t="n">
+        <v>26990000</v>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7479,29 +7483,29 @@
       <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504va-bq165w-core-5-120u-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407aa-ly360w-ultra-5-325-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:12:00.028+07:00</t>
+          <t>2026-08-07T15:46:33.275+07:00</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:22</t>
+          <t>2026-10-01 12:52:03</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 16 X1607CA-MB387W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD IPS)</t>
+          <t>Laptop ASUS Vivobook 14 X1407CA-LY203W (Ultra 5-225H/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B173" s="3" t="n">
@@ -7517,33 +7521,33 @@
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb387w-ultra-5-225h-16gb-512gb-16-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407ca-ly203w-ultra-5-225h-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T16:08:06.906+07:00</t>
+          <t>2026-08-20T10:22:08.041+07:00</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:27</t>
+          <t>2026-10-01 12:52:08</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 16 X1607CA-MB399W (Ultra 7-255H/ 16GB/ 512GB/ 16" FHD IPS)</t>
+          <t>Laptop ASUS Vivobook 15 X1504MA-BQ632W (Core 5-320/ 8GB/ 512GB/ 15" FHD IPS)</t>
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>36490000</v>
+        <v>26990000</v>
       </c>
       <c r="C174" s="2" t="inlineStr"/>
       <c r="D174" s="2" t="inlineStr"/>
@@ -7555,33 +7559,33 @@
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb399w-ultra-7-255h-16gb-512gb-16-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq632w-core-5-320-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T15:36:19.591+07:00</t>
+          <t>2026-08-18T15:43:54.381+07:00</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:32</t>
+          <t>2026-10-01 12:52:13</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Flip TP3407AA-SG029W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop ASUS Vivobook 15 X1504MA-BQ633W (Core 7-350/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>41990000</v>
+        <v>30490000</v>
       </c>
       <c r="C175" s="2" t="inlineStr"/>
       <c r="D175" s="2" t="inlineStr"/>
@@ -7593,33 +7597,33 @@
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-flip-tp3407aa-sg029w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq633w-core-7-350-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T14:55:40.249+07:00</t>
+          <t>2026-09-26T12:47:34.397+07:00</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:37</t>
+          <t>2026-10-01 12:52:18</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ4821W (Ryzen 5/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop ASUS Vivobook 15 X1504VA-BQ165W (Core 5-120U/ 8GB/ 512GB/ 15" FHD IPS)</t>
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>22990000</v>
+        <v>20990000</v>
       </c>
       <c r="C176" s="2" t="inlineStr"/>
       <c r="D176" s="2" t="inlineStr"/>
@@ -7631,33 +7635,33 @@
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1504fa-bq4821w-ryzen-5-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504va-bq165w-core-5-120u-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:55:57.447+07:00</t>
+          <t>2026-08-18T16:12:00.028+07:00</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:42</t>
+          <t>2026-10-01 12:52:23</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ340W (Ryzen 5/ 16GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop ASUS Vivobook 16 X1607CA-MB387W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD IPS)</t>
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>28490000</v>
+        <v>33490000</v>
       </c>
       <c r="C177" s="2" t="inlineStr"/>
       <c r="D177" s="2" t="inlineStr"/>
@@ -7669,33 +7673,33 @@
       <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-go-15-e1504fa-bq340w-ryzen-5-16gb-512gb-156-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb387w-ultra-5-225h-16gb-512gb-16-fhd-ips</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:55:13.502+07:00</t>
+          <t>2026-08-20T16:08:06.906+07:00</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:47</t>
+          <t>2026-10-01 12:52:28</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 M3407KA-SF034W (Ryzen AI 5-330/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop ASUS Vivobook 16 X1607CA-MB399W (Ultra 7-255H/ 16GB/ 512GB/ 16" FHD IPS)</t>
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>33990000</v>
+        <v>36490000</v>
       </c>
       <c r="C178" s="2" t="inlineStr"/>
       <c r="D178" s="2" t="inlineStr"/>
@@ -7707,33 +7711,33 @@
       <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-m3407ka-sf034w-ryzen-ai-5-330-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb399w-ultra-7-255h-16gb-512gb-16-fhd-ips</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T12:02:07.653+07:00</t>
+          <t>2026-08-20T15:36:19.591+07:00</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:52</t>
+          <t>2026-10-01 12:52:33</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407AA-SF945W (Ultra 5-325/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop ASUS Vivobook Flip TP3407AA-SG029W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>37490000</v>
+        <v>41990000</v>
       </c>
       <c r="C179" s="2" t="inlineStr"/>
       <c r="D179" s="2" t="inlineStr"/>
@@ -7745,33 +7749,33 @@
       <c r="F179" s="2" t="inlineStr"/>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf945w-ultra-5-325-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-flip-tp3407aa-sg029w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T11:09:17.449+07:00</t>
+          <t>2026-08-18T14:55:40.249+07:00</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:33:57</t>
+          <t>2026-10-01 12:52:38</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407VA-LY147W (Core 5-210H/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ4821W (Ryzen 5/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>34990000</v>
+        <v>22990000</v>
       </c>
       <c r="C180" s="2" t="inlineStr"/>
       <c r="D180" s="2" t="inlineStr"/>
@@ -7783,42 +7787,36 @@
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407va-ly147w-core-5-210h-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1504fa-bq4821w-ryzen-5-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T11:42:14.925+07:00</t>
+          <t>2026-09-24T15:55:57.447+07:00</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:02</t>
+          <t>2026-10-01 12:52:43</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS VivoBook S14 S3407CA-SF913W (Ultra 5-225H/ 16GB/ 512GB/ 14" OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ340W (Ryzen 5/ 16GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>27890000</v>
-      </c>
-      <c r="C181" s="2" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>28490000</v>
+      </c>
+      <c r="C181" s="2" t="inlineStr"/>
+      <c r="D181" s="2" t="inlineStr"/>
       <c r="E181" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7827,33 +7825,33 @@
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s14-s3407ca-sf913w-ultra-5-225h-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-go-15-e1504fa-bq340w-ryzen-5-16gb-512gb-156-fhd-ips</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T13:01:54.572+07:00</t>
+          <t>2026-09-24T15:55:13.502+07:00</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:07</t>
+          <t>2026-10-01 12:52:48</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UM3406GA-QD075W (Ryzen 7/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop ASUS Vivobook S 14 M3407KA-SF034W (Ryzen AI 5-330/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>39990000</v>
+        <v>33990000</v>
       </c>
       <c r="C182" s="2" t="inlineStr"/>
       <c r="D182" s="2" t="inlineStr"/>
@@ -7865,33 +7863,33 @@
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ga-qd075w-ryzen-7-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-m3407ka-sf034w-ryzen-ai-5-330-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T16:03:07.024+07:00</t>
+          <t>2026-08-18T12:02:07.653+07:00</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:12</t>
+          <t>2026-10-01 12:52:53</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1531W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407AA-SF945W (Ultra 5-325/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>42990000</v>
+        <v>37490000</v>
       </c>
       <c r="C183" s="2" t="inlineStr"/>
       <c r="D183" s="2" t="inlineStr"/>
@@ -7903,42 +7901,36 @@
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1531w-ultra-9-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf945w-ultra-5-325-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T08:45:55.514+07:00</t>
+          <t>2026-08-18T11:09:17.449+07:00</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:17</t>
+          <t>2026-10-01 12:52:58</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1713W (Ultra 5-225H/ 16GB/ 512GB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407VA-LY147W (Core 5-210H/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="C184" s="2" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t>-21%</t>
-        </is>
-      </c>
+        <v>34990000</v>
+      </c>
+      <c r="C184" s="2" t="inlineStr"/>
+      <c r="D184" s="2" t="inlineStr"/>
       <c r="E184" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7947,36 +7939,42 @@
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1713w-ultra-5-225h-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407va-ly147w-core-5-210h-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:16:16.703+07:00</t>
+          <t>2026-08-18T11:42:14.925+07:00</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:22</t>
+          <t>2026-10-01 12:53:03</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST630W (Ultra 7-255H/ 16GB/ 512GB/ 14" 3K OLED)</t>
+          <t>Laptop ASUS VivoBook S14 S3407CA-SF913W (Ultra 5-225H/ 16GB/ 512GB/ 14" OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="C185" s="2" t="inlineStr"/>
-      <c r="D185" s="2" t="inlineStr"/>
+        <v>27890000</v>
+      </c>
+      <c r="C185" s="2" t="n">
+        <v>29990000</v>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -7985,33 +7983,33 @@
       <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st630w-ultra-7-255h-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s14-s3407ca-sf913w-ultra-5-225h-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T15:05:39.807+07:00</t>
+          <t>2026-09-26T13:01:54.572+07:00</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:27</t>
+          <t>2026-10-01 12:53:08</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3407NA-QD132WS (Snapdragon X2 Elite X2E-88-100/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop ASUS Zenbook 14 UM3406GA-QD075W (Ryzen 7/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>48990000</v>
+        <v>39990000</v>
       </c>
       <c r="C186" s="2" t="inlineStr"/>
       <c r="D186" s="2" t="inlineStr"/>
@@ -8023,33 +8021,33 @@
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd132ws-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ga-qd075w-ryzen-7-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:47:13.916+07:00</t>
+          <t>2026-08-17T16:03:07.024+07:00</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:32</t>
+          <t>2026-10-01 12:53:13</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook A14 UX3407NA-QD254W (Snapdragon X2 Elite X2E-88-100/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1531W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED)</t>
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>63990000</v>
+        <v>42990000</v>
       </c>
       <c r="C187" s="2" t="inlineStr"/>
       <c r="D187" s="2" t="inlineStr"/>
@@ -8061,36 +8059,42 @@
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd254w-32gb-1tb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1531w-ultra-9-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:46:55.101+07:00</t>
+          <t>2026-08-18T08:45:55.514+07:00</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:37</t>
+          <t>2026-10-01 12:53:18</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook A16 UX3607OA-SQ137WS (Snapdragon X2 Elite Extreme X2E94100/ 24GB/ 512GB/ 16" 3K OLED/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1713W (Ultra 5-225H/ 16GB/ 512GB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>58990000</v>
-      </c>
-      <c r="C188" s="2" t="inlineStr"/>
-      <c r="D188" s="2" t="inlineStr"/>
+        <v>30990000</v>
+      </c>
+      <c r="C188" s="2" t="n">
+        <v>38990000</v>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>-21%</t>
+        </is>
+      </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -8099,33 +8103,33 @@
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 16 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 24 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-16-ux3607oa-sq137ws-24gb-512gb-16-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1713w-ultra-5-225h-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:43:18.337+07:00</t>
+          <t>2026-09-25T10:16:16.703+07:00</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:42</t>
+          <t>2026-10-01 12:53:23</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN138WS (Ultra X9/ 32GB/ 1TB/ 14" 3K OLED Touch 144Hz)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST630W (Ultra 7-255H/ 16GB/ 512GB/ 14" 3K OLED)</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>89990000</v>
+        <v>40990000</v>
       </c>
       <c r="C189" s="2" t="inlineStr"/>
       <c r="D189" s="2" t="inlineStr"/>
@@ -8137,33 +8141,33 @@
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn138ws-ultra-x9-32gb-1tb-14-3k-oled-touch-144hz</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st630w-ultra-7-255h-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T12:04:03.945+07:00</t>
+          <t>2026-08-17T15:05:39.807+07:00</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:47</t>
+          <t>2026-10-01 12:53:28</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN439WS (Ultra X7/ 32GB/ 512GB/ 14" 3K OLED Touch 144Hz)</t>
+          <t>Laptop ASUS Zenbook 14 UX3407NA-QD132WS (Snapdragon X2 Elite X2E-88-100/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B190" s="3" t="n">
-        <v>82990000</v>
+        <v>48990000</v>
       </c>
       <c r="C190" s="2" t="inlineStr"/>
       <c r="D190" s="2" t="inlineStr"/>
@@ -8175,33 +8179,33 @@
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn439ws-ultra-x7-32gb-512gb-14-3k-oled-touch-144hz</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd132ws-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T11:44:06.982+07:00</t>
+          <t>2026-08-24T11:47:13.916+07:00</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:52</t>
+          <t>2026-10-01 12:53:33</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ProArt PX13 HN7306EA-LX050W (Ryzen AI Max+ 395/ 32GB/ 1TB/ 13.3" 3K OLED Touch)</t>
+          <t>Laptop ASUS Zenbook A14 UX3407NA-QD254W (Snapdragon X2 Elite X2E-88-100/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>76990000</v>
+        <v>63990000</v>
       </c>
       <c r="C191" s="2" t="inlineStr"/>
       <c r="D191" s="2" t="inlineStr"/>
@@ -8213,33 +8217,33 @@
       <c r="F191" s="2" t="inlineStr"/>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 13.3 inch | Dòng CPU: Ryzen AI MAX+ | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-pro-art-hn7306ea-lx050w-ryzen-ai-max-395-32gb-1tb-13-3-3k-oled-touch</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd254w-32gb-1tb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:58:08.111+07:00</t>
+          <t>2026-08-24T11:46:55.101+07:00</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:34:57</t>
+          <t>2026-10-01 12:53:38</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook S 14 UX5406AA-SU348W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED Touch)</t>
+          <t>Laptop ASUS Zenbook A16 UX3607OA-SQ137WS (Snapdragon X2 Elite Extreme X2E94100/ 24GB/ 512GB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>50990000</v>
+        <v>58990000</v>
       </c>
       <c r="C192" s="2" t="inlineStr"/>
       <c r="D192" s="2" t="inlineStr"/>
@@ -8251,33 +8255,33 @@
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 16 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 24 GB</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-s-14-ux5406aa-su348w-ultra-9-16gb-512gb-14-3k-oled-touch</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-16-ux3607oa-sq137ws-24gb-512gb-16-3k-oled</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T10:26:19.879+07:00</t>
+          <t>2026-08-24T11:43:18.337+07:00</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:02</t>
+          <t>2026-10-01 12:53:43</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook S 16 UM5606GA-SS441W (Ryzen AI 9 465/ 16GB/ 512GB/ 16" 3K OLED)</t>
+          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN138WS (Ultra X9/ 32GB/ 1TB/ 14" 3K OLED Touch 144Hz)</t>
         </is>
       </c>
       <c r="B193" s="3" t="n">
-        <v>49490000</v>
+        <v>89990000</v>
       </c>
       <c r="C193" s="2" t="inlineStr"/>
       <c r="D193" s="2" t="inlineStr"/>
@@ -8289,42 +8293,36 @@
       <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ryzen AI 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-s-15-um5606ga-ss441w-ryzen-ai-9-465-16gb-512gb-15-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn138ws-ultra-x9-32gb-1tb-14-3k-oled-touch-144hz</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T16:22:14.948+07:00</t>
+          <t>2026-08-17T12:04:03.945+07:00</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:06</t>
+          <t>2026-10-01 12:53:48</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - 71092480 (I7-1355U/ 16GB/ 512GB/ Win 11/ Office/ Microsoft 365)</t>
+          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN439WS (Ultra X7/ 32GB/ 512GB/ 14" 3K OLED Touch 144Hz)</t>
         </is>
       </c>
       <c r="B194" s="3" t="n">
-        <v>25390000</v>
-      </c>
-      <c r="C194" s="2" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>82990000</v>
+      </c>
+      <c r="C194" s="2" t="inlineStr"/>
+      <c r="D194" s="2" t="inlineStr"/>
       <c r="E194" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -8333,42 +8331,36 @@
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-15-dc15250-71092480-i7-1355u-16gb-512gb-win-11-office-microsoft-365</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn439ws-ultra-x7-32gb-512gb-14-3k-oled-touch-144hz</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T10:56:32.257+07:00</t>
+          <t>2026-08-17T11:44:06.982+07:00</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:12</t>
+          <t>2026-10-01 12:53:53</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I3-100U/ 8GB/ 512GB/ 15.6" FHD 120Hz/DOS) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop ASUS ProArt PX13 HN7306EA-LX050W (Ryzen AI Max+ 395/ 32GB/ 1TB/ 13.3" 3K OLED Touch)</t>
         </is>
       </c>
       <c r="B195" s="3" t="n">
-        <v>14390000</v>
-      </c>
-      <c r="C195" s="2" t="n">
-        <v>14990000</v>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>76990000</v>
+      </c>
+      <c r="C195" s="2" t="inlineStr"/>
+      <c r="D195" s="2" t="inlineStr"/>
       <c r="E195" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -8377,42 +8369,36 @@
       <c r="F195" s="2" t="inlineStr"/>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 13.3 inch | Dòng CPU: Ryzen AI MAX+ | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i3-100u-8gb-512gb-15-6-fhd-120hz</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-pro-art-hn7306ea-lx050w-ryzen-ai-max-395-32gb-1tb-13-3-3k-oled-touch</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T10:44:17.994+07:00</t>
+          <t>2026-09-24T15:58:08.111+07:00</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:17</t>
+          <t>2026-10-01 12:53:58</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I5-1334U/ 8GB/ 512GB/ 15.6" FHD/DOS) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop ASUS Zenbook S 14 UX5406AA-SU348W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED Touch)</t>
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>15990000</v>
-      </c>
-      <c r="C196" s="2" t="n">
-        <v>17490000</v>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
+        <v>50990000</v>
+      </c>
+      <c r="C196" s="2" t="inlineStr"/>
+      <c r="D196" s="2" t="inlineStr"/>
       <c r="E196" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -8421,42 +8407,36 @@
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i5-1334u-8gb-512gb-15-6-fhd</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-s-14-ux5406aa-su348w-ultra-9-16gb-512gb-14-3k-oled-touch</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:07:57.107+07:00</t>
+          <t>2026-08-17T10:26:19.879+07:00</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:22</t>
+          <t>2026-10-01 12:54:03</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 16 DC16251 (I5-120U/ 8GB/ 512GB/ 16" FHD+ Touch/ Win 11) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop ASUS Zenbook S 16 UM5606GA-SS441W (Ryzen AI 9 465/ 16GB/ 512GB/ 16" 3K OLED)</t>
         </is>
       </c>
       <c r="B197" s="3" t="n">
-        <v>18390000</v>
-      </c>
-      <c r="C197" s="2" t="n">
-        <v>19990000</v>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
-        <is>
-          <t>-8%</t>
-        </is>
-      </c>
+        <v>49490000</v>
+      </c>
+      <c r="C197" s="2" t="inlineStr"/>
+      <c r="D197" s="2" t="inlineStr"/>
       <c r="E197" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -8465,22 +8445,110 @@
       <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ryzen AI 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-16-dc16251-i5-120u-8gb-512gb-16-fhd-touch-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-s-15-um5606ga-ss441w-ryzen-ai-9-465-16gb-512gb-15-3k-oled</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T13:45:33.424+07:00</t>
+          <t>2026-09-24T16:22:14.948+07:00</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:35:27</t>
+          <t>2026-10-01 12:54:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Dell 15 DC15250 - 71092480 (I7-1355U/ 16GB/ 512GB/ Win 11/ Office/ Microsoft 365)</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="n">
+        <v>25390000</v>
+      </c>
+      <c r="C198" s="2" t="n">
+        <v>25990000</v>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr"/>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-dell-15-dc15250-71092480-i7-1355u-16gb-512gb-win-11-office-microsoft-365</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17T10:56:32.257+07:00</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:54:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I3-100U/ 8GB/ 512GB/ 15.6" FHD 120Hz/DOS) - Nhập Khẩu Chính Hãng</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="n">
+        <v>14390000</v>
+      </c>
+      <c r="C199" s="2" t="n">
+        <v>14990000</v>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i3-100u-8gb-512gb-15-6-fhd-120hz</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21T10:44:17.994+07:00</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:54:18</t>
         </is>
       </c>
     </row>

--- a/laptop_gearvn_all.xlsx
+++ b/laptop_gearvn_all.xlsx
@@ -503,56 +503,58 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0016W (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>31990000</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
+        <v>28790000</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0016w-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:25:26.316+07:00</t>
+          <t>2026-08-03T10:54:41.9+07:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:06</t>
+          <t>2026-10-03 12:17:46</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0017W (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>34990000</v>
+        <v>36290000</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>35990000</v>
+        <v>38990000</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -563,36 +565,42 @@
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: Arc | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0017w-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:28:01.415+07:00</t>
+          <t>2026-09-10T13:51:05.888+07:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:12</t>
+          <t>2026-10-03 12:17:52</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Max C13WF-421VN (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0442WS (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>44990000</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
+        <v>37190000</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -601,36 +609,42 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc 140V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13vf-421vn-i7-13620h-rtx-5060-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0442ws-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T16:26:05.15+07:00</t>
+          <t>2026-08-03T09:55:42.594+07:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:17</t>
+          <t>2026-10-03 12:17:57</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Max C13WE-422VN (I7-13620H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0450WS (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>42990000</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
+        <v>29790000</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>31990000</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -639,42 +653,36 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc 130V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn-i7-13620h-rtx-5050-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0450ws-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27T10:38:57.001+07:00</t>
+          <t>2026-08-03T09:56:18.911+07:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:22</t>
+          <t>2026-10-03 12:18:02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>34890000</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>35990000</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>199990000</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -683,42 +691,36 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
+          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T14:54:13.66+07:00</t>
+          <t>2026-09-18T11:12:30.954+07:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:27</t>
+          <t>2026-10-03 12:18:07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB027W (Core 3/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>79990000</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>80990000</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1%</t>
-        </is>
-      </c>
+        <v>22990000</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -727,33 +729,33 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb027w-core-3-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:43:38.331+07:00</t>
+          <t>2026-08-18T16:52:41.33+07:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:32</t>
+          <t>2026-10-03 12:18:12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB029W (Core 7/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>85990000</v>
+        <v>35490000</v>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
@@ -765,74 +767,80 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb029w-core-7-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T17:51:09.908+07:00</t>
+          <t>2026-08-20T15:05:22.575+07:00</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:37</t>
+          <t>2026-10-03 12:18:17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming GIGABYTE AORUS Master 16 6XJM4VNE64SH (Ryzen 9 9955HX3D/ RTX 5070 Ti 12GB/ 32GB/ 1TB/ 16" QHD+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB220W (Core 7/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>86990000</v>
+        <v>30490000</v>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gigabyte-aorus-master-16-6xjm4vne64sh-ryzen-9-9955hx3d-rtx-5070-ti-12gb-32gb-1tb-16-qhd-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb220w-core-7-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T11:46:50.068+07:00</t>
+          <t>2026-08-20T11:43:31.989+07:00</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:42</t>
+          <t>2026-10-03 12:18:22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 83RQ00DBVN (Core 3-304/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop Asus Vivobook 14 X1404V (Core 5-120U/ 8GB/ 256GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
+        <v>16590000</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>18990000</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -841,29 +849,29 @@
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-14iwc11-83rq00dbvn-core-3-304-8gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404v-core-5-120u-8gb-256gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:16:44.995+07:00</t>
+          <t>2026-08-07T13:41:37.603+07:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:47</t>
+          <t>2026-10-03 12:18:27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB005YVN (Ryzen 5-125/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VA-EB355W (Core 7-150U/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -877,31 +885,35 @@
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb005yvn-ryzen-5-125-8gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb355w-core-7-150u-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T15:01:44.794+07:00</t>
+          <t>2026-08-20T11:17:32.016+07:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:52</t>
+          <t>2026-10-03 12:18:32</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB0060VN (Ryzen 7-155/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VA-EB609W (Core 3-100U/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>27990000</v>
+        <v>21990000</v>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
@@ -911,38 +923,42 @@
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb0060vn-ryzen-7-155-8gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb609w-core-3-100u-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T14:35:59.897+07:00</t>
+          <t>2026-08-18T16:33:25.424+07:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:57</t>
+          <t>2026-10-03 12:18:37</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 3 82XQ012HUS (Ryzen 5/ 8GB/ 512GB/ 15.6" FHD/ Abyss Blue/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VAP-V14.C58256 (Core 5-120U/ 16GB/ 256GB/ 14" FHD IPS/ Win 11/ Quiet Blue)</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>16390000</v>
+        <v>17890000</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>17990000</v>
+        <v>18990000</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -951,71 +967,79 @@
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-82xq012hus-ryzen-5-8gb-512gb-15-6-fhd-abyss-blue-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404vap-v14-c58256-core-5-120u-8gb-256gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02T09:22:52.764+07:00</t>
+          <t>2026-09-14T17:42:34.369+07:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:02</t>
+          <t>2026-10-03 12:18:42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 83S1003GVN</t>
+          <t>Laptop Asus VivoBook 14 X1407AA-LY360W (Ultra 5-325/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>44540000</v>
+        <v>26490000</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>47990000</v>
+        <v>26990000</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-83s1003gvn</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407aa-ly360w-ultra-5-325-16gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T10:29:16.152+07:00</t>
+          <t>2026-08-07T15:46:33.275+07:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:07</t>
+          <t>2026-10-03 12:18:47</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 OLED 83S1006RVN (Ryzen AI 7-445/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1407CA-LY203W (Ultra 5-225H/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>32990000</v>
+        <v>33490000</v>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr"/>
@@ -1027,33 +1051,33 @@
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-oled-83s1006rvn-ryzen-ai-7-445-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407ca-ly203w-ultra-5-225h-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T11:54:44.05+07:00</t>
+          <t>2026-08-20T10:22:08.041+07:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:12</t>
+          <t>2026-10-03 12:18:52</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00ABVN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 15 X1504MA-BQ632W (Core 5-320/ 8GB/ 512GB/ 15" FHD IPS)</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>30990000</v>
+        <v>26990000</v>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
@@ -1065,33 +1089,33 @@
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00abvn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq632w-core-5-320-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T14:05:59.687+07:00</t>
+          <t>2026-08-18T15:43:54.381+07:00</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:17</t>
+          <t>2026-10-03 12:18:57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00F5VN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 15 X1504MA-BQ633W (Core 7-350/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>34990000</v>
+        <v>30490000</v>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr"/>
@@ -1103,33 +1127,33 @@
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00f5vn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq633w-core-7-350-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:17:34.624+07:00</t>
+          <t>2026-09-26T12:47:34.397+07:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:22</t>
+          <t>2026-10-03 12:19:02</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002EVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 15 X1504VA-BQ165W (Core 5-120U/ 8GB/ 512GB/ 15" FHD IPS)</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>55990000</v>
+        <v>20990000</v>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
@@ -1141,33 +1165,33 @@
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002evn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504va-bq165w-core-5-120u-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T10:21:35.763+07:00</t>
+          <t>2026-08-18T16:12:00.028+07:00</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:27</t>
+          <t>2026-10-03 12:19:07</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002FVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 16 X1607CA-MB387W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD IPS)</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>55990000</v>
+        <v>33490000</v>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr"/>
@@ -1179,33 +1203,33 @@
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002fvn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb387w-ultra-5-225h-16gb-512gb-16-fhd-ips</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T20:29:51.634+07:00</t>
+          <t>2026-08-20T16:08:06.906+07:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:32</t>
+          <t>2026-10-03 12:19:12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0075VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 16 X1607CA-MB399W (Ultra 7-255H/ 16GB/ 512GB/ 16" FHD IPS)</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>46990000</v>
+        <v>36490000</v>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1215,31 +1239,35 @@
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0075vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb399w-ultra-7-255h-16gb-512gb-16-fhd-ips</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:19:34.771+07:00</t>
+          <t>2026-08-20T15:36:19.591+07:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:37</t>
+          <t>2026-10-03 12:19:17</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0076VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook Flip TP3407AA-SG029W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>46990000</v>
+        <v>41990000</v>
       </c>
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr"/>
@@ -1256,28 +1284,28 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0076vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-flip-tp3407aa-sg029w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:20:20.027+07:00</t>
+          <t>2026-08-18T14:55:40.249+07:00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:42</t>
+          <t>2026-10-03 12:19:22</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK0015VN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ4821W (Ryzen 5/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>72990000</v>
+        <v>22990000</v>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1289,33 +1317,33 @@
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk0015vn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1504fa-bq4821w-ryzen-5-8gb-512gb-15-fhd-ips</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:21:45.74+07:00</t>
+          <t>2026-09-24T15:55:57.447+07:00</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:47</t>
+          <t>2026-10-03 12:19:27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK006GVN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ340W (Ryzen 5/ 16GB/ 512GB/ 15.6" FHD IPS)</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>72990000</v>
+        <v>28490000</v>
       </c>
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr"/>
@@ -1327,33 +1355,33 @@
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk006gvn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-go-15-e1504fa-bq340w-ryzen-5-16gb-512gb-156-fhd-ips</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:23:05.36+07:00</t>
+          <t>2026-09-24T15:55:13.502+07:00</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:52</t>
+          <t>2026-10-03 12:19:32</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 POLED 83QK009PVN (Ultra X9-378H/ 32GB/ 1TB/ 14" 2.8K WQXGA POLED Touch/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 M3407KA-SF034W (Ryzen AI 5-330/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>70990000</v>
+        <v>33990000</v>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr"/>
@@ -1365,42 +1393,36 @@
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-poled-83qk009pvn-ultra-x9-378h-32gb-1tb-14-2-8k-wqxga-poled-touch-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-m3407ka-sf034w-ryzen-ai-5-330-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T20:11:25.828+07:00</t>
+          <t>2026-08-18T12:02:07.653+07:00</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:57</t>
+          <t>2026-10-03 12:19:37</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407AA-SF945W (Ultra 5-325/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>33900000</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>34900000</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>37490000</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -1409,114 +1431,118 @@
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf945w-ultra-5-325-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:39:36.938+07:00</t>
+          <t>2026-08-18T11:09:17.449+07:00</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:02</t>
+          <t>2026-10-03 12:19:42</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop ASUS Vivobook S 14 S3407VA-LY147W (Core 5-210H/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>36900000</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>37900000</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
+        <v>34990000</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407va-ly147w-core-5-210h-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:34:21.041+07:00</t>
+          <t>2026-08-18T11:42:14.925+07:00</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:07</t>
+          <t>2026-10-03 12:19:47</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
+          <t>Laptop ASUS VivoBook S14 S3407CA-SF913W (Ultra 5-225H/ 16GB/ 512GB/ 14" OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>44900000</v>
+        <v>27890000</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46490000</v>
+        <v>29990000</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-s14-s3407ca-sf913w-ultra-5-225h-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:43:00.949+07:00</t>
+          <t>2026-09-26T13:01:54.572+07:00</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:12</t>
+          <t>2026-10-03 12:19:52</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UM3406GA-QD075W (Ryzen 7/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>23990000</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>24990000</v>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>39990000</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -1525,42 +1551,36 @@
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ga-qd075w-ryzen-7-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:36:48.562+07:00</t>
+          <t>2026-08-17T16:03:07.024+07:00</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:17</t>
+          <t>2026-10-03 12:19:57</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1531W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED)</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>61990000</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>62990000</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>42990000</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -1569,40 +1589,40 @@
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1531w-ultra-9-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T15:49:38.229+07:00</t>
+          <t>2026-08-18T08:45:55.514+07:00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:23</t>
+          <t>2026-10-03 12:20:01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1713W (Ultra 5-225H/ 16GB/ 512GB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>34690000</v>
+        <v>30990000</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>37990000</v>
+        <v>38990000</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-21%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1613,73 +1633,71 @@
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1713w-ultra-5-225h-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T10:28:18.636+07:00</t>
+          <t>2026-09-25T10:16:16.703+07:00</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:28</t>
+          <t>2026-10-03 12:20:07</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3405CA-ST630W (Ultra 7-255H/ 16GB/ 512GB/ 14" 3K OLED)</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>25490000</v>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>25990000</v>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>40990000</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st630w-ultra-7-255h-16gb-512gb-14-3k-oled</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:41:40.106+07:00</t>
+          <t>2026-08-17T15:05:39.807+07:00</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:33</t>
+          <t>2026-10-03 12:20:12</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 14S AI+ G3MG-050VN (Ultra 7-355/ 16GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop ASUS Zenbook 14 UX3407NA-QD132WS (Snapdragon X2 Elite X2E-88-100/ 16GB/ 512GB/ 14" FHD OLED)</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>36490000</v>
+        <v>48990000</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
@@ -1691,42 +1709,36 @@
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-14s-ai-g3mg-050vn-ultra-7-355-16gb-1tb-14-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd132ws-16gb-512gb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T17:51:58.168+07:00</t>
+          <t>2026-08-24T11:47:13.916+07:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:38</t>
+          <t>2026-10-03 12:20:17</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
+          <t>Laptop ASUS Zenbook A14 UX3407NA-QD254W (Snapdragon X2 Elite X2E-88-100/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>22190000</v>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>22690000</v>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>63990000</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -1735,42 +1747,36 @@
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd254w-32gb-1tb-14-fhd-oled</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T15:28:04.144+07:00</t>
+          <t>2026-08-24T11:46:55.101+07:00</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:43</t>
+          <t>2026-10-03 12:20:21</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
+          <t>Laptop ASUS Zenbook A16 UX3607OA-SQ137WS (Snapdragon X2 Elite Extreme X2E94100/ 24GB/ 512GB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>43990000</v>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>44990000</v>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>58990000</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -1779,42 +1785,36 @@
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 16 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 24 GB</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-16-ux3607oa-sq137ws-24gb-512gb-16-3k-oled</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:49:42.234+07:00</t>
+          <t>2026-08-24T11:43:18.337+07:00</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:48</t>
+          <t>2026-10-03 12:20:26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
+          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN138WS (Ultra X9/ 32GB/ 1TB/ 14" 3K OLED Touch 144Hz)</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>33990000</v>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>89990000</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -1823,42 +1823,36 @@
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 7 | Dung lượng SSD: 1024 GB | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn138ws-ultra-x9-32gb-1tb-14-3k-oled-touch-144hz</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T16:07:23.364+07:00</t>
+          <t>2026-08-17T12:04:03.945+07:00</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:53</t>
+          <t>2026-10-03 12:20:31</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
+          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN439WS (Ultra X7/ 32GB/ 512GB/ 14" 3K OLED Touch 144Hz)</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>37990000</v>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
+        <v>82990000</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -1867,42 +1861,36 @@
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 13.3 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn439ws-ultra-x7-32gb-512gb-14-3k-oled-touch-144hz</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T11:20:56.718+07:00</t>
+          <t>2026-08-17T11:44:06.982+07:00</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:58</t>
+          <t>2026-10-03 12:20:36</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN (Ultra 7-355/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop ASUS ProArt PX13 HN7306EA-LX050W (Ryzen AI Max+ 395/ 32GB/ 1TB/ 13.3" 3K OLED Touch)</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>44490000</v>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>48990000</v>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
+        <v>76990000</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -1911,33 +1899,33 @@
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel® Arc™ graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 13.3 inch | Dòng CPU: Ryzen AI MAX+ | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-pro-art-hn7306ea-lx050w-ryzen-ai-max-395-32gb-1tb-13-3-3k-oled-touch</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28T10:53:12.84+07:00</t>
+          <t>2026-09-24T15:58:08.111+07:00</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:03</t>
+          <t>2026-10-03 12:20:41</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop ASUS Zenbook S 14 UX5406AA-SU348W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED Touch)</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>59990000</v>
+        <v>50990000</v>
       </c>
       <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr"/>
@@ -1947,68 +1935,80 @@
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-s-14-ux5406aa-su348w-ultra-9-16gb-512gb-14-3k-oled-touch</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T09:54:52.677+07:00</t>
+          <t>2026-08-17T10:26:19.879+07:00</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:09</t>
+          <t>2026-10-03 12:20:46</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
+          <t>Laptop ASUS Zenbook S 16 UM5606GA-SS441W (Ryzen AI 9 465/ 16GB/ 512GB/ 16" 3K OLED)</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>59990000</v>
+        <v>49490000</v>
       </c>
       <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ryzen AI 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-zenbook-s-15-um5606ga-ss441w-ryzen-ai-9-465-16gb-512gb-15-3k-oled</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T10:17:43.984+07:00</t>
+          <t>2026-09-24T16:22:14.948+07:00</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:14</t>
+          <t>2026-10-03 12:20:51</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/ RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
+          <t>Laptop Dell 15 DC15250 - 71092480 (I7-1355U/ 16GB/ 512GB/ Win 11/ Office/ Microsoft 365)</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>82990000</v>
+        <v>25390000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>83990000</v>
+        <v>25990000</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2019,40 +2019,40 @@
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-dell-15-dc15250-71092480-i7-1355u-16gb-512gb-win-11-office-microsoft-365</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T15:48:57.837+07:00</t>
+          <t>2026-09-17T10:56:32.257+07:00</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:19</t>
+          <t>2026-10-03 12:20:56</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
+          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I3-100U/ 8GB/ 512GB/ 15.6" FHD 120Hz/DOS) - Nhập Khẩu Chính Hãng</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>86990000</v>
+        <v>14390000</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>87990000</v>
+        <v>14990000</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2063,22 +2063,22 @@
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
+          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i3-100u-8gb-512gb-15-6-fhd-120hz</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T17:54:02.495+07:00</t>
+          <t>2026-08-21T10:44:17.994+07:00</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:24</t>
+          <t>2026-10-03 12:21:01</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:06</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:11</t>
+          <t>2026-10-03 12:18:07</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:16</t>
+          <t>2026-10-03 12:18:12</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:21</t>
+          <t>2026-10-03 12:18:17</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:26</t>
+          <t>2026-10-03 12:18:22</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:31</t>
+          <t>2026-10-03 12:18:28</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:36</t>
+          <t>2026-10-03 12:18:33</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:41</t>
+          <t>2026-10-03 12:18:38</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:46</t>
+          <t>2026-10-03 12:18:43</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:51</t>
+          <t>2026-10-03 12:18:49</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:56</t>
+          <t>2026-10-03 12:18:54</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:00</t>
+          <t>2026-10-03 12:18:59</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:05</t>
+          <t>2026-10-03 12:19:04</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:10</t>
+          <t>2026-10-03 12:19:10</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:16</t>
+          <t>2026-10-03 12:19:15</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:20</t>
+          <t>2026-10-03 12:19:20</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:25</t>
+          <t>2026-10-03 12:19:25</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:30</t>
+          <t>2026-10-03 12:19:30</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:35</t>
+          <t>2026-10-03 12:19:35</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:40</t>
+          <t>2026-10-03 12:19:40</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:45</t>
+          <t>2026-10-03 12:19:45</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:50</t>
+          <t>2026-10-03 12:19:50</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:55</t>
+          <t>2026-10-03 12:19:55</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:00</t>
+          <t>2026-10-03 12:20:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:05</t>
+          <t>2026-10-03 12:20:05</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:10</t>
+          <t>2026-10-03 12:20:10</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:15</t>
+          <t>2026-10-03 12:20:15</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:20</t>
+          <t>2026-10-03 12:20:20</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:25</t>
+          <t>2026-10-03 12:20:25</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:30</t>
+          <t>2026-10-03 12:20:30</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:35</t>
+          <t>2026-10-03 12:20:35</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:40</t>
+          <t>2026-10-03 12:20:40</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:45</t>
+          <t>2026-10-03 12:20:45</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:50</t>
+          <t>2026-10-03 12:20:50</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:55</t>
+          <t>2026-10-03 12:20:55</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:59</t>
+          <t>2026-10-03 12:21:00</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:04</t>
+          <t>2026-10-03 12:21:05</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:09</t>
+          <t>2026-10-03 12:21:10</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:14</t>
+          <t>2026-10-03 12:21:15</t>
         </is>
       </c>
     </row>
@@ -3740,27 +3740,21 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:19</t>
+          <t>2026-10-03 12:21:20</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G16 G614PH-S5101W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 240Hz/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2610VN (I5-13420H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>47490000</v>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v>53990000</v>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>-12%</t>
-        </is>
-      </c>
+        <v>31990000</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3769,36 +3763,42 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-s5101w</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2610vn-i5-13420h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T11:28:04.811+07:00</t>
+          <t>2026-06-30T15:25:26.316+07:00</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:02</t>
+          <t>2026-10-03 12:17:50</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G16 G614PH-TS118W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-418VN (I5-13420H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>52990000</v>
-      </c>
-      <c r="C83" s="2" t="inlineStr"/>
-      <c r="D83" s="2" t="inlineStr"/>
+        <v>34990000</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>35990000</v>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3807,42 +3807,36 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-ts118w</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-c13weo-418vn-i5-13420h-rtx-5050-8gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T11:49:35.857+07:00</t>
+          <t>2026-06-30T15:28:01.415+07:00</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:07</t>
+          <t>2026-10-03 12:17:55</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G16 G614PM-TS147W (Ryzen 9-8940HX/ RTX 5060 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Max C13WF-421VN (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>54690000</v>
-      </c>
-      <c r="C84" s="2" t="n">
-        <v>59990000</v>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
+        <v>44990000</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr"/>
+      <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3851,33 +3845,33 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614pm-ts147w</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13vf-421vn-i7-13620h-rtx-5060-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:15:11.541+07:00</t>
+          <t>2026-09-23T16:26:05.15+07:00</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:12</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix SCAR G835LXG-TQ473W (Ultra 9-290HX Plus/ RTX 5090/ 64GB/ 2TB/ 18" Mini LED 240Hz/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 Max C13WE-422VN (I7-13620H/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD IPS 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>179990000</v>
+        <v>42990000</v>
       </c>
       <c r="C85" s="2" t="inlineStr"/>
       <c r="D85" s="2" t="inlineStr"/>
@@ -3889,70 +3883,86 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 18 inch | Độ phân giải: UHD+ (3840x2400) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-scar-g835lxg-tq473w-ultra-9-290hx-plus-rtx-5090-64gb-2tb-18-qhd-mini-led-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-max-c13we-422vn-i7-13620h-rtx-5050-8gb-16gb-512gb-15-6-fhd-ips-144hz-win-11</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:58:23.481+07:00</t>
+          <t>2026-07-27T10:38:57.001+07:00</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:17</t>
+          <t>2026-10-03 12:18:05</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus G16 GU606AM-TB032W (Ultra 9-386H/ RTX 5060 8GB/ 32GB/ 1TB/ 16" 2.5K OLED/ Win 11)</t>
+          <t>Laptop gaming MSI Katana 15 B13VEK-2440VN (I7-13620H/ RTX 4050/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>89990000</v>
-      </c>
-      <c r="C86" s="2" t="inlineStr"/>
-      <c r="D86" s="2" t="inlineStr"/>
+        <v>34890000</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>35990000</v>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-g16-gu606am-tb032w-ultra-9-386h-rtx-5060-8gb-32gb-1tb-16-2-5k-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-katana-15-b13vek-2440vn</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T17:05:02.313+07:00</t>
+          <t>2026-06-30T14:54:13.66+07:00</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:22</t>
+          <t>2026-10-03 12:18:10</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU405AR-SY016W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WF-007VN (Ultra 9-386H/ RTX 5060/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>96990000</v>
-      </c>
-      <c r="C87" s="2" t="inlineStr"/>
-      <c r="D87" s="2" t="inlineStr"/>
+        <v>79990000</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>80990000</v>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -3961,33 +3971,33 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405ar-sy016w-ultra-9-rtx-5070-ti-32gb-1tb-14-3k-oled-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-007vn</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:47:29.287+07:00</t>
+          <t>2026-06-30T15:43:38.331+07:00</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:27</t>
+          <t>2026-10-03 12:18:15</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU405AW-SY029W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WG-008VN (Ultra 9-386H/ RTX 5070 8GB/ 32GB/ 1TB/ 16" QHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>119990000</v>
+        <v>85990000</v>
       </c>
       <c r="C88" s="2" t="inlineStr"/>
       <c r="D88" s="2" t="inlineStr"/>
@@ -3999,71 +4009,71 @@
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405aw-sy029w-ultra-9-rtx-5080-32gb-1tb-14-3k-oled-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-stealth-16-ai-b3wg-008vn</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:47:45.327+07:00</t>
+          <t>2026-09-22T17:51:09.908+07:00</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:32</t>
+          <t>2026-10-03 12:18:20</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR115W (Ultra 7-255H/ RTX 5070/ 16GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop gaming GIGABYTE AORUS Master 16 6XJM4VNE64SH (Ryzen 9 9955HX3D/ RTX 5070 Ti 12GB/ 32GB/ 1TB/ 16" QHD+ OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>74990000</v>
+        <v>86990000</v>
       </c>
       <c r="C89" s="2" t="inlineStr"/>
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr115w-ultra-7-255h-rtx-5070-16gb-512gb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-gigabyte-aorus-master-16-6xjm4vne64sh-ryzen-9-9955hx3d-rtx-5070-ti-12gb-32gb-1tb-16-qhd-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:46:00.864+07:00</t>
+          <t>2026-09-24T11:46:50.068+07:00</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:37</t>
+          <t>2026-10-03 12:18:25</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR141W (Ultra 7-255H/ RTX 5070/ 32GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 14IWC11 83RQ00DBVN (Core 3-304/ 8GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>83990000</v>
+        <v>24990000</v>
       </c>
       <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr"/>
@@ -4075,33 +4085,33 @@
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr141w-ultra-7-255h-rtx-5070-32gb-512gb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-14iwc11-83rq00dbvn-core-3-304-8gb-512gb-14-wuxga-win-11</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:46:21.05+07:00</t>
+          <t>2026-09-07T10:16:44.995+07:00</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:42</t>
+          <t>2026-10-03 12:18:30</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AR-TB027W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB005YVN (Ryzen 5-125/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>99990000</v>
+        <v>25990000</v>
       </c>
       <c r="C91" s="2" t="inlineStr"/>
       <c r="D91" s="2" t="inlineStr"/>
@@ -4111,35 +4121,31 @@
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
-        </is>
-      </c>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ar-tb027w-ultra-9-rtx-5070-ti-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb005yvn-ryzen-5-125-8gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:10.531+07:00</t>
+          <t>2026-08-13T15:01:44.794+07:00</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:47</t>
+          <t>2026-10-03 12:18:35</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB052WS (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 16AHP10 83KB0060VN (Ryzen 7-155/ 8GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>139990000</v>
+        <v>27990000</v>
       </c>
       <c r="C92" s="2" t="inlineStr"/>
       <c r="D92" s="2" t="inlineStr"/>
@@ -4149,120 +4155,114 @@
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
-        </is>
-      </c>
+      <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb052ws-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-16ahp10-83kb0060vn-ryzen-7-155-8gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:28.879+07:00</t>
+          <t>2026-08-13T14:35:59.897+07:00</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:52</t>
+          <t>2026-10-03 12:18:40</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB121W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 3 82XQ012HUS (Ryzen 5/ 8GB/ 512GB/ 15.6" FHD/ Abyss Blue/ Win 11)</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>124990000</v>
-      </c>
-      <c r="C93" s="2" t="inlineStr"/>
-      <c r="D93" s="2" t="inlineStr"/>
+        <v>16390000</v>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>17990000</v>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
-        </is>
-      </c>
+      <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb121w-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-3-82xq012hus-ryzen-5-8gb-512gb-15-6-fhd-abyss-blue-win-11</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:44.227+07:00</t>
+          <t>2026-10-02T09:22:52.764+07:00</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:57</t>
+          <t>2026-10-03 12:18:45</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AX-TB042WS (Ultra 9/ RTX 5090/ 64GB/ 2TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 83S1003GVN</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>169990000</v>
-      </c>
-      <c r="C94" s="2" t="inlineStr"/>
-      <c r="D94" s="2" t="inlineStr"/>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>44540000</v>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>47990000</v>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ax-tb042ws-ultra-9-rtx-5090-64gb-2tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-83s1003gvn</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:44:50.259+07:00</t>
+          <t>2026-08-28T10:29:16.152+07:00</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:02</t>
+          <t>2026-10-03 12:18:50</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA 165Hz/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AGP11 OLED 83S1006RVN (Ryzen AI 7-445/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>57390000</v>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v>58990000</v>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+        <v>32990000</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr"/>
+      <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4271,42 +4271,36 @@
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: AMD Radeon 840M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14agp11-oled-83s1006rvn-ryzen-ai-7-445-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:35:45.75+07:00</t>
+          <t>2026-08-13T11:54:44.05+07:00</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:07</t>
+          <t>2026-10-03 12:18:55</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN329W (Ryzen 7-8845HS/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00ABVN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>27690000</v>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v>37490000</v>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>-26%</t>
-        </is>
-      </c>
+        <v>30990000</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr"/>
+      <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4315,42 +4309,36 @@
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn329w-ryzen-7-8845hs-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00abvn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:04:13.749+07:00</t>
+          <t>2026-08-13T14:05:59.687+07:00</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:12</t>
+          <t>2026-10-03 12:19:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN390W (Ryzen 7-155/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
+          <t>Laptop Lenovo IdeaPad Slim 5 14AKP10 OLED 83HX00F5VN (Ryzen AI 5-330/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>28990000</v>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>34990000</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr"/>
+      <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4359,82 +4347,74 @@
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: AMD Radeon 820M Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn390w-ryzen-7-155-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-ideapad-slim-5-14akp10-oled-83hx00f5vn-ryzen-ai-5-330-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T11:05:26.118+07:00</t>
+          <t>2026-09-07T10:17:34.624+07:00</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:17</t>
+          <t>2026-10-03 12:19:05</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUG-RL129W (Ryzen 7-7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002EVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>29990000</v>
-      </c>
-      <c r="C98" s="2" t="n">
-        <v>30990000</v>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr"/>
+        <v>55990000</v>
+      </c>
+      <c r="C98" s="2" t="inlineStr"/>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nug-rl129w-ryzen-7-7445hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002evn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:41:09.162+07:00</t>
+          <t>2026-08-13T10:21:35.763+07:00</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:22</t>
+          <t>2026-10-03 12:19:11</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUQ-RL007W (Ryzen 7-170/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM002FVN (Ultra 7-355/ 32GB/ 1TB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>36290000</v>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
+        <v>55990000</v>
+      </c>
+      <c r="C99" s="2" t="inlineStr"/>
+      <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4443,77 +4423,67 @@
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nuq-rl007w-ryzen-7-170-rtx-4050-6gb-16gb-512gb-16-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm002fvn-ultra-7-355-32gb-1tb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:10:34.588+07:00</t>
+          <t>2026-08-12T20:29:51.634+07:00</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:27</t>
+          <t>2026-10-03 12:19:16</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0075VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>41260000</v>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v>45390000</v>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>-9%</t>
-        </is>
-      </c>
+        <v>46990000</v>
+      </c>
+      <c r="C100" s="2" t="inlineStr"/>
+      <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
-        </is>
-      </c>
+      <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0075vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T14:06:48.719+07:00</t>
+          <t>2026-09-07T10:19:34.771+07:00</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:33</t>
+          <t>2026-10-03 12:19:21</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA401EA-RG041W (Ryzen AI Max+ 392/ 32GB/ 512GB/ 14" 2.5K/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 14IPH11 OLED 83QM0076VN (Ultra 7-355/ 16GB/ 512GB/ 14" WUXGA OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>59990000</v>
+        <v>46990000</v>
       </c>
       <c r="C101" s="2" t="inlineStr"/>
       <c r="D101" s="2" t="inlineStr"/>
@@ -4525,33 +4495,33 @@
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen AI MAX+ | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon 8060S | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401ea-rg041w-ryzen-ai-max-392-32gb-512gb-14-2-5k-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-14iph11-oled-83qm0076vn-ultra-7-355-16gb-512gb-14-wuxga-oled-win-11</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T09:33:26.048+07:00</t>
+          <t>2026-09-07T10:20:20.027+07:00</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:38</t>
+          <t>2026-10-03 12:19:26</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA401UH-RG001W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK0015VN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>49990000</v>
+        <v>72990000</v>
       </c>
       <c r="C102" s="2" t="inlineStr"/>
       <c r="D102" s="2" t="inlineStr"/>
@@ -4563,33 +4533,33 @@
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401uh-rg001w-ryzen-7-260-rtx-5050-16gb-512gb-14-qhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk0015vn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:59:55.007+07:00</t>
+          <t>2026-09-07T10:21:45.74+07:00</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:43</t>
+          <t>2026-10-03 12:19:31</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA401UM-RG049W (Ryzen 7 260/ RTX 5060/ 32GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 OLED 83QK006GVN (Ultra 7-355/ 32GB/ 1TB/ 14" 2.8K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>64990000</v>
+        <v>72990000</v>
       </c>
       <c r="C103" s="2" t="inlineStr"/>
       <c r="D103" s="2" t="inlineStr"/>
@@ -4601,33 +4571,33 @@
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401um-rg049w-ryzen-7-260-rtx-5060-32gb-512gb-14-qhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-oled-83qk006gvn-ultra-7-355-32gb-1tb-14-2-8k-oled-win-11</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T13:00:47.55+07:00</t>
+          <t>2026-09-07T10:23:05.36+07:00</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:48</t>
+          <t>2026-10-03 12:19:36</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA608UHI-TU121W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
+          <t>Laptop Lenovo Yoga Slim 7 Ultra 14IPH11 POLED 83QK009PVN (Ultra X9-378H/ 32GB/ 1TB/ 14" 2.8K WQXGA POLED Touch/ Win 11)</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>48990000</v>
+        <v>70990000</v>
       </c>
       <c r="C104" s="2" t="inlineStr"/>
       <c r="D104" s="2" t="inlineStr"/>
@@ -4639,36 +4609,42 @@
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608uhi-tu121w-ryzen-7-260-rtx-5050-16gb-512gb-16-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-lenovo-yoga-slim-7-ultra-14iph11-poled-83qk009pvn-ultra-x9-378h-32gb-1tb-14-2-8k-wqxga-poled-touch-win-11</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T11:22:30.725+07:00</t>
+          <t>2026-08-12T20:11:25.828+07:00</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:53</t>
+          <t>2026-10-03 12:19:41</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS TUF Gaming FA608UMI-TU162W (Ryzen 7 260/ RTX 5060/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
+          <t>Laptop LG Gram 14Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 14.0" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>51990000</v>
-      </c>
-      <c r="C105" s="2" t="inlineStr"/>
-      <c r="D105" s="2" t="inlineStr"/>
+        <v>33900000</v>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>34900000</v>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4677,296 +4653,280 @@
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608umi-tu162w-ryzen-7-260-rtx-5060-16gb-512gb-16-fhd-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-14z90u-g-an55a5-ultra-5-325-16gb-512gb-14-0-fhd-win-11</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T11:01:50.971+07:00</t>
+          <t>2026-07-01T13:39:36.938+07:00</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:58</t>
+          <t>2026-10-03 12:19:46</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS V16 V3607VJ-TK189W (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 16" WUXGA 144Hz/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AN55A5 (Ultra 5-325/ 16GB/ 512GB/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>26490000</v>
+        <v>36900000</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>29990000</v>
+        <v>37900000</v>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
-        </is>
-      </c>
+      <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-v16-v3607vj-tk189w-core-5-210h-rtx-3050-6gb-16gb-512gb-16-wuxga-144hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-an55a5-ultra-5-325-16gb-512gb-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15T16:26:14.526+07:00</t>
+          <t>2026-07-01T13:34:21.041+07:00</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:03</t>
+          <t>2026-10-03 12:19:52</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
+          <t>Laptop LG Gram Pro 16Z90U-G.AV85A5 (Ultra 7-355/ 32GB/ 512GB/ Intel Graphics/ 16.0" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>31990000</v>
+        <v>44900000</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>32790000</v>
+        <v>46490000</v>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
-        </is>
-      </c>
+      <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
+          <t>https://gearvn.com/products/laptop-lg-gram-pro-16z90u-g-av85a5-ultra-7-355-32gb-512gb-intel-graphics-16-0-wqxga-win-11</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30T11:59:37.483+07:00</t>
+          <t>2026-07-01T13:43:00.949+07:00</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:08</t>
+          <t>2026-10-03 12:19:57</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming GIGABYTE A16 CVHI3MY893SH (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
+          <t>Laptop LG Grambook 15U50U-G.AV55A5 (Ultra 5-115U/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>36990000</v>
+        <v>23990000</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>38990000</v>
+        <v>24990000</v>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3my893sh</t>
+          <t>https://gearvn.com/products/laptop-lg-grambook-15u50u-g-av55a5-ultra-5-115u-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T14:40:23.197+07:00</t>
+          <t>2026-07-01T13:36:48.562+07:00</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:13</t>
+          <t>2026-10-03 12:20:02</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte A16 A16-3THK3VN893SH (Ryzen 7 260/ RTX 5050 8GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop gaming MSI Crosshair 16 HX E14WEK-076VN (I9-14900HX/ 32GB/ 1TB/ RTX 5050/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>35990000</v>
+        <v>61990000</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>40990000</v>
+        <v>62990000</v>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: i9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-ga63h-3thk3vn893sh</t>
+          <t>https://gearvn.com/products/laptop-msi-crosshair-16-hx-e14wek-076vn-i9-14900hx-32gb-1tb-rtx-5050-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30T09:54:12.234+07:00</t>
+          <t>2026-09-23T15:49:38.229+07:00</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:18</t>
+          <t>2026-10-03 12:20:07</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9LJR2VNF93SH (Ryzen 5 7533HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop gaming MSI Cyborg 15 C13WEO-417VN (I7-13620H/ RTX 5050/ 16GB/ 512GB/ 15.6" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>29990000</v>
+        <v>34690000</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>30990000</v>
+        <v>37990000</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9ljr2vnf93sh-ryzen-5-7533hs-rtx-3050-6gb-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-cyborg-15-c13weo-417vn-i7-13620h-16gb-512gb-rtx-5050-15-6-fhd-144hz-win11</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T15:10:54.55+07:00</t>
+          <t>2026-09-21T10:28:18.636+07:00</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:23</t>
+          <t>2026-10-03 12:20:12</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9MJR2VNF93SH (Ryzen 5 7533HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
+          <t>Laptop MSI Modern 14 H1M-014VN (Core 7 150U/ 16GB/ 512GB/ UMA/ 14" FHD/ Win11)</t>
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="C111" s="2" t="inlineStr"/>
-      <c r="D111" s="2" t="inlineStr"/>
-      <c r="E111" s="2" t="inlineStr"/>
+        <v>25490000</v>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>25990000</v>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+        </is>
+      </c>
       <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
-        </is>
-      </c>
+      <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9mjr2vnf93sh-ryzen-5-7533hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-14-h1m-014vn-core-7-150u-16gb-512gb-uma-14-fhd-win11</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:50:39.975+07:00</t>
+          <t>2026-06-25T15:41:40.106+07:00</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:28</t>
+          <t>2026-10-03 12:20:17</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
+          <t>Laptop MSI Modern 14S AI+ G3MG-050VN (Ultra 7-355/ 16GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>115990000</v>
-      </c>
-      <c r="C112" s="2" t="n">
-        <v>117990000</v>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>36490000</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr"/>
+      <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -4975,36 +4935,42 @@
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-14s-ai-g3mg-050vn-ultra-7-355-16gb-1tb-14-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05T14:44:14.658+07:00</t>
+          <t>2026-09-22T17:51:58.168+07:00</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:33</t>
+          <t>2026-10-03 12:20:22</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15AHP11 83TN0040VN (Ryzen 7-250/ RTX 5050 8GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
+          <t>Laptop MSI Modern 15 F1MG-1225VN (CORE 5-120U/ 16GB /512GB / 15.6 FHD/ WIN11)</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>43990000</v>
-      </c>
-      <c r="C113" s="2" t="inlineStr"/>
-      <c r="D113" s="2" t="inlineStr"/>
+        <v>22190000</v>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>22690000</v>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5013,40 +4979,40 @@
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15ahp11-83tn0040vn-ryzen-7-250-rtx-5050-8gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-15-f1mg-1225vn-core-5-120u-16gb-512gb-15-6-fhd-win11</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T09:36:14.406+07:00</t>
+          <t>2026-07-09T15:28:04.144+07:00</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:38</t>
+          <t>2026-10-03 12:20:27</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Modern 16S AI+ G3MG-058VN (Core Ultra 7 355/ 16GB/ 1TB/ 16" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>38990000</v>
+        <v>43990000</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>41990000</v>
+        <v>44990000</v>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -5057,40 +5023,40 @@
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-ai-g3mg-058vn-core-ultra-7-355-16gb-1tb-16-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:38.199+07:00</t>
+          <t>2026-06-25T15:49:42.234+07:00</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:43</t>
+          <t>2026-10-03 12:20:32</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S0006RVN (Ryzen 7-7735HS/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Modern 16S G3MG-016VN (Core 7 350/ 16GB/ 1TB/ 16" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>30990000</v>
+        <v>33990000</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>32990000</v>
+        <v>34990000</v>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5101,36 +5067,42 @@
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core 7 | Dung lượng SSD: 1024 GB | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0006rvn-ryzen-7-7735hs-rtx-3050-6gb-16gb-1tb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-modern-16s-g3mg-016vn-core-7-350-16gb-1tb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22T11:31:57.635+07:00</t>
+          <t>2026-06-25T16:07:23.364+07:00</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:48</t>
+          <t>2026-10-03 12:20:37</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S000DCVN (Ryzen 7-170/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop MSI Prestige 13 AI+ Evo A2VMG 040VN</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>32990000</v>
-      </c>
-      <c r="C116" s="2" t="inlineStr"/>
-      <c r="D116" s="2" t="inlineStr"/>
+        <v>37990000</v>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5139,36 +5111,42 @@
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Card đồ họa: Intel Arc | Kích thước màn hình: 13.3 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s000dcvn-ryzen-7-170-rtx-3050-6gb-16gb-1tb-15-6-fhd-ips-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-13-ai-evo-a2vmg-040vn</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21T10:03:17.431+07:00</t>
+          <t>2026-08-17T11:20:56.718+07:00</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:53</t>
+          <t>2026-10-03 12:20:42</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003VVN (Core 5-205H/ RTX 3050 6GB/ 8GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 AI+ D3MG-022VN (Ultra 7-355/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>36990000</v>
-      </c>
-      <c r="C117" s="2" t="inlineStr"/>
-      <c r="D117" s="2" t="inlineStr"/>
+        <v>44490000</v>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>48990000</v>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5177,33 +5155,33 @@
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 8 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
+          <t>Card đồ họa: Intel® Arc™ graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ultra 7 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003vvn-core-5-205h-rtx-3050-6gb-8gb-512gb-15-3-wuxga-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-ai-d3mg-022vn</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T19:41:42.305+07:00</t>
+          <t>2026-09-28T10:53:12.84+07:00</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:58</t>
+          <t>2026-10-03 12:20:47</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003WVN (Core 5-205H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - Starry Night Over the Rhône-260VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>41990000</v>
+        <v>59990000</v>
       </c>
       <c r="C118" s="2" t="inlineStr"/>
       <c r="D118" s="2" t="inlineStr"/>
@@ -5213,86 +5191,68 @@
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200)</t>
-        </is>
-      </c>
+      <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003wvn-core-5-205h-rtx-3050-6gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-starry-night-over-the-rhone-260vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T16:50:55.152+07:00</t>
+          <t>2026-06-30T09:54:52.677+07:00</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:03</t>
+          <t>2026-10-03 12:20:52</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRX10 83JE01AGVN (I7-13645HX/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop MSI Prestige 14 Flip AI+ Vincent van Gogh Edition - The Starry Night-259VN (Ultra 9-378H/ 32GB/ 1TB/ 14.0" FHD+ OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>39490000</v>
-      </c>
-      <c r="C119" s="2" t="n">
-        <v>40990000</v>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>59990000</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr"/>
+      <c r="D119" s="2" t="inlineStr"/>
+      <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
-        </is>
-      </c>
+      <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx10-83je01agvn</t>
+          <t>https://gearvn.com/products/laptop-msi-prestige-14-flip-ai-vincent-van-gogh-edition-the-starry-night-259vn-ultra-9-378h-32gb-1tb-14-0-fhd-oled-win-11</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19T16:43:38.321+07:00</t>
+          <t>2026-06-30T10:17:43.984+07:00</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:08</t>
+          <t>2026-10-03 12:20:57</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Raider A16 HX B8WH-031VN (Ryzen 9 8940HX/ 32GB/ 1TB/ RTX 5070Ti/ 16" QHD+ 240Hz/ Win11)</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>43990000</v>
+        <v>82990000</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>45990000</v>
+        <v>83990000</v>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -5303,36 +5263,42 @@
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
+          <t>https://gearvn.com/products/laptop-msi-raider-a16-hx-b8wh-031vn-ryzen-9-8940hx-32gb-1tb-rtx-5070ti-16-qhd-240hz-win11</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T16:32:05.969+07:00</t>
+          <t>2026-09-23T15:48:57.837+07:00</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:13</t>
+          <t>2026-10-03 12:21:02</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
+          <t>Laptop gaming MSI Stealth 16 AI+ B3WGX-051VN (Ultra 9-386H/ RTX 5070 12GB/ 32GB/ 1TB/ 16" 2K+ OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>33990000</v>
-      </c>
-      <c r="C121" s="2" t="inlineStr"/>
-      <c r="D121" s="2" t="inlineStr"/>
+        <v>86990000</v>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>87990000</v>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5341,40 +5307,40 @@
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-msi-stealth-16-ai-b3wgx-051vn-core-ultra-9-386h-32gb-1tb-rtx-5070-16-qhd-oled-240hz-win11</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T15:23:00.628+07:00</t>
+          <t>2026-09-22T17:54:02.495+07:00</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:18</t>
+          <t>2026-10-03 12:21:08</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0016W (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix G16 G614PH-S5101W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>28790000</v>
+        <v>47490000</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>30990000</v>
+        <v>53990000</v>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-12%</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -5383,40 +5349,38 @@
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+        </is>
+      </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0016w-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-s5101w</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T10:54:41.9+07:00</t>
+          <t>2026-09-10T11:28:04.811+07:00</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:35:55</t>
+          <t>2026-10-03 12:18:06</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0017W (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix G16 G614PH-TS118W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>36290000</v>
-      </c>
-      <c r="C123" s="2" t="n">
-        <v>38990000</v>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>52990000</v>
+      </c>
+      <c r="C123" s="2" t="inlineStr"/>
+      <c r="D123" s="2" t="inlineStr"/>
       <c r="E123" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5425,40 +5389,40 @@
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: Arc | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 144 Hz</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0017w-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-ts118w</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T13:51:05.888+07:00</t>
+          <t>2026-08-13T11:49:35.857+07:00</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:00</t>
+          <t>2026-10-03 12:18:12</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0442WS (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix G16 G614PM-TS147W (Ryzen 9-8940HX/ RTX 5060 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>37190000</v>
+        <v>54690000</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>39990000</v>
+        <v>59990000</v>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-9%</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -5469,42 +5433,36 @@
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc 140V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0442ws-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614pm-ts147w</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T09:55:42.594+07:00</t>
+          <t>2026-09-07T10:15:11.541+07:00</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:05</t>
+          <t>2026-10-03 12:18:18</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0450WS (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Strix SCAR G835LXG-TQ473W (Ultra 9-290HX Plus/ RTX 5090/ 64GB/ 2TB/ 18" Mini LED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>29790000</v>
-      </c>
-      <c r="C125" s="2" t="n">
-        <v>31990000</v>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>-7%</t>
-        </is>
-      </c>
+        <v>179990000</v>
+      </c>
+      <c r="C125" s="2" t="inlineStr"/>
+      <c r="D125" s="2" t="inlineStr"/>
       <c r="E125" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5513,33 +5471,33 @@
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc 130V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 18 inch | Độ phân giải: UHD+ (3840x2400) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0450ws-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-scar-g835lxg-tq473w-ultra-9-290hx-plus-rtx-5090-64gb-2tb-18-qhd-mini-led-240hz-win-11</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03T09:56:18.911+07:00</t>
+          <t>2026-09-26T12:58:23.481+07:00</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:10</t>
+          <t>2026-10-03 12:18:23</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus G16 GU606AM-TB032W (Ultra 9-386H/ RTX 5060 8GB/ 32GB/ 1TB/ 16" 2.5K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>199990000</v>
+        <v>89990000</v>
       </c>
       <c r="C126" s="2" t="inlineStr"/>
       <c r="D126" s="2" t="inlineStr"/>
@@ -5549,35 +5507,31 @@
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
-        </is>
-      </c>
+      <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-g16-gu606am-tb032w-ultra-9-386h-rtx-5060-8gb-32gb-1tb-16-2-5k-oled-win-11</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18T11:12:30.954+07:00</t>
+          <t>2026-10-01T17:05:02.313+07:00</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:15</t>
+          <t>2026-10-03 12:18:28</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB027W (Core 3/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU405AR-SY016W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>22990000</v>
+        <v>96990000</v>
       </c>
       <c r="C127" s="2" t="inlineStr"/>
       <c r="D127" s="2" t="inlineStr"/>
@@ -5589,33 +5543,33 @@
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb027w-core-3-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405ar-sy016w-ultra-9-rtx-5070-ti-32gb-1tb-14-3k-oled-120hz-win-11</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:52:41.33+07:00</t>
+          <t>2026-09-06T15:47:29.287+07:00</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:20</t>
+          <t>2026-10-03 12:18:33</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB029W (Core 7/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU405AW-SY029W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>35490000</v>
+        <v>119990000</v>
       </c>
       <c r="C128" s="2" t="inlineStr"/>
       <c r="D128" s="2" t="inlineStr"/>
@@ -5627,33 +5581,33 @@
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb029w-core-7-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405aw-sy029w-ultra-9-rtx-5080-32gb-1tb-14-3k-oled-120hz-win-11</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T15:05:22.575+07:00</t>
+          <t>2026-09-06T15:47:45.327+07:00</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:25</t>
+          <t>2026-10-03 12:18:38</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404MA-EB220W (Core 7/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR115W (Ultra 7-255H/ RTX 5070/ 16GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>30490000</v>
+        <v>74990000</v>
       </c>
       <c r="C129" s="2" t="inlineStr"/>
       <c r="D129" s="2" t="inlineStr"/>
@@ -5665,42 +5619,36 @@
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb220w-core-7-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr115w-ultra-7-255h-rtx-5070-16gb-512gb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:43:31.989+07:00</t>
+          <t>2026-09-06T15:46:00.864+07:00</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:30</t>
+          <t>2026-10-03 12:18:43</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus Vivobook 14 X1404V (Core 5-120U/ 8GB/ 256GB/ 14" FHD/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR141W (Ultra 7-255H/ RTX 5070/ 32GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>16590000</v>
-      </c>
-      <c r="C130" s="2" t="n">
-        <v>18990000</v>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>-13%</t>
-        </is>
-      </c>
+        <v>83990000</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr"/>
+      <c r="D130" s="2" t="inlineStr"/>
       <c r="E130" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5709,33 +5657,33 @@
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404v-core-5-120u-8gb-256gb-14-fhd-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr141w-ultra-7-255h-rtx-5070-32gb-512gb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T13:41:37.603+07:00</t>
+          <t>2026-09-06T15:46:21.05+07:00</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:35</t>
+          <t>2026-10-03 12:18:48</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VA-EB355W (Core 7-150U/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AR-TB027W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>25990000</v>
+        <v>99990000</v>
       </c>
       <c r="C131" s="2" t="inlineStr"/>
       <c r="D131" s="2" t="inlineStr"/>
@@ -5747,33 +5695,33 @@
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb355w-core-7-150u-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ar-tb027w-ultra-9-rtx-5070-ti-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:17:32.016+07:00</t>
+          <t>2026-09-06T15:45:10.531+07:00</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:40</t>
+          <t>2026-10-03 12:18:53</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VA-EB609W (Core 3-100U/ 8GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB052WS (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>21990000</v>
+        <v>139990000</v>
       </c>
       <c r="C132" s="2" t="inlineStr"/>
       <c r="D132" s="2" t="inlineStr"/>
@@ -5785,42 +5733,36 @@
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb609w-core-3-100u-8gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb052ws-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:33:25.424+07:00</t>
+          <t>2026-09-06T15:45:28.879+07:00</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:45</t>
+          <t>2026-10-03 12:18:58</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1404VAP-V14.C58256 (Core 5-120U/ 16GB/ 256GB/ 14" FHD IPS/ Win 11/ Quiet Blue)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB121W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>17890000</v>
-      </c>
-      <c r="C133" s="2" t="n">
-        <v>18990000</v>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>-6%</t>
-        </is>
-      </c>
+        <v>124990000</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr"/>
+      <c r="D133" s="2" t="inlineStr"/>
       <c r="E133" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5829,42 +5771,36 @@
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404vap-v14-c58256-core-5-120u-8gb-256gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb121w-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:42:34.369+07:00</t>
+          <t>2026-09-06T15:45:44.227+07:00</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:50</t>
+          <t>2026-10-03 12:19:03</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Laptop Asus VivoBook 14 X1407AA-LY360W (Ultra 5-325/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
+          <t>Laptop gaming ASUS ROG Zephyrus GU606AX-TB042WS (Ultra 9/ RTX 5090/ 64GB/ 2TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>26490000</v>
-      </c>
-      <c r="C134" s="2" t="n">
-        <v>26990000</v>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>-2%</t>
-        </is>
-      </c>
+        <v>169990000</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr"/>
+      <c r="D134" s="2" t="inlineStr"/>
       <c r="E134" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5873,36 +5809,42 @@
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407aa-ly360w-ultra-5-325-16gb-512gb-14-wuxga-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ax-tb042ws-ultra-9-rtx-5090-64gb-2tb-16-2-5k-oled-240hz-win-11</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07T15:46:33.275+07:00</t>
+          <t>2026-09-06T15:44:50.259+07:00</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:55</t>
+          <t>2026-10-03 12:19:08</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 14 X1407CA-LY203W (Ultra 5-225H/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming ASUS TUF Gaming A14 FA401GM-RG013W (Ryzen AI 9 465/ RTX 5060 8GB/ 32GB/ 1TB/ 14" WQXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>33490000</v>
-      </c>
-      <c r="C135" s="2" t="inlineStr"/>
-      <c r="D135" s="2" t="inlineStr"/>
+        <v>57390000</v>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>58990000</v>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5911,36 +5853,42 @@
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen AI 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1407ca-ly203w-ultra-5-225h-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a14-fa401gm-rg013w</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T10:22:08.041+07:00</t>
+          <t>2026-09-14T17:35:45.75+07:00</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:00</t>
+          <t>2026-10-03 12:19:13</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504MA-BQ632W (Core 5-320/ 8GB/ 512GB/ 15" FHD IPS)</t>
+          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN329W (Ryzen 7-8845HS/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>26990000</v>
-      </c>
-      <c r="C136" s="2" t="inlineStr"/>
-      <c r="D136" s="2" t="inlineStr"/>
+        <v>27690000</v>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>37490000</v>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>-26%</t>
+        </is>
+      </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5949,36 +5897,42 @@
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq632w-core-5-320-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn329w-ryzen-7-8845hs-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T15:43:54.381+07:00</t>
+          <t>2026-09-17T11:04:13.749+07:00</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:05</t>
+          <t>2026-10-03 12:19:18</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504MA-BQ633W (Core 7-350/ 8GB/ 512GB/ 15.6" FHD IPS/ Win 11)</t>
+          <t>Laptop gaming ASUS TUF Gaming A15 FA506NCG-HN390W (Ryzen 7-155/ RTX 3050 4GB/ 16GB/ 512GB/ 15.6" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>30490000</v>
-      </c>
-      <c r="C137" s="2" t="inlineStr"/>
-      <c r="D137" s="2" t="inlineStr"/>
+        <v>27490000</v>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>37490000</v>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>-27%</t>
+        </is>
+      </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -5987,74 +5941,82 @@
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504ma-bq633w-core-7-350-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a15-fa506ncg-hn390w-ryzen-7-155-rtx-3050-4gb-16gb-512gb-15-6-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:47:34.397+07:00</t>
+          <t>2026-10-02T16:10:58.832+07:00</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:10</t>
+          <t>2026-10-03 12:19:23</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 15 X1504VA-BQ165W (Core 5-120U/ 8GB/ 512GB/ 15" FHD IPS)</t>
+          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUG-RL129W (Ryzen 7-7445HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>20990000</v>
-      </c>
-      <c r="C138" s="2" t="inlineStr"/>
-      <c r="D138" s="2" t="inlineStr"/>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+        <v>29990000</v>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>30990000</v>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-15-x1504va-bq165w-core-5-120u-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nug-rl129w-ryzen-7-7445hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:12:00.028+07:00</t>
+          <t>2026-09-14T17:41:09.162+07:00</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:15</t>
+          <t>2026-10-03 12:19:28</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 16 X1607CA-MB387W (Ultra 5-225H/ 16GB/ 512GB/ 16" FHD IPS)</t>
+          <t>Laptop gaming ASUS TUF Gaming A16 FA607NUQ-RL007W (Ryzen 7-170/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>33490000</v>
-      </c>
-      <c r="C139" s="2" t="inlineStr"/>
-      <c r="D139" s="2" t="inlineStr"/>
+        <v>36290000</v>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6063,36 +6025,42 @@
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb387w-ultra-5-225h-16gb-512gb-16-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-a16-fa607nuq-rl007w-ryzen-7-170-rtx-4050-6gb-16gb-512gb-16-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T16:08:06.906+07:00</t>
+          <t>2026-09-25T10:10:34.588+07:00</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:20</t>
+          <t>2026-10-03 12:19:33</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook 16 X1607CA-MB399W (Ultra 7-255H/ 16GB/ 512GB/ 16" FHD IPS)</t>
+          <t>Laptop gaming Asus TUF Gaming F16 FX608JHI-TU209W (I7-14650HX/ RTX 5050/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>36490000</v>
-      </c>
-      <c r="C140" s="2" t="inlineStr"/>
-      <c r="D140" s="2" t="inlineStr"/>
+        <v>41260000</v>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>45390000</v>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>-9%</t>
+        </is>
+      </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6101,33 +6069,33 @@
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-16-x1607ca-mb399w-ultra-7-255h-16gb-512gb-16-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-f16-fx608jhi-tu209w</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T15:36:19.591+07:00</t>
+          <t>2026-06-30T14:06:48.719+07:00</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:25</t>
+          <t>2026-10-03 12:19:39</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Flip TP3407AA-SG029W (Ultra 7-355/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA401EA-RG041W (Ryzen AI Max+ 392/ 32GB/ 512GB/ 14" 2.5K/ Win 11)</t>
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>41990000</v>
+        <v>59990000</v>
       </c>
       <c r="C141" s="2" t="inlineStr"/>
       <c r="D141" s="2" t="inlineStr"/>
@@ -6139,33 +6107,33 @@
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen AI MAX+ | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon 8060S | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-flip-tp3407aa-sg029w-ultra-7-355-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401ea-rg041w-ryzen-ai-max-392-32gb-512gb-14-2-5k-win-11</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T14:55:40.249+07:00</t>
+          <t>2026-08-14T09:33:26.048+07:00</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:30</t>
+          <t>2026-10-03 12:19:44</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ4821W (Ryzen 5/ 8GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA401UH-RG001W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>22990000</v>
+        <v>49990000</v>
       </c>
       <c r="C142" s="2" t="inlineStr"/>
       <c r="D142" s="2" t="inlineStr"/>
@@ -6177,33 +6145,33 @@
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-go-14-e1504fa-bq4821w-ryzen-5-8gb-512gb-15-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401uh-rg001w-ryzen-7-260-rtx-5050-16gb-512gb-14-qhd-win-11</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:55:57.447+07:00</t>
+          <t>2026-09-26T12:59:55.007+07:00</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:36</t>
+          <t>2026-10-03 12:19:49</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook Go 15 E1504FA-BQ340W (Ryzen 5/ 16GB/ 512GB/ 15.6" FHD IPS)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA401UM-RG049W (Ryzen 7 260/ RTX 5060/ 32GB/ 512GB/ 14" 2.5K 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>28490000</v>
+        <v>64990000</v>
       </c>
       <c r="C143" s="2" t="inlineStr"/>
       <c r="D143" s="2" t="inlineStr"/>
@@ -6215,33 +6183,33 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Ryzen 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-go-15-e1504fa-bq340w-ryzen-5-16gb-512gb-156-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa401um-rg049w-ryzen-7-260-rtx-5060-32gb-512gb-14-qhd-win-11</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:55:13.502+07:00</t>
+          <t>2026-09-26T13:00:47.55+07:00</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:41</t>
+          <t>2026-10-03 12:19:54</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 M3407KA-SF034W (Ryzen AI 5-330/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA608UHI-TU121W (Ryzen 7 260/ RTX 5050/ 16GB/ 512GB/ 16" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>33990000</v>
+        <v>48990000</v>
       </c>
       <c r="C144" s="2" t="inlineStr"/>
       <c r="D144" s="2" t="inlineStr"/>
@@ -6253,33 +6221,33 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-m3407ka-sf034w-ryzen-ai-5-330-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608uhi-tu121w-ryzen-7-260-rtx-5050-16gb-512gb-16-wuxga-win-11</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T12:02:07.653+07:00</t>
+          <t>2026-08-14T11:22:30.725+07:00</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:46</t>
+          <t>2026-10-03 12:19:59</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407AA-SF945W (Ultra 5-325/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop gaming ASUS TUF Gaming FA608UMI-TU162W (Ryzen 7 260/ RTX 5060/ 16GB/ 512GB/ 16" FHD 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>37490000</v>
+        <v>51990000</v>
       </c>
       <c r="C145" s="2" t="inlineStr"/>
       <c r="D145" s="2" t="inlineStr"/>
@@ -6291,36 +6259,42 @@
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407aa-sf945w-ultra-5-325-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-tuf-gaming-fa608umi-tu162w-ryzen-7-260-rtx-5060-16gb-512gb-16-fhd-144hz-win-11</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T11:09:17.449+07:00</t>
+          <t>2026-08-14T11:01:50.971+07:00</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:51</t>
+          <t>2026-10-03 12:20:04</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Vivobook S 14 S3407VA-LY147W (Core 5-210H/ 16GB/ 512GB/ 14" FHD IPS)</t>
+          <t>Laptop gaming ASUS V16 V3607VJ-TK189W (Core 5-210H/ RTX 3050 6GB/ 16GB/ 512GB/ 16" WUXGA 144Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>34990000</v>
-      </c>
-      <c r="C146" s="2" t="inlineStr"/>
-      <c r="D146" s="2" t="inlineStr"/>
+        <v>26490000</v>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>29990000</v>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6329,238 +6303,252 @@
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s-14-s3407va-ly147w-core-5-210h-16gb-512gb-14-fhd-ips</t>
+          <t>https://gearvn.com/products/laptop-gaming-asus-v16-v3607vj-tk189w-core-5-210h-rtx-3050-6gb-16gb-512gb-16-wuxga-144hz-win-11</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T11:42:14.925+07:00</t>
+          <t>2026-09-15T16:26:14.526+07:00</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:56</t>
+          <t>2026-10-03 12:20:09</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS VivoBook S14 S3407CA-SF913W (Ultra 5-225H/ 16GB/ 512GB/ 14" OLED/ Win 11)</t>
+          <t>Laptop gaming Gigabyte A16 CMHH2VN893SH (Core i5-13420H/ GeForce RTX™ 4050/ 16GB/ 512GB/ Win 11)</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>27890000</v>
+        <v>31990000</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>29990000</v>
+        <v>32790000</v>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>-7%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-vivobook-s14-s3407ca-sf913w-ultra-5-225h-16gb-512gb-14-wuxga-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cmhh2vn893sh</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T13:01:54.572+07:00</t>
+          <t>2026-09-30T11:59:37.483+07:00</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:01</t>
+          <t>2026-10-03 12:20:14</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UM3406GA-QD075W (Ryzen 7/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop gaming GIGABYTE A16 CVHI3MY893SH (I7-13620H/ RTX 5060 8GB/ 16GB/ 512GB/ 16" FHD+ 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>39990000</v>
-      </c>
-      <c r="C148" s="2" t="inlineStr"/>
-      <c r="D148" s="2" t="inlineStr"/>
+        <v>36990000</v>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>38990000</v>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Ryzen AI 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-um3406ga-qd075w-ryzen-7-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-cvhi3my893sh</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T16:03:07.024+07:00</t>
+          <t>2026-08-14T14:40:23.197+07:00</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:06</t>
+          <t>2026-10-03 12:20:19</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1531W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED)</t>
+          <t>Laptop gaming Gigabyte A16 A16-3THK3VN893SH (Ryzen 7 260/ RTX 5050 8GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>42990000</v>
-      </c>
-      <c r="C149" s="2" t="inlineStr"/>
-      <c r="D149" s="2" t="inlineStr"/>
+        <v>35990000</v>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>40990000</v>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1531w-ultra-9-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-a16-ga63h-3thk3vn893sh</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T08:45:55.514+07:00</t>
+          <t>2026-07-30T09:54:12.234+07:00</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:11</t>
+          <t>2026-10-03 12:20:24</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST1713W (Ultra 5-225H/ 16GB/ 512GB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9LJR2VNF93SH (Ryzen 5 7533HS/ RTX 3050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B150" s="3" t="n">
+        <v>29990000</v>
+      </c>
+      <c r="C150" s="2" t="n">
         <v>30990000</v>
       </c>
-      <c r="C150" s="2" t="n">
-        <v>38990000</v>
-      </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>-21%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
+          <t>Tặng ngay 1 x Balo Gigabyte Gaming (trị giá 350.000đ) | [Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st1713w-ultra-5-225h-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9ljr2vnf93sh-ryzen-5-7533hs-rtx-3050-6gb-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25T10:16:16.703+07:00</t>
+          <t>2026-07-31T15:10:54.55+07:00</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:16</t>
+          <t>2026-10-03 12:20:29</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3405CA-ST630W (Ultra 7-255H/ 16GB/ 512GB/ 14" 3K OLED)</t>
+          <t>Laptop gaming Gigabyte Eagle GL6J EAGLE-9MJR2VNF93SH (Ryzen 5 7533HS/ RTX 4050 6GB/ 16GB/ 512GB/ 16" FHD+/ Win 11)</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>40990000</v>
+        <v>34990000</v>
       </c>
       <c r="C151" s="2" t="inlineStr"/>
       <c r="D151" s="2" t="inlineStr"/>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
-        </is>
-      </c>
+      <c r="E151" s="2" t="inlineStr"/>
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Ryzen 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 16 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3405ca-st630w-ultra-7-255h-16gb-512gb-14-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-gigabyte-eagle-gl6j-eagle-9mjr2vnf93sh-ryzen-5-7533hs-rtx-4050-6gb-16gb-512gb-16-fhd-win-11</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T15:05:39.807+07:00</t>
+          <t>2026-09-18T13:50:39.975+07:00</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:21</t>
+          <t>2026-10-03 12:20:34</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook 14 UX3407NA-QD132WS (Snapdragon X2 Elite X2E-88-100/ 16GB/ 512GB/ 14" FHD OLED)</t>
+          <t>Laptop gaming Lenovo Legion Pro 7 16IAX10H 83F500JGVN (Ultra 9-275HX/ RTX 5070 Ti/ 32GB/ 1TB/ 16" OLED 240Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>48990000</v>
-      </c>
-      <c r="C152" s="2" t="inlineStr"/>
-      <c r="D152" s="2" t="inlineStr"/>
+        <v>115990000</v>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>117990000</v>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6569,33 +6557,33 @@
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd132ws-16gb-512gb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-legion-pro-7-16iax10h-83f500jgvn</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:47:13.916+07:00</t>
+          <t>2026-07-05T14:44:14.658+07:00</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:26</t>
+          <t>2026-10-03 12:20:39</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook A14 UX3407NA-QD254W (Snapdragon X2 Elite X2E-88-100/ 32GB/ 1TB/ 14" FHD OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ 15AHP11 83TN0040VN (Ryzen 7-250/ RTX 5050 8GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>63990000</v>
+        <v>43990000</v>
       </c>
       <c r="C153" s="2" t="inlineStr"/>
       <c r="D153" s="2" t="inlineStr"/>
@@ -6607,36 +6595,42 @@
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 14 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-14-ux3407na-qd254w-32gb-1tb-14-fhd-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15ahp11-83tn0040vn-ryzen-7-250-rtx-5050-8gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:46:55.101+07:00</t>
+          <t>2026-09-21T09:36:14.406+07:00</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:31</t>
+          <t>2026-10-03 12:20:44</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook A16 UX3607OA-SQ137WS (Snapdragon X2 Elite Extreme X2E94100/ 24GB/ 512GB/ 16" 3K OLED/ Win 11)</t>
+          <t>Laptop gaming Lenovo LOQ Essential 15ARP10E 83S0004FVN (Ryzen 7 7735HS/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>58990000</v>
-      </c>
-      <c r="C154" s="2" t="inlineStr"/>
-      <c r="D154" s="2" t="inlineStr"/>
+        <v>38990000</v>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>41990000</v>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6645,36 +6639,42 @@
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Qualcomm Adreno GPU | Kích thước màn hình: 16 inch | Dòng CPU: Snapdragon X2 Elite | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 24 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-16-ux3607oa-sq137ws-24gb-512gb-16-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0004fvn</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:43:18.337+07:00</t>
+          <t>2026-07-15T09:36:38.199+07:00</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:36</t>
+          <t>2026-10-03 12:20:49</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN138WS (Ultra X9/ 32GB/ 1TB/ 14" 3K OLED Touch 144Hz)</t>
+          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S0006RVN (Ryzen 7-7735HS/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>89990000</v>
-      </c>
-      <c r="C155" s="2" t="inlineStr"/>
-      <c r="D155" s="2" t="inlineStr"/>
+        <v>30990000</v>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>32990000</v>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6683,33 +6683,33 @@
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X9 | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn138ws-ultra-x9-32gb-1tb-14-3k-oled-touch-144hz</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s0006rvn-ryzen-7-7735hs-rtx-3050-6gb-16gb-1tb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T12:04:03.945+07:00</t>
+          <t>2026-09-22T11:31:57.635+07:00</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:41</t>
+          <t>2026-10-03 12:20:54</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook Duo 14 UX8407AA-SN439WS (Ultra X7/ 32GB/ 512GB/ 14" 3K OLED Touch 144Hz)</t>
+          <t>Laptop gaming Lenovo LOQ 15ARP10E 83S000DCVN (Ryzen 7-170/ RTX 3050 6GB/ 16GB/ 1TB/ 15.6" FHD IPS/ Win 11)</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>82990000</v>
+        <v>32990000</v>
       </c>
       <c r="C156" s="2" t="inlineStr"/>
       <c r="D156" s="2" t="inlineStr"/>
@@ -6721,33 +6721,33 @@
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Arc Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra X7 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Ryzen 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-duo-14-ux8407aa-sn439ws-ultra-x7-32gb-512gb-14-3k-oled-touch-144hz</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15arp10e-83s000dcvn-ryzen-7-170-rtx-3050-6gb-16gb-1tb-15-6-fhd-ips-win-11</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T11:44:06.982+07:00</t>
+          <t>2026-09-21T10:03:17.431+07:00</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:46</t>
+          <t>2026-10-03 12:20:59</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS ProArt PX13 HN7306EA-LX050W (Ryzen AI Max+ 395/ 32GB/ 1TB/ 13.3" 3K OLED Touch)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003VVN (Core 5-205H/ RTX 3050 6GB/ 8GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>76990000</v>
+        <v>36990000</v>
       </c>
       <c r="C157" s="2" t="inlineStr"/>
       <c r="D157" s="2" t="inlineStr"/>
@@ -6759,33 +6759,33 @@
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 13.3 inch | Dòng CPU: Ryzen AI MAX+ | Dung lượng SSD: 1024 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 32 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 8 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200) | Tần số quét: 165 Hz</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-pro-art-hn7306ea-lx050w-ryzen-ai-max-395-32gb-1tb-13-3-3k-oled-touch</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003vvn-core-5-205h-rtx-3050-6gb-8gb-512gb-15-3-wuxga-165hz-win-11</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T15:58:08.111+07:00</t>
+          <t>2026-08-12T19:41:42.305+07:00</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:52</t>
+          <t>2026-10-03 12:21:04</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook S 14 UX5406AA-SU348W (Ultra 9/ 16GB/ 512GB/ 14" 3K OLED Touch)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRH11E 83Y9003WVN (Core 5-205H/ RTX 3050 6GB/ 16GB/ 512GB/ 15.3" WUXGA 165Hz/ Win 11)</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>50990000</v>
+        <v>41990000</v>
       </c>
       <c r="C158" s="2" t="inlineStr"/>
       <c r="D158" s="2" t="inlineStr"/>
@@ -6797,36 +6797,42 @@
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: Core 5 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 3050 | Kích thước màn hình: 15.3 inch | Độ phân giải: WUXGA (1920x1200)</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-s-14-ux5406aa-su348w-ultra-9-16gb-512gb-14-3k-oled-touch</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irh11e-83y9003wvn-core-5-205h-rtx-3050-6gb-16gb-512gb-15-3-wuxga-165hz-win-11</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17T10:26:19.879+07:00</t>
+          <t>2026-08-12T16:50:55.152+07:00</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:57</t>
+          <t>2026-10-03 12:21:09</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Laptop ASUS Zenbook S 16 UM5606GA-SS441W (Ryzen AI 9 465/ 16GB/ 512GB/ 16" 3K OLED)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX10 83JE01AGVN (I7-13645HX/ RTX 5050 8GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>49490000</v>
-      </c>
-      <c r="C159" s="2" t="inlineStr"/>
-      <c r="D159" s="2" t="inlineStr"/>
+        <v>39490000</v>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>40990000</v>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6835,40 +6841,40 @@
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: AMD Radeon Graphics | Kích thước màn hình: 16 inch | Dòng CPU: Ryzen AI 9 | Dung lượng SSD: 512 GB | Tấm nền: OLED | Độ phân giải: 3K (2880x1800) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-asus-zenbook-s-15-um5606ga-ss441w-ryzen-ai-9-465-16gb-512gb-15-3k-oled</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx10-83je01agvn</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24T16:22:14.948+07:00</t>
+          <t>2026-09-19T16:43:38.321+07:00</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:02</t>
+          <t>2026-10-03 12:21:14</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 DC15250 - 71092480 (I7-1355U/ 16GB/ 512GB/ Win 11/ Office/ Microsoft 365)</t>
+          <t>Laptop gaming Lenovo LOQ 15IRX9 83DV01ALVN (I7-13650HX/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>25390000</v>
+        <v>43990000</v>
       </c>
       <c r="C160" s="2" t="n">
-        <v>25990000</v>
+        <v>45990000</v>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-4%</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -6879,42 +6885,36 @@
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: i7 | Dung lượng SSD: 512 GB | Tấm nền: WVA | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-15-dc15250-71092480-i7-1355u-16gb-512gb-win-11-office-microsoft-365</t>
+          <t>https://gearvn.com/products/laptop-gaming-lenovo-loq-15irx9-83dv01alvn</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T10:56:32.257+07:00</t>
+          <t>2026-09-18T16:32:05.969+07:00</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:07</t>
+          <t>2026-10-03 12:21:19</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Laptop Dell 15 Pro Essential PV15250 VKVKD (I3-100U/ 8GB/ 512GB/ 15.6" FHD 120Hz/DOS) - Nhập Khẩu Chính Hãng</t>
+          <t>Laptop gaming MSI Cyborg 15 Black Edition A13VEO-2608VN (I7-13620H/ RTX 4050 6GB/ 16GB/ 512GB/ 15.6" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>14390000</v>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v>14990000</v>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>-4%</t>
-        </is>
-      </c>
+        <v>33990000</v>
+      </c>
+      <c r="C161" s="2" t="inlineStr"/>
+      <c r="D161" s="2" t="inlineStr"/>
       <c r="E161" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -6923,22 +6923,22 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 15.6 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+          <t>Dòng CPU: i7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 4050 | Kích thước màn hình: 15.6 inch | Độ phân giải: Full HD (1920x1080) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-dell-15-pro-essential-pv15250-vkvkd-i3-100u-8gb-512gb-15-6-fhd-120hz</t>
+          <t>https://gearvn.com/products/laptop-gaming-msi-cyborg-15-black-edition-a13veo-2608vn-i7-13620h-rtx-4050-6gb-16gb-512gb-15-6-fhd-win-11</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T10:44:17.994+07:00</t>
+          <t>2026-06-30T15:23:00.628+07:00</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:11</t>
+          <t>2026-10-03 12:21:24</t>
         </is>
       </c>
     </row>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:35:57</t>
+          <t>2026-10-03 12:17:55</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:03</t>
+          <t>2026-10-03 12:18:00</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:08</t>
+          <t>2026-10-03 12:18:05</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:13</t>
+          <t>2026-10-03 12:18:10</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:18</t>
+          <t>2026-10-03 12:18:15</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:23</t>
+          <t>2026-10-03 12:18:20</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:28</t>
+          <t>2026-10-03 12:18:25</t>
         </is>
       </c>
     </row>
@@ -7290,7 +7290,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:33</t>
+          <t>2026-10-03 12:18:30</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:38</t>
+          <t>2026-10-03 12:18:35</t>
         </is>
       </c>
     </row>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:43</t>
+          <t>2026-10-03 12:18:40</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:49</t>
+          <t>2026-10-03 12:18:45</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:54</t>
+          <t>2026-10-03 12:18:51</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:36:59</t>
+          <t>2026-10-03 12:18:56</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:04</t>
+          <t>2026-10-03 12:19:01</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:09</t>
+          <t>2026-10-03 12:19:06</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:14</t>
+          <t>2026-10-03 12:19:11</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:19</t>
+          <t>2026-10-03 12:19:16</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:24</t>
+          <t>2026-10-03 12:19:21</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:29</t>
+          <t>2026-10-03 12:19:26</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:34</t>
+          <t>2026-10-03 12:19:31</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:39</t>
+          <t>2026-10-03 12:19:36</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:44</t>
+          <t>2026-10-03 12:19:41</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:49</t>
+          <t>2026-10-03 12:19:46</t>
         </is>
       </c>
     </row>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:54</t>
+          <t>2026-10-03 12:19:51</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:37:59</t>
+          <t>2026-10-03 12:19:56</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:04</t>
+          <t>2026-10-03 12:20:01</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:09</t>
+          <t>2026-10-03 12:20:06</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8122,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:14</t>
+          <t>2026-10-03 12:20:11</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:19</t>
+          <t>2026-10-03 12:20:16</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:24</t>
+          <t>2026-10-03 12:20:21</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:29</t>
+          <t>2026-10-03 12:20:26</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:34</t>
+          <t>2026-10-03 12:20:31</t>
         </is>
       </c>
     </row>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:39</t>
+          <t>2026-10-03 12:20:36</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:44</t>
+          <t>2026-10-03 12:20:41</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:49</t>
+          <t>2026-10-03 12:20:46</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:38:54</t>
+          <t>2026-10-03 12:20:51</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:00</t>
+          <t>2026-10-03 12:20:56</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:05</t>
+          <t>2026-10-03 12:21:01</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:10</t>
+          <t>2026-10-03 12:21:06</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:39:15</t>
+          <t>2026-10-03 12:21:11</t>
         </is>
       </c>
     </row>

--- a/laptop_gearvn_all.xlsx
+++ b/laptop_gearvn_all.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J201"/>
+  <dimension ref="A1:J203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -503,18 +503,18 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G16 G614PH-S5101W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 240Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0017W (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>47490000</v>
+        <v>36290000</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>53990000</v>
+        <v>38990000</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>-12%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -525,36 +525,42 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: Radeon | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: Arc | Kích thước màn hình: 14 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 144 Hz</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-s5101w</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0017w-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T11:28:04.811+07:00</t>
+          <t>2026-09-10T13:51:05.888+07:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:19:28</t>
+          <t>2026-10-08 13:04:44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G16 G614PH-TS118W (Ryzen 9-8940HX/ RTX 5050 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0442WS (Ultra 7-258V/ 32GB/ 1TB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>52990000</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
+        <v>37190000</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>39990000</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>-7%</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -563,40 +569,40 @@
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5050 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
+          <t>Card đồ họa: Intel Arc 140V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 7 | Dung lượng SSD: 1024 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 32 GB</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614ph-ts118w</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0442ws-ultra-7-258v-32gb-1tb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13T11:49:35.857+07:00</t>
+          <t>2026-08-03T09:55:42.594+07:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:19:33</t>
+          <t>2026-10-08 13:04:50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix G16 G614PM-TS147W (Ryzen 9-8940HX/ RTX 5060 8GB/ 16GB/ 512GB/ 16" WQXGA 300Hz/ Win 11)</t>
+          <t>Laptop Asus ExpertBook P5 P5405CSA-NZ0450WS (Ultra 5-226V/ 16GB/ 512GB/ 14" WQXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>54690000</v>
+        <v>29790000</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>59990000</v>
+        <v>31990000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-9%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -607,33 +613,33 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ryzen 9 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5060 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 300 Hz</t>
+          <t>Card đồ họa: Intel Arc 130V GPU | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Độ phân giải: 2K+ (2560x1600) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-g16-g614pm-ts147w</t>
+          <t>https://gearvn.com/products/laptop-asus-expertbook-p5-p5405csa-nz0450ws-ultra-5-226v-16gb-512gb-14-wqxga-win-11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T10:15:11.541+07:00</t>
+          <t>2026-08-03T09:56:18.911+07:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:19:39</t>
+          <t>2026-10-08 13:04:55</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Strix SCAR G835LXG-TQ473W (Ultra 9-290HX Plus/ RTX 5090/ 64GB/ 2TB/ 18" Mini LED 240Hz/ Win 11)</t>
+          <t>Laptop gaming Asus ROG Zephyrus Duo 16 GX651AX-SR050WS (Ultra 9-386H/ 64GB/ 2TB/ 16" 3K OLED/ Win 11)</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>179990000</v>
+        <v>199990000</v>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr"/>
@@ -645,33 +651,33 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 18 inch | Độ phân giải: UHD+ (3840x2400) | Tần số quét: 240 Hz</t>
+          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 2048 GB | Dòng GPU: RTX 5090 | Kích thước màn hình: 16 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-strix-scar-g835lxg-tq473w-ultra-9-290hx-plus-rtx-5090-64gb-2tb-18-qhd-mini-led-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-rog-zephyrus-duo-16-gx651ax-sr050ws-intel-u9-386h-64gbd5-2tb-3k-120hz-oled-w11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:58:23.481+07:00</t>
+          <t>2026-09-18T11:12:30.954+07:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:19:44</t>
+          <t>2026-10-08 13:05:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus G16 GU606AM-TB032W (Ultra 9-386H/ RTX 5060 8GB/ 32GB/ 1TB/ 16" 2.5K OLED/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB027W (Core 3/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>89990000</v>
+        <v>22990000</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
@@ -681,31 +687,35 @@
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-g16-gu606am-tb032w-ultra-9-386h-rtx-5060-8gb-32gb-1tb-16-2-5k-oled-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb027w-core-3-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01T17:05:02.313+07:00</t>
+          <t>2026-08-18T16:52:41.33+07:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:19:49</t>
+          <t>2026-10-08 13:05:05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU405AR-SY016W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB029W (Core 7/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>96990000</v>
+        <v>35490000</v>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr"/>
@@ -717,33 +727,33 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405ar-sy016w-ultra-9-rtx-5070-ti-32gb-1tb-14-3k-oled-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb029w-core-7-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:47:29.287+07:00</t>
+          <t>2026-08-20T15:05:22.575+07:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:19:54</t>
+          <t>2026-10-08 13:05:10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU405AW-SY029W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 14" 3K OLED 120Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404MA-EB220W (Core 7/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>119990000</v>
+        <v>30490000</v>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
@@ -755,36 +765,42 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 14 inch | Độ phân giải: 3K (2880x1800) | Tần số quét: 120 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu405aw-sy029w-ultra-9-rtx-5080-32gb-1tb-14-3k-oled-120hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404ma-eb220w-core-7-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:47:45.327+07:00</t>
+          <t>2026-08-20T11:43:31.989+07:00</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:19:59</t>
+          <t>2026-10-08 13:05:15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR115W (Ultra 7-255H/ RTX 5070/ 16GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop Asus Vivobook 14 X1404V (Core 5-120U/ 8GB/ 256GB/ 14" FHD/ Win 11)</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>74990000</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
+        <v>16590000</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>18990000</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>-13%</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -793,33 +809,33 @@
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 16 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr115w-ultra-7-255h-rtx-5070-16gb-512gb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404v-core-5-120u-8gb-256gb-14-fhd-win-11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:46:00.864+07:00</t>
+          <t>2026-08-07T13:41:37.603+07:00</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:20:04</t>
+          <t>2026-10-08 13:05:21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU605CP-QR141W (Ultra 7-255H/ RTX 5070/ 32GB/ 512GB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VA-EB355W (Core 7-150U/ 16GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>83990000</v>
+        <v>25990000</v>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
@@ -831,33 +847,33 @@
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 7 | Dung lượng RAM: 32 GB | Dung lượng SSD: 512 GB | Dòng GPU: RTX 5070 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 7 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu605cp-qr141w-ultra-7-255h-rtx-5070-32gb-512gb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb355w-core-7-150u-16gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:46:21.05+07:00</t>
+          <t>2026-08-20T11:17:32.016+07:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:20:09</t>
+          <t>2026-10-08 13:05:26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AR-TB027W (Ultra 9/ RTX 5070 Ti/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VA-EB609W (Core 3-100U/ 8GB/ 512GB/ 14" FHD IPS)</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>99990000</v>
+        <v>21990000</v>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
@@ -869,36 +885,42 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5070 Ti | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 3 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 8 GB</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606ar-tb027w-ultra-9-rtx-5070-ti-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404va-eb609w-core-3-100u-8gb-512gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:10.531+07:00</t>
+          <t>2026-08-18T16:33:25.424+07:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:20:14</t>
+          <t>2026-10-08 13:05:31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB052WS (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop ASUS Vivobook 14 X1404VAP-V14.C58256 (Core 5-120U/ 16GB/ 256GB/ 14" FHD IPS/ Win 11/ Quiet Blue)</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>139990000</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
+        <v>17890000</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>18990000</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -907,36 +929,42 @@
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Core Ultra 9 | Dung lượng RAM: 64 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel UHD Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core 5 | Dung lượng SSD: 256 GB | Tấm nền: IPS | Độ phân giải: Full HD (1920x1080) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu606aw-tb052ws-ultra-9-rtx-5080-32gb-1tb-16-2-5k-oled-240hz-win-11</t>
+          <t>https://gearvn.com/products/laptop-asus-vivobook-14-x1404vap-v14-c58256-core-5-120u-8gb-256gb-14-fhd-ips</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06T15:45:28.879+07:00</t>
+          <t>2026-09-14T17:42:34.369+07:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:20:19</t>
+          <t>2026-10-08 13:05:36</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Laptop gaming ASUS ROG Zephyrus GU606AW-TB121W (Ultra 9/ RTX 5080/ 32GB/ 1TB/ 16" 2.5K OLED 240Hz/ Win 11)</t>
+          <t>Laptop Asus VivoBook 14 X1407AA-LY360W (Ultra 5-325/ 16GB/ 512GB/ 14" WUXGA/ Win 11)</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>124990000</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr"/>
+        <v>26490000</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>26990000</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>[Laptop] Giảm 1% tối đa 500k cho HSSV khi mua laptop</t>
@@ -945,33 +973,33 @@
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Dòng CPU: Ultra 9 | Dung lượng RAM: 32 GB | Dung lượng SSD: 1024 GB | Dòng GPU: RTX 5080 | Kích thước màn hình: 16 inch | Độ phân giải: 2K+ (2560x1600) | Tần số quét: 240 Hz</t>
+          <t>Card đồ họa: Intel Graphics | Kích thước màn hình: 14 inch | Dòng CPU: Core Ultra 5 | Dung lượng SSD: 512 GB | Tấm nền: IPS | Độ phân giải: WUXGA (1920x1200) | Dung lượng RAM: 16 GB</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://gearvn.com/products/laptop-gaming-asus-rog-zephyrus-gu